--- a/AAII_Financials/Quarterly/ZTO_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/ZTO_QTR_FIN.xlsx
@@ -5,7 +5,7 @@
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\sundeep\Stocks_Automation\AAII_Financials\Quarterly\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\sundeep\Private\Investing\Automation\AAII\AAII_Financials\Quarterly\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -17,7 +17,7 @@
   <definedNames>
     <definedName name="Ticker">#REF!</definedName>
   </definedNames>
-  <calcPr calcId="152511" calcMode="manual" concurrentCalc="0"/>
+  <calcPr calcId="152511" calcMode="manual"/>
 </workbook>
 </file>
 
@@ -794,25 +794,25 @@
         <v>3</v>
       </c>
       <c r="D8" s="3">
-        <v>1253200</v>
+        <v>1261700</v>
       </c>
       <c r="E8" s="3">
-        <v>1344900</v>
+        <v>1354100</v>
       </c>
       <c r="F8" s="3">
-        <v>1240400</v>
+        <v>1248800</v>
       </c>
       <c r="G8" s="3">
-        <v>1363000</v>
+        <v>1372300</v>
       </c>
       <c r="H8" s="3">
-        <v>1235100</v>
+        <v>1243500</v>
       </c>
       <c r="I8" s="3">
-        <v>1195300</v>
+        <v>1203500</v>
       </c>
       <c r="J8" s="3">
-        <v>1091400</v>
+        <v>1098800</v>
       </c>
       <c r="K8" s="3">
         <v>1270000</v>
@@ -886,25 +886,25 @@
         <v>4</v>
       </c>
       <c r="D9" s="3">
-        <v>879500</v>
+        <v>885500</v>
       </c>
       <c r="E9" s="3">
-        <v>888700</v>
+        <v>894700</v>
       </c>
       <c r="F9" s="3">
-        <v>892000</v>
+        <v>898000</v>
       </c>
       <c r="G9" s="3">
-        <v>980200</v>
+        <v>986900</v>
       </c>
       <c r="H9" s="3">
-        <v>897600</v>
+        <v>903700</v>
       </c>
       <c r="I9" s="3">
-        <v>891100</v>
+        <v>897200</v>
       </c>
       <c r="J9" s="3">
-        <v>867800</v>
+        <v>873700</v>
       </c>
       <c r="K9" s="3">
         <v>959900</v>
@@ -978,25 +978,25 @@
         <v>5</v>
       </c>
       <c r="D10" s="3">
-        <v>373700</v>
+        <v>376200</v>
       </c>
       <c r="E10" s="3">
-        <v>456300</v>
+        <v>459400</v>
       </c>
       <c r="F10" s="3">
-        <v>348400</v>
+        <v>350800</v>
       </c>
       <c r="G10" s="3">
-        <v>382800</v>
+        <v>385400</v>
       </c>
       <c r="H10" s="3">
-        <v>337500</v>
+        <v>339800</v>
       </c>
       <c r="I10" s="3">
-        <v>304200</v>
+        <v>306200</v>
       </c>
       <c r="J10" s="3">
-        <v>223600</v>
+        <v>225100</v>
       </c>
       <c r="K10" s="3">
         <v>310100</v>
@@ -1300,7 +1300,7 @@
         <v>-1300</v>
       </c>
       <c r="H14" s="3">
-        <v>-4700</v>
+        <v>-4800</v>
       </c>
       <c r="I14" s="3" t="s">
         <v>8</v>
@@ -1506,22 +1506,22 @@
         <v>8</v>
       </c>
       <c r="E17" s="3">
-        <v>947500</v>
+        <v>954000</v>
       </c>
       <c r="F17" s="3">
-        <v>971100</v>
+        <v>977700</v>
       </c>
       <c r="G17" s="3">
-        <v>1022100</v>
+        <v>1029100</v>
       </c>
       <c r="H17" s="3">
-        <v>930100</v>
+        <v>936400</v>
       </c>
       <c r="I17" s="3">
-        <v>921100</v>
+        <v>927400</v>
       </c>
       <c r="J17" s="3">
-        <v>937300</v>
+        <v>943600</v>
       </c>
       <c r="K17" s="3">
         <v>986700</v>
@@ -1598,22 +1598,22 @@
         <v>8</v>
       </c>
       <c r="E18" s="3">
-        <v>397400</v>
+        <v>400100</v>
       </c>
       <c r="F18" s="3">
-        <v>269300</v>
+        <v>271100</v>
       </c>
       <c r="G18" s="3">
-        <v>340900</v>
+        <v>343200</v>
       </c>
       <c r="H18" s="3">
-        <v>305000</v>
+        <v>307100</v>
       </c>
       <c r="I18" s="3">
-        <v>274200</v>
+        <v>276000</v>
       </c>
       <c r="J18" s="3">
-        <v>154100</v>
+        <v>155200</v>
       </c>
       <c r="K18" s="3">
         <v>283300</v>
@@ -1724,22 +1724,22 @@
         <v>8</v>
       </c>
       <c r="E20" s="3">
-        <v>41400</v>
+        <v>41700</v>
       </c>
       <c r="F20" s="3">
-        <v>32800</v>
+        <v>33000</v>
       </c>
       <c r="G20" s="3">
-        <v>28200</v>
+        <v>28400</v>
       </c>
       <c r="H20" s="3">
-        <v>23600</v>
+        <v>23800</v>
       </c>
       <c r="I20" s="3">
-        <v>31000</v>
+        <v>31200</v>
       </c>
       <c r="J20" s="3">
-        <v>13400</v>
+        <v>13500</v>
       </c>
       <c r="K20" s="3">
         <v>9900</v>
@@ -1816,22 +1816,22 @@
         <v>8</v>
       </c>
       <c r="E21" s="3">
-        <v>441400</v>
+        <v>444400</v>
       </c>
       <c r="F21" s="3">
-        <v>396900</v>
+        <v>399600</v>
       </c>
       <c r="G21" s="3">
-        <v>373100</v>
+        <v>375700</v>
       </c>
       <c r="H21" s="3">
-        <v>327700</v>
+        <v>329900</v>
       </c>
       <c r="I21" s="3">
-        <v>310600</v>
+        <v>312700</v>
       </c>
       <c r="J21" s="3">
-        <v>254900</v>
+        <v>256700</v>
       </c>
       <c r="K21" s="3">
         <v>300500</v>
@@ -1905,16 +1905,16 @@
         <v>17</v>
       </c>
       <c r="D22" s="3">
-        <v>11600</v>
+        <v>11700</v>
       </c>
       <c r="E22" s="3">
         <v>10000</v>
       </c>
       <c r="F22" s="3">
-        <v>9900</v>
+        <v>10000</v>
       </c>
       <c r="G22" s="3">
-        <v>10500</v>
+        <v>10600</v>
       </c>
       <c r="H22" s="3">
         <v>4400</v>
@@ -1923,7 +1923,7 @@
         <v>3200</v>
       </c>
       <c r="J22" s="3">
-        <v>8200</v>
+        <v>8300</v>
       </c>
       <c r="K22" s="3">
         <v>3400</v>
@@ -1997,25 +1997,25 @@
         <v>18</v>
       </c>
       <c r="D23" s="3">
-        <v>360400</v>
+        <v>362900</v>
       </c>
       <c r="E23" s="3">
-        <v>428800</v>
+        <v>431800</v>
       </c>
       <c r="F23" s="3">
-        <v>292200</v>
+        <v>294200</v>
       </c>
       <c r="G23" s="3">
-        <v>358600</v>
+        <v>361000</v>
       </c>
       <c r="H23" s="3">
-        <v>324200</v>
+        <v>326400</v>
       </c>
       <c r="I23" s="3">
-        <v>302000</v>
+        <v>304100</v>
       </c>
       <c r="J23" s="3">
-        <v>159300</v>
+        <v>160400</v>
       </c>
       <c r="K23" s="3">
         <v>289800</v>
@@ -2089,25 +2089,25 @@
         <v>19</v>
       </c>
       <c r="D24" s="3">
-        <v>37500</v>
+        <v>37700</v>
       </c>
       <c r="E24" s="3">
-        <v>79500</v>
+        <v>80000</v>
       </c>
       <c r="F24" s="3">
-        <v>62800</v>
+        <v>63300</v>
       </c>
       <c r="G24" s="3">
-        <v>69100</v>
+        <v>69600</v>
       </c>
       <c r="H24" s="3">
-        <v>60700</v>
+        <v>61100</v>
       </c>
       <c r="I24" s="3">
-        <v>60500</v>
+        <v>60900</v>
       </c>
       <c r="J24" s="3">
-        <v>35200</v>
+        <v>35500</v>
       </c>
       <c r="K24" s="3">
         <v>51200</v>
@@ -2276,22 +2276,22 @@
         <v>8</v>
       </c>
       <c r="E26" s="3">
-        <v>349400</v>
+        <v>351700</v>
       </c>
       <c r="F26" s="3">
-        <v>229400</v>
+        <v>230900</v>
       </c>
       <c r="G26" s="3">
-        <v>289500</v>
+        <v>291500</v>
       </c>
       <c r="H26" s="3">
-        <v>263600</v>
+        <v>265400</v>
       </c>
       <c r="I26" s="3">
-        <v>241500</v>
+        <v>243100</v>
       </c>
       <c r="J26" s="3">
-        <v>124100</v>
+        <v>124900</v>
       </c>
       <c r="K26" s="3">
         <v>238600</v>
@@ -2368,22 +2368,22 @@
         <v>8</v>
       </c>
       <c r="E27" s="3">
-        <v>350900</v>
+        <v>353300</v>
       </c>
       <c r="F27" s="3">
-        <v>230600</v>
+        <v>232200</v>
       </c>
       <c r="G27" s="3">
-        <v>298600</v>
+        <v>300600</v>
       </c>
       <c r="H27" s="3">
-        <v>267200</v>
+        <v>269000</v>
       </c>
       <c r="I27" s="3">
-        <v>249300</v>
+        <v>251000</v>
       </c>
       <c r="J27" s="3">
-        <v>125100</v>
+        <v>126000</v>
       </c>
       <c r="K27" s="3">
         <v>242800</v>
@@ -2828,22 +2828,22 @@
         <v>8</v>
       </c>
       <c r="E32" s="3">
-        <v>-41400</v>
+        <v>-41700</v>
       </c>
       <c r="F32" s="3">
-        <v>-32800</v>
+        <v>-33000</v>
       </c>
       <c r="G32" s="3">
-        <v>-28200</v>
+        <v>-28400</v>
       </c>
       <c r="H32" s="3">
-        <v>-23600</v>
+        <v>-23800</v>
       </c>
       <c r="I32" s="3">
-        <v>-31000</v>
+        <v>-31200</v>
       </c>
       <c r="J32" s="3">
-        <v>-13400</v>
+        <v>-13500</v>
       </c>
       <c r="K32" s="3">
         <v>-9900</v>
@@ -2920,22 +2920,22 @@
         <v>8</v>
       </c>
       <c r="E33" s="3">
-        <v>350900</v>
+        <v>353300</v>
       </c>
       <c r="F33" s="3">
-        <v>230600</v>
+        <v>232200</v>
       </c>
       <c r="G33" s="3">
-        <v>298600</v>
+        <v>300600</v>
       </c>
       <c r="H33" s="3">
-        <v>267200</v>
+        <v>269000</v>
       </c>
       <c r="I33" s="3">
-        <v>249300</v>
+        <v>251000</v>
       </c>
       <c r="J33" s="3">
-        <v>125100</v>
+        <v>126000</v>
       </c>
       <c r="K33" s="3">
         <v>242800</v>
@@ -3104,22 +3104,22 @@
         <v>8</v>
       </c>
       <c r="E35" s="3">
-        <v>350900</v>
+        <v>353300</v>
       </c>
       <c r="F35" s="3">
-        <v>230600</v>
+        <v>232200</v>
       </c>
       <c r="G35" s="3">
-        <v>298600</v>
+        <v>300600</v>
       </c>
       <c r="H35" s="3">
-        <v>267200</v>
+        <v>269000</v>
       </c>
       <c r="I35" s="3">
-        <v>249300</v>
+        <v>251000</v>
       </c>
       <c r="J35" s="3">
-        <v>125100</v>
+        <v>126000</v>
       </c>
       <c r="K35" s="3">
         <v>242800</v>
@@ -3358,25 +3358,25 @@
         <v>34</v>
       </c>
       <c r="D41" s="3">
-        <v>1282000</v>
+        <v>1290700</v>
       </c>
       <c r="E41" s="3">
-        <v>1074500</v>
+        <v>1081800</v>
       </c>
       <c r="F41" s="3">
-        <v>1319500</v>
+        <v>1328400</v>
       </c>
       <c r="G41" s="3">
-        <v>1614500</v>
+        <v>1625500</v>
       </c>
       <c r="H41" s="3">
-        <v>2014900</v>
+        <v>2028600</v>
       </c>
       <c r="I41" s="3">
-        <v>1370800</v>
+        <v>1380200</v>
       </c>
       <c r="J41" s="3">
-        <v>1367100</v>
+        <v>1376400</v>
       </c>
       <c r="K41" s="3">
         <v>1339400</v>
@@ -3450,25 +3450,25 @@
         <v>35</v>
       </c>
       <c r="D42" s="3">
-        <v>1056700</v>
+        <v>1063900</v>
       </c>
       <c r="E42" s="3">
-        <v>1098600</v>
+        <v>1106100</v>
       </c>
       <c r="F42" s="3">
-        <v>1225900</v>
+        <v>1234300</v>
       </c>
       <c r="G42" s="3">
-        <v>794400</v>
+        <v>799800</v>
       </c>
       <c r="H42" s="3">
-        <v>960100</v>
+        <v>966600</v>
       </c>
       <c r="I42" s="3">
-        <v>719500</v>
+        <v>724400</v>
       </c>
       <c r="J42" s="3">
-        <v>552600</v>
+        <v>556400</v>
       </c>
       <c r="K42" s="3">
         <v>392000</v>
@@ -3542,25 +3542,25 @@
         <v>36</v>
       </c>
       <c r="D43" s="3">
-        <v>332000</v>
+        <v>334300</v>
       </c>
       <c r="E43" s="3">
-        <v>320200</v>
+        <v>322400</v>
       </c>
       <c r="F43" s="3">
-        <v>253100</v>
+        <v>254800</v>
       </c>
       <c r="G43" s="3">
-        <v>287900</v>
+        <v>289800</v>
       </c>
       <c r="H43" s="3">
-        <v>265700</v>
+        <v>267500</v>
       </c>
       <c r="I43" s="3">
-        <v>265900</v>
+        <v>267700</v>
       </c>
       <c r="J43" s="3">
-        <v>262300</v>
+        <v>264100</v>
       </c>
       <c r="K43" s="3">
         <v>300200</v>
@@ -3640,13 +3640,13 @@
         <v>3700</v>
       </c>
       <c r="F44" s="3">
-        <v>4000</v>
+        <v>4100</v>
       </c>
       <c r="G44" s="3">
         <v>5600</v>
       </c>
       <c r="H44" s="3">
-        <v>8900</v>
+        <v>9000</v>
       </c>
       <c r="I44" s="3">
         <v>4000</v>
@@ -3726,25 +3726,25 @@
         <v>38</v>
       </c>
       <c r="D45" s="3">
-        <v>739700</v>
+        <v>744800</v>
       </c>
       <c r="E45" s="3">
-        <v>725200</v>
+        <v>730200</v>
       </c>
       <c r="F45" s="3">
-        <v>688700</v>
+        <v>693400</v>
       </c>
       <c r="G45" s="3">
-        <v>677100</v>
+        <v>681700</v>
       </c>
       <c r="H45" s="3">
-        <v>583800</v>
+        <v>587800</v>
       </c>
       <c r="I45" s="3">
-        <v>563900</v>
+        <v>567700</v>
       </c>
       <c r="J45" s="3">
-        <v>576300</v>
+        <v>580200</v>
       </c>
       <c r="K45" s="3">
         <v>528800</v>
@@ -3818,25 +3818,25 @@
         <v>39</v>
       </c>
       <c r="D46" s="3">
-        <v>3414300</v>
+        <v>3437600</v>
       </c>
       <c r="E46" s="3">
-        <v>3222200</v>
+        <v>3244100</v>
       </c>
       <c r="F46" s="3">
-        <v>3491200</v>
+        <v>3515000</v>
       </c>
       <c r="G46" s="3">
-        <v>3379500</v>
+        <v>3402500</v>
       </c>
       <c r="H46" s="3">
-        <v>3833300</v>
+        <v>3859400</v>
       </c>
       <c r="I46" s="3">
-        <v>2924200</v>
+        <v>2944100</v>
       </c>
       <c r="J46" s="3">
-        <v>2766500</v>
+        <v>2785400</v>
       </c>
       <c r="K46" s="3">
         <v>2571900</v>
@@ -3910,25 +3910,25 @@
         <v>40</v>
       </c>
       <c r="D47" s="3">
-        <v>2596600</v>
+        <v>2614300</v>
       </c>
       <c r="E47" s="3">
-        <v>2184500</v>
+        <v>2199400</v>
       </c>
       <c r="F47" s="3">
-        <v>1874600</v>
+        <v>1887400</v>
       </c>
       <c r="G47" s="3">
-        <v>1815200</v>
+        <v>1827600</v>
       </c>
       <c r="H47" s="3">
-        <v>1336300</v>
+        <v>1345400</v>
       </c>
       <c r="I47" s="3">
-        <v>1160000</v>
+        <v>1167900</v>
       </c>
       <c r="J47" s="3">
-        <v>1013000</v>
+        <v>1019900</v>
       </c>
       <c r="K47" s="3">
         <v>960200</v>
@@ -4002,25 +4002,25 @@
         <v>41</v>
       </c>
       <c r="D48" s="3">
-        <v>4489800</v>
+        <v>4520300</v>
       </c>
       <c r="E48" s="3">
-        <v>4377500</v>
+        <v>4407300</v>
       </c>
       <c r="F48" s="3">
-        <v>4224300</v>
+        <v>4253100</v>
       </c>
       <c r="G48" s="3">
-        <v>4090200</v>
+        <v>4118000</v>
       </c>
       <c r="H48" s="3">
-        <v>3975400</v>
+        <v>4002400</v>
       </c>
       <c r="I48" s="3">
-        <v>3819100</v>
+        <v>3845100</v>
       </c>
       <c r="J48" s="3">
-        <v>3682100</v>
+        <v>3707100</v>
       </c>
       <c r="K48" s="3">
         <v>3558500</v>
@@ -4094,25 +4094,25 @@
         <v>42</v>
       </c>
       <c r="D49" s="3">
-        <v>1368200</v>
+        <v>1377500</v>
       </c>
       <c r="E49" s="3">
-        <v>1372700</v>
+        <v>1382000</v>
       </c>
       <c r="F49" s="3">
-        <v>1371800</v>
+        <v>1381100</v>
       </c>
       <c r="G49" s="3">
-        <v>1341300</v>
+        <v>1350400</v>
       </c>
       <c r="H49" s="3">
-        <v>1330700</v>
+        <v>1339800</v>
       </c>
       <c r="I49" s="3">
-        <v>1341000</v>
+        <v>1350200</v>
       </c>
       <c r="J49" s="3">
-        <v>1329000</v>
+        <v>1338000</v>
       </c>
       <c r="K49" s="3">
         <v>1324400</v>
@@ -4370,25 +4370,25 @@
         <v>45</v>
       </c>
       <c r="D52" s="3">
-        <v>208100</v>
+        <v>209500</v>
       </c>
       <c r="E52" s="3">
-        <v>173200</v>
+        <v>174400</v>
       </c>
       <c r="F52" s="3">
-        <v>180700</v>
+        <v>181900</v>
       </c>
       <c r="G52" s="3">
-        <v>216400</v>
+        <v>217800</v>
       </c>
       <c r="H52" s="3">
-        <v>238300</v>
+        <v>239900</v>
       </c>
       <c r="I52" s="3">
-        <v>215000</v>
+        <v>216500</v>
       </c>
       <c r="J52" s="3">
-        <v>232700</v>
+        <v>234300</v>
       </c>
       <c r="K52" s="3">
         <v>233800</v>
@@ -4554,25 +4554,25 @@
         <v>47</v>
       </c>
       <c r="D54" s="3">
-        <v>12077000</v>
+        <v>12159200</v>
       </c>
       <c r="E54" s="3">
-        <v>11330100</v>
+        <v>11407200</v>
       </c>
       <c r="F54" s="3">
-        <v>11142600</v>
+        <v>11218400</v>
       </c>
       <c r="G54" s="3">
-        <v>10842500</v>
+        <v>10916300</v>
       </c>
       <c r="H54" s="3">
-        <v>10714100</v>
+        <v>10787000</v>
       </c>
       <c r="I54" s="3">
-        <v>9459300</v>
+        <v>9523700</v>
       </c>
       <c r="J54" s="3">
-        <v>9023200</v>
+        <v>9084600</v>
       </c>
       <c r="K54" s="3">
         <v>8648800</v>
@@ -4714,25 +4714,25 @@
         <v>50</v>
       </c>
       <c r="D57" s="3">
-        <v>274900</v>
+        <v>276700</v>
       </c>
       <c r="E57" s="3">
-        <v>266300</v>
+        <v>268200</v>
       </c>
       <c r="F57" s="3">
-        <v>284200</v>
+        <v>286100</v>
       </c>
       <c r="G57" s="3">
-        <v>304100</v>
+        <v>306200</v>
       </c>
       <c r="H57" s="3">
-        <v>245600</v>
+        <v>247300</v>
       </c>
       <c r="I57" s="3">
-        <v>263900</v>
+        <v>265700</v>
       </c>
       <c r="J57" s="3">
-        <v>237200</v>
+        <v>238900</v>
       </c>
       <c r="K57" s="3">
         <v>269700</v>
@@ -4806,25 +4806,25 @@
         <v>51</v>
       </c>
       <c r="D58" s="3">
-        <v>1324500</v>
+        <v>1333500</v>
       </c>
       <c r="E58" s="3">
-        <v>925300</v>
+        <v>931600</v>
       </c>
       <c r="F58" s="3">
-        <v>938800</v>
+        <v>945200</v>
       </c>
       <c r="G58" s="3">
-        <v>772500</v>
+        <v>777700</v>
       </c>
       <c r="H58" s="3">
-        <v>992500</v>
+        <v>999300</v>
       </c>
       <c r="I58" s="3">
-        <v>1008600</v>
+        <v>1015500</v>
       </c>
       <c r="J58" s="3">
-        <v>842100</v>
+        <v>847900</v>
       </c>
       <c r="K58" s="3">
         <v>500600</v>
@@ -4898,25 +4898,25 @@
         <v>52</v>
       </c>
       <c r="D59" s="3">
-        <v>1317700</v>
+        <v>1326700</v>
       </c>
       <c r="E59" s="3">
-        <v>1256200</v>
+        <v>1264800</v>
       </c>
       <c r="F59" s="3">
-        <v>1414600</v>
+        <v>1424200</v>
       </c>
       <c r="G59" s="3">
-        <v>1188600</v>
+        <v>1196700</v>
       </c>
       <c r="H59" s="3">
-        <v>1178400</v>
+        <v>1186400</v>
       </c>
       <c r="I59" s="3">
-        <v>1071700</v>
+        <v>1079000</v>
       </c>
       <c r="J59" s="3">
-        <v>1113400</v>
+        <v>1121000</v>
       </c>
       <c r="K59" s="3">
         <v>1020300</v>
@@ -4990,25 +4990,25 @@
         <v>53</v>
       </c>
       <c r="D60" s="3">
-        <v>2917100</v>
+        <v>2936900</v>
       </c>
       <c r="E60" s="3">
-        <v>2447800</v>
+        <v>2464500</v>
       </c>
       <c r="F60" s="3">
-        <v>2637600</v>
+        <v>2655500</v>
       </c>
       <c r="G60" s="3">
-        <v>2265200</v>
+        <v>2280700</v>
       </c>
       <c r="H60" s="3">
-        <v>2416500</v>
+        <v>2433000</v>
       </c>
       <c r="I60" s="3">
-        <v>2344200</v>
+        <v>2360200</v>
       </c>
       <c r="J60" s="3">
-        <v>2192800</v>
+        <v>2207700</v>
       </c>
       <c r="K60" s="3">
         <v>1790600</v>
@@ -5082,19 +5082,19 @@
         <v>54</v>
       </c>
       <c r="D61" s="3">
-        <v>996000</v>
+        <v>1002800</v>
       </c>
       <c r="E61" s="3">
-        <v>988400</v>
+        <v>995200</v>
       </c>
       <c r="F61" s="3">
-        <v>934800</v>
+        <v>941100</v>
       </c>
       <c r="G61" s="3">
-        <v>937400</v>
+        <v>943800</v>
       </c>
       <c r="H61" s="3">
-        <v>965400</v>
+        <v>972000</v>
       </c>
       <c r="I61" s="3">
         <v>0</v>
@@ -5174,25 +5174,25 @@
         <v>55</v>
       </c>
       <c r="D62" s="3">
-        <v>109700</v>
+        <v>110500</v>
       </c>
       <c r="E62" s="3">
-        <v>115300</v>
+        <v>116000</v>
       </c>
       <c r="F62" s="3">
-        <v>113500</v>
+        <v>114200</v>
       </c>
       <c r="G62" s="3">
-        <v>118300</v>
+        <v>119100</v>
       </c>
       <c r="H62" s="3">
-        <v>100900</v>
+        <v>101600</v>
       </c>
       <c r="I62" s="3">
-        <v>109200</v>
+        <v>110000</v>
       </c>
       <c r="J62" s="3">
-        <v>113900</v>
+        <v>114700</v>
       </c>
       <c r="K62" s="3">
         <v>116900</v>
@@ -5542,25 +5542,25 @@
         <v>58</v>
       </c>
       <c r="D66" s="3">
-        <v>4082800</v>
+        <v>4110600</v>
       </c>
       <c r="E66" s="3">
-        <v>3610800</v>
+        <v>3635400</v>
       </c>
       <c r="F66" s="3">
-        <v>3746300</v>
+        <v>3771800</v>
       </c>
       <c r="G66" s="3">
-        <v>3382300</v>
+        <v>3405300</v>
       </c>
       <c r="H66" s="3">
-        <v>3545700</v>
+        <v>3569800</v>
       </c>
       <c r="I66" s="3">
-        <v>2511400</v>
+        <v>2528500</v>
       </c>
       <c r="J66" s="3">
-        <v>2337900</v>
+        <v>2353800</v>
       </c>
       <c r="K66" s="3">
         <v>1947500</v>
@@ -6036,25 +6036,25 @@
         <v>64</v>
       </c>
       <c r="D72" s="3">
-        <v>4751300</v>
+        <v>4783600</v>
       </c>
       <c r="E72" s="3">
-        <v>4463300</v>
+        <v>4493700</v>
       </c>
       <c r="F72" s="3">
-        <v>4248000</v>
+        <v>4276900</v>
       </c>
       <c r="G72" s="3">
-        <v>4067800</v>
+        <v>4095500</v>
       </c>
       <c r="H72" s="3">
-        <v>3769200</v>
+        <v>3794800</v>
       </c>
       <c r="I72" s="3">
-        <v>3502000</v>
+        <v>3525800</v>
       </c>
       <c r="J72" s="3">
-        <v>3258200</v>
+        <v>3280400</v>
       </c>
       <c r="K72" s="3">
         <v>3129900</v>
@@ -6404,25 +6404,25 @@
         <v>68</v>
       </c>
       <c r="D76" s="3">
-        <v>7994200</v>
+        <v>8048600</v>
       </c>
       <c r="E76" s="3">
-        <v>7719300</v>
+        <v>7771800</v>
       </c>
       <c r="F76" s="3">
-        <v>7396200</v>
+        <v>7446600</v>
       </c>
       <c r="G76" s="3">
-        <v>7460300</v>
+        <v>7511000</v>
       </c>
       <c r="H76" s="3">
-        <v>7168400</v>
+        <v>7217200</v>
       </c>
       <c r="I76" s="3">
-        <v>6948000</v>
+        <v>6995300</v>
       </c>
       <c r="J76" s="3">
-        <v>6685300</v>
+        <v>6730800</v>
       </c>
       <c r="K76" s="3">
         <v>6701200</v>
@@ -6688,22 +6688,22 @@
         <v>8</v>
       </c>
       <c r="E81" s="3">
-        <v>350900</v>
+        <v>353300</v>
       </c>
       <c r="F81" s="3">
-        <v>230600</v>
+        <v>232200</v>
       </c>
       <c r="G81" s="3">
-        <v>298600</v>
+        <v>300600</v>
       </c>
       <c r="H81" s="3">
-        <v>267200</v>
+        <v>269000</v>
       </c>
       <c r="I81" s="3">
-        <v>249300</v>
+        <v>251000</v>
       </c>
       <c r="J81" s="3">
-        <v>125100</v>
+        <v>126000</v>
       </c>
       <c r="K81" s="3">
         <v>242800</v>
@@ -7363,25 +7363,25 @@
         <v>78</v>
       </c>
       <c r="D89" s="3">
-        <v>405700</v>
+        <v>408500</v>
       </c>
       <c r="E89" s="3">
-        <v>519400</v>
+        <v>522900</v>
       </c>
       <c r="F89" s="3">
-        <v>378100</v>
+        <v>380600</v>
       </c>
       <c r="G89" s="3">
-        <v>520500</v>
+        <v>524100</v>
       </c>
       <c r="H89" s="3">
-        <v>389800</v>
+        <v>392500</v>
       </c>
       <c r="I89" s="3">
-        <v>522000</v>
+        <v>525600</v>
       </c>
       <c r="J89" s="3">
-        <v>152600</v>
+        <v>153700</v>
       </c>
       <c r="K89" s="3">
         <v>416600</v>
@@ -7765,25 +7765,25 @@
         <v>83</v>
       </c>
       <c r="D94" s="3">
-        <v>-555900</v>
+        <v>-559700</v>
       </c>
       <c r="E94" s="3">
-        <v>-489000</v>
+        <v>-492300</v>
       </c>
       <c r="F94" s="3">
-        <v>-810100</v>
+        <v>-815600</v>
       </c>
       <c r="G94" s="3">
-        <v>-604900</v>
+        <v>-609000</v>
       </c>
       <c r="H94" s="3">
-        <v>-654000</v>
+        <v>-658500</v>
       </c>
       <c r="I94" s="3">
-        <v>-498400</v>
+        <v>-501800</v>
       </c>
       <c r="J94" s="3">
-        <v>-457700</v>
+        <v>-460800</v>
       </c>
       <c r="K94" s="3">
         <v>-387700</v>
@@ -8259,25 +8259,25 @@
         <v>89</v>
       </c>
       <c r="D100" s="3">
-        <v>349300</v>
+        <v>351700</v>
       </c>
       <c r="E100" s="3">
-        <v>-272600</v>
+        <v>-274500</v>
       </c>
       <c r="F100" s="3">
-        <v>116100</v>
+        <v>116900</v>
       </c>
       <c r="G100" s="3">
-        <v>-235700</v>
+        <v>-237300</v>
       </c>
       <c r="H100" s="3">
-        <v>875700</v>
+        <v>881600</v>
       </c>
       <c r="I100" s="3">
-        <v>-21700</v>
+        <v>-21800</v>
       </c>
       <c r="J100" s="3">
-        <v>356300</v>
+        <v>358800</v>
       </c>
       <c r="K100" s="3">
         <v>-108500</v>
@@ -8354,7 +8354,7 @@
         <v>1300</v>
       </c>
       <c r="E101" s="3">
-        <v>14500</v>
+        <v>14600</v>
       </c>
       <c r="F101" s="3">
         <v>-1200</v>
@@ -8363,10 +8363,10 @@
         <v>-8200</v>
       </c>
       <c r="H101" s="3">
-        <v>31000</v>
+        <v>31200</v>
       </c>
       <c r="I101" s="3">
-        <v>26700</v>
+        <v>26900</v>
       </c>
       <c r="J101" s="3">
         <v>-2900</v>
@@ -8446,22 +8446,22 @@
         <v>8</v>
       </c>
       <c r="E102" s="3">
-        <v>-227700</v>
+        <v>-229300</v>
       </c>
       <c r="F102" s="3">
-        <v>-317200</v>
+        <v>-319300</v>
       </c>
       <c r="G102" s="3">
-        <v>-328300</v>
+        <v>-330500</v>
       </c>
       <c r="H102" s="3">
-        <v>642500</v>
+        <v>646800</v>
       </c>
       <c r="I102" s="3">
-        <v>28700</v>
+        <v>28900</v>
       </c>
       <c r="J102" s="3">
-        <v>48400</v>
+        <v>48700</v>
       </c>
       <c r="K102" s="3">
         <v>-86200</v>

--- a/AAII_Financials/Quarterly/ZTO_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/ZTO_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="154" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="145" uniqueCount="92">
   <si>
     <t>ZTO</t>
   </si>
@@ -656,416 +656,441 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AF102"/>
+  <dimension ref="A5:AH102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="6.140625" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="8" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="12" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="16" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="20" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="24" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="28" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="29" max="29" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="30" max="30" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="31" max="32" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="33" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="22" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="26" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="30" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="32" max="32" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="33" max="34" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="35" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:34" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:34" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45382</v>
+      </c>
+      <c r="E7" s="2">
+        <v>45291</v>
+      </c>
+      <c r="F7" s="2">
         <v>45199</v>
       </c>
-      <c r="E7" s="2">
+      <c r="G7" s="2">
         <v>45107</v>
       </c>
-      <c r="F7" s="2">
+      <c r="H7" s="2">
         <v>45016</v>
       </c>
-      <c r="G7" s="2">
+      <c r="I7" s="2">
         <v>44926</v>
       </c>
-      <c r="H7" s="2">
+      <c r="J7" s="2">
         <v>44834</v>
       </c>
-      <c r="I7" s="2">
+      <c r="K7" s="2">
         <v>44742</v>
       </c>
-      <c r="J7" s="2">
+      <c r="L7" s="2">
         <v>44651</v>
       </c>
-      <c r="K7" s="2">
+      <c r="M7" s="2">
         <v>44561</v>
       </c>
-      <c r="L7" s="2">
+      <c r="N7" s="2">
         <v>44469</v>
       </c>
-      <c r="M7" s="2">
+      <c r="O7" s="2">
         <v>44377</v>
       </c>
-      <c r="N7" s="2">
+      <c r="P7" s="2">
         <v>44286</v>
       </c>
-      <c r="O7" s="2">
+      <c r="Q7" s="2">
         <v>44196</v>
       </c>
-      <c r="P7" s="2">
+      <c r="R7" s="2">
         <v>44104</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="S7" s="2">
         <v>44012</v>
       </c>
-      <c r="R7" s="2">
+      <c r="T7" s="2">
         <v>43921</v>
       </c>
-      <c r="S7" s="2">
+      <c r="U7" s="2">
         <v>43830</v>
       </c>
-      <c r="T7" s="2">
+      <c r="V7" s="2">
         <v>43738</v>
       </c>
-      <c r="U7" s="2">
+      <c r="W7" s="2">
         <v>43646</v>
       </c>
-      <c r="V7" s="2">
+      <c r="X7" s="2">
         <v>43555</v>
       </c>
-      <c r="W7" s="2">
+      <c r="Y7" s="2">
         <v>43465</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Z7" s="2">
         <v>43373</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="AA7" s="2">
         <v>43281</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AB7" s="2">
         <v>43190</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AC7" s="2">
         <v>43100</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AD7" s="2">
         <v>43008</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AE7" s="2">
         <v>42916</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AF7" s="2">
         <v>42825</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AG7" s="2">
         <v>42735</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AH7" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="8" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
-        <v>1261700</v>
+        <v>1376100</v>
       </c>
       <c r="E8" s="3">
-        <v>1354100</v>
+        <v>1467200</v>
       </c>
       <c r="F8" s="3">
-        <v>1248800</v>
+        <v>1253900</v>
       </c>
       <c r="G8" s="3">
-        <v>1372300</v>
+        <v>1345700</v>
       </c>
       <c r="H8" s="3">
-        <v>1243500</v>
+        <v>1241100</v>
       </c>
       <c r="I8" s="3">
+        <v>1363800</v>
+      </c>
+      <c r="J8" s="3">
+        <v>1235800</v>
+      </c>
+      <c r="K8" s="3">
         <v>1203500</v>
       </c>
-      <c r="J8" s="3">
+      <c r="L8" s="3">
         <v>1098800</v>
       </c>
-      <c r="K8" s="3">
+      <c r="M8" s="3">
         <v>1270000</v>
       </c>
-      <c r="L8" s="3">
+      <c r="N8" s="3">
         <v>1050600</v>
       </c>
-      <c r="M8" s="3">
+      <c r="O8" s="3">
         <v>1052000</v>
       </c>
-      <c r="N8" s="3">
+      <c r="P8" s="3">
         <v>929600</v>
       </c>
-      <c r="O8" s="3">
+      <c r="Q8" s="3">
         <v>1149400</v>
       </c>
-      <c r="P8" s="3">
+      <c r="R8" s="3">
         <v>978300</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="S8" s="3">
         <v>943500</v>
       </c>
-      <c r="R8" s="3">
+      <c r="T8" s="3">
         <v>617800</v>
       </c>
-      <c r="S8" s="3">
+      <c r="U8" s="3">
         <v>1054200</v>
       </c>
-      <c r="T8" s="3">
+      <c r="V8" s="3">
         <v>821500</v>
       </c>
-      <c r="U8" s="3">
+      <c r="W8" s="3">
         <v>828600</v>
       </c>
-      <c r="V8" s="3">
+      <c r="X8" s="3">
         <v>695800</v>
       </c>
-      <c r="W8" s="3">
+      <c r="Y8" s="3">
         <v>817300</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Z8" s="3">
         <v>592700</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="AA8" s="3">
         <v>587500</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AB8" s="3">
         <v>508600</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AC8" s="3">
         <v>642800</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AD8" s="3">
         <v>466500</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AE8" s="3">
         <v>441000</v>
       </c>
-      <c r="AD8" s="3">
+      <c r="AF8" s="3">
         <v>380200</v>
       </c>
-      <c r="AE8" s="3">
+      <c r="AG8" s="3">
         <v>464000</v>
       </c>
-      <c r="AF8" s="3">
+      <c r="AH8" s="3">
         <v>342200</v>
       </c>
     </row>
-    <row r="9" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
-        <v>885500</v>
+        <v>961300</v>
       </c>
       <c r="E9" s="3">
-        <v>894700</v>
+        <v>1035000</v>
       </c>
       <c r="F9" s="3">
-        <v>898000</v>
+        <v>880000</v>
       </c>
       <c r="G9" s="3">
-        <v>986900</v>
+        <v>889200</v>
       </c>
       <c r="H9" s="3">
-        <v>903700</v>
+        <v>892500</v>
       </c>
       <c r="I9" s="3">
+        <v>980800</v>
+      </c>
+      <c r="J9" s="3">
+        <v>898100</v>
+      </c>
+      <c r="K9" s="3">
         <v>897200</v>
       </c>
-      <c r="J9" s="3">
+      <c r="L9" s="3">
         <v>873700</v>
       </c>
-      <c r="K9" s="3">
+      <c r="M9" s="3">
         <v>959900</v>
       </c>
-      <c r="L9" s="3">
+      <c r="N9" s="3">
         <v>827700</v>
       </c>
-      <c r="M9" s="3">
+      <c r="O9" s="3">
         <v>811700</v>
       </c>
-      <c r="N9" s="3">
+      <c r="P9" s="3">
         <v>772100</v>
       </c>
-      <c r="O9" s="3">
+      <c r="Q9" s="3">
         <v>890700</v>
       </c>
-      <c r="P9" s="3">
+      <c r="R9" s="3">
         <v>773300</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="S9" s="3">
         <v>682800</v>
       </c>
-      <c r="R9" s="3">
+      <c r="T9" s="3">
         <v>488600</v>
       </c>
-      <c r="S9" s="3">
+      <c r="U9" s="3">
         <v>746900</v>
       </c>
-      <c r="T9" s="3">
+      <c r="V9" s="3">
         <v>572400</v>
       </c>
-      <c r="U9" s="3">
+      <c r="W9" s="3">
         <v>558400</v>
       </c>
-      <c r="V9" s="3">
+      <c r="X9" s="3">
         <v>504200</v>
       </c>
-      <c r="W9" s="3">
+      <c r="Y9" s="3">
         <v>592200</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Z9" s="3">
         <v>407200</v>
       </c>
-      <c r="Y9" s="3">
+      <c r="AA9" s="3">
         <v>383600</v>
       </c>
-      <c r="Z9" s="3">
+      <c r="AB9" s="3">
         <v>360500</v>
       </c>
-      <c r="AA9" s="3">
+      <c r="AC9" s="3">
         <v>441900</v>
       </c>
-      <c r="AB9" s="3">
+      <c r="AD9" s="3">
         <v>297600</v>
       </c>
-      <c r="AC9" s="3">
+      <c r="AE9" s="3">
         <v>274200</v>
       </c>
-      <c r="AD9" s="3">
+      <c r="AF9" s="3">
         <v>274000</v>
       </c>
-      <c r="AE9" s="3">
+      <c r="AG9" s="3">
         <v>295100</v>
       </c>
-      <c r="AF9" s="3">
+      <c r="AH9" s="3">
         <v>218200</v>
       </c>
     </row>
-    <row r="10" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
-        <v>376200</v>
+        <v>414800</v>
       </c>
       <c r="E10" s="3">
-        <v>459400</v>
+        <v>432200</v>
       </c>
       <c r="F10" s="3">
-        <v>350800</v>
+        <v>373900</v>
       </c>
       <c r="G10" s="3">
-        <v>385400</v>
+        <v>456500</v>
       </c>
       <c r="H10" s="3">
-        <v>339800</v>
+        <v>348600</v>
       </c>
       <c r="I10" s="3">
+        <v>383100</v>
+      </c>
+      <c r="J10" s="3">
+        <v>337700</v>
+      </c>
+      <c r="K10" s="3">
         <v>306200</v>
       </c>
-      <c r="J10" s="3">
+      <c r="L10" s="3">
         <v>225100</v>
       </c>
-      <c r="K10" s="3">
+      <c r="M10" s="3">
         <v>310100</v>
       </c>
-      <c r="L10" s="3">
+      <c r="N10" s="3">
         <v>222900</v>
       </c>
-      <c r="M10" s="3">
+      <c r="O10" s="3">
         <v>240400</v>
       </c>
-      <c r="N10" s="3">
+      <c r="P10" s="3">
         <v>157500</v>
       </c>
-      <c r="O10" s="3">
+      <c r="Q10" s="3">
         <v>258700</v>
       </c>
-      <c r="P10" s="3">
+      <c r="R10" s="3">
         <v>205000</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="S10" s="3">
         <v>260700</v>
       </c>
-      <c r="R10" s="3">
+      <c r="T10" s="3">
         <v>129200</v>
       </c>
-      <c r="S10" s="3">
+      <c r="U10" s="3">
         <v>307400</v>
       </c>
-      <c r="T10" s="3">
+      <c r="V10" s="3">
         <v>249100</v>
       </c>
-      <c r="U10" s="3">
+      <c r="W10" s="3">
         <v>270200</v>
       </c>
-      <c r="V10" s="3">
+      <c r="X10" s="3">
         <v>191600</v>
       </c>
-      <c r="W10" s="3">
+      <c r="Y10" s="3">
         <v>225100</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Z10" s="3">
         <v>185500</v>
       </c>
-      <c r="Y10" s="3">
+      <c r="AA10" s="3">
         <v>204000</v>
       </c>
-      <c r="Z10" s="3">
+      <c r="AB10" s="3">
         <v>148100</v>
       </c>
-      <c r="AA10" s="3">
+      <c r="AC10" s="3">
         <v>200800</v>
       </c>
-      <c r="AB10" s="3">
+      <c r="AD10" s="3">
         <v>168900</v>
       </c>
-      <c r="AC10" s="3">
+      <c r="AE10" s="3">
         <v>166800</v>
       </c>
-      <c r="AD10" s="3">
+      <c r="AF10" s="3">
         <v>106300</v>
       </c>
-      <c r="AE10" s="3">
+      <c r="AG10" s="3">
         <v>168900</v>
       </c>
-      <c r="AF10" s="3">
+      <c r="AH10" s="3">
         <v>124000</v>
       </c>
     </row>
-    <row r="11" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -1098,8 +1123,10 @@
       <c r="AD11" s="3"/>
       <c r="AE11" s="3"/>
       <c r="AF11" s="3"/>
-    </row>
-    <row r="12" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="AG11" s="3"/>
+      <c r="AH11" s="3"/>
+    </row>
+    <row r="12" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
@@ -1190,8 +1217,14 @@
       <c r="AF12" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="13" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="AG12" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AH12" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="13" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1282,88 +1315,94 @@
       <c r="AF13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="AG13" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3">
+        <v>66000</v>
+      </c>
+      <c r="E14" s="3">
+        <v>600</v>
+      </c>
+      <c r="F14" s="3">
         <v>-1500</v>
       </c>
-      <c r="E14" s="3">
+      <c r="G14" s="3">
         <v>100</v>
       </c>
-      <c r="F14" s="3" t="s">
+      <c r="H14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="G14" s="3">
+      <c r="I14" s="3">
         <v>-1300</v>
       </c>
-      <c r="H14" s="3">
-        <v>-4800</v>
-      </c>
-      <c r="I14" s="3" t="s">
+      <c r="J14" s="3">
+        <v>-4700</v>
+      </c>
+      <c r="K14" s="3" t="s">
         <v>8</v>
-      </c>
-      <c r="J14" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="K14" s="3">
-        <v>-300</v>
       </c>
       <c r="L14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="M14" s="3" t="s">
-        <v>8</v>
+      <c r="M14" s="3">
+        <v>-300</v>
       </c>
       <c r="N14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="O14" s="3">
+      <c r="O14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="P14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q14" s="3">
         <v>-200</v>
       </c>
-      <c r="P14" s="3">
-        <v>0</v>
-      </c>
-      <c r="Q14" s="3">
-        <v>0</v>
-      </c>
       <c r="R14" s="3">
         <v>0</v>
       </c>
       <c r="S14" s="3">
+        <v>0</v>
+      </c>
+      <c r="T14" s="3">
+        <v>0</v>
+      </c>
+      <c r="U14" s="3">
         <v>9000</v>
       </c>
-      <c r="T14" s="3">
-        <v>0</v>
-      </c>
-      <c r="U14" s="3">
-        <v>0</v>
-      </c>
       <c r="V14" s="3">
+        <v>0</v>
+      </c>
+      <c r="W14" s="3">
+        <v>0</v>
+      </c>
+      <c r="X14" s="3">
         <v>100</v>
       </c>
-      <c r="W14" s="3">
-        <v>0</v>
-      </c>
-      <c r="X14" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="Y14" s="3" t="s">
-        <v>8</v>
+      <c r="Y14" s="3">
+        <v>0</v>
       </c>
       <c r="Z14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AA14" s="3">
-        <v>4500</v>
+      <c r="AA14" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="AB14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AC14" s="3" t="s">
-        <v>8</v>
+      <c r="AC14" s="3">
+        <v>4500</v>
       </c>
       <c r="AD14" s="3" t="s">
         <v>8</v>
@@ -1374,8 +1413,14 @@
       <c r="AF14" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="15" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="AG14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AH14" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="15" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1466,8 +1511,14 @@
       <c r="AF15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="AG15" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:34" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1497,192 +1548,206 @@
       <c r="AD16" s="3"/>
       <c r="AE16" s="3"/>
       <c r="AF16" s="3"/>
-    </row>
-    <row r="17" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG16" s="3"/>
+      <c r="AH16" s="3"/>
+    </row>
+    <row r="17" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="D17" s="3" t="s">
-        <v>8</v>
+      <c r="D17" s="3">
+        <v>1128900</v>
       </c>
       <c r="E17" s="3">
-        <v>954000</v>
+        <v>1087200</v>
       </c>
       <c r="F17" s="3">
-        <v>977700</v>
+        <v>917600</v>
       </c>
       <c r="G17" s="3">
-        <v>1029100</v>
+        <v>948100</v>
       </c>
       <c r="H17" s="3">
-        <v>936400</v>
+        <v>971700</v>
       </c>
       <c r="I17" s="3">
+        <v>1022700</v>
+      </c>
+      <c r="J17" s="3">
+        <v>930600</v>
+      </c>
+      <c r="K17" s="3">
         <v>927400</v>
       </c>
-      <c r="J17" s="3">
+      <c r="L17" s="3">
         <v>943600</v>
       </c>
-      <c r="K17" s="3">
+      <c r="M17" s="3">
         <v>986700</v>
       </c>
-      <c r="L17" s="3">
+      <c r="N17" s="3">
         <v>857200</v>
       </c>
-      <c r="M17" s="3">
+      <c r="O17" s="3">
         <v>843000</v>
       </c>
-      <c r="N17" s="3">
+      <c r="P17" s="3">
         <v>838700</v>
       </c>
-      <c r="O17" s="3">
+      <c r="Q17" s="3">
         <v>931200</v>
       </c>
-      <c r="P17" s="3">
+      <c r="R17" s="3">
         <v>806000</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="S17" s="3">
         <v>700800</v>
       </c>
-      <c r="R17" s="3">
+      <c r="T17" s="3">
         <v>559100</v>
       </c>
-      <c r="S17" s="3">
+      <c r="U17" s="3">
         <v>784600</v>
       </c>
-      <c r="T17" s="3">
+      <c r="V17" s="3">
         <v>603000</v>
       </c>
-      <c r="U17" s="3">
+      <c r="W17" s="3">
         <v>600600</v>
       </c>
-      <c r="V17" s="3">
+      <c r="X17" s="3">
         <v>580300</v>
       </c>
-      <c r="W17" s="3">
+      <c r="Y17" s="3">
         <v>620800</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Z17" s="3">
         <v>439900</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="AA17" s="3">
         <v>421100</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AB17" s="3">
         <v>408300</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AC17" s="3">
         <v>465300</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AD17" s="3">
         <v>326300</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AE17" s="3">
         <v>304300</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AF17" s="3">
         <v>284700</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AG17" s="3">
         <v>322800</v>
       </c>
-      <c r="AF17" s="3">
+      <c r="AH17" s="3">
         <v>234400</v>
       </c>
     </row>
-    <row r="18" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="D18" s="3" t="s">
-        <v>8</v>
+      <c r="D18" s="3">
+        <v>247100</v>
       </c>
       <c r="E18" s="3">
-        <v>400100</v>
+        <v>380000</v>
       </c>
       <c r="F18" s="3">
-        <v>271100</v>
+        <v>336300</v>
       </c>
       <c r="G18" s="3">
-        <v>343200</v>
+        <v>397600</v>
       </c>
       <c r="H18" s="3">
-        <v>307100</v>
+        <v>269500</v>
       </c>
       <c r="I18" s="3">
+        <v>341100</v>
+      </c>
+      <c r="J18" s="3">
+        <v>305200</v>
+      </c>
+      <c r="K18" s="3">
         <v>276000</v>
       </c>
-      <c r="J18" s="3">
+      <c r="L18" s="3">
         <v>155200</v>
       </c>
-      <c r="K18" s="3">
+      <c r="M18" s="3">
         <v>283300</v>
       </c>
-      <c r="L18" s="3">
+      <c r="N18" s="3">
         <v>193400</v>
       </c>
-      <c r="M18" s="3">
+      <c r="O18" s="3">
         <v>209100</v>
       </c>
-      <c r="N18" s="3">
+      <c r="P18" s="3">
         <v>90900</v>
       </c>
-      <c r="O18" s="3">
+      <c r="Q18" s="3">
         <v>218200</v>
       </c>
-      <c r="P18" s="3">
+      <c r="R18" s="3">
         <v>172300</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="S18" s="3">
         <v>242600</v>
       </c>
-      <c r="R18" s="3">
+      <c r="T18" s="3">
         <v>58700</v>
       </c>
-      <c r="S18" s="3">
+      <c r="U18" s="3">
         <v>269700</v>
       </c>
-      <c r="T18" s="3">
+      <c r="V18" s="3">
         <v>218500</v>
       </c>
-      <c r="U18" s="3">
+      <c r="W18" s="3">
         <v>228100</v>
       </c>
-      <c r="V18" s="3">
+      <c r="X18" s="3">
         <v>115500</v>
       </c>
-      <c r="W18" s="3">
+      <c r="Y18" s="3">
         <v>196500</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Z18" s="3">
         <v>152800</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="AA18" s="3">
         <v>166400</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AB18" s="3">
         <v>100200</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AC18" s="3">
         <v>177500</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AD18" s="3">
         <v>140200</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AE18" s="3">
         <v>136700</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AF18" s="3">
         <v>95500</v>
       </c>
-      <c r="AE18" s="3">
+      <c r="AG18" s="3">
         <v>141200</v>
       </c>
-      <c r="AF18" s="3">
+      <c r="AH18" s="3">
         <v>107800</v>
       </c>
     </row>
-    <row r="19" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1715,243 +1780,257 @@
       <c r="AD19" s="3"/>
       <c r="AE19" s="3"/>
       <c r="AF19" s="3"/>
-    </row>
-    <row r="20" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG19" s="3"/>
+      <c r="AH19" s="3"/>
+    </row>
+    <row r="20" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="D20" s="3" t="s">
-        <v>8</v>
+      <c r="D20" s="3">
+        <v>40500</v>
       </c>
       <c r="E20" s="3">
-        <v>41700</v>
+        <v>23200</v>
       </c>
       <c r="F20" s="3">
-        <v>33000</v>
+        <v>35900</v>
       </c>
       <c r="G20" s="3">
-        <v>28400</v>
+        <v>41400</v>
       </c>
       <c r="H20" s="3">
-        <v>23800</v>
+        <v>32800</v>
       </c>
       <c r="I20" s="3">
+        <v>28200</v>
+      </c>
+      <c r="J20" s="3">
+        <v>23600</v>
+      </c>
+      <c r="K20" s="3">
         <v>31200</v>
       </c>
-      <c r="J20" s="3">
+      <c r="L20" s="3">
         <v>13500</v>
       </c>
-      <c r="K20" s="3">
+      <c r="M20" s="3">
         <v>9900</v>
       </c>
-      <c r="L20" s="3">
+      <c r="N20" s="3">
         <v>12600</v>
       </c>
-      <c r="M20" s="3">
+      <c r="O20" s="3">
         <v>15600</v>
       </c>
-      <c r="N20" s="3">
+      <c r="P20" s="3">
         <v>13100</v>
       </c>
-      <c r="O20" s="3">
+      <c r="Q20" s="3">
         <v>3200</v>
       </c>
-      <c r="P20" s="3">
+      <c r="R20" s="3">
         <v>4800</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="S20" s="3">
         <v>17200</v>
       </c>
-      <c r="R20" s="3">
+      <c r="T20" s="3">
         <v>22500</v>
       </c>
-      <c r="S20" s="3">
+      <c r="U20" s="3">
         <v>137200</v>
       </c>
-      <c r="T20" s="3">
+      <c r="V20" s="3">
         <v>27300</v>
       </c>
-      <c r="U20" s="3">
+      <c r="W20" s="3">
         <v>25500</v>
       </c>
-      <c r="V20" s="3">
+      <c r="X20" s="3">
         <v>18300</v>
       </c>
-      <c r="W20" s="3">
+      <c r="Y20" s="3">
         <v>21500</v>
       </c>
-      <c r="X20" s="3">
+      <c r="Z20" s="3">
         <v>24800</v>
       </c>
-      <c r="Y20" s="3">
+      <c r="AA20" s="3">
         <v>91900</v>
       </c>
-      <c r="Z20" s="3">
+      <c r="AB20" s="3">
         <v>3400</v>
       </c>
-      <c r="AA20" s="3">
+      <c r="AC20" s="3">
         <v>5700</v>
       </c>
-      <c r="AB20" s="3">
+      <c r="AD20" s="3">
         <v>2600</v>
       </c>
-      <c r="AC20" s="3">
+      <c r="AE20" s="3">
         <v>5500</v>
       </c>
-      <c r="AD20" s="3">
+      <c r="AF20" s="3">
         <v>3700</v>
       </c>
-      <c r="AE20" s="3">
+      <c r="AG20" s="3">
         <v>3500</v>
       </c>
-      <c r="AF20" s="3">
+      <c r="AH20" s="3">
         <v>1400</v>
       </c>
     </row>
-    <row r="21" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="D21" s="3" t="s">
-        <v>8</v>
+      <c r="D21" s="3">
+        <v>396200</v>
       </c>
       <c r="E21" s="3">
-        <v>444400</v>
+        <v>401600</v>
       </c>
       <c r="F21" s="3">
-        <v>399600</v>
+        <v>377700</v>
       </c>
       <c r="G21" s="3">
-        <v>375700</v>
+        <v>441600</v>
       </c>
       <c r="H21" s="3">
-        <v>329900</v>
+        <v>397100</v>
       </c>
       <c r="I21" s="3">
+        <v>373400</v>
+      </c>
+      <c r="J21" s="3">
+        <v>327900</v>
+      </c>
+      <c r="K21" s="3">
         <v>312700</v>
       </c>
-      <c r="J21" s="3">
+      <c r="L21" s="3">
         <v>256700</v>
       </c>
-      <c r="K21" s="3">
+      <c r="M21" s="3">
         <v>300500</v>
       </c>
-      <c r="L21" s="3">
+      <c r="N21" s="3">
         <v>202200</v>
       </c>
-      <c r="M21" s="3">
+      <c r="O21" s="3">
         <v>231000</v>
       </c>
-      <c r="N21" s="3">
+      <c r="P21" s="3">
         <v>178800</v>
       </c>
-      <c r="O21" s="3">
+      <c r="Q21" s="3">
         <v>227200</v>
       </c>
-      <c r="P21" s="3">
+      <c r="R21" s="3">
         <v>184900</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="S21" s="3">
         <v>262500</v>
       </c>
-      <c r="R21" s="3">
+      <c r="T21" s="3">
         <v>145600</v>
       </c>
-      <c r="S21" s="3">
+      <c r="U21" s="3">
         <v>418900</v>
       </c>
-      <c r="T21" s="3">
+      <c r="V21" s="3">
         <v>246500</v>
       </c>
-      <c r="U21" s="3">
+      <c r="W21" s="3">
         <v>255900</v>
       </c>
-      <c r="V21" s="3">
+      <c r="X21" s="3">
         <v>176900</v>
       </c>
-      <c r="W21" s="3">
+      <c r="Y21" s="3">
         <v>223700</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Z21" s="3">
         <v>179800</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="AA21" s="3">
         <v>259900</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AB21" s="3">
         <v>130400</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AC21" s="3">
         <v>183000</v>
       </c>
-      <c r="AB21" s="3">
+      <c r="AD21" s="3">
         <v>144500</v>
       </c>
-      <c r="AC21" s="3">
+      <c r="AE21" s="3">
         <v>143100</v>
       </c>
-      <c r="AD21" s="3">
+      <c r="AF21" s="3">
         <v>118100</v>
       </c>
-      <c r="AE21" s="3">
+      <c r="AG21" s="3">
         <v>178100</v>
       </c>
-      <c r="AF21" s="3">
+      <c r="AH21" s="3">
         <v>105200</v>
       </c>
     </row>
-    <row r="22" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
-        <v>11700</v>
+        <v>11600</v>
       </c>
       <c r="E22" s="3">
+        <v>8500</v>
+      </c>
+      <c r="F22" s="3">
+        <v>11600</v>
+      </c>
+      <c r="G22" s="3">
         <v>10000</v>
       </c>
-      <c r="F22" s="3">
-        <v>10000</v>
-      </c>
-      <c r="G22" s="3">
-        <v>10600</v>
-      </c>
       <c r="H22" s="3">
+        <v>9900</v>
+      </c>
+      <c r="I22" s="3">
+        <v>10500</v>
+      </c>
+      <c r="J22" s="3">
         <v>4400</v>
       </c>
-      <c r="I22" s="3">
+      <c r="K22" s="3">
         <v>3200</v>
       </c>
-      <c r="J22" s="3">
+      <c r="L22" s="3">
         <v>8300</v>
       </c>
-      <c r="K22" s="3">
+      <c r="M22" s="3">
         <v>3400</v>
       </c>
-      <c r="L22" s="3">
+      <c r="N22" s="3">
         <v>7400</v>
       </c>
-      <c r="M22" s="3">
+      <c r="O22" s="3">
         <v>4900</v>
       </c>
-      <c r="N22" s="3">
+      <c r="P22" s="3">
         <v>2200</v>
       </c>
-      <c r="O22" s="3">
+      <c r="Q22" s="3">
         <v>1700</v>
       </c>
-      <c r="P22" s="3">
+      <c r="R22" s="3">
         <v>2000</v>
       </c>
-      <c r="Q22" s="3">
+      <c r="S22" s="3">
         <v>1300</v>
       </c>
-      <c r="R22" s="3">
-        <v>0</v>
-      </c>
-      <c r="S22" s="3">
-        <v>0</v>
-      </c>
       <c r="T22" s="3">
         <v>0</v>
       </c>
@@ -1971,212 +2050,230 @@
         <v>0</v>
       </c>
       <c r="Z22" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA22" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB22" s="3">
         <v>100</v>
       </c>
-      <c r="AA22" s="3">
+      <c r="AC22" s="3">
         <v>400</v>
       </c>
-      <c r="AB22" s="3">
+      <c r="AD22" s="3">
         <v>400</v>
       </c>
-      <c r="AC22" s="3">
+      <c r="AE22" s="3">
         <v>700</v>
       </c>
-      <c r="AD22" s="3">
+      <c r="AF22" s="3">
         <v>800</v>
       </c>
-      <c r="AE22" s="3">
+      <c r="AG22" s="3">
         <v>100</v>
       </c>
-      <c r="AF22" s="3">
+      <c r="AH22" s="3">
         <v>500</v>
       </c>
     </row>
-    <row r="23" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
-        <v>362900</v>
+        <v>276000</v>
       </c>
       <c r="E23" s="3">
-        <v>431800</v>
+        <v>394700</v>
       </c>
       <c r="F23" s="3">
-        <v>294200</v>
+        <v>360600</v>
       </c>
       <c r="G23" s="3">
-        <v>361000</v>
+        <v>429100</v>
       </c>
       <c r="H23" s="3">
-        <v>326400</v>
+        <v>292300</v>
       </c>
       <c r="I23" s="3">
+        <v>358800</v>
+      </c>
+      <c r="J23" s="3">
+        <v>324400</v>
+      </c>
+      <c r="K23" s="3">
         <v>304100</v>
       </c>
-      <c r="J23" s="3">
+      <c r="L23" s="3">
         <v>160400</v>
       </c>
-      <c r="K23" s="3">
+      <c r="M23" s="3">
         <v>289800</v>
       </c>
-      <c r="L23" s="3">
+      <c r="N23" s="3">
         <v>198600</v>
       </c>
-      <c r="M23" s="3">
+      <c r="O23" s="3">
         <v>219900</v>
       </c>
-      <c r="N23" s="3">
+      <c r="P23" s="3">
         <v>101700</v>
       </c>
-      <c r="O23" s="3">
+      <c r="Q23" s="3">
         <v>219700</v>
       </c>
-      <c r="P23" s="3">
+      <c r="R23" s="3">
         <v>175000</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="S23" s="3">
         <v>258500</v>
       </c>
-      <c r="R23" s="3">
+      <c r="T23" s="3">
         <v>81200</v>
       </c>
-      <c r="S23" s="3">
+      <c r="U23" s="3">
         <v>406900</v>
       </c>
-      <c r="T23" s="3">
+      <c r="V23" s="3">
         <v>245800</v>
       </c>
-      <c r="U23" s="3">
+      <c r="W23" s="3">
         <v>253500</v>
       </c>
-      <c r="V23" s="3">
+      <c r="X23" s="3">
         <v>133900</v>
       </c>
-      <c r="W23" s="3">
+      <c r="Y23" s="3">
         <v>218000</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Z23" s="3">
         <v>177600</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="AA23" s="3">
         <v>258300</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AB23" s="3">
         <v>103500</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AC23" s="3">
         <v>182800</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AD23" s="3">
         <v>142500</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AE23" s="3">
         <v>141400</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AF23" s="3">
         <v>98400</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AG23" s="3">
         <v>144600</v>
       </c>
-      <c r="AF23" s="3">
+      <c r="AH23" s="3">
         <v>108700</v>
       </c>
     </row>
-    <row r="24" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
-        <v>37700</v>
+        <v>78200</v>
       </c>
       <c r="E24" s="3">
-        <v>80000</v>
+        <v>88000</v>
       </c>
       <c r="F24" s="3">
-        <v>63300</v>
+        <v>37500</v>
       </c>
       <c r="G24" s="3">
-        <v>69600</v>
+        <v>79500</v>
       </c>
       <c r="H24" s="3">
-        <v>61100</v>
+        <v>62900</v>
       </c>
       <c r="I24" s="3">
+        <v>69200</v>
+      </c>
+      <c r="J24" s="3">
+        <v>60700</v>
+      </c>
+      <c r="K24" s="3">
         <v>60900</v>
       </c>
-      <c r="J24" s="3">
+      <c r="L24" s="3">
         <v>35500</v>
       </c>
-      <c r="K24" s="3">
+      <c r="M24" s="3">
         <v>51200</v>
       </c>
-      <c r="L24" s="3">
+      <c r="N24" s="3">
         <v>32600</v>
       </c>
-      <c r="M24" s="3">
+      <c r="O24" s="3">
         <v>36600</v>
       </c>
-      <c r="N24" s="3">
+      <c r="P24" s="3">
         <v>21500</v>
       </c>
-      <c r="O24" s="3">
+      <c r="Q24" s="3">
         <v>40300</v>
       </c>
-      <c r="P24" s="3">
+      <c r="R24" s="3">
         <v>-4100</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="S24" s="3">
         <v>44000</v>
       </c>
-      <c r="R24" s="3">
+      <c r="T24" s="3">
         <v>20500</v>
       </c>
-      <c r="S24" s="3">
+      <c r="U24" s="3">
         <v>51000</v>
       </c>
-      <c r="T24" s="3">
+      <c r="V24" s="3">
         <v>41500</v>
       </c>
-      <c r="U24" s="3">
+      <c r="W24" s="3">
         <v>44100</v>
       </c>
-      <c r="V24" s="3">
+      <c r="X24" s="3">
         <v>29200</v>
       </c>
-      <c r="W24" s="3">
+      <c r="Y24" s="3">
         <v>32300</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Z24" s="3">
         <v>28200</v>
       </c>
-      <c r="Y24" s="3">
+      <c r="AA24" s="3">
         <v>49100</v>
       </c>
-      <c r="Z24" s="3">
+      <c r="AB24" s="3">
         <v>22100</v>
       </c>
-      <c r="AA24" s="3">
+      <c r="AC24" s="3">
         <v>1300</v>
       </c>
-      <c r="AB24" s="3">
+      <c r="AD24" s="3">
         <v>35300</v>
       </c>
-      <c r="AC24" s="3">
+      <c r="AE24" s="3">
         <v>34600</v>
       </c>
-      <c r="AD24" s="3">
+      <c r="AF24" s="3">
         <v>24200</v>
       </c>
-      <c r="AE24" s="3">
+      <c r="AG24" s="3">
         <v>36600</v>
       </c>
-      <c r="AF24" s="3">
+      <c r="AH24" s="3">
         <v>27100</v>
       </c>
     </row>
-    <row r="25" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2267,192 +2364,210 @@
       <c r="AF25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG25" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="D26" s="3" t="s">
-        <v>8</v>
+      <c r="D26" s="3">
+        <v>197800</v>
       </c>
       <c r="E26" s="3">
-        <v>351700</v>
+        <v>306700</v>
       </c>
       <c r="F26" s="3">
-        <v>230900</v>
+        <v>323100</v>
       </c>
       <c r="G26" s="3">
-        <v>291500</v>
+        <v>349600</v>
       </c>
       <c r="H26" s="3">
-        <v>265400</v>
+        <v>229500</v>
       </c>
       <c r="I26" s="3">
+        <v>289700</v>
+      </c>
+      <c r="J26" s="3">
+        <v>263700</v>
+      </c>
+      <c r="K26" s="3">
         <v>243100</v>
       </c>
-      <c r="J26" s="3">
+      <c r="L26" s="3">
         <v>124900</v>
       </c>
-      <c r="K26" s="3">
+      <c r="M26" s="3">
         <v>238600</v>
       </c>
-      <c r="L26" s="3">
+      <c r="N26" s="3">
         <v>166000</v>
       </c>
-      <c r="M26" s="3">
+      <c r="O26" s="3">
         <v>183300</v>
       </c>
-      <c r="N26" s="3">
+      <c r="P26" s="3">
         <v>80200</v>
       </c>
-      <c r="O26" s="3">
+      <c r="Q26" s="3">
         <v>179400</v>
       </c>
-      <c r="P26" s="3">
+      <c r="R26" s="3">
         <v>179100</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="S26" s="3">
         <v>214600</v>
       </c>
-      <c r="R26" s="3">
+      <c r="T26" s="3">
         <v>60700</v>
       </c>
-      <c r="S26" s="3">
+      <c r="U26" s="3">
         <v>355800</v>
       </c>
-      <c r="T26" s="3">
+      <c r="V26" s="3">
         <v>204200</v>
       </c>
-      <c r="U26" s="3">
+      <c r="W26" s="3">
         <v>209400</v>
       </c>
-      <c r="V26" s="3">
+      <c r="X26" s="3">
         <v>104700</v>
       </c>
-      <c r="W26" s="3">
+      <c r="Y26" s="3">
         <v>185700</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Z26" s="3">
         <v>149400</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="AA26" s="3">
         <v>209100</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AB26" s="3">
         <v>81300</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AC26" s="3">
         <v>181500</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AD26" s="3">
         <v>107200</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AE26" s="3">
         <v>106800</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AF26" s="3">
         <v>74200</v>
       </c>
-      <c r="AE26" s="3">
+      <c r="AG26" s="3">
         <v>108000</v>
       </c>
-      <c r="AF26" s="3">
+      <c r="AH26" s="3">
         <v>81600</v>
       </c>
     </row>
-    <row r="27" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="D27" s="3" t="s">
-        <v>8</v>
+      <c r="D27" s="3">
+        <v>197000</v>
       </c>
       <c r="E27" s="3">
-        <v>353300</v>
+        <v>302900</v>
       </c>
       <c r="F27" s="3">
-        <v>232200</v>
+        <v>324000</v>
       </c>
       <c r="G27" s="3">
-        <v>300600</v>
+        <v>351100</v>
       </c>
       <c r="H27" s="3">
-        <v>269000</v>
+        <v>230800</v>
       </c>
       <c r="I27" s="3">
+        <v>298800</v>
+      </c>
+      <c r="J27" s="3">
+        <v>267300</v>
+      </c>
+      <c r="K27" s="3">
         <v>251000</v>
       </c>
-      <c r="J27" s="3">
+      <c r="L27" s="3">
         <v>126000</v>
       </c>
-      <c r="K27" s="3">
+      <c r="M27" s="3">
         <v>242800</v>
       </c>
-      <c r="L27" s="3">
+      <c r="N27" s="3">
         <v>165800</v>
       </c>
-      <c r="M27" s="3">
+      <c r="O27" s="3">
         <v>185600</v>
       </c>
-      <c r="N27" s="3">
+      <c r="P27" s="3">
         <v>76600</v>
       </c>
-      <c r="O27" s="3">
+      <c r="Q27" s="3">
         <v>179300</v>
       </c>
-      <c r="P27" s="3">
+      <c r="R27" s="3">
         <v>177000</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="S27" s="3">
         <v>213400</v>
       </c>
-      <c r="R27" s="3">
+      <c r="T27" s="3">
         <v>59100</v>
       </c>
-      <c r="S27" s="3">
+      <c r="U27" s="3">
         <v>358200</v>
       </c>
-      <c r="T27" s="3">
+      <c r="V27" s="3">
         <v>204000</v>
       </c>
-      <c r="U27" s="3">
+      <c r="W27" s="3">
         <v>207700</v>
       </c>
-      <c r="V27" s="3">
+      <c r="X27" s="3">
         <v>103600</v>
       </c>
-      <c r="W27" s="3">
+      <c r="Y27" s="3">
         <v>185200</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Z27" s="3">
         <v>148300</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="AA27" s="3">
         <v>208700</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AB27" s="3">
         <v>79900</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AC27" s="3">
         <v>181400</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AD27" s="3">
         <v>106400</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AE27" s="3">
         <v>106400</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AF27" s="3">
         <v>73200</v>
       </c>
-      <c r="AE27" s="3">
+      <c r="AG27" s="3">
         <v>105700</v>
       </c>
-      <c r="AF27" s="3">
+      <c r="AH27" s="3">
         <v>73700</v>
       </c>
     </row>
-    <row r="28" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2543,8 +2658,14 @@
       <c r="AF28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG28" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2635,8 +2756,14 @@
       <c r="AF29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG29" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2727,8 +2854,14 @@
       <c r="AF30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG30" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2819,192 +2952,210 @@
       <c r="AF31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG31" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="D32" s="3" t="s">
-        <v>8</v>
+      <c r="D32" s="3">
+        <v>-40500</v>
       </c>
       <c r="E32" s="3">
-        <v>-41700</v>
+        <v>-23200</v>
       </c>
       <c r="F32" s="3">
-        <v>-33000</v>
+        <v>-35900</v>
       </c>
       <c r="G32" s="3">
-        <v>-28400</v>
+        <v>-41400</v>
       </c>
       <c r="H32" s="3">
-        <v>-23800</v>
+        <v>-32800</v>
       </c>
       <c r="I32" s="3">
+        <v>-28200</v>
+      </c>
+      <c r="J32" s="3">
+        <v>-23600</v>
+      </c>
+      <c r="K32" s="3">
         <v>-31200</v>
       </c>
-      <c r="J32" s="3">
+      <c r="L32" s="3">
         <v>-13500</v>
       </c>
-      <c r="K32" s="3">
+      <c r="M32" s="3">
         <v>-9900</v>
       </c>
-      <c r="L32" s="3">
+      <c r="N32" s="3">
         <v>-12600</v>
       </c>
-      <c r="M32" s="3">
+      <c r="O32" s="3">
         <v>-15600</v>
       </c>
-      <c r="N32" s="3">
+      <c r="P32" s="3">
         <v>-13100</v>
       </c>
-      <c r="O32" s="3">
+      <c r="Q32" s="3">
         <v>-3200</v>
       </c>
-      <c r="P32" s="3">
+      <c r="R32" s="3">
         <v>-4800</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="S32" s="3">
         <v>-17200</v>
       </c>
-      <c r="R32" s="3">
+      <c r="T32" s="3">
         <v>-22500</v>
       </c>
-      <c r="S32" s="3">
+      <c r="U32" s="3">
         <v>-137200</v>
       </c>
-      <c r="T32" s="3">
+      <c r="V32" s="3">
         <v>-27300</v>
       </c>
-      <c r="U32" s="3">
+      <c r="W32" s="3">
         <v>-25500</v>
       </c>
-      <c r="V32" s="3">
+      <c r="X32" s="3">
         <v>-18300</v>
       </c>
-      <c r="W32" s="3">
+      <c r="Y32" s="3">
         <v>-21500</v>
       </c>
-      <c r="X32" s="3">
+      <c r="Z32" s="3">
         <v>-24800</v>
       </c>
-      <c r="Y32" s="3">
+      <c r="AA32" s="3">
         <v>-91900</v>
       </c>
-      <c r="Z32" s="3">
+      <c r="AB32" s="3">
         <v>-3400</v>
       </c>
-      <c r="AA32" s="3">
+      <c r="AC32" s="3">
         <v>-5700</v>
       </c>
-      <c r="AB32" s="3">
+      <c r="AD32" s="3">
         <v>-2600</v>
       </c>
-      <c r="AC32" s="3">
+      <c r="AE32" s="3">
         <v>-5500</v>
       </c>
-      <c r="AD32" s="3">
+      <c r="AF32" s="3">
         <v>-3700</v>
       </c>
-      <c r="AE32" s="3">
+      <c r="AG32" s="3">
         <v>-3500</v>
       </c>
-      <c r="AF32" s="3">
+      <c r="AH32" s="3">
         <v>-1400</v>
       </c>
     </row>
-    <row r="33" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="D33" s="3" t="s">
-        <v>8</v>
+      <c r="D33" s="3">
+        <v>197000</v>
       </c>
       <c r="E33" s="3">
-        <v>353300</v>
+        <v>302900</v>
       </c>
       <c r="F33" s="3">
-        <v>232200</v>
+        <v>324000</v>
       </c>
       <c r="G33" s="3">
-        <v>300600</v>
+        <v>351100</v>
       </c>
       <c r="H33" s="3">
-        <v>269000</v>
+        <v>230800</v>
       </c>
       <c r="I33" s="3">
+        <v>298800</v>
+      </c>
+      <c r="J33" s="3">
+        <v>267300</v>
+      </c>
+      <c r="K33" s="3">
         <v>251000</v>
       </c>
-      <c r="J33" s="3">
+      <c r="L33" s="3">
         <v>126000</v>
       </c>
-      <c r="K33" s="3">
+      <c r="M33" s="3">
         <v>242800</v>
       </c>
-      <c r="L33" s="3">
+      <c r="N33" s="3">
         <v>165800</v>
       </c>
-      <c r="M33" s="3">
+      <c r="O33" s="3">
         <v>185600</v>
       </c>
-      <c r="N33" s="3">
+      <c r="P33" s="3">
         <v>76600</v>
       </c>
-      <c r="O33" s="3">
+      <c r="Q33" s="3">
         <v>179300</v>
       </c>
-      <c r="P33" s="3">
+      <c r="R33" s="3">
         <v>177000</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="S33" s="3">
         <v>213400</v>
       </c>
-      <c r="R33" s="3">
+      <c r="T33" s="3">
         <v>59100</v>
       </c>
-      <c r="S33" s="3">
+      <c r="U33" s="3">
         <v>358200</v>
       </c>
-      <c r="T33" s="3">
+      <c r="V33" s="3">
         <v>204000</v>
       </c>
-      <c r="U33" s="3">
+      <c r="W33" s="3">
         <v>207700</v>
       </c>
-      <c r="V33" s="3">
+      <c r="X33" s="3">
         <v>103600</v>
       </c>
-      <c r="W33" s="3">
+      <c r="Y33" s="3">
         <v>185200</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Z33" s="3">
         <v>148300</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="AA33" s="3">
         <v>208700</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AB33" s="3">
         <v>79900</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AC33" s="3">
         <v>181400</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AD33" s="3">
         <v>106400</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AE33" s="3">
         <v>106400</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AF33" s="3">
         <v>73200</v>
       </c>
-      <c r="AE33" s="3">
+      <c r="AG33" s="3">
         <v>105700</v>
       </c>
-      <c r="AF33" s="3">
+      <c r="AH33" s="3">
         <v>73700</v>
       </c>
     </row>
-    <row r="34" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3095,197 +3246,215 @@
       <c r="AF34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG34" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="D35" s="3" t="s">
-        <v>8</v>
+      <c r="D35" s="3">
+        <v>197000</v>
       </c>
       <c r="E35" s="3">
-        <v>353300</v>
+        <v>302900</v>
       </c>
       <c r="F35" s="3">
-        <v>232200</v>
+        <v>324000</v>
       </c>
       <c r="G35" s="3">
-        <v>300600</v>
+        <v>351100</v>
       </c>
       <c r="H35" s="3">
-        <v>269000</v>
+        <v>230800</v>
       </c>
       <c r="I35" s="3">
+        <v>298800</v>
+      </c>
+      <c r="J35" s="3">
+        <v>267300</v>
+      </c>
+      <c r="K35" s="3">
         <v>251000</v>
       </c>
-      <c r="J35" s="3">
+      <c r="L35" s="3">
         <v>126000</v>
       </c>
-      <c r="K35" s="3">
+      <c r="M35" s="3">
         <v>242800</v>
       </c>
-      <c r="L35" s="3">
+      <c r="N35" s="3">
         <v>165800</v>
       </c>
-      <c r="M35" s="3">
+      <c r="O35" s="3">
         <v>185600</v>
       </c>
-      <c r="N35" s="3">
+      <c r="P35" s="3">
         <v>76600</v>
       </c>
-      <c r="O35" s="3">
+      <c r="Q35" s="3">
         <v>179300</v>
       </c>
-      <c r="P35" s="3">
+      <c r="R35" s="3">
         <v>177000</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="S35" s="3">
         <v>213400</v>
       </c>
-      <c r="R35" s="3">
+      <c r="T35" s="3">
         <v>59100</v>
       </c>
-      <c r="S35" s="3">
+      <c r="U35" s="3">
         <v>358200</v>
       </c>
-      <c r="T35" s="3">
+      <c r="V35" s="3">
         <v>204000</v>
       </c>
-      <c r="U35" s="3">
+      <c r="W35" s="3">
         <v>207700</v>
       </c>
-      <c r="V35" s="3">
+      <c r="X35" s="3">
         <v>103600</v>
       </c>
-      <c r="W35" s="3">
+      <c r="Y35" s="3">
         <v>185200</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Z35" s="3">
         <v>148300</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="AA35" s="3">
         <v>208700</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AB35" s="3">
         <v>79900</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AC35" s="3">
         <v>181400</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AD35" s="3">
         <v>106400</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AE35" s="3">
         <v>106400</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AF35" s="3">
         <v>73200</v>
       </c>
-      <c r="AE35" s="3">
+      <c r="AG35" s="3">
         <v>105700</v>
       </c>
-      <c r="AF35" s="3">
+      <c r="AH35" s="3">
         <v>73700</v>
       </c>
     </row>
-    <row r="37" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:34" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45382</v>
+      </c>
+      <c r="E38" s="2">
+        <v>45291</v>
+      </c>
+      <c r="F38" s="2">
         <v>45199</v>
       </c>
-      <c r="E38" s="2">
+      <c r="G38" s="2">
         <v>45107</v>
       </c>
-      <c r="F38" s="2">
+      <c r="H38" s="2">
         <v>45016</v>
       </c>
-      <c r="G38" s="2">
+      <c r="I38" s="2">
         <v>44926</v>
       </c>
-      <c r="H38" s="2">
+      <c r="J38" s="2">
         <v>44834</v>
       </c>
-      <c r="I38" s="2">
+      <c r="K38" s="2">
         <v>44742</v>
       </c>
-      <c r="J38" s="2">
+      <c r="L38" s="2">
         <v>44651</v>
       </c>
-      <c r="K38" s="2">
+      <c r="M38" s="2">
         <v>44561</v>
       </c>
-      <c r="L38" s="2">
+      <c r="N38" s="2">
         <v>44469</v>
       </c>
-      <c r="M38" s="2">
+      <c r="O38" s="2">
         <v>44377</v>
       </c>
-      <c r="N38" s="2">
+      <c r="P38" s="2">
         <v>44286</v>
       </c>
-      <c r="O38" s="2">
+      <c r="Q38" s="2">
         <v>44196</v>
       </c>
-      <c r="P38" s="2">
+      <c r="R38" s="2">
         <v>44104</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="S38" s="2">
         <v>44012</v>
       </c>
-      <c r="R38" s="2">
+      <c r="T38" s="2">
         <v>43921</v>
       </c>
-      <c r="S38" s="2">
+      <c r="U38" s="2">
         <v>43830</v>
       </c>
-      <c r="T38" s="2">
+      <c r="V38" s="2">
         <v>43738</v>
       </c>
-      <c r="U38" s="2">
+      <c r="W38" s="2">
         <v>43646</v>
       </c>
-      <c r="V38" s="2">
+      <c r="X38" s="2">
         <v>43555</v>
       </c>
-      <c r="W38" s="2">
+      <c r="Y38" s="2">
         <v>43465</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Z38" s="2">
         <v>43373</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="AA38" s="2">
         <v>43281</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AB38" s="2">
         <v>43190</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AC38" s="2">
         <v>43100</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AD38" s="2">
         <v>43008</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AE38" s="2">
         <v>42916</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AF38" s="2">
         <v>42825</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AG38" s="2">
         <v>42735</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AH38" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="39" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3318,8 +3487,10 @@
       <c r="AD39" s="3"/>
       <c r="AE39" s="3"/>
       <c r="AF39" s="3"/>
-    </row>
-    <row r="40" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG39" s="3"/>
+      <c r="AH39" s="3"/>
+    </row>
+    <row r="40" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3352,836 +3523,892 @@
       <c r="AD40" s="3"/>
       <c r="AE40" s="3"/>
       <c r="AF40" s="3"/>
-    </row>
-    <row r="41" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG40" s="3"/>
+      <c r="AH40" s="3"/>
+    </row>
+    <row r="41" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
-        <v>1290700</v>
+        <v>1738600</v>
       </c>
       <c r="E41" s="3">
-        <v>1081800</v>
+        <v>1704000</v>
       </c>
       <c r="F41" s="3">
-        <v>1328400</v>
+        <v>1282800</v>
       </c>
       <c r="G41" s="3">
-        <v>1625500</v>
+        <v>1075100</v>
       </c>
       <c r="H41" s="3">
-        <v>2028600</v>
+        <v>1320200</v>
       </c>
       <c r="I41" s="3">
+        <v>1615500</v>
+      </c>
+      <c r="J41" s="3">
+        <v>2016100</v>
+      </c>
+      <c r="K41" s="3">
         <v>1380200</v>
       </c>
-      <c r="J41" s="3">
+      <c r="L41" s="3">
         <v>1376400</v>
       </c>
-      <c r="K41" s="3">
+      <c r="M41" s="3">
         <v>1339400</v>
       </c>
-      <c r="L41" s="3">
+      <c r="N41" s="3">
         <v>1472400</v>
       </c>
-      <c r="M41" s="3">
+      <c r="O41" s="3">
         <v>1737600</v>
       </c>
-      <c r="N41" s="3">
+      <c r="P41" s="3">
         <v>1590500</v>
       </c>
-      <c r="O41" s="3">
+      <c r="Q41" s="3">
         <v>1978400</v>
       </c>
-      <c r="P41" s="3">
+      <c r="R41" s="3">
         <v>2418000</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="S41" s="3">
         <v>775400</v>
       </c>
-      <c r="R41" s="3">
+      <c r="T41" s="3">
         <v>792000</v>
       </c>
-      <c r="S41" s="3">
+      <c r="U41" s="3">
         <v>811500</v>
       </c>
-      <c r="T41" s="3">
+      <c r="V41" s="3">
         <v>789200</v>
       </c>
-      <c r="U41" s="3">
+      <c r="W41" s="3">
         <v>1086500</v>
       </c>
-      <c r="V41" s="3">
+      <c r="X41" s="3">
         <v>926800</v>
       </c>
-      <c r="W41" s="3">
+      <c r="Y41" s="3">
         <v>671300</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Z41" s="3">
         <v>877700</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="AA41" s="3">
         <v>848700</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AB41" s="3">
         <v>486000</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AC41" s="3">
         <v>805100</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AD41" s="3">
         <v>768800</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AE41" s="3">
         <v>848000</v>
       </c>
-      <c r="AD41" s="3">
+      <c r="AF41" s="3">
         <v>920400</v>
       </c>
-      <c r="AE41" s="3">
+      <c r="AG41" s="3">
         <v>1641600</v>
       </c>
-      <c r="AF41" s="3">
+      <c r="AH41" s="3">
         <v>287600</v>
       </c>
     </row>
-    <row r="42" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
-        <v>1063900</v>
+        <v>972400</v>
       </c>
       <c r="E42" s="3">
-        <v>1106100</v>
+        <v>1029900</v>
       </c>
       <c r="F42" s="3">
-        <v>1234300</v>
+        <v>1057400</v>
       </c>
       <c r="G42" s="3">
-        <v>799800</v>
+        <v>1099300</v>
       </c>
       <c r="H42" s="3">
-        <v>966600</v>
+        <v>1226600</v>
       </c>
       <c r="I42" s="3">
+        <v>794900</v>
+      </c>
+      <c r="J42" s="3">
+        <v>960600</v>
+      </c>
+      <c r="K42" s="3">
         <v>724400</v>
       </c>
-      <c r="J42" s="3">
+      <c r="L42" s="3">
         <v>556400</v>
       </c>
-      <c r="K42" s="3">
+      <c r="M42" s="3">
         <v>392000</v>
       </c>
-      <c r="L42" s="3">
+      <c r="N42" s="3">
         <v>336100</v>
       </c>
-      <c r="M42" s="3">
+      <c r="O42" s="3">
         <v>450800</v>
       </c>
-      <c r="N42" s="3">
+      <c r="P42" s="3">
         <v>794000</v>
       </c>
-      <c r="O42" s="3">
+      <c r="Q42" s="3">
         <v>513700</v>
       </c>
-      <c r="P42" s="3">
+      <c r="R42" s="3">
         <v>708000</v>
       </c>
-      <c r="Q42" s="3">
+      <c r="S42" s="3">
         <v>1243400</v>
       </c>
-      <c r="R42" s="3">
+      <c r="T42" s="3">
         <v>1596100</v>
       </c>
-      <c r="S42" s="3">
+      <c r="U42" s="3">
         <v>1711200</v>
       </c>
-      <c r="T42" s="3">
+      <c r="V42" s="3">
         <v>1763500</v>
       </c>
-      <c r="U42" s="3">
+      <c r="W42" s="3">
         <v>1414900</v>
       </c>
-      <c r="V42" s="3">
+      <c r="X42" s="3">
         <v>1717000</v>
       </c>
-      <c r="W42" s="3">
+      <c r="Y42" s="3">
         <v>1975100</v>
       </c>
-      <c r="X42" s="3">
+      <c r="Z42" s="3">
         <v>1664900</v>
       </c>
-      <c r="Y42" s="3">
+      <c r="AA42" s="3">
         <v>1343800</v>
       </c>
-      <c r="Z42" s="3">
+      <c r="AB42" s="3">
         <v>795600</v>
       </c>
-      <c r="AA42" s="3">
+      <c r="AC42" s="3">
         <v>775400</v>
       </c>
-      <c r="AB42" s="3">
+      <c r="AD42" s="3">
         <v>819600</v>
       </c>
-      <c r="AC42" s="3">
+      <c r="AE42" s="3">
         <v>769700</v>
       </c>
-      <c r="AD42" s="3">
+      <c r="AF42" s="3">
         <v>700700</v>
       </c>
-      <c r="AE42" s="3" t="s">
+      <c r="AG42" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AF42" s="3" t="s">
+      <c r="AH42" s="3" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="43" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
-        <v>334300</v>
+        <v>240500</v>
       </c>
       <c r="E43" s="3">
-        <v>322400</v>
+        <v>256400</v>
       </c>
       <c r="F43" s="3">
-        <v>254800</v>
+        <v>332200</v>
       </c>
       <c r="G43" s="3">
-        <v>289800</v>
+        <v>320400</v>
       </c>
       <c r="H43" s="3">
-        <v>267500</v>
+        <v>253200</v>
       </c>
       <c r="I43" s="3">
+        <v>288000</v>
+      </c>
+      <c r="J43" s="3">
+        <v>265800</v>
+      </c>
+      <c r="K43" s="3">
         <v>267700</v>
       </c>
-      <c r="J43" s="3">
+      <c r="L43" s="3">
         <v>264100</v>
       </c>
-      <c r="K43" s="3">
+      <c r="M43" s="3">
         <v>300200</v>
       </c>
-      <c r="L43" s="3">
+      <c r="N43" s="3">
         <v>260500</v>
       </c>
-      <c r="M43" s="3">
+      <c r="O43" s="3">
         <v>262000</v>
       </c>
-      <c r="N43" s="3">
+      <c r="P43" s="3">
         <v>187900</v>
       </c>
-      <c r="O43" s="3">
+      <c r="Q43" s="3">
         <v>182600</v>
       </c>
-      <c r="P43" s="3">
+      <c r="R43" s="3">
         <v>252900</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="S43" s="3">
         <v>174200</v>
       </c>
-      <c r="R43" s="3">
+      <c r="T43" s="3">
         <v>210600</v>
       </c>
-      <c r="S43" s="3">
+      <c r="U43" s="3">
         <v>194200</v>
       </c>
-      <c r="T43" s="3">
+      <c r="V43" s="3">
         <v>172000</v>
       </c>
-      <c r="U43" s="3">
+      <c r="W43" s="3">
         <v>177300</v>
       </c>
-      <c r="V43" s="3">
+      <c r="X43" s="3">
         <v>171100</v>
       </c>
-      <c r="W43" s="3">
+      <c r="Y43" s="3">
         <v>162900</v>
       </c>
-      <c r="X43" s="3">
+      <c r="Z43" s="3">
         <v>120200</v>
       </c>
-      <c r="Y43" s="3">
+      <c r="AA43" s="3">
         <v>209200</v>
       </c>
-      <c r="Z43" s="3">
+      <c r="AB43" s="3">
         <v>69200</v>
       </c>
-      <c r="AA43" s="3">
+      <c r="AC43" s="3">
         <v>53700</v>
       </c>
-      <c r="AB43" s="3">
+      <c r="AD43" s="3">
         <v>31000</v>
       </c>
-      <c r="AC43" s="3">
+      <c r="AE43" s="3">
         <v>28800</v>
       </c>
-      <c r="AD43" s="3">
+      <c r="AF43" s="3">
         <v>25200</v>
       </c>
-      <c r="AE43" s="3">
+      <c r="AG43" s="3">
         <v>29600</v>
       </c>
-      <c r="AF43" s="3">
+      <c r="AH43" s="3">
         <v>17800</v>
       </c>
     </row>
-    <row r="44" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>5700</v>
+      </c>
+      <c r="E44" s="3">
+        <v>3900</v>
+      </c>
+      <c r="F44" s="3">
         <v>3800</v>
       </c>
-      <c r="E44" s="3">
+      <c r="G44" s="3">
         <v>3700</v>
       </c>
-      <c r="F44" s="3">
-        <v>4100</v>
-      </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
+        <v>4000</v>
+      </c>
+      <c r="I44" s="3">
         <v>5600</v>
       </c>
-      <c r="H44" s="3">
-        <v>9000</v>
-      </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
+        <v>8900</v>
+      </c>
+      <c r="K44" s="3">
         <v>4000</v>
       </c>
-      <c r="J44" s="3">
+      <c r="L44" s="3">
         <v>8200</v>
       </c>
-      <c r="K44" s="3">
+      <c r="M44" s="3">
         <v>11400</v>
       </c>
-      <c r="L44" s="3">
+      <c r="N44" s="3">
         <v>7100</v>
       </c>
-      <c r="M44" s="3">
+      <c r="O44" s="3">
         <v>5700</v>
-      </c>
-      <c r="N44" s="3">
-        <v>7400</v>
-      </c>
-      <c r="O44" s="3">
-        <v>7400</v>
       </c>
       <c r="P44" s="3">
         <v>7400</v>
       </c>
       <c r="Q44" s="3">
+        <v>7400</v>
+      </c>
+      <c r="R44" s="3">
+        <v>7400</v>
+      </c>
+      <c r="S44" s="3">
         <v>9500</v>
       </c>
-      <c r="R44" s="3">
+      <c r="T44" s="3">
         <v>8900</v>
       </c>
-      <c r="S44" s="3">
+      <c r="U44" s="3">
         <v>6800</v>
       </c>
-      <c r="T44" s="3">
+      <c r="V44" s="3">
         <v>5600</v>
       </c>
-      <c r="U44" s="3">
+      <c r="W44" s="3">
         <v>5400</v>
       </c>
-      <c r="V44" s="3">
+      <c r="X44" s="3">
         <v>4700</v>
       </c>
-      <c r="W44" s="3">
+      <c r="Y44" s="3">
         <v>6400</v>
       </c>
-      <c r="X44" s="3">
+      <c r="Z44" s="3">
         <v>5200</v>
       </c>
-      <c r="Y44" s="3">
+      <c r="AA44" s="3">
         <v>5600</v>
       </c>
-      <c r="Z44" s="3">
+      <c r="AB44" s="3">
         <v>4400</v>
       </c>
-      <c r="AA44" s="3">
+      <c r="AC44" s="3">
         <v>5100</v>
       </c>
-      <c r="AB44" s="3">
+      <c r="AD44" s="3">
         <v>4200</v>
       </c>
-      <c r="AC44" s="3">
+      <c r="AE44" s="3">
         <v>4300</v>
       </c>
-      <c r="AD44" s="3">
+      <c r="AF44" s="3">
         <v>4600</v>
       </c>
-      <c r="AE44" s="3">
+      <c r="AG44" s="3">
         <v>4900</v>
       </c>
-      <c r="AF44" s="3">
+      <c r="AH44" s="3">
         <v>4100</v>
       </c>
     </row>
-    <row r="45" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
-        <v>744800</v>
+        <v>737100</v>
       </c>
       <c r="E45" s="3">
-        <v>730200</v>
+        <v>729600</v>
       </c>
       <c r="F45" s="3">
-        <v>693400</v>
+        <v>740200</v>
       </c>
       <c r="G45" s="3">
-        <v>681700</v>
+        <v>725700</v>
       </c>
       <c r="H45" s="3">
-        <v>587800</v>
+        <v>689100</v>
       </c>
       <c r="I45" s="3">
+        <v>677500</v>
+      </c>
+      <c r="J45" s="3">
+        <v>584100</v>
+      </c>
+      <c r="K45" s="3">
         <v>567700</v>
       </c>
-      <c r="J45" s="3">
+      <c r="L45" s="3">
         <v>580200</v>
       </c>
-      <c r="K45" s="3">
+      <c r="M45" s="3">
         <v>528800</v>
       </c>
-      <c r="L45" s="3">
+      <c r="N45" s="3">
         <v>552300</v>
       </c>
-      <c r="M45" s="3">
+      <c r="O45" s="3">
         <v>501800</v>
       </c>
-      <c r="N45" s="3">
+      <c r="P45" s="3">
         <v>511200</v>
       </c>
-      <c r="O45" s="3">
+      <c r="Q45" s="3">
         <v>425500</v>
       </c>
-      <c r="P45" s="3">
+      <c r="R45" s="3">
         <v>433900</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="S45" s="3">
         <v>423200</v>
       </c>
-      <c r="R45" s="3">
+      <c r="T45" s="3">
         <v>378400</v>
       </c>
-      <c r="S45" s="3">
+      <c r="U45" s="3">
         <v>371100</v>
       </c>
-      <c r="T45" s="3">
+      <c r="V45" s="3">
         <v>313400</v>
       </c>
-      <c r="U45" s="3">
+      <c r="W45" s="3">
         <v>374900</v>
       </c>
-      <c r="V45" s="3">
+      <c r="X45" s="3">
         <v>264700</v>
       </c>
-      <c r="W45" s="3">
+      <c r="Y45" s="3">
         <v>268100</v>
       </c>
-      <c r="X45" s="3">
+      <c r="Z45" s="3">
         <v>213400</v>
       </c>
-      <c r="Y45" s="3">
+      <c r="AA45" s="3">
         <v>191900</v>
       </c>
-      <c r="Z45" s="3">
+      <c r="AB45" s="3">
         <v>168000</v>
       </c>
-      <c r="AA45" s="3">
+      <c r="AC45" s="3">
         <v>197700</v>
       </c>
-      <c r="AB45" s="3">
+      <c r="AD45" s="3">
         <v>172000</v>
       </c>
-      <c r="AC45" s="3">
+      <c r="AE45" s="3">
         <v>168000</v>
       </c>
-      <c r="AD45" s="3">
+      <c r="AF45" s="3">
         <v>226600</v>
       </c>
-      <c r="AE45" s="3">
+      <c r="AG45" s="3">
         <v>241600</v>
       </c>
-      <c r="AF45" s="3">
+      <c r="AH45" s="3">
         <v>149500</v>
       </c>
     </row>
-    <row r="46" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
-        <v>3437600</v>
+        <v>3694300</v>
       </c>
       <c r="E46" s="3">
-        <v>3244100</v>
+        <v>3723900</v>
       </c>
       <c r="F46" s="3">
-        <v>3515000</v>
+        <v>3416300</v>
       </c>
       <c r="G46" s="3">
-        <v>3402500</v>
+        <v>3224000</v>
       </c>
       <c r="H46" s="3">
-        <v>3859400</v>
+        <v>3493200</v>
       </c>
       <c r="I46" s="3">
+        <v>3381500</v>
+      </c>
+      <c r="J46" s="3">
+        <v>3835500</v>
+      </c>
+      <c r="K46" s="3">
         <v>2944100</v>
       </c>
-      <c r="J46" s="3">
+      <c r="L46" s="3">
         <v>2785400</v>
       </c>
-      <c r="K46" s="3">
+      <c r="M46" s="3">
         <v>2571900</v>
       </c>
-      <c r="L46" s="3">
+      <c r="N46" s="3">
         <v>2628500</v>
       </c>
-      <c r="M46" s="3">
+      <c r="O46" s="3">
         <v>2957900</v>
       </c>
-      <c r="N46" s="3">
+      <c r="P46" s="3">
         <v>3091000</v>
       </c>
-      <c r="O46" s="3">
+      <c r="Q46" s="3">
         <v>3107600</v>
       </c>
-      <c r="P46" s="3">
+      <c r="R46" s="3">
         <v>3820200</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="S46" s="3">
         <v>2625600</v>
       </c>
-      <c r="R46" s="3">
+      <c r="T46" s="3">
         <v>2986000</v>
       </c>
-      <c r="S46" s="3">
+      <c r="U46" s="3">
         <v>3094700</v>
       </c>
-      <c r="T46" s="3">
+      <c r="V46" s="3">
         <v>3043800</v>
       </c>
-      <c r="U46" s="3">
+      <c r="W46" s="3">
         <v>3059000</v>
       </c>
-      <c r="V46" s="3">
+      <c r="X46" s="3">
         <v>3084200</v>
       </c>
-      <c r="W46" s="3">
+      <c r="Y46" s="3">
         <v>3083800</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Z46" s="3">
         <v>2881400</v>
       </c>
-      <c r="Y46" s="3">
+      <c r="AA46" s="3">
         <v>2599300</v>
       </c>
-      <c r="Z46" s="3">
+      <c r="AB46" s="3">
         <v>1523100</v>
       </c>
-      <c r="AA46" s="3">
+      <c r="AC46" s="3">
         <v>1837000</v>
       </c>
-      <c r="AB46" s="3">
+      <c r="AD46" s="3">
         <v>1795600</v>
       </c>
-      <c r="AC46" s="3">
+      <c r="AE46" s="3">
         <v>1818900</v>
       </c>
-      <c r="AD46" s="3">
+      <c r="AF46" s="3">
         <v>1877500</v>
       </c>
-      <c r="AE46" s="3">
+      <c r="AG46" s="3">
         <v>1917600</v>
       </c>
-      <c r="AF46" s="3">
+      <c r="AH46" s="3">
         <v>459000</v>
       </c>
     </row>
-    <row r="47" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
-        <v>2614300</v>
+        <v>2484700</v>
       </c>
       <c r="E47" s="3">
-        <v>2199400</v>
+        <v>2372900</v>
       </c>
       <c r="F47" s="3">
-        <v>1887400</v>
+        <v>2598100</v>
       </c>
       <c r="G47" s="3">
-        <v>1827600</v>
+        <v>2185800</v>
       </c>
       <c r="H47" s="3">
-        <v>1345400</v>
+        <v>1875700</v>
       </c>
       <c r="I47" s="3">
+        <v>1816200</v>
+      </c>
+      <c r="J47" s="3">
+        <v>1337100</v>
+      </c>
+      <c r="K47" s="3">
         <v>1167900</v>
       </c>
-      <c r="J47" s="3">
+      <c r="L47" s="3">
         <v>1019900</v>
       </c>
-      <c r="K47" s="3">
+      <c r="M47" s="3">
         <v>960200</v>
       </c>
-      <c r="L47" s="3">
+      <c r="N47" s="3">
         <v>996500</v>
       </c>
-      <c r="M47" s="3">
+      <c r="O47" s="3">
         <v>1076500</v>
       </c>
-      <c r="N47" s="3">
+      <c r="P47" s="3">
         <v>1100900</v>
       </c>
-      <c r="O47" s="3">
+      <c r="Q47" s="3">
         <v>1049100</v>
       </c>
-      <c r="P47" s="3">
+      <c r="R47" s="3">
         <v>898800</v>
       </c>
-      <c r="Q47" s="3">
+      <c r="S47" s="3">
         <v>876900</v>
       </c>
-      <c r="R47" s="3">
+      <c r="T47" s="3">
         <v>771500</v>
       </c>
-      <c r="S47" s="3">
+      <c r="U47" s="3">
         <v>709100</v>
       </c>
-      <c r="T47" s="3">
+      <c r="V47" s="3">
         <v>347600</v>
       </c>
-      <c r="U47" s="3">
+      <c r="W47" s="3">
         <v>336200</v>
       </c>
-      <c r="V47" s="3">
+      <c r="X47" s="3">
         <v>332500</v>
       </c>
-      <c r="W47" s="3">
+      <c r="Y47" s="3">
         <v>320600</v>
       </c>
-      <c r="X47" s="3">
+      <c r="Z47" s="3">
         <v>239300</v>
       </c>
-      <c r="Y47" s="3">
+      <c r="AA47" s="3">
         <v>215800</v>
       </c>
-      <c r="Z47" s="3">
+      <c r="AB47" s="3">
         <v>86400</v>
       </c>
-      <c r="AA47" s="3">
+      <c r="AC47" s="3">
         <v>90600</v>
       </c>
-      <c r="AB47" s="3">
+      <c r="AD47" s="3">
         <v>82600</v>
       </c>
-      <c r="AC47" s="3">
+      <c r="AE47" s="3">
         <v>78200</v>
       </c>
-      <c r="AD47" s="3">
+      <c r="AF47" s="3">
         <v>76400</v>
       </c>
-      <c r="AE47" s="3">
+      <c r="AG47" s="3">
         <v>78100</v>
       </c>
-      <c r="AF47" s="3">
+      <c r="AH47" s="3">
         <v>69300</v>
       </c>
     </row>
-    <row r="48" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
-        <v>4520300</v>
+        <v>4634300</v>
       </c>
       <c r="E48" s="3">
-        <v>4407300</v>
+        <v>4539000</v>
       </c>
       <c r="F48" s="3">
-        <v>4253100</v>
+        <v>4492400</v>
       </c>
       <c r="G48" s="3">
-        <v>4118000</v>
+        <v>4380000</v>
       </c>
       <c r="H48" s="3">
-        <v>4002400</v>
+        <v>4226800</v>
       </c>
       <c r="I48" s="3">
+        <v>4092500</v>
+      </c>
+      <c r="J48" s="3">
+        <v>3977700</v>
+      </c>
+      <c r="K48" s="3">
         <v>3845100</v>
       </c>
-      <c r="J48" s="3">
+      <c r="L48" s="3">
         <v>3707100</v>
       </c>
-      <c r="K48" s="3">
+      <c r="M48" s="3">
         <v>3558500</v>
       </c>
-      <c r="L48" s="3">
+      <c r="N48" s="3">
         <v>3435000</v>
       </c>
-      <c r="M48" s="3">
+      <c r="O48" s="3">
         <v>3191700</v>
       </c>
-      <c r="N48" s="3">
+      <c r="P48" s="3">
         <v>2895100</v>
       </c>
-      <c r="O48" s="3">
+      <c r="Q48" s="3">
         <v>2706200</v>
       </c>
-      <c r="P48" s="3">
+      <c r="R48" s="3">
         <v>2552500</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="S48" s="3">
         <v>2274600</v>
       </c>
-      <c r="R48" s="3">
+      <c r="T48" s="3">
         <v>2237200</v>
       </c>
-      <c r="S48" s="3">
+      <c r="U48" s="3">
         <v>2059100</v>
       </c>
-      <c r="T48" s="3">
+      <c r="V48" s="3">
         <v>1814900</v>
       </c>
-      <c r="U48" s="3">
+      <c r="W48" s="3">
         <v>1577900</v>
       </c>
-      <c r="V48" s="3">
+      <c r="X48" s="3">
         <v>1532300</v>
       </c>
-      <c r="W48" s="3">
+      <c r="Y48" s="3">
         <v>1312300</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Z48" s="3">
         <v>1117100</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="AA48" s="3">
         <v>1015500</v>
       </c>
-      <c r="Z48" s="3">
+      <c r="AB48" s="3">
         <v>983700</v>
       </c>
-      <c r="AA48" s="3">
+      <c r="AC48" s="3">
         <v>960700</v>
       </c>
-      <c r="AB48" s="3">
+      <c r="AD48" s="3">
         <v>866600</v>
       </c>
-      <c r="AC48" s="3">
+      <c r="AE48" s="3">
         <v>765200</v>
       </c>
-      <c r="AD48" s="3">
+      <c r="AF48" s="3">
         <v>668800</v>
       </c>
-      <c r="AE48" s="3">
+      <c r="AG48" s="3">
         <v>591300</v>
       </c>
-      <c r="AF48" s="3">
+      <c r="AH48" s="3">
         <v>479700</v>
       </c>
     </row>
-    <row r="49" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
-        <v>1377500</v>
+        <v>1373200</v>
       </c>
       <c r="E49" s="3">
-        <v>1382000</v>
+        <v>1368000</v>
       </c>
       <c r="F49" s="3">
-        <v>1381100</v>
+        <v>1369000</v>
       </c>
       <c r="G49" s="3">
-        <v>1350400</v>
+        <v>1373500</v>
       </c>
       <c r="H49" s="3">
-        <v>1339800</v>
+        <v>1372500</v>
       </c>
       <c r="I49" s="3">
+        <v>1342100</v>
+      </c>
+      <c r="J49" s="3">
+        <v>1331500</v>
+      </c>
+      <c r="K49" s="3">
         <v>1350200</v>
       </c>
-      <c r="J49" s="3">
+      <c r="L49" s="3">
         <v>1338000</v>
       </c>
-      <c r="K49" s="3">
+      <c r="M49" s="3">
         <v>1324400</v>
       </c>
-      <c r="L49" s="3">
+      <c r="N49" s="3">
         <v>1333000</v>
       </c>
-      <c r="M49" s="3">
+      <c r="O49" s="3">
         <v>1321600</v>
       </c>
-      <c r="N49" s="3">
+      <c r="P49" s="3">
         <v>1295800</v>
       </c>
-      <c r="O49" s="3">
+      <c r="Q49" s="3">
         <v>1203300</v>
       </c>
-      <c r="P49" s="3">
+      <c r="R49" s="3">
         <v>1236400</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="S49" s="3">
         <v>1195900</v>
       </c>
-      <c r="R49" s="3">
+      <c r="T49" s="3">
         <v>1154200</v>
       </c>
-      <c r="S49" s="3">
+      <c r="U49" s="3">
         <v>1046800</v>
       </c>
-      <c r="T49" s="3">
+      <c r="V49" s="3">
         <v>1029800</v>
       </c>
-      <c r="U49" s="3">
+      <c r="W49" s="3">
         <v>987300</v>
       </c>
-      <c r="V49" s="3">
+      <c r="X49" s="3">
         <v>983500</v>
       </c>
-      <c r="W49" s="3">
+      <c r="Y49" s="3">
         <v>909900</v>
       </c>
-      <c r="X49" s="3">
+      <c r="Z49" s="3">
         <v>873300</v>
       </c>
-      <c r="Y49" s="3">
+      <c r="AA49" s="3">
         <v>861700</v>
       </c>
-      <c r="Z49" s="3">
+      <c r="AB49" s="3">
         <v>880200</v>
       </c>
-      <c r="AA49" s="3">
+      <c r="AC49" s="3">
         <v>876300</v>
       </c>
-      <c r="AB49" s="3">
+      <c r="AD49" s="3">
         <v>841400</v>
       </c>
-      <c r="AC49" s="3">
+      <c r="AE49" s="3">
         <v>835000</v>
       </c>
-      <c r="AD49" s="3">
+      <c r="AF49" s="3">
         <v>815900</v>
       </c>
-      <c r="AE49" s="3">
+      <c r="AG49" s="3">
         <v>794000</v>
       </c>
-      <c r="AF49" s="3">
+      <c r="AH49" s="3">
         <v>777200</v>
       </c>
     </row>
-    <row r="50" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -4272,8 +4499,14 @@
       <c r="AF50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG50" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -4364,100 +4597,112 @@
       <c r="AF51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG51" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
-        <v>209500</v>
+        <v>230700</v>
       </c>
       <c r="E52" s="3">
-        <v>174400</v>
+        <v>218500</v>
       </c>
       <c r="F52" s="3">
-        <v>181900</v>
+        <v>208200</v>
       </c>
       <c r="G52" s="3">
-        <v>217800</v>
+        <v>173300</v>
       </c>
       <c r="H52" s="3">
-        <v>239900</v>
+        <v>180800</v>
       </c>
       <c r="I52" s="3">
         <v>216500</v>
       </c>
       <c r="J52" s="3">
+        <v>238500</v>
+      </c>
+      <c r="K52" s="3">
+        <v>216500</v>
+      </c>
+      <c r="L52" s="3">
         <v>234300</v>
       </c>
-      <c r="K52" s="3">
+      <c r="M52" s="3">
         <v>233800</v>
       </c>
-      <c r="L52" s="3">
+      <c r="N52" s="3">
         <v>230200</v>
       </c>
-      <c r="M52" s="3">
+      <c r="O52" s="3">
         <v>251600</v>
       </c>
-      <c r="N52" s="3">
+      <c r="P52" s="3">
         <v>250600</v>
       </c>
-      <c r="O52" s="3">
+      <c r="Q52" s="3">
         <v>175100</v>
       </c>
-      <c r="P52" s="3">
+      <c r="R52" s="3">
         <v>172000</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="S52" s="3">
         <v>170900</v>
       </c>
-      <c r="R52" s="3">
+      <c r="T52" s="3">
         <v>179500</v>
       </c>
-      <c r="S52" s="3">
+      <c r="U52" s="3">
         <v>156400</v>
       </c>
-      <c r="T52" s="3">
+      <c r="V52" s="3">
         <v>391500</v>
       </c>
-      <c r="U52" s="3">
+      <c r="W52" s="3">
         <v>232100</v>
       </c>
-      <c r="V52" s="3">
+      <c r="X52" s="3">
         <v>172600</v>
       </c>
-      <c r="W52" s="3">
+      <c r="Y52" s="3">
         <v>136600</v>
       </c>
-      <c r="X52" s="3">
+      <c r="Z52" s="3">
         <v>108700</v>
       </c>
-      <c r="Y52" s="3">
+      <c r="AA52" s="3">
         <v>108200</v>
       </c>
-      <c r="Z52" s="3">
+      <c r="AB52" s="3">
         <v>87800</v>
       </c>
-      <c r="AA52" s="3">
+      <c r="AC52" s="3">
         <v>68500</v>
       </c>
-      <c r="AB52" s="3">
+      <c r="AD52" s="3">
         <v>45800</v>
       </c>
-      <c r="AC52" s="3">
+      <c r="AE52" s="3">
         <v>34600</v>
       </c>
-      <c r="AD52" s="3">
+      <c r="AF52" s="3">
         <v>28700</v>
       </c>
-      <c r="AE52" s="3">
+      <c r="AG52" s="3">
         <v>22500</v>
       </c>
-      <c r="AF52" s="3">
+      <c r="AH52" s="3">
         <v>26400</v>
       </c>
     </row>
-    <row r="53" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -4548,100 +4793,112 @@
       <c r="AF53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG53" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
-        <v>12159200</v>
+        <v>12417200</v>
       </c>
       <c r="E54" s="3">
-        <v>11407200</v>
+        <v>12222400</v>
       </c>
       <c r="F54" s="3">
-        <v>11218400</v>
+        <v>12084000</v>
       </c>
       <c r="G54" s="3">
-        <v>10916300</v>
+        <v>11336700</v>
       </c>
       <c r="H54" s="3">
-        <v>10787000</v>
+        <v>11149000</v>
       </c>
       <c r="I54" s="3">
+        <v>10848800</v>
+      </c>
+      <c r="J54" s="3">
+        <v>10720300</v>
+      </c>
+      <c r="K54" s="3">
         <v>9523700</v>
       </c>
-      <c r="J54" s="3">
+      <c r="L54" s="3">
         <v>9084600</v>
       </c>
-      <c r="K54" s="3">
+      <c r="M54" s="3">
         <v>8648800</v>
       </c>
-      <c r="L54" s="3">
+      <c r="N54" s="3">
         <v>8623200</v>
       </c>
-      <c r="M54" s="3">
+      <c r="O54" s="3">
         <v>8799300</v>
       </c>
-      <c r="N54" s="3">
+      <c r="P54" s="3">
         <v>8633300</v>
       </c>
-      <c r="O54" s="3">
+      <c r="Q54" s="3">
         <v>8241300</v>
       </c>
-      <c r="P54" s="3">
+      <c r="R54" s="3">
         <v>8679900</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="S54" s="3">
         <v>7144000</v>
       </c>
-      <c r="R54" s="3">
+      <c r="T54" s="3">
         <v>7328400</v>
       </c>
-      <c r="S54" s="3">
+      <c r="U54" s="3">
         <v>7066200</v>
       </c>
-      <c r="T54" s="3">
+      <c r="V54" s="3">
         <v>6627600</v>
       </c>
-      <c r="U54" s="3">
+      <c r="W54" s="3">
         <v>6192400</v>
       </c>
-      <c r="V54" s="3">
+      <c r="X54" s="3">
         <v>6105100</v>
       </c>
-      <c r="W54" s="3">
+      <c r="Y54" s="3">
         <v>5763100</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Z54" s="3">
         <v>5219700</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="AA54" s="3">
         <v>4800400</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AB54" s="3">
         <v>3561300</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AC54" s="3">
         <v>3833100</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AD54" s="3">
         <v>3632000</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AE54" s="3">
         <v>3531800</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AF54" s="3">
         <v>3467300</v>
       </c>
-      <c r="AE54" s="3">
+      <c r="AG54" s="3">
         <v>3403600</v>
       </c>
-      <c r="AF54" s="3">
+      <c r="AH54" s="3">
         <v>1811700</v>
       </c>
     </row>
-    <row r="55" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -4674,8 +4931,10 @@
       <c r="AD55" s="3"/>
       <c r="AE55" s="3"/>
       <c r="AF55" s="3"/>
-    </row>
-    <row r="56" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG55" s="3"/>
+      <c r="AH55" s="3"/>
+    </row>
+    <row r="56" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -4708,165 +4967,173 @@
       <c r="AD56" s="3"/>
       <c r="AE56" s="3"/>
       <c r="AF56" s="3"/>
-    </row>
-    <row r="57" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG56" s="3"/>
+      <c r="AH56" s="3"/>
+    </row>
+    <row r="57" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
-        <v>276700</v>
+        <v>322500</v>
       </c>
       <c r="E57" s="3">
-        <v>268200</v>
+        <v>353300</v>
       </c>
       <c r="F57" s="3">
-        <v>286100</v>
+        <v>275000</v>
       </c>
       <c r="G57" s="3">
-        <v>306200</v>
+        <v>266500</v>
       </c>
       <c r="H57" s="3">
-        <v>247300</v>
+        <v>284400</v>
       </c>
       <c r="I57" s="3">
+        <v>304300</v>
+      </c>
+      <c r="J57" s="3">
+        <v>245700</v>
+      </c>
+      <c r="K57" s="3">
         <v>265700</v>
       </c>
-      <c r="J57" s="3">
+      <c r="L57" s="3">
         <v>238900</v>
       </c>
-      <c r="K57" s="3">
+      <c r="M57" s="3">
         <v>269700</v>
       </c>
-      <c r="L57" s="3">
+      <c r="N57" s="3">
         <v>231300</v>
       </c>
-      <c r="M57" s="3">
+      <c r="O57" s="3">
         <v>229300</v>
       </c>
-      <c r="N57" s="3">
+      <c r="P57" s="3">
         <v>222800</v>
       </c>
-      <c r="O57" s="3">
+      <c r="Q57" s="3">
         <v>227700</v>
       </c>
-      <c r="P57" s="3">
+      <c r="R57" s="3">
         <v>216400</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="S57" s="3">
         <v>162900</v>
       </c>
-      <c r="R57" s="3">
+      <c r="T57" s="3">
         <v>185600</v>
       </c>
-      <c r="S57" s="3">
+      <c r="U57" s="3">
         <v>227200</v>
       </c>
-      <c r="T57" s="3">
+      <c r="V57" s="3">
         <v>167200</v>
       </c>
-      <c r="U57" s="3">
+      <c r="W57" s="3">
         <v>181100</v>
       </c>
-      <c r="V57" s="3">
+      <c r="X57" s="3">
         <v>157100</v>
       </c>
-      <c r="W57" s="3">
+      <c r="Y57" s="3">
         <v>190500</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Z57" s="3">
         <v>117200</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="AA57" s="3">
         <v>130700</v>
       </c>
-      <c r="Z57" s="3">
+      <c r="AB57" s="3">
         <v>133200</v>
       </c>
-      <c r="AA57" s="3">
+      <c r="AC57" s="3">
         <v>132000</v>
       </c>
-      <c r="AB57" s="3">
+      <c r="AD57" s="3">
         <v>84900</v>
       </c>
-      <c r="AC57" s="3">
+      <c r="AE57" s="3">
         <v>73000</v>
       </c>
-      <c r="AD57" s="3">
+      <c r="AF57" s="3">
         <v>98200</v>
       </c>
-      <c r="AE57" s="3">
+      <c r="AG57" s="3">
         <v>92600</v>
       </c>
-      <c r="AF57" s="3">
+      <c r="AH57" s="3">
         <v>65500</v>
       </c>
     </row>
-    <row r="58" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
-        <v>1333500</v>
+        <v>1110900</v>
       </c>
       <c r="E58" s="3">
-        <v>931600</v>
+        <v>1072900</v>
       </c>
       <c r="F58" s="3">
-        <v>945200</v>
+        <v>1325200</v>
       </c>
       <c r="G58" s="3">
-        <v>777700</v>
+        <v>925800</v>
       </c>
       <c r="H58" s="3">
-        <v>999300</v>
+        <v>939300</v>
       </c>
       <c r="I58" s="3">
+        <v>772900</v>
+      </c>
+      <c r="J58" s="3">
+        <v>993100</v>
+      </c>
+      <c r="K58" s="3">
         <v>1015500</v>
       </c>
-      <c r="J58" s="3">
+      <c r="L58" s="3">
         <v>847900</v>
       </c>
-      <c r="K58" s="3">
+      <c r="M58" s="3">
         <v>500600</v>
       </c>
-      <c r="L58" s="3">
+      <c r="N58" s="3">
         <v>678800</v>
       </c>
-      <c r="M58" s="3">
+      <c r="O58" s="3">
         <v>537500</v>
       </c>
-      <c r="N58" s="3">
+      <c r="P58" s="3">
         <v>433100</v>
       </c>
-      <c r="O58" s="3">
+      <c r="Q58" s="3">
         <v>244900</v>
       </c>
-      <c r="P58" s="3">
+      <c r="R58" s="3">
         <v>413300</v>
       </c>
-      <c r="Q58" s="3">
+      <c r="S58" s="3">
         <v>322200</v>
       </c>
-      <c r="R58" s="3">
+      <c r="T58" s="3">
         <v>47300</v>
       </c>
-      <c r="S58" s="3">
-        <v>0</v>
-      </c>
-      <c r="T58" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="U58" s="3" t="s">
-        <v>8</v>
+      <c r="U58" s="3">
+        <v>0</v>
       </c>
       <c r="V58" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="W58" s="3">
-        <v>0</v>
-      </c>
-      <c r="X58" s="3">
-        <v>0</v>
+      <c r="W58" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="X58" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="Y58" s="3">
         <v>0</v>
@@ -4875,232 +5142,250 @@
         <v>0</v>
       </c>
       <c r="AA58" s="3">
-        <v>37100</v>
+        <v>0</v>
       </c>
       <c r="AB58" s="3">
-        <v>37100</v>
+        <v>0</v>
       </c>
       <c r="AC58" s="3">
         <v>37100</v>
       </c>
       <c r="AD58" s="3">
+        <v>37100</v>
+      </c>
+      <c r="AE58" s="3">
+        <v>37100</v>
+      </c>
+      <c r="AF58" s="3">
         <v>101800</v>
       </c>
-      <c r="AE58" s="3">
+      <c r="AG58" s="3">
         <v>65400</v>
       </c>
-      <c r="AF58" s="3">
+      <c r="AH58" s="3">
         <v>43600</v>
       </c>
     </row>
-    <row r="59" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
-        <v>1326700</v>
+        <v>1780200</v>
       </c>
       <c r="E59" s="3">
-        <v>1264800</v>
+        <v>1345400</v>
       </c>
       <c r="F59" s="3">
-        <v>1424200</v>
+        <v>1318500</v>
       </c>
       <c r="G59" s="3">
-        <v>1196700</v>
+        <v>1256900</v>
       </c>
       <c r="H59" s="3">
-        <v>1186400</v>
+        <v>1415400</v>
       </c>
       <c r="I59" s="3">
+        <v>1189300</v>
+      </c>
+      <c r="J59" s="3">
+        <v>1179100</v>
+      </c>
+      <c r="K59" s="3">
         <v>1079000</v>
       </c>
-      <c r="J59" s="3">
+      <c r="L59" s="3">
         <v>1121000</v>
       </c>
-      <c r="K59" s="3">
+      <c r="M59" s="3">
         <v>1020300</v>
       </c>
-      <c r="L59" s="3">
+      <c r="N59" s="3">
         <v>902400</v>
       </c>
-      <c r="M59" s="3">
+      <c r="O59" s="3">
         <v>855200</v>
       </c>
-      <c r="N59" s="3">
+      <c r="P59" s="3">
         <v>966600</v>
       </c>
-      <c r="O59" s="3">
+      <c r="Q59" s="3">
         <v>828600</v>
       </c>
-      <c r="P59" s="3">
+      <c r="R59" s="3">
         <v>822800</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="S59" s="3">
         <v>808400</v>
       </c>
-      <c r="R59" s="3">
+      <c r="T59" s="3">
         <v>1052600</v>
       </c>
-      <c r="S59" s="3">
+      <c r="U59" s="3">
         <v>801600</v>
       </c>
-      <c r="T59" s="3">
+      <c r="V59" s="3">
         <v>687500</v>
       </c>
-      <c r="U59" s="3">
+      <c r="W59" s="3">
         <v>630100</v>
       </c>
-      <c r="V59" s="3">
+      <c r="X59" s="3">
         <v>711200</v>
       </c>
-      <c r="W59" s="3">
+      <c r="Y59" s="3">
         <v>556200</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Z59" s="3">
         <v>432100</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="AA59" s="3">
         <v>419700</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AB59" s="3">
         <v>424600</v>
       </c>
-      <c r="AA59" s="3">
+      <c r="AC59" s="3">
         <v>446300</v>
       </c>
-      <c r="AB59" s="3">
+      <c r="AD59" s="3">
         <v>419000</v>
       </c>
-      <c r="AC59" s="3">
+      <c r="AE59" s="3">
         <v>349800</v>
       </c>
-      <c r="AD59" s="3">
+      <c r="AF59" s="3">
         <v>311200</v>
       </c>
-      <c r="AE59" s="3">
+      <c r="AG59" s="3">
         <v>354300</v>
       </c>
-      <c r="AF59" s="3">
+      <c r="AH59" s="3">
         <v>296300</v>
       </c>
     </row>
-    <row r="60" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
-        <v>2936900</v>
+        <v>3213700</v>
       </c>
       <c r="E60" s="3">
-        <v>2464500</v>
+        <v>2771700</v>
       </c>
       <c r="F60" s="3">
-        <v>2655500</v>
+        <v>2918800</v>
       </c>
       <c r="G60" s="3">
-        <v>2280700</v>
+        <v>2449300</v>
       </c>
       <c r="H60" s="3">
-        <v>2433000</v>
+        <v>2639100</v>
       </c>
       <c r="I60" s="3">
+        <v>2266600</v>
+      </c>
+      <c r="J60" s="3">
+        <v>2417900</v>
+      </c>
+      <c r="K60" s="3">
         <v>2360200</v>
       </c>
-      <c r="J60" s="3">
+      <c r="L60" s="3">
         <v>2207700</v>
       </c>
-      <c r="K60" s="3">
+      <c r="M60" s="3">
         <v>1790600</v>
       </c>
-      <c r="L60" s="3">
+      <c r="N60" s="3">
         <v>1812500</v>
       </c>
-      <c r="M60" s="3">
+      <c r="O60" s="3">
         <v>1622000</v>
       </c>
-      <c r="N60" s="3">
+      <c r="P60" s="3">
         <v>1622600</v>
       </c>
-      <c r="O60" s="3">
+      <c r="Q60" s="3">
         <v>1301200</v>
       </c>
-      <c r="P60" s="3">
+      <c r="R60" s="3">
         <v>1452600</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="S60" s="3">
         <v>1293500</v>
       </c>
-      <c r="R60" s="3">
+      <c r="T60" s="3">
         <v>1285600</v>
       </c>
-      <c r="S60" s="3">
+      <c r="U60" s="3">
         <v>1028700</v>
       </c>
-      <c r="T60" s="3">
+      <c r="V60" s="3">
         <v>854700</v>
       </c>
-      <c r="U60" s="3">
+      <c r="W60" s="3">
         <v>811200</v>
       </c>
-      <c r="V60" s="3">
+      <c r="X60" s="3">
         <v>868200</v>
       </c>
-      <c r="W60" s="3">
+      <c r="Y60" s="3">
         <v>746700</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Z60" s="3">
         <v>549300</v>
       </c>
-      <c r="Y60" s="3">
+      <c r="AA60" s="3">
         <v>550400</v>
       </c>
-      <c r="Z60" s="3">
+      <c r="AB60" s="3">
         <v>557800</v>
       </c>
-      <c r="AA60" s="3">
+      <c r="AC60" s="3">
         <v>615300</v>
       </c>
-      <c r="AB60" s="3">
+      <c r="AD60" s="3">
         <v>541000</v>
       </c>
-      <c r="AC60" s="3">
+      <c r="AE60" s="3">
         <v>459900</v>
       </c>
-      <c r="AD60" s="3">
+      <c r="AF60" s="3">
         <v>511200</v>
       </c>
-      <c r="AE60" s="3">
+      <c r="AG60" s="3">
         <v>512300</v>
       </c>
-      <c r="AF60" s="3">
+      <c r="AH60" s="3">
         <v>405500</v>
       </c>
     </row>
-    <row r="61" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
-        <v>1002800</v>
+        <v>989100</v>
       </c>
       <c r="E61" s="3">
-        <v>995200</v>
+        <v>971200</v>
       </c>
       <c r="F61" s="3">
-        <v>941100</v>
+        <v>996600</v>
       </c>
       <c r="G61" s="3">
-        <v>943800</v>
+        <v>989000</v>
       </c>
       <c r="H61" s="3">
-        <v>972000</v>
+        <v>935300</v>
       </c>
       <c r="I61" s="3">
-        <v>0</v>
+        <v>938000</v>
       </c>
       <c r="J61" s="3">
-        <v>0</v>
+        <v>966000</v>
       </c>
       <c r="K61" s="3">
         <v>0</v>
@@ -5168,100 +5453,112 @@
       <c r="AF61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG61" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
-        <v>110500</v>
+        <v>147200</v>
       </c>
       <c r="E62" s="3">
-        <v>116000</v>
+        <v>151200</v>
       </c>
       <c r="F62" s="3">
-        <v>114200</v>
+        <v>109800</v>
       </c>
       <c r="G62" s="3">
-        <v>119100</v>
+        <v>115300</v>
       </c>
       <c r="H62" s="3">
-        <v>101600</v>
+        <v>113500</v>
       </c>
       <c r="I62" s="3">
+        <v>118400</v>
+      </c>
+      <c r="J62" s="3">
+        <v>101000</v>
+      </c>
+      <c r="K62" s="3">
         <v>110000</v>
       </c>
-      <c r="J62" s="3">
+      <c r="L62" s="3">
         <v>114700</v>
       </c>
-      <c r="K62" s="3">
+      <c r="M62" s="3">
         <v>116900</v>
       </c>
-      <c r="L62" s="3">
+      <c r="N62" s="3">
         <v>120300</v>
       </c>
-      <c r="M62" s="3">
+      <c r="O62" s="3">
         <v>115800</v>
       </c>
-      <c r="N62" s="3">
+      <c r="P62" s="3">
         <v>110200</v>
       </c>
-      <c r="O62" s="3">
+      <c r="Q62" s="3">
         <v>105400</v>
       </c>
-      <c r="P62" s="3">
+      <c r="R62" s="3">
         <v>99300</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="S62" s="3">
         <v>104200</v>
       </c>
-      <c r="R62" s="3">
+      <c r="T62" s="3">
         <v>117500</v>
       </c>
-      <c r="S62" s="3">
+      <c r="U62" s="3">
         <v>124100</v>
       </c>
-      <c r="T62" s="3">
+      <c r="V62" s="3">
         <v>95900</v>
       </c>
-      <c r="U62" s="3">
+      <c r="W62" s="3">
         <v>96500</v>
       </c>
-      <c r="V62" s="3">
+      <c r="X62" s="3">
         <v>121000</v>
       </c>
-      <c r="W62" s="3">
+      <c r="Y62" s="3">
         <v>39500</v>
       </c>
-      <c r="X62" s="3">
+      <c r="Z62" s="3">
         <v>33600</v>
       </c>
-      <c r="Y62" s="3">
+      <c r="AA62" s="3">
         <v>33400</v>
       </c>
-      <c r="Z62" s="3">
+      <c r="AB62" s="3">
         <v>34000</v>
       </c>
-      <c r="AA62" s="3">
+      <c r="AC62" s="3">
         <v>35700</v>
       </c>
-      <c r="AB62" s="3">
+      <c r="AD62" s="3">
         <v>30000</v>
       </c>
-      <c r="AC62" s="3">
+      <c r="AE62" s="3">
         <v>30300</v>
       </c>
-      <c r="AD62" s="3">
+      <c r="AF62" s="3">
         <v>23500</v>
       </c>
-      <c r="AE62" s="3">
+      <c r="AG62" s="3">
         <v>19000</v>
       </c>
-      <c r="AF62" s="3">
+      <c r="AH62" s="3">
         <v>19100</v>
       </c>
     </row>
-    <row r="63" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -5352,8 +5649,14 @@
       <c r="AF63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG63" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -5444,8 +5747,14 @@
       <c r="AF64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG64" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -5536,100 +5845,112 @@
       <c r="AF65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG65" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
-        <v>4110600</v>
+        <v>4425500</v>
       </c>
       <c r="E66" s="3">
-        <v>3635400</v>
+        <v>3960100</v>
       </c>
       <c r="F66" s="3">
-        <v>3771800</v>
+        <v>4085100</v>
       </c>
       <c r="G66" s="3">
-        <v>3405300</v>
+        <v>3612900</v>
       </c>
       <c r="H66" s="3">
-        <v>3569800</v>
+        <v>3748500</v>
       </c>
       <c r="I66" s="3">
+        <v>3384200</v>
+      </c>
+      <c r="J66" s="3">
+        <v>3547700</v>
+      </c>
+      <c r="K66" s="3">
         <v>2528500</v>
       </c>
-      <c r="J66" s="3">
+      <c r="L66" s="3">
         <v>2353800</v>
       </c>
-      <c r="K66" s="3">
+      <c r="M66" s="3">
         <v>1947500</v>
       </c>
-      <c r="L66" s="3">
+      <c r="N66" s="3">
         <v>1953500</v>
       </c>
-      <c r="M66" s="3">
+      <c r="O66" s="3">
         <v>1753500</v>
       </c>
-      <c r="N66" s="3">
+      <c r="P66" s="3">
         <v>1752700</v>
       </c>
-      <c r="O66" s="3">
+      <c r="Q66" s="3">
         <v>1423500</v>
       </c>
-      <c r="P66" s="3">
+      <c r="R66" s="3">
         <v>1568300</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="S66" s="3">
         <v>1414400</v>
       </c>
-      <c r="R66" s="3">
+      <c r="T66" s="3">
         <v>1419300</v>
       </c>
-      <c r="S66" s="3">
+      <c r="U66" s="3">
         <v>1168400</v>
       </c>
-      <c r="T66" s="3">
+      <c r="V66" s="3">
         <v>965800</v>
       </c>
-      <c r="U66" s="3">
+      <c r="W66" s="3">
         <v>919500</v>
       </c>
-      <c r="V66" s="3">
+      <c r="X66" s="3">
         <v>999600</v>
       </c>
-      <c r="W66" s="3">
+      <c r="Y66" s="3">
         <v>793800</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Z66" s="3">
         <v>588000</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="AA66" s="3">
         <v>584900</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AB66" s="3">
         <v>592700</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AC66" s="3">
         <v>651900</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AD66" s="3">
         <v>571800</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AE66" s="3">
         <v>491000</v>
       </c>
-      <c r="AD66" s="3">
+      <c r="AF66" s="3">
         <v>535400</v>
       </c>
-      <c r="AE66" s="3">
+      <c r="AG66" s="3">
         <v>532100</v>
       </c>
-      <c r="AF66" s="3">
+      <c r="AH66" s="3">
         <v>424600</v>
       </c>
     </row>
-    <row r="67" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -5662,8 +5983,10 @@
       <c r="AD67" s="3"/>
       <c r="AE67" s="3"/>
       <c r="AF67" s="3"/>
-    </row>
-    <row r="68" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG67" s="3"/>
+      <c r="AH67" s="3"/>
+    </row>
+    <row r="68" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -5754,8 +6077,14 @@
       <c r="AF68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG68" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -5846,8 +6175,14 @@
       <c r="AF69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG69" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -5936,10 +6271,16 @@
         <v>0</v>
       </c>
       <c r="AF70" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG70" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH70" s="3">
         <v>304900</v>
       </c>
     </row>
-    <row r="71" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="71" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -6030,100 +6371,112 @@
       <c r="AF71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG71" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
-        <v>4783600</v>
+        <v>4700600</v>
       </c>
       <c r="E72" s="3">
-        <v>4493700</v>
+        <v>5015400</v>
       </c>
       <c r="F72" s="3">
-        <v>4276900</v>
+        <v>4754000</v>
       </c>
       <c r="G72" s="3">
-        <v>4095500</v>
+        <v>4465900</v>
       </c>
       <c r="H72" s="3">
-        <v>3794800</v>
+        <v>4250500</v>
       </c>
       <c r="I72" s="3">
+        <v>4070100</v>
+      </c>
+      <c r="J72" s="3">
+        <v>3771300</v>
+      </c>
+      <c r="K72" s="3">
         <v>3525800</v>
       </c>
-      <c r="J72" s="3">
+      <c r="L72" s="3">
         <v>3280400</v>
       </c>
-      <c r="K72" s="3">
+      <c r="M72" s="3">
         <v>3129900</v>
       </c>
-      <c r="L72" s="3">
+      <c r="N72" s="3">
         <v>2978700</v>
       </c>
-      <c r="M72" s="3">
+      <c r="O72" s="3">
         <v>3182700</v>
       </c>
-      <c r="N72" s="3">
+      <c r="P72" s="3">
         <v>3093800</v>
       </c>
-      <c r="O72" s="3">
+      <c r="Q72" s="3">
         <v>2928600</v>
       </c>
-      <c r="P72" s="3">
+      <c r="R72" s="3">
         <v>2910500</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="S72" s="3">
         <v>2733500</v>
       </c>
-      <c r="R72" s="3">
+      <c r="T72" s="3">
         <v>2697900</v>
       </c>
-      <c r="S72" s="3">
+      <c r="U72" s="3">
         <v>2575600</v>
       </c>
-      <c r="T72" s="3">
+      <c r="V72" s="3">
         <v>2246600</v>
       </c>
-      <c r="U72" s="3">
+      <c r="W72" s="3">
         <v>2000300</v>
       </c>
-      <c r="V72" s="3">
+      <c r="X72" s="3">
         <v>1784800</v>
       </c>
-      <c r="W72" s="3">
+      <c r="Y72" s="3">
         <v>1605100</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Z72" s="3">
         <v>1368400</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="AA72" s="3">
         <v>1220100</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AB72" s="3">
         <v>1036800</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AC72" s="3">
         <v>989800</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AD72" s="3">
         <v>808400</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AE72" s="3">
         <v>702000</v>
       </c>
-      <c r="AD72" s="3">
+      <c r="AF72" s="3">
         <v>583600</v>
       </c>
-      <c r="AE72" s="3">
+      <c r="AG72" s="3">
         <v>510400</v>
       </c>
-      <c r="AF72" s="3">
+      <c r="AH72" s="3">
         <v>404700</v>
       </c>
     </row>
-    <row r="73" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -6214,8 +6567,14 @@
       <c r="AF73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG73" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -6306,8 +6665,14 @@
       <c r="AF74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG74" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -6398,100 +6763,112 @@
       <c r="AF75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG75" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
-        <v>8048600</v>
+        <v>7991600</v>
       </c>
       <c r="E76" s="3">
-        <v>7771800</v>
+        <v>8262200</v>
       </c>
       <c r="F76" s="3">
-        <v>7446600</v>
+        <v>7998900</v>
       </c>
       <c r="G76" s="3">
-        <v>7511000</v>
+        <v>7723800</v>
       </c>
       <c r="H76" s="3">
-        <v>7217200</v>
+        <v>7400500</v>
       </c>
       <c r="I76" s="3">
+        <v>7464600</v>
+      </c>
+      <c r="J76" s="3">
+        <v>7172500</v>
+      </c>
+      <c r="K76" s="3">
         <v>6995300</v>
       </c>
-      <c r="J76" s="3">
+      <c r="L76" s="3">
         <v>6730800</v>
       </c>
-      <c r="K76" s="3">
+      <c r="M76" s="3">
         <v>6701200</v>
       </c>
-      <c r="L76" s="3">
+      <c r="N76" s="3">
         <v>6669700</v>
       </c>
-      <c r="M76" s="3">
+      <c r="O76" s="3">
         <v>7045800</v>
       </c>
-      <c r="N76" s="3">
+      <c r="P76" s="3">
         <v>6880500</v>
       </c>
-      <c r="O76" s="3">
+      <c r="Q76" s="3">
         <v>6817900</v>
       </c>
-      <c r="P76" s="3">
+      <c r="R76" s="3">
         <v>7111600</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="S76" s="3">
         <v>5729500</v>
       </c>
-      <c r="R76" s="3">
+      <c r="T76" s="3">
         <v>5909100</v>
       </c>
-      <c r="S76" s="3">
+      <c r="U76" s="3">
         <v>5897800</v>
       </c>
-      <c r="T76" s="3">
+      <c r="V76" s="3">
         <v>5661800</v>
       </c>
-      <c r="U76" s="3">
+      <c r="W76" s="3">
         <v>5272900</v>
       </c>
-      <c r="V76" s="3">
+      <c r="X76" s="3">
         <v>5105500</v>
       </c>
-      <c r="W76" s="3">
+      <c r="Y76" s="3">
         <v>4969400</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Z76" s="3">
         <v>4631700</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="AA76" s="3">
         <v>4215500</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AB76" s="3">
         <v>2968500</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AC76" s="3">
         <v>3181200</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AD76" s="3">
         <v>3060200</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AE76" s="3">
         <v>3040800</v>
       </c>
-      <c r="AD76" s="3">
+      <c r="AF76" s="3">
         <v>2931800</v>
       </c>
-      <c r="AE76" s="3">
+      <c r="AG76" s="3">
         <v>2871500</v>
       </c>
-      <c r="AF76" s="3">
+      <c r="AH76" s="3">
         <v>1082100</v>
       </c>
     </row>
-    <row r="77" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -6582,197 +6959,215 @@
       <c r="AF77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG77" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:34" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45382</v>
+      </c>
+      <c r="E80" s="2">
+        <v>45291</v>
+      </c>
+      <c r="F80" s="2">
         <v>45199</v>
       </c>
-      <c r="E80" s="2">
+      <c r="G80" s="2">
         <v>45107</v>
       </c>
-      <c r="F80" s="2">
+      <c r="H80" s="2">
         <v>45016</v>
       </c>
-      <c r="G80" s="2">
+      <c r="I80" s="2">
         <v>44926</v>
       </c>
-      <c r="H80" s="2">
+      <c r="J80" s="2">
         <v>44834</v>
       </c>
-      <c r="I80" s="2">
+      <c r="K80" s="2">
         <v>44742</v>
       </c>
-      <c r="J80" s="2">
+      <c r="L80" s="2">
         <v>44651</v>
       </c>
-      <c r="K80" s="2">
+      <c r="M80" s="2">
         <v>44561</v>
       </c>
-      <c r="L80" s="2">
+      <c r="N80" s="2">
         <v>44469</v>
       </c>
-      <c r="M80" s="2">
+      <c r="O80" s="2">
         <v>44377</v>
       </c>
-      <c r="N80" s="2">
+      <c r="P80" s="2">
         <v>44286</v>
       </c>
-      <c r="O80" s="2">
+      <c r="Q80" s="2">
         <v>44196</v>
       </c>
-      <c r="P80" s="2">
+      <c r="R80" s="2">
         <v>44104</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="S80" s="2">
         <v>44012</v>
       </c>
-      <c r="R80" s="2">
+      <c r="T80" s="2">
         <v>43921</v>
       </c>
-      <c r="S80" s="2">
+      <c r="U80" s="2">
         <v>43830</v>
       </c>
-      <c r="T80" s="2">
+      <c r="V80" s="2">
         <v>43738</v>
       </c>
-      <c r="U80" s="2">
+      <c r="W80" s="2">
         <v>43646</v>
       </c>
-      <c r="V80" s="2">
+      <c r="X80" s="2">
         <v>43555</v>
       </c>
-      <c r="W80" s="2">
+      <c r="Y80" s="2">
         <v>43465</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Z80" s="2">
         <v>43373</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="AA80" s="2">
         <v>43281</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AB80" s="2">
         <v>43190</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AC80" s="2">
         <v>43100</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AD80" s="2">
         <v>43008</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AE80" s="2">
         <v>42916</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AF80" s="2">
         <v>42825</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AG80" s="2">
         <v>42735</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AH80" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="81" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="D81" s="3" t="s">
-        <v>8</v>
+      <c r="D81" s="3">
+        <v>197000</v>
       </c>
       <c r="E81" s="3">
-        <v>353300</v>
+        <v>302900</v>
       </c>
       <c r="F81" s="3">
-        <v>232200</v>
+        <v>324000</v>
       </c>
       <c r="G81" s="3">
-        <v>300600</v>
+        <v>351100</v>
       </c>
       <c r="H81" s="3">
-        <v>269000</v>
+        <v>230800</v>
       </c>
       <c r="I81" s="3">
+        <v>298800</v>
+      </c>
+      <c r="J81" s="3">
+        <v>267300</v>
+      </c>
+      <c r="K81" s="3">
         <v>251000</v>
       </c>
-      <c r="J81" s="3">
+      <c r="L81" s="3">
         <v>126000</v>
       </c>
-      <c r="K81" s="3">
+      <c r="M81" s="3">
         <v>242800</v>
       </c>
-      <c r="L81" s="3">
+      <c r="N81" s="3">
         <v>165800</v>
       </c>
-      <c r="M81" s="3">
+      <c r="O81" s="3">
         <v>185600</v>
       </c>
-      <c r="N81" s="3">
+      <c r="P81" s="3">
         <v>76600</v>
       </c>
-      <c r="O81" s="3">
+      <c r="Q81" s="3">
         <v>179300</v>
       </c>
-      <c r="P81" s="3">
+      <c r="R81" s="3">
         <v>177000</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="S81" s="3">
         <v>213400</v>
       </c>
-      <c r="R81" s="3">
+      <c r="T81" s="3">
         <v>59100</v>
       </c>
-      <c r="S81" s="3">
+      <c r="U81" s="3">
         <v>358200</v>
       </c>
-      <c r="T81" s="3">
+      <c r="V81" s="3">
         <v>204000</v>
       </c>
-      <c r="U81" s="3">
+      <c r="W81" s="3">
         <v>207700</v>
       </c>
-      <c r="V81" s="3">
+      <c r="X81" s="3">
         <v>103600</v>
       </c>
-      <c r="W81" s="3">
+      <c r="Y81" s="3">
         <v>185200</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Z81" s="3">
         <v>148300</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="AA81" s="3">
         <v>208700</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AB81" s="3">
         <v>79900</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AC81" s="3">
         <v>181400</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AD81" s="3">
         <v>106400</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AE81" s="3">
         <v>106400</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AF81" s="3">
         <v>73200</v>
       </c>
-      <c r="AE81" s="3">
+      <c r="AG81" s="3">
         <v>105700</v>
       </c>
-      <c r="AF81" s="3">
+      <c r="AH81" s="3">
         <v>73700</v>
       </c>
     </row>
-    <row r="82" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -6805,8 +7200,10 @@
       <c r="AD82" s="3"/>
       <c r="AE82" s="3"/>
       <c r="AF82" s="3"/>
-    </row>
-    <row r="83" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG82" s="3"/>
+      <c r="AH82" s="3"/>
+    </row>
+    <row r="83" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
@@ -6897,8 +7294,14 @@
       <c r="AF83" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="84" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG83" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH83" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -6989,8 +7392,14 @@
       <c r="AF84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG84" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -7081,8 +7490,14 @@
       <c r="AF85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG85" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -7173,8 +7588,14 @@
       <c r="AF86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG86" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -7265,8 +7686,14 @@
       <c r="AF87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG87" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -7357,100 +7784,112 @@
       <c r="AF88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG88" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
-        <v>408500</v>
+        <v>280600</v>
       </c>
       <c r="E89" s="3">
-        <v>522900</v>
+        <v>542000</v>
       </c>
       <c r="F89" s="3">
-        <v>380600</v>
+        <v>405900</v>
       </c>
       <c r="G89" s="3">
-        <v>524100</v>
+        <v>519700</v>
       </c>
       <c r="H89" s="3">
-        <v>392500</v>
+        <v>378300</v>
       </c>
       <c r="I89" s="3">
+        <v>520800</v>
+      </c>
+      <c r="J89" s="3">
+        <v>390100</v>
+      </c>
+      <c r="K89" s="3">
         <v>525600</v>
       </c>
-      <c r="J89" s="3">
+      <c r="L89" s="3">
         <v>153700</v>
       </c>
-      <c r="K89" s="3">
+      <c r="M89" s="3">
         <v>416600</v>
       </c>
-      <c r="L89" s="3">
+      <c r="N89" s="3">
         <v>254000</v>
       </c>
-      <c r="M89" s="3">
+      <c r="O89" s="3">
         <v>277500</v>
       </c>
-      <c r="N89" s="3">
+      <c r="P89" s="3">
         <v>68500</v>
       </c>
-      <c r="O89" s="3">
+      <c r="Q89" s="3">
         <v>284000</v>
       </c>
-      <c r="P89" s="3">
+      <c r="R89" s="3">
         <v>218200</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="S89" s="3">
         <v>184500</v>
       </c>
-      <c r="R89" s="3">
+      <c r="T89" s="3">
         <v>28000</v>
       </c>
-      <c r="S89" s="3">
+      <c r="U89" s="3">
         <v>348100</v>
       </c>
-      <c r="T89" s="3">
+      <c r="V89" s="3">
         <v>221200</v>
       </c>
-      <c r="U89" s="3">
+      <c r="W89" s="3">
         <v>304500</v>
       </c>
-      <c r="V89" s="3">
+      <c r="X89" s="3">
         <v>96300</v>
       </c>
-      <c r="W89" s="3">
+      <c r="Y89" s="3">
         <v>261800</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Z89" s="3">
         <v>127600</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="AA89" s="3">
         <v>206600</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AB89" s="3">
         <v>30700</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AC89" s="3">
         <v>203600</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AD89" s="3">
         <v>152000</v>
       </c>
-      <c r="AC89" s="3">
+      <c r="AE89" s="3">
         <v>134100</v>
       </c>
-      <c r="AD89" s="3">
+      <c r="AF89" s="3">
         <v>48200</v>
       </c>
-      <c r="AE89" s="3">
+      <c r="AG89" s="3">
         <v>166300</v>
       </c>
-      <c r="AF89" s="3">
+      <c r="AH89" s="3">
         <v>121000</v>
       </c>
     </row>
-    <row r="90" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -7483,13 +7922,15 @@
       <c r="AD90" s="3"/>
       <c r="AE90" s="3"/>
       <c r="AF90" s="3"/>
-    </row>
-    <row r="91" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG90" s="3"/>
+      <c r="AH90" s="3"/>
+    </row>
+    <row r="91" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
-        <v>0</v>
+        <v>-2167300</v>
       </c>
       <c r="E91" s="3">
         <v>0</v>
@@ -7575,8 +8016,14 @@
       <c r="AF91" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="92" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG91" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH91" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -7667,8 +8114,14 @@
       <c r="AF92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG92" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -7759,100 +8212,112 @@
       <c r="AF93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG93" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
-        <v>-559700</v>
+        <v>-328600</v>
       </c>
       <c r="E94" s="3">
-        <v>-492300</v>
+        <v>163200</v>
       </c>
       <c r="F94" s="3">
-        <v>-815600</v>
+        <v>-556200</v>
       </c>
       <c r="G94" s="3">
-        <v>-609000</v>
+        <v>-489300</v>
       </c>
       <c r="H94" s="3">
-        <v>-658500</v>
+        <v>-810500</v>
       </c>
       <c r="I94" s="3">
+        <v>-605300</v>
+      </c>
+      <c r="J94" s="3">
+        <v>-654400</v>
+      </c>
+      <c r="K94" s="3">
         <v>-501800</v>
       </c>
-      <c r="J94" s="3">
+      <c r="L94" s="3">
         <v>-460800</v>
       </c>
-      <c r="K94" s="3">
+      <c r="M94" s="3">
         <v>-387700</v>
       </c>
-      <c r="L94" s="3">
+      <c r="N94" s="3">
         <v>-197000</v>
       </c>
-      <c r="M94" s="3">
+      <c r="O94" s="3">
         <v>-26500</v>
       </c>
-      <c r="N94" s="3">
+      <c r="P94" s="3">
         <v>-627900</v>
       </c>
-      <c r="O94" s="3">
+      <c r="Q94" s="3">
         <v>-406000</v>
       </c>
-      <c r="P94" s="3">
+      <c r="R94" s="3">
         <v>173900</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="S94" s="3">
         <v>-161800</v>
       </c>
-      <c r="R94" s="3">
+      <c r="T94" s="3">
         <v>-112800</v>
       </c>
-      <c r="S94" s="3">
+      <c r="U94" s="3">
         <v>-314600</v>
       </c>
-      <c r="T94" s="3">
+      <c r="V94" s="3">
         <v>-626500</v>
       </c>
-      <c r="U94" s="3">
+      <c r="W94" s="3">
         <v>229000</v>
       </c>
-      <c r="V94" s="3">
+      <c r="X94" s="3">
         <v>136200</v>
       </c>
-      <c r="W94" s="3">
+      <c r="Y94" s="3">
         <v>-483600</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Z94" s="3">
         <v>-321300</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="AA94" s="3">
         <v>-790700</v>
       </c>
-      <c r="Z94" s="3">
+      <c r="AB94" s="3">
         <v>-229200</v>
       </c>
-      <c r="AA94" s="3">
+      <c r="AC94" s="3">
         <v>-107200</v>
       </c>
-      <c r="AB94" s="3">
+      <c r="AD94" s="3">
         <v>-167600</v>
       </c>
-      <c r="AC94" s="3">
+      <c r="AE94" s="3">
         <v>-168800</v>
       </c>
-      <c r="AD94" s="3">
+      <c r="AF94" s="3">
         <v>-771600</v>
       </c>
-      <c r="AE94" s="3">
+      <c r="AG94" s="3">
         <v>-158200</v>
       </c>
-      <c r="AF94" s="3">
+      <c r="AH94" s="3">
         <v>-129200</v>
       </c>
     </row>
-    <row r="95" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -7885,8 +8350,10 @@
       <c r="AD95" s="3"/>
       <c r="AE95" s="3"/>
       <c r="AF95" s="3"/>
-    </row>
-    <row r="96" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG95" s="3"/>
+      <c r="AH95" s="3"/>
+    </row>
+    <row r="96" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -7977,8 +8444,14 @@
       <c r="AF96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG96" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -8069,8 +8542,14 @@
       <c r="AF97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG97" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -8161,8 +8640,14 @@
       <c r="AF98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG98" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -8253,280 +8738,304 @@
       <c r="AF99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG99" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
-        <v>351700</v>
+        <v>18000</v>
       </c>
       <c r="E100" s="3">
-        <v>-274500</v>
+        <v>-299300</v>
       </c>
       <c r="F100" s="3">
-        <v>116900</v>
+        <v>349500</v>
       </c>
       <c r="G100" s="3">
-        <v>-237300</v>
+        <v>-272800</v>
       </c>
       <c r="H100" s="3">
-        <v>881600</v>
+        <v>116100</v>
       </c>
       <c r="I100" s="3">
+        <v>-235900</v>
+      </c>
+      <c r="J100" s="3">
+        <v>876200</v>
+      </c>
+      <c r="K100" s="3">
         <v>-21800</v>
       </c>
-      <c r="J100" s="3">
+      <c r="L100" s="3">
         <v>358800</v>
       </c>
-      <c r="K100" s="3">
+      <c r="M100" s="3">
         <v>-108500</v>
       </c>
-      <c r="L100" s="3">
+      <c r="N100" s="3">
         <v>-308000</v>
       </c>
-      <c r="M100" s="3">
+      <c r="O100" s="3">
         <v>-135500</v>
       </c>
-      <c r="N100" s="3">
+      <c r="P100" s="3">
         <v>142800</v>
       </c>
-      <c r="O100" s="3">
+      <c r="Q100" s="3">
         <v>-87400</v>
       </c>
-      <c r="P100" s="3">
+      <c r="R100" s="3">
         <v>1267700</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="S100" s="3">
         <v>9600</v>
       </c>
-      <c r="R100" s="3">
+      <c r="T100" s="3">
         <v>47000</v>
       </c>
-      <c r="S100" s="3">
+      <c r="U100" s="3">
         <v>2000</v>
       </c>
-      <c r="T100" s="3">
+      <c r="V100" s="3">
         <v>79800</v>
       </c>
-      <c r="U100" s="3">
+      <c r="W100" s="3">
         <v>-380900</v>
       </c>
-      <c r="V100" s="3">
+      <c r="X100" s="3">
         <v>-2100</v>
       </c>
-      <c r="W100" s="3">
+      <c r="Y100" s="3">
         <v>-22300</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Z100" s="3">
         <v>193200</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="AA100" s="3">
         <v>926600</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AB100" s="3">
         <v>-115500</v>
       </c>
-      <c r="AA100" s="3">
+      <c r="AC100" s="3">
         <v>-30000</v>
       </c>
-      <c r="AB100" s="3">
+      <c r="AD100" s="3">
         <v>-59900</v>
       </c>
-      <c r="AC100" s="3">
+      <c r="AE100" s="3">
         <v>-104800</v>
       </c>
-      <c r="AD100" s="3">
+      <c r="AF100" s="3">
         <v>36400</v>
       </c>
-      <c r="AE100" s="3">
+      <c r="AG100" s="3">
         <v>1358900</v>
       </c>
-      <c r="AF100" s="3">
+      <c r="AH100" s="3">
         <v>-3900</v>
       </c>
     </row>
-    <row r="101" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>5300</v>
+      </c>
+      <c r="E101" s="3">
+        <v>600</v>
+      </c>
+      <c r="F101" s="3">
         <v>1300</v>
       </c>
-      <c r="E101" s="3">
-        <v>14600</v>
-      </c>
-      <c r="F101" s="3">
+      <c r="G101" s="3">
+        <v>14500</v>
+      </c>
+      <c r="H101" s="3">
         <v>-1200</v>
       </c>
-      <c r="G101" s="3">
+      <c r="I101" s="3">
         <v>-8200</v>
       </c>
-      <c r="H101" s="3">
-        <v>31200</v>
-      </c>
-      <c r="I101" s="3">
+      <c r="J101" s="3">
+        <v>31000</v>
+      </c>
+      <c r="K101" s="3">
         <v>26900</v>
       </c>
-      <c r="J101" s="3">
+      <c r="L101" s="3">
         <v>-2900</v>
       </c>
-      <c r="K101" s="3">
+      <c r="M101" s="3">
         <v>-6600</v>
       </c>
-      <c r="L101" s="3">
+      <c r="N101" s="3">
         <v>-300</v>
       </c>
-      <c r="M101" s="3">
+      <c r="O101" s="3">
         <v>-19200</v>
       </c>
-      <c r="N101" s="3">
+      <c r="P101" s="3">
         <v>4800</v>
       </c>
-      <c r="O101" s="3">
+      <c r="Q101" s="3">
         <v>-78800</v>
       </c>
-      <c r="P101" s="3">
+      <c r="R101" s="3">
         <v>-16100</v>
       </c>
-      <c r="Q101" s="3">
+      <c r="S101" s="3">
         <v>300</v>
       </c>
-      <c r="R101" s="3">
+      <c r="T101" s="3">
         <v>2700</v>
       </c>
-      <c r="S101" s="3">
+      <c r="U101" s="3">
         <v>-2000</v>
       </c>
-      <c r="T101" s="3">
+      <c r="V101" s="3">
         <v>5200</v>
       </c>
-      <c r="U101" s="3">
+      <c r="W101" s="3">
         <v>3300</v>
       </c>
-      <c r="V101" s="3">
+      <c r="X101" s="3">
         <v>-6900</v>
       </c>
-      <c r="W101" s="3">
+      <c r="Y101" s="3">
         <v>4700</v>
       </c>
-      <c r="X101" s="3">
+      <c r="Z101" s="3">
         <v>14200</v>
       </c>
-      <c r="Y101" s="3">
+      <c r="AA101" s="3">
         <v>32400</v>
       </c>
-      <c r="Z101" s="3">
+      <c r="AB101" s="3">
         <v>-12800</v>
       </c>
-      <c r="AA101" s="3">
+      <c r="AC101" s="3">
         <v>-16600</v>
       </c>
-      <c r="AB101" s="3">
+      <c r="AD101" s="3">
         <v>-17500</v>
       </c>
-      <c r="AC101" s="3">
+      <c r="AE101" s="3">
         <v>-10400</v>
       </c>
-      <c r="AD101" s="3">
+      <c r="AF101" s="3">
         <v>-18100</v>
       </c>
-      <c r="AE101" s="3">
+      <c r="AG101" s="3">
         <v>40700</v>
       </c>
-      <c r="AF101" s="3">
+      <c r="AH101" s="3">
         <v>400</v>
       </c>
     </row>
-    <row r="102" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
-      <c r="D102" s="3" t="s">
-        <v>8</v>
+      <c r="D102" s="3">
+        <v>-24700</v>
       </c>
       <c r="E102" s="3">
-        <v>-229300</v>
+        <v>406600</v>
       </c>
       <c r="F102" s="3">
-        <v>-319300</v>
+        <v>200600</v>
       </c>
       <c r="G102" s="3">
-        <v>-330500</v>
+        <v>-227900</v>
       </c>
       <c r="H102" s="3">
-        <v>646800</v>
+        <v>-317400</v>
       </c>
       <c r="I102" s="3">
+        <v>-328400</v>
+      </c>
+      <c r="J102" s="3">
+        <v>642800</v>
+      </c>
+      <c r="K102" s="3">
         <v>28900</v>
       </c>
-      <c r="J102" s="3">
+      <c r="L102" s="3">
         <v>48700</v>
       </c>
-      <c r="K102" s="3">
+      <c r="M102" s="3">
         <v>-86200</v>
       </c>
-      <c r="L102" s="3">
+      <c r="N102" s="3">
         <v>-251300</v>
       </c>
-      <c r="M102" s="3">
+      <c r="O102" s="3">
         <v>96300</v>
       </c>
-      <c r="N102" s="3">
+      <c r="P102" s="3">
         <v>-411900</v>
       </c>
-      <c r="O102" s="3">
+      <c r="Q102" s="3">
         <v>-288300</v>
       </c>
-      <c r="P102" s="3">
+      <c r="R102" s="3">
         <v>1643600</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="S102" s="3">
         <v>32700</v>
       </c>
-      <c r="R102" s="3">
+      <c r="T102" s="3">
         <v>-35000</v>
       </c>
-      <c r="S102" s="3">
+      <c r="U102" s="3">
         <v>33500</v>
       </c>
-      <c r="T102" s="3">
+      <c r="V102" s="3">
         <v>-320300</v>
       </c>
-      <c r="U102" s="3">
+      <c r="W102" s="3">
         <v>155900</v>
       </c>
-      <c r="V102" s="3">
+      <c r="X102" s="3">
         <v>223500</v>
       </c>
-      <c r="W102" s="3">
+      <c r="Y102" s="3">
         <v>-239400</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Z102" s="3">
         <v>13700</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="AA102" s="3">
         <v>374800</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AB102" s="3">
         <v>-326900</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AC102" s="3">
         <v>49800</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AD102" s="3">
         <v>-92900</v>
       </c>
-      <c r="AC102" s="3">
+      <c r="AE102" s="3">
         <v>-150000</v>
       </c>
-      <c r="AD102" s="3">
+      <c r="AF102" s="3">
         <v>-705100</v>
       </c>
-      <c r="AE102" s="3">
+      <c r="AG102" s="3">
         <v>1407600</v>
       </c>
-      <c r="AF102" s="3">
+      <c r="AH102" s="3">
         <v>-11700</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/ZTO_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/ZTO_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="145" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="146" uniqueCount="92">
   <si>
     <t>ZTO</t>
   </si>
@@ -656,441 +656,454 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AH102"/>
+  <dimension ref="A5:AI102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="6.140625" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="22" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="26" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="29" max="30" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="31" max="31" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="32" max="32" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="33" max="34" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="35" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="15" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="19" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="23" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="27" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="30" max="31" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="32" max="32" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="33" max="33" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="34" max="35" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="36" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:35" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:35" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45473</v>
+      </c>
+      <c r="E7" s="2">
         <v>45382</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45291</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45199</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45107</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45016</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>44926</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>44834</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44742</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44651</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44561</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44469</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44377</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44286</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44196</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44104</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44012</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>43921</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>43830</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>43738</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>43646</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>43555</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>43465</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>43373</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>43281</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43190</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>43100</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>43008</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AF7" s="2">
         <v>42916</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AG7" s="2">
         <v>42825</v>
       </c>
-      <c r="AG7" s="2">
+      <c r="AH7" s="2">
         <v>42735</v>
       </c>
-      <c r="AH7" s="2">
+      <c r="AI7" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="8" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
-        <v>1376100</v>
+        <v>1512200</v>
       </c>
       <c r="E8" s="3">
-        <v>1467200</v>
+        <v>1404200</v>
       </c>
       <c r="F8" s="3">
-        <v>1253900</v>
+        <v>1497100</v>
       </c>
       <c r="G8" s="3">
-        <v>1345700</v>
+        <v>1279500</v>
       </c>
       <c r="H8" s="3">
-        <v>1241100</v>
+        <v>1373200</v>
       </c>
       <c r="I8" s="3">
-        <v>1363800</v>
+        <v>1266500</v>
       </c>
       <c r="J8" s="3">
+        <v>1391700</v>
+      </c>
+      <c r="K8" s="3">
         <v>1235800</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>1203500</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>1098800</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>1270000</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>1050600</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>1052000</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>929600</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>1149400</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>978300</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>943500</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>617800</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>1054200</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>821500</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>828600</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>695800</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>817300</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>592700</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AB8" s="3">
         <v>587500</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AC8" s="3">
         <v>508600</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AD8" s="3">
         <v>642800</v>
       </c>
-      <c r="AD8" s="3">
+      <c r="AE8" s="3">
         <v>466500</v>
       </c>
-      <c r="AE8" s="3">
+      <c r="AF8" s="3">
         <v>441000</v>
       </c>
-      <c r="AF8" s="3">
+      <c r="AG8" s="3">
         <v>380200</v>
       </c>
-      <c r="AG8" s="3">
+      <c r="AH8" s="3">
         <v>464000</v>
       </c>
-      <c r="AH8" s="3">
+      <c r="AI8" s="3">
         <v>342200</v>
       </c>
     </row>
-    <row r="9" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
-        <v>961300</v>
+        <v>1001700</v>
       </c>
       <c r="E9" s="3">
-        <v>1035000</v>
+        <v>980900</v>
       </c>
       <c r="F9" s="3">
-        <v>880000</v>
+        <v>1056100</v>
       </c>
       <c r="G9" s="3">
-        <v>889200</v>
+        <v>898000</v>
       </c>
       <c r="H9" s="3">
-        <v>892500</v>
+        <v>907300</v>
       </c>
       <c r="I9" s="3">
-        <v>980800</v>
+        <v>910700</v>
       </c>
       <c r="J9" s="3">
+        <v>1000800</v>
+      </c>
+      <c r="K9" s="3">
         <v>898100</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>897200</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>873700</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>959900</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>827700</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>811700</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>772100</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>890700</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>773300</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>682800</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>488600</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>746900</v>
       </c>
-      <c r="V9" s="3">
+      <c r="W9" s="3">
         <v>572400</v>
       </c>
-      <c r="W9" s="3">
+      <c r="X9" s="3">
         <v>558400</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Y9" s="3">
         <v>504200</v>
       </c>
-      <c r="Y9" s="3">
+      <c r="Z9" s="3">
         <v>592200</v>
       </c>
-      <c r="Z9" s="3">
+      <c r="AA9" s="3">
         <v>407200</v>
       </c>
-      <c r="AA9" s="3">
+      <c r="AB9" s="3">
         <v>383600</v>
       </c>
-      <c r="AB9" s="3">
+      <c r="AC9" s="3">
         <v>360500</v>
       </c>
-      <c r="AC9" s="3">
+      <c r="AD9" s="3">
         <v>441900</v>
       </c>
-      <c r="AD9" s="3">
+      <c r="AE9" s="3">
         <v>297600</v>
       </c>
-      <c r="AE9" s="3">
+      <c r="AF9" s="3">
         <v>274200</v>
       </c>
-      <c r="AF9" s="3">
+      <c r="AG9" s="3">
         <v>274000</v>
       </c>
-      <c r="AG9" s="3">
+      <c r="AH9" s="3">
         <v>295100</v>
       </c>
-      <c r="AH9" s="3">
+      <c r="AI9" s="3">
         <v>218200</v>
       </c>
     </row>
-    <row r="10" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
-        <v>414800</v>
+        <v>510400</v>
       </c>
       <c r="E10" s="3">
-        <v>432200</v>
+        <v>423200</v>
       </c>
       <c r="F10" s="3">
-        <v>373900</v>
+        <v>441000</v>
       </c>
       <c r="G10" s="3">
-        <v>456500</v>
+        <v>381600</v>
       </c>
       <c r="H10" s="3">
-        <v>348600</v>
+        <v>465900</v>
       </c>
       <c r="I10" s="3">
-        <v>383100</v>
+        <v>355700</v>
       </c>
       <c r="J10" s="3">
+        <v>390900</v>
+      </c>
+      <c r="K10" s="3">
         <v>337700</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>306200</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>225100</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>310100</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>222900</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>240400</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>157500</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>258700</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>205000</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>260700</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>129200</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>307400</v>
       </c>
-      <c r="V10" s="3">
+      <c r="W10" s="3">
         <v>249100</v>
       </c>
-      <c r="W10" s="3">
+      <c r="X10" s="3">
         <v>270200</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Y10" s="3">
         <v>191600</v>
       </c>
-      <c r="Y10" s="3">
+      <c r="Z10" s="3">
         <v>225100</v>
       </c>
-      <c r="Z10" s="3">
+      <c r="AA10" s="3">
         <v>185500</v>
       </c>
-      <c r="AA10" s="3">
+      <c r="AB10" s="3">
         <v>204000</v>
       </c>
-      <c r="AB10" s="3">
+      <c r="AC10" s="3">
         <v>148100</v>
       </c>
-      <c r="AC10" s="3">
+      <c r="AD10" s="3">
         <v>200800</v>
       </c>
-      <c r="AD10" s="3">
+      <c r="AE10" s="3">
         <v>168900</v>
       </c>
-      <c r="AE10" s="3">
+      <c r="AF10" s="3">
         <v>166800</v>
       </c>
-      <c r="AF10" s="3">
+      <c r="AG10" s="3">
         <v>106300</v>
       </c>
-      <c r="AG10" s="3">
+      <c r="AH10" s="3">
         <v>168900</v>
       </c>
-      <c r="AH10" s="3">
+      <c r="AI10" s="3">
         <v>124000</v>
       </c>
     </row>
-    <row r="11" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -1125,8 +1138,9 @@
       <c r="AF11" s="3"/>
       <c r="AG11" s="3"/>
       <c r="AH11" s="3"/>
-    </row>
-    <row r="12" spans="1:34" x14ac:dyDescent="0.2">
+      <c r="AI11" s="3"/>
+    </row>
+    <row r="12" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
@@ -1223,8 +1237,11 @@
       <c r="AH12" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="13" spans="1:34" x14ac:dyDescent="0.2">
+      <c r="AI12" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="13" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1321,43 +1338,46 @@
       <c r="AH13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:34" x14ac:dyDescent="0.2">
+      <c r="AI13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3">
-        <v>66000</v>
+        <v>25800</v>
       </c>
       <c r="E14" s="3">
+        <v>67400</v>
+      </c>
+      <c r="F14" s="3">
         <v>600</v>
       </c>
-      <c r="F14" s="3">
+      <c r="G14" s="3">
         <v>-1500</v>
       </c>
-      <c r="G14" s="3">
+      <c r="H14" s="3">
         <v>100</v>
       </c>
-      <c r="H14" s="3" t="s">
+      <c r="I14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="I14" s="3">
+      <c r="J14" s="3">
         <v>-1300</v>
       </c>
-      <c r="J14" s="3">
+      <c r="K14" s="3">
         <v>-4700</v>
-      </c>
-      <c r="K14" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="L14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="M14" s="3">
+      <c r="M14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="N14" s="3">
         <v>-300</v>
-      </c>
-      <c r="N14" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="O14" s="3" t="s">
         <v>8</v>
@@ -1365,12 +1385,12 @@
       <c r="P14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Q14" s="3">
+      <c r="Q14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="R14" s="3">
         <v>-200</v>
       </c>
-      <c r="R14" s="3">
-        <v>0</v>
-      </c>
       <c r="S14" s="3">
         <v>0</v>
       </c>
@@ -1378,22 +1398,22 @@
         <v>0</v>
       </c>
       <c r="U14" s="3">
+        <v>0</v>
+      </c>
+      <c r="V14" s="3">
         <v>9000</v>
       </c>
-      <c r="V14" s="3">
-        <v>0</v>
-      </c>
       <c r="W14" s="3">
         <v>0</v>
       </c>
       <c r="X14" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y14" s="3">
         <v>100</v>
       </c>
-      <c r="Y14" s="3">
-        <v>0</v>
-      </c>
-      <c r="Z14" s="3" t="s">
-        <v>8</v>
+      <c r="Z14" s="3">
+        <v>0</v>
       </c>
       <c r="AA14" s="3" t="s">
         <v>8</v>
@@ -1401,11 +1421,11 @@
       <c r="AB14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AC14" s="3">
+      <c r="AC14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AD14" s="3">
         <v>4500</v>
-      </c>
-      <c r="AD14" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="AE14" s="3" t="s">
         <v>8</v>
@@ -1419,8 +1439,11 @@
       <c r="AH14" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="15" spans="1:34" x14ac:dyDescent="0.2">
+      <c r="AI14" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="15" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1517,8 +1540,11 @@
       <c r="AH15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:34" x14ac:dyDescent="0.2">
+      <c r="AI15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:35" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1550,204 +1576,211 @@
       <c r="AF16" s="3"/>
       <c r="AG16" s="3"/>
       <c r="AH16" s="3"/>
-    </row>
-    <row r="17" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI16" s="3"/>
+    </row>
+    <row r="17" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
-        <v>1128900</v>
+        <v>1084600</v>
       </c>
       <c r="E17" s="3">
-        <v>1087200</v>
+        <v>1152000</v>
       </c>
       <c r="F17" s="3">
-        <v>917600</v>
+        <v>1109400</v>
       </c>
       <c r="G17" s="3">
-        <v>948100</v>
+        <v>936300</v>
       </c>
       <c r="H17" s="3">
-        <v>971700</v>
+        <v>967400</v>
       </c>
       <c r="I17" s="3">
-        <v>1022700</v>
+        <v>991500</v>
       </c>
       <c r="J17" s="3">
+        <v>1043600</v>
+      </c>
+      <c r="K17" s="3">
         <v>930600</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>927400</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>943600</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>986700</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>857200</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>843000</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>838700</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>931200</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>806000</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>700800</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>559100</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>784600</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>603000</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>600600</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>580300</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>620800</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>439900</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>421100</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3">
         <v>408300</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AD17" s="3">
         <v>465300</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AE17" s="3">
         <v>326300</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AF17" s="3">
         <v>304300</v>
       </c>
-      <c r="AF17" s="3">
+      <c r="AG17" s="3">
         <v>284700</v>
       </c>
-      <c r="AG17" s="3">
+      <c r="AH17" s="3">
         <v>322800</v>
       </c>
-      <c r="AH17" s="3">
+      <c r="AI17" s="3">
         <v>234400</v>
       </c>
     </row>
-    <row r="18" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
-        <v>247100</v>
+        <v>427500</v>
       </c>
       <c r="E18" s="3">
-        <v>380000</v>
+        <v>252200</v>
       </c>
       <c r="F18" s="3">
-        <v>336300</v>
+        <v>387800</v>
       </c>
       <c r="G18" s="3">
-        <v>397600</v>
+        <v>343200</v>
       </c>
       <c r="H18" s="3">
-        <v>269500</v>
+        <v>405700</v>
       </c>
       <c r="I18" s="3">
-        <v>341100</v>
+        <v>275000</v>
       </c>
       <c r="J18" s="3">
+        <v>348100</v>
+      </c>
+      <c r="K18" s="3">
         <v>305200</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>276000</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>155200</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>283300</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>193400</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>209100</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>90900</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>218200</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>172300</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>242600</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>58700</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>269700</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>218500</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>228100</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>115500</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>196500</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>152800</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>166400</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AC18" s="3">
         <v>100200</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AD18" s="3">
         <v>177500</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AE18" s="3">
         <v>140200</v>
       </c>
-      <c r="AE18" s="3">
+      <c r="AF18" s="3">
         <v>136700</v>
       </c>
-      <c r="AF18" s="3">
+      <c r="AG18" s="3">
         <v>95500</v>
       </c>
-      <c r="AG18" s="3">
+      <c r="AH18" s="3">
         <v>141200</v>
       </c>
-      <c r="AH18" s="3">
+      <c r="AI18" s="3">
         <v>107800</v>
       </c>
     </row>
-    <row r="19" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1782,258 +1815,265 @@
       <c r="AF19" s="3"/>
       <c r="AG19" s="3"/>
       <c r="AH19" s="3"/>
-    </row>
-    <row r="20" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI19" s="3"/>
+    </row>
+    <row r="20" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
-        <v>40500</v>
+        <v>50500</v>
       </c>
       <c r="E20" s="3">
-        <v>23200</v>
+        <v>41300</v>
       </c>
       <c r="F20" s="3">
-        <v>35900</v>
+        <v>23700</v>
       </c>
       <c r="G20" s="3">
-        <v>41400</v>
+        <v>36600</v>
       </c>
       <c r="H20" s="3">
-        <v>32800</v>
+        <v>42300</v>
       </c>
       <c r="I20" s="3">
-        <v>28200</v>
+        <v>33500</v>
       </c>
       <c r="J20" s="3">
+        <v>28800</v>
+      </c>
+      <c r="K20" s="3">
         <v>23600</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>31200</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>13500</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>9900</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>12600</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>15600</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>13100</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>3200</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>4800</v>
       </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3">
         <v>17200</v>
       </c>
-      <c r="T20" s="3">
+      <c r="U20" s="3">
         <v>22500</v>
       </c>
-      <c r="U20" s="3">
+      <c r="V20" s="3">
         <v>137200</v>
       </c>
-      <c r="V20" s="3">
+      <c r="W20" s="3">
         <v>27300</v>
       </c>
-      <c r="W20" s="3">
+      <c r="X20" s="3">
         <v>25500</v>
       </c>
-      <c r="X20" s="3">
+      <c r="Y20" s="3">
         <v>18300</v>
       </c>
-      <c r="Y20" s="3">
+      <c r="Z20" s="3">
         <v>21500</v>
       </c>
-      <c r="Z20" s="3">
+      <c r="AA20" s="3">
         <v>24800</v>
       </c>
-      <c r="AA20" s="3">
+      <c r="AB20" s="3">
         <v>91900</v>
       </c>
-      <c r="AB20" s="3">
+      <c r="AC20" s="3">
         <v>3400</v>
       </c>
-      <c r="AC20" s="3">
+      <c r="AD20" s="3">
         <v>5700</v>
       </c>
-      <c r="AD20" s="3">
+      <c r="AE20" s="3">
         <v>2600</v>
       </c>
-      <c r="AE20" s="3">
+      <c r="AF20" s="3">
         <v>5500</v>
       </c>
-      <c r="AF20" s="3">
+      <c r="AG20" s="3">
         <v>3700</v>
       </c>
-      <c r="AG20" s="3">
+      <c r="AH20" s="3">
         <v>3500</v>
       </c>
-      <c r="AH20" s="3">
+      <c r="AI20" s="3">
         <v>1400</v>
       </c>
     </row>
-    <row r="21" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
-        <v>396200</v>
+        <v>473700</v>
       </c>
       <c r="E21" s="3">
-        <v>401600</v>
+        <v>404300</v>
       </c>
       <c r="F21" s="3">
-        <v>377700</v>
+        <v>409800</v>
       </c>
       <c r="G21" s="3">
-        <v>441600</v>
+        <v>385400</v>
       </c>
       <c r="H21" s="3">
-        <v>397100</v>
+        <v>450600</v>
       </c>
       <c r="I21" s="3">
-        <v>373400</v>
+        <v>405200</v>
       </c>
       <c r="J21" s="3">
+        <v>381000</v>
+      </c>
+      <c r="K21" s="3">
         <v>327900</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>312700</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>256700</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>300500</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>202200</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>231000</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>178800</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>227200</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>184900</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>262500</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>145600</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>418900</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>246500</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>255900</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3">
         <v>176900</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="Z21" s="3">
         <v>223700</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AA21" s="3">
         <v>179800</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AB21" s="3">
         <v>259900</v>
       </c>
-      <c r="AB21" s="3">
+      <c r="AC21" s="3">
         <v>130400</v>
       </c>
-      <c r="AC21" s="3">
+      <c r="AD21" s="3">
         <v>183000</v>
       </c>
-      <c r="AD21" s="3">
+      <c r="AE21" s="3">
         <v>144500</v>
       </c>
-      <c r="AE21" s="3">
+      <c r="AF21" s="3">
         <v>143100</v>
       </c>
-      <c r="AF21" s="3">
+      <c r="AG21" s="3">
         <v>118100</v>
       </c>
-      <c r="AG21" s="3">
+      <c r="AH21" s="3">
         <v>178100</v>
       </c>
-      <c r="AH21" s="3">
+      <c r="AI21" s="3">
         <v>105200</v>
       </c>
     </row>
-    <row r="22" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
-        <v>11600</v>
+        <v>16300</v>
       </c>
       <c r="E22" s="3">
-        <v>8500</v>
+        <v>11800</v>
       </c>
       <c r="F22" s="3">
-        <v>11600</v>
+        <v>8700</v>
       </c>
       <c r="G22" s="3">
-        <v>10000</v>
+        <v>11800</v>
       </c>
       <c r="H22" s="3">
-        <v>9900</v>
+        <v>10200</v>
       </c>
       <c r="I22" s="3">
-        <v>10500</v>
+        <v>10100</v>
       </c>
       <c r="J22" s="3">
+        <v>10700</v>
+      </c>
+      <c r="K22" s="3">
         <v>4400</v>
       </c>
-      <c r="K22" s="3">
+      <c r="L22" s="3">
         <v>3200</v>
       </c>
-      <c r="L22" s="3">
+      <c r="M22" s="3">
         <v>8300</v>
       </c>
-      <c r="M22" s="3">
+      <c r="N22" s="3">
         <v>3400</v>
       </c>
-      <c r="N22" s="3">
+      <c r="O22" s="3">
         <v>7400</v>
       </c>
-      <c r="O22" s="3">
+      <c r="P22" s="3">
         <v>4900</v>
       </c>
-      <c r="P22" s="3">
+      <c r="Q22" s="3">
         <v>2200</v>
       </c>
-      <c r="Q22" s="3">
+      <c r="R22" s="3">
         <v>1700</v>
       </c>
-      <c r="R22" s="3">
+      <c r="S22" s="3">
         <v>2000</v>
       </c>
-      <c r="S22" s="3">
+      <c r="T22" s="3">
         <v>1300</v>
       </c>
-      <c r="T22" s="3">
-        <v>0</v>
-      </c>
       <c r="U22" s="3">
         <v>0</v>
       </c>
@@ -2056,224 +2096,233 @@
         <v>0</v>
       </c>
       <c r="AB22" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC22" s="3">
         <v>100</v>
-      </c>
-      <c r="AC22" s="3">
-        <v>400</v>
       </c>
       <c r="AD22" s="3">
         <v>400</v>
       </c>
       <c r="AE22" s="3">
+        <v>400</v>
+      </c>
+      <c r="AF22" s="3">
         <v>700</v>
       </c>
-      <c r="AF22" s="3">
+      <c r="AG22" s="3">
         <v>800</v>
       </c>
-      <c r="AG22" s="3">
+      <c r="AH22" s="3">
         <v>100</v>
       </c>
-      <c r="AH22" s="3">
+      <c r="AI22" s="3">
         <v>500</v>
       </c>
     </row>
-    <row r="23" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
-        <v>276000</v>
+        <v>461700</v>
       </c>
       <c r="E23" s="3">
-        <v>394700</v>
+        <v>281700</v>
       </c>
       <c r="F23" s="3">
-        <v>360600</v>
+        <v>402800</v>
       </c>
       <c r="G23" s="3">
-        <v>429100</v>
+        <v>368000</v>
       </c>
       <c r="H23" s="3">
-        <v>292300</v>
+        <v>437800</v>
       </c>
       <c r="I23" s="3">
-        <v>358800</v>
+        <v>298300</v>
       </c>
       <c r="J23" s="3">
+        <v>366100</v>
+      </c>
+      <c r="K23" s="3">
         <v>324400</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>304100</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>160400</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>289800</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>198600</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>219900</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>101700</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>219700</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>175000</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>258500</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>81200</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>406900</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>245800</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>253500</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>133900</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>218000</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>177600</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>258300</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>103500</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AD23" s="3">
         <v>182800</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AE23" s="3">
         <v>142500</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AF23" s="3">
         <v>141400</v>
       </c>
-      <c r="AF23" s="3">
+      <c r="AG23" s="3">
         <v>98400</v>
       </c>
-      <c r="AG23" s="3">
+      <c r="AH23" s="3">
         <v>144600</v>
       </c>
-      <c r="AH23" s="3">
+      <c r="AI23" s="3">
         <v>108700</v>
       </c>
     </row>
-    <row r="24" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
-        <v>78200</v>
+        <v>93800</v>
       </c>
       <c r="E24" s="3">
-        <v>88000</v>
+        <v>79800</v>
       </c>
       <c r="F24" s="3">
-        <v>37500</v>
+        <v>89800</v>
       </c>
       <c r="G24" s="3">
-        <v>79500</v>
+        <v>38300</v>
       </c>
       <c r="H24" s="3">
-        <v>62900</v>
+        <v>81100</v>
       </c>
       <c r="I24" s="3">
-        <v>69200</v>
+        <v>64100</v>
       </c>
       <c r="J24" s="3">
+        <v>70600</v>
+      </c>
+      <c r="K24" s="3">
         <v>60700</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>60900</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>35500</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>51200</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>32600</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>36600</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>21500</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>40300</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>-4100</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>44000</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>20500</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>51000</v>
       </c>
-      <c r="V24" s="3">
+      <c r="W24" s="3">
         <v>41500</v>
       </c>
-      <c r="W24" s="3">
+      <c r="X24" s="3">
         <v>44100</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Y24" s="3">
         <v>29200</v>
       </c>
-      <c r="Y24" s="3">
+      <c r="Z24" s="3">
         <v>32300</v>
       </c>
-      <c r="Z24" s="3">
+      <c r="AA24" s="3">
         <v>28200</v>
       </c>
-      <c r="AA24" s="3">
+      <c r="AB24" s="3">
         <v>49100</v>
       </c>
-      <c r="AB24" s="3">
+      <c r="AC24" s="3">
         <v>22100</v>
       </c>
-      <c r="AC24" s="3">
+      <c r="AD24" s="3">
         <v>1300</v>
       </c>
-      <c r="AD24" s="3">
+      <c r="AE24" s="3">
         <v>35300</v>
       </c>
-      <c r="AE24" s="3">
+      <c r="AF24" s="3">
         <v>34600</v>
       </c>
-      <c r="AF24" s="3">
+      <c r="AG24" s="3">
         <v>24200</v>
       </c>
-      <c r="AG24" s="3">
+      <c r="AH24" s="3">
         <v>36600</v>
       </c>
-      <c r="AH24" s="3">
+      <c r="AI24" s="3">
         <v>27100</v>
       </c>
     </row>
-    <row r="25" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2370,204 +2419,213 @@
       <c r="AH25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
-        <v>197800</v>
+        <v>367900</v>
       </c>
       <c r="E26" s="3">
-        <v>306700</v>
+        <v>201800</v>
       </c>
       <c r="F26" s="3">
-        <v>323100</v>
+        <v>313000</v>
       </c>
       <c r="G26" s="3">
-        <v>349600</v>
+        <v>329700</v>
       </c>
       <c r="H26" s="3">
-        <v>229500</v>
+        <v>356700</v>
       </c>
       <c r="I26" s="3">
-        <v>289700</v>
+        <v>234200</v>
       </c>
       <c r="J26" s="3">
+        <v>295600</v>
+      </c>
+      <c r="K26" s="3">
         <v>263700</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>243100</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>124900</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>238600</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>166000</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>183300</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>80200</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>179400</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>179100</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>214600</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>60700</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>355800</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>204200</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>209400</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>104700</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>185700</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>149400</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>209100</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AC26" s="3">
         <v>81300</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AD26" s="3">
         <v>181500</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AE26" s="3">
         <v>107200</v>
       </c>
-      <c r="AE26" s="3">
+      <c r="AF26" s="3">
         <v>106800</v>
       </c>
-      <c r="AF26" s="3">
+      <c r="AG26" s="3">
         <v>74200</v>
       </c>
-      <c r="AG26" s="3">
+      <c r="AH26" s="3">
         <v>108000</v>
       </c>
-      <c r="AH26" s="3">
+      <c r="AI26" s="3">
         <v>81600</v>
       </c>
     </row>
-    <row r="27" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
-        <v>197000</v>
+        <v>368200</v>
       </c>
       <c r="E27" s="3">
-        <v>302900</v>
+        <v>201000</v>
       </c>
       <c r="F27" s="3">
-        <v>324000</v>
+        <v>309100</v>
       </c>
       <c r="G27" s="3">
-        <v>351100</v>
+        <v>330600</v>
       </c>
       <c r="H27" s="3">
-        <v>230800</v>
+        <v>358300</v>
       </c>
       <c r="I27" s="3">
-        <v>298800</v>
+        <v>235500</v>
       </c>
       <c r="J27" s="3">
+        <v>304900</v>
+      </c>
+      <c r="K27" s="3">
         <v>267300</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>251000</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>126000</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>242800</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>165800</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>185600</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>76600</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>179300</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>177000</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>213400</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>59100</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>358200</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>204000</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>207700</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>103600</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>185200</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>148300</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>208700</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AC27" s="3">
         <v>79900</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AD27" s="3">
         <v>181400</v>
-      </c>
-      <c r="AD27" s="3">
-        <v>106400</v>
       </c>
       <c r="AE27" s="3">
         <v>106400</v>
       </c>
       <c r="AF27" s="3">
+        <v>106400</v>
+      </c>
+      <c r="AG27" s="3">
         <v>73200</v>
       </c>
-      <c r="AG27" s="3">
+      <c r="AH27" s="3">
         <v>105700</v>
       </c>
-      <c r="AH27" s="3">
+      <c r="AI27" s="3">
         <v>73700</v>
       </c>
     </row>
-    <row r="28" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2664,8 +2722,11 @@
       <c r="AH28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2762,8 +2823,11 @@
       <c r="AH29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2860,8 +2924,11 @@
       <c r="AH30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2958,204 +3025,213 @@
       <c r="AH31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
-        <v>-40500</v>
+        <v>-50500</v>
       </c>
       <c r="E32" s="3">
-        <v>-23200</v>
+        <v>-41300</v>
       </c>
       <c r="F32" s="3">
-        <v>-35900</v>
+        <v>-23700</v>
       </c>
       <c r="G32" s="3">
-        <v>-41400</v>
+        <v>-36600</v>
       </c>
       <c r="H32" s="3">
-        <v>-32800</v>
+        <v>-42300</v>
       </c>
       <c r="I32" s="3">
-        <v>-28200</v>
+        <v>-33500</v>
       </c>
       <c r="J32" s="3">
+        <v>-28800</v>
+      </c>
+      <c r="K32" s="3">
         <v>-23600</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>-31200</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>-13500</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>-9900</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>-12600</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>-15600</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>-13100</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>-3200</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>-4800</v>
       </c>
-      <c r="S32" s="3">
+      <c r="T32" s="3">
         <v>-17200</v>
       </c>
-      <c r="T32" s="3">
+      <c r="U32" s="3">
         <v>-22500</v>
       </c>
-      <c r="U32" s="3">
+      <c r="V32" s="3">
         <v>-137200</v>
       </c>
-      <c r="V32" s="3">
+      <c r="W32" s="3">
         <v>-27300</v>
       </c>
-      <c r="W32" s="3">
+      <c r="X32" s="3">
         <v>-25500</v>
       </c>
-      <c r="X32" s="3">
+      <c r="Y32" s="3">
         <v>-18300</v>
       </c>
-      <c r="Y32" s="3">
+      <c r="Z32" s="3">
         <v>-21500</v>
       </c>
-      <c r="Z32" s="3">
+      <c r="AA32" s="3">
         <v>-24800</v>
       </c>
-      <c r="AA32" s="3">
+      <c r="AB32" s="3">
         <v>-91900</v>
       </c>
-      <c r="AB32" s="3">
+      <c r="AC32" s="3">
         <v>-3400</v>
       </c>
-      <c r="AC32" s="3">
+      <c r="AD32" s="3">
         <v>-5700</v>
       </c>
-      <c r="AD32" s="3">
+      <c r="AE32" s="3">
         <v>-2600</v>
       </c>
-      <c r="AE32" s="3">
+      <c r="AF32" s="3">
         <v>-5500</v>
       </c>
-      <c r="AF32" s="3">
+      <c r="AG32" s="3">
         <v>-3700</v>
       </c>
-      <c r="AG32" s="3">
+      <c r="AH32" s="3">
         <v>-3500</v>
       </c>
-      <c r="AH32" s="3">
+      <c r="AI32" s="3">
         <v>-1400</v>
       </c>
     </row>
-    <row r="33" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
-        <v>197000</v>
+        <v>368200</v>
       </c>
       <c r="E33" s="3">
-        <v>302900</v>
+        <v>201000</v>
       </c>
       <c r="F33" s="3">
-        <v>324000</v>
+        <v>309100</v>
       </c>
       <c r="G33" s="3">
-        <v>351100</v>
+        <v>330600</v>
       </c>
       <c r="H33" s="3">
-        <v>230800</v>
+        <v>358300</v>
       </c>
       <c r="I33" s="3">
-        <v>298800</v>
+        <v>235500</v>
       </c>
       <c r="J33" s="3">
+        <v>304900</v>
+      </c>
+      <c r="K33" s="3">
         <v>267300</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>251000</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>126000</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>242800</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>165800</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>185600</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>76600</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>179300</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>177000</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>213400</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>59100</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>358200</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>204000</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>207700</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>103600</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>185200</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>148300</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>208700</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AC33" s="3">
         <v>79900</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AD33" s="3">
         <v>181400</v>
-      </c>
-      <c r="AD33" s="3">
-        <v>106400</v>
       </c>
       <c r="AE33" s="3">
         <v>106400</v>
       </c>
       <c r="AF33" s="3">
+        <v>106400</v>
+      </c>
+      <c r="AG33" s="3">
         <v>73200</v>
       </c>
-      <c r="AG33" s="3">
+      <c r="AH33" s="3">
         <v>105700</v>
       </c>
-      <c r="AH33" s="3">
+      <c r="AI33" s="3">
         <v>73700</v>
       </c>
     </row>
-    <row r="34" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3252,209 +3328,218 @@
       <c r="AH34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
-        <v>197000</v>
+        <v>368200</v>
       </c>
       <c r="E35" s="3">
-        <v>302900</v>
+        <v>201000</v>
       </c>
       <c r="F35" s="3">
-        <v>324000</v>
+        <v>309100</v>
       </c>
       <c r="G35" s="3">
-        <v>351100</v>
+        <v>330600</v>
       </c>
       <c r="H35" s="3">
-        <v>230800</v>
+        <v>358300</v>
       </c>
       <c r="I35" s="3">
-        <v>298800</v>
+        <v>235500</v>
       </c>
       <c r="J35" s="3">
+        <v>304900</v>
+      </c>
+      <c r="K35" s="3">
         <v>267300</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>251000</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>126000</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>242800</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>165800</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>185600</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>76600</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>179300</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>177000</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>213400</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>59100</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>358200</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>204000</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>207700</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>103600</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>185200</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>148300</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>208700</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AC35" s="3">
         <v>79900</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AD35" s="3">
         <v>181400</v>
-      </c>
-      <c r="AD35" s="3">
-        <v>106400</v>
       </c>
       <c r="AE35" s="3">
         <v>106400</v>
       </c>
       <c r="AF35" s="3">
+        <v>106400</v>
+      </c>
+      <c r="AG35" s="3">
         <v>73200</v>
       </c>
-      <c r="AG35" s="3">
+      <c r="AH35" s="3">
         <v>105700</v>
       </c>
-      <c r="AH35" s="3">
+      <c r="AI35" s="3">
         <v>73700</v>
       </c>
     </row>
-    <row r="37" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:35" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45473</v>
+      </c>
+      <c r="E38" s="2">
         <v>45382</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45291</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45199</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45107</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45016</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>44926</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>44834</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44742</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44651</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44561</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44469</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44377</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44286</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44196</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44104</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44012</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>43921</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>43830</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>43738</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>43646</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>43555</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>43465</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>43373</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>43281</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43190</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>43100</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>43008</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AF38" s="2">
         <v>42916</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AG38" s="2">
         <v>42825</v>
       </c>
-      <c r="AG38" s="2">
+      <c r="AH38" s="2">
         <v>42735</v>
       </c>
-      <c r="AH38" s="2">
+      <c r="AI38" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="39" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3489,8 +3574,9 @@
       <c r="AF39" s="3"/>
       <c r="AG39" s="3"/>
       <c r="AH39" s="3"/>
-    </row>
-    <row r="40" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI39" s="3"/>
+    </row>
+    <row r="40" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3525,343 +3611,353 @@
       <c r="AF40" s="3"/>
       <c r="AG40" s="3"/>
       <c r="AH40" s="3"/>
-    </row>
-    <row r="41" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI40" s="3"/>
+    </row>
+    <row r="41" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
-        <v>1738600</v>
+        <v>1486200</v>
       </c>
       <c r="E41" s="3">
-        <v>1704000</v>
+        <v>1774100</v>
       </c>
       <c r="F41" s="3">
-        <v>1282800</v>
+        <v>1738800</v>
       </c>
       <c r="G41" s="3">
-        <v>1075100</v>
+        <v>1308900</v>
       </c>
       <c r="H41" s="3">
-        <v>1320200</v>
+        <v>1097000</v>
       </c>
       <c r="I41" s="3">
-        <v>1615500</v>
+        <v>1347200</v>
       </c>
       <c r="J41" s="3">
+        <v>1648400</v>
+      </c>
+      <c r="K41" s="3">
         <v>2016100</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>1380200</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>1376400</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>1339400</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>1472400</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>1737600</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>1590500</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>1978400</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>2418000</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>775400</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>792000</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>811500</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>789200</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>1086500</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>926800</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>671300</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AA41" s="3">
         <v>877700</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AB41" s="3">
         <v>848700</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AC41" s="3">
         <v>486000</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AD41" s="3">
         <v>805100</v>
       </c>
-      <c r="AD41" s="3">
+      <c r="AE41" s="3">
         <v>768800</v>
       </c>
-      <c r="AE41" s="3">
+      <c r="AF41" s="3">
         <v>848000</v>
       </c>
-      <c r="AF41" s="3">
+      <c r="AG41" s="3">
         <v>920400</v>
       </c>
-      <c r="AG41" s="3">
+      <c r="AH41" s="3">
         <v>1641600</v>
       </c>
-      <c r="AH41" s="3">
+      <c r="AI41" s="3">
         <v>287600</v>
       </c>
     </row>
-    <row r="42" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
-        <v>972400</v>
+        <v>1395500</v>
       </c>
       <c r="E42" s="3">
-        <v>1029900</v>
+        <v>992300</v>
       </c>
       <c r="F42" s="3">
-        <v>1057400</v>
+        <v>1051000</v>
       </c>
       <c r="G42" s="3">
-        <v>1099300</v>
+        <v>1078900</v>
       </c>
       <c r="H42" s="3">
-        <v>1226600</v>
+        <v>1121700</v>
       </c>
       <c r="I42" s="3">
-        <v>794900</v>
+        <v>1251700</v>
       </c>
       <c r="J42" s="3">
+        <v>811100</v>
+      </c>
+      <c r="K42" s="3">
         <v>960600</v>
       </c>
-      <c r="K42" s="3">
+      <c r="L42" s="3">
         <v>724400</v>
       </c>
-      <c r="L42" s="3">
+      <c r="M42" s="3">
         <v>556400</v>
       </c>
-      <c r="M42" s="3">
+      <c r="N42" s="3">
         <v>392000</v>
       </c>
-      <c r="N42" s="3">
+      <c r="O42" s="3">
         <v>336100</v>
       </c>
-      <c r="O42" s="3">
+      <c r="P42" s="3">
         <v>450800</v>
       </c>
-      <c r="P42" s="3">
+      <c r="Q42" s="3">
         <v>794000</v>
       </c>
-      <c r="Q42" s="3">
+      <c r="R42" s="3">
         <v>513700</v>
       </c>
-      <c r="R42" s="3">
+      <c r="S42" s="3">
         <v>708000</v>
       </c>
-      <c r="S42" s="3">
+      <c r="T42" s="3">
         <v>1243400</v>
       </c>
-      <c r="T42" s="3">
+      <c r="U42" s="3">
         <v>1596100</v>
       </c>
-      <c r="U42" s="3">
+      <c r="V42" s="3">
         <v>1711200</v>
       </c>
-      <c r="V42" s="3">
+      <c r="W42" s="3">
         <v>1763500</v>
       </c>
-      <c r="W42" s="3">
+      <c r="X42" s="3">
         <v>1414900</v>
       </c>
-      <c r="X42" s="3">
+      <c r="Y42" s="3">
         <v>1717000</v>
       </c>
-      <c r="Y42" s="3">
+      <c r="Z42" s="3">
         <v>1975100</v>
       </c>
-      <c r="Z42" s="3">
+      <c r="AA42" s="3">
         <v>1664900</v>
       </c>
-      <c r="AA42" s="3">
+      <c r="AB42" s="3">
         <v>1343800</v>
       </c>
-      <c r="AB42" s="3">
+      <c r="AC42" s="3">
         <v>795600</v>
       </c>
-      <c r="AC42" s="3">
+      <c r="AD42" s="3">
         <v>775400</v>
       </c>
-      <c r="AD42" s="3">
+      <c r="AE42" s="3">
         <v>819600</v>
       </c>
-      <c r="AE42" s="3">
+      <c r="AF42" s="3">
         <v>769700</v>
       </c>
-      <c r="AF42" s="3">
+      <c r="AG42" s="3">
         <v>700700</v>
-      </c>
-      <c r="AG42" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="AH42" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="43" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI42" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="43" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
-        <v>240500</v>
+        <v>271900</v>
       </c>
       <c r="E43" s="3">
-        <v>256400</v>
+        <v>245400</v>
       </c>
       <c r="F43" s="3">
-        <v>332200</v>
+        <v>261700</v>
       </c>
       <c r="G43" s="3">
-        <v>320400</v>
+        <v>339000</v>
       </c>
       <c r="H43" s="3">
-        <v>253200</v>
+        <v>326900</v>
       </c>
       <c r="I43" s="3">
-        <v>288000</v>
+        <v>258400</v>
       </c>
       <c r="J43" s="3">
+        <v>293900</v>
+      </c>
+      <c r="K43" s="3">
         <v>265800</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>267700</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>264100</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>300200</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>260500</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>262000</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>187900</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>182600</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>252900</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>174200</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>210600</v>
       </c>
-      <c r="U43" s="3">
+      <c r="V43" s="3">
         <v>194200</v>
       </c>
-      <c r="V43" s="3">
+      <c r="W43" s="3">
         <v>172000</v>
       </c>
-      <c r="W43" s="3">
+      <c r="X43" s="3">
         <v>177300</v>
       </c>
-      <c r="X43" s="3">
+      <c r="Y43" s="3">
         <v>171100</v>
       </c>
-      <c r="Y43" s="3">
+      <c r="Z43" s="3">
         <v>162900</v>
       </c>
-      <c r="Z43" s="3">
+      <c r="AA43" s="3">
         <v>120200</v>
       </c>
-      <c r="AA43" s="3">
+      <c r="AB43" s="3">
         <v>209200</v>
       </c>
-      <c r="AB43" s="3">
+      <c r="AC43" s="3">
         <v>69200</v>
       </c>
-      <c r="AC43" s="3">
+      <c r="AD43" s="3">
         <v>53700</v>
       </c>
-      <c r="AD43" s="3">
+      <c r="AE43" s="3">
         <v>31000</v>
       </c>
-      <c r="AE43" s="3">
+      <c r="AF43" s="3">
         <v>28800</v>
       </c>
-      <c r="AF43" s="3">
+      <c r="AG43" s="3">
         <v>25200</v>
       </c>
-      <c r="AG43" s="3">
+      <c r="AH43" s="3">
         <v>29600</v>
       </c>
-      <c r="AH43" s="3">
+      <c r="AI43" s="3">
         <v>17800</v>
       </c>
     </row>
-    <row r="44" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>4000</v>
+      </c>
+      <c r="E44" s="3">
+        <v>5800</v>
+      </c>
+      <c r="F44" s="3">
+        <v>4000</v>
+      </c>
+      <c r="G44" s="3">
+        <v>3900</v>
+      </c>
+      <c r="H44" s="3">
+        <v>3800</v>
+      </c>
+      <c r="I44" s="3">
+        <v>4100</v>
+      </c>
+      <c r="J44" s="3">
         <v>5700</v>
       </c>
-      <c r="E44" s="3">
-        <v>3900</v>
-      </c>
-      <c r="F44" s="3">
-        <v>3800</v>
-      </c>
-      <c r="G44" s="3">
-        <v>3700</v>
-      </c>
-      <c r="H44" s="3">
+      <c r="K44" s="3">
+        <v>8900</v>
+      </c>
+      <c r="L44" s="3">
         <v>4000</v>
       </c>
-      <c r="I44" s="3">
-        <v>5600</v>
-      </c>
-      <c r="J44" s="3">
-        <v>8900</v>
-      </c>
-      <c r="K44" s="3">
-        <v>4000</v>
-      </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>8200</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>11400</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>7100</v>
       </c>
-      <c r="O44" s="3">
+      <c r="P44" s="3">
         <v>5700</v>
-      </c>
-      <c r="P44" s="3">
-        <v>7400</v>
       </c>
       <c r="Q44" s="3">
         <v>7400</v>
@@ -3870,545 +3966,563 @@
         <v>7400</v>
       </c>
       <c r="S44" s="3">
+        <v>7400</v>
+      </c>
+      <c r="T44" s="3">
         <v>9500</v>
       </c>
-      <c r="T44" s="3">
+      <c r="U44" s="3">
         <v>8900</v>
       </c>
-      <c r="U44" s="3">
+      <c r="V44" s="3">
         <v>6800</v>
       </c>
-      <c r="V44" s="3">
+      <c r="W44" s="3">
         <v>5600</v>
       </c>
-      <c r="W44" s="3">
+      <c r="X44" s="3">
         <v>5400</v>
       </c>
-      <c r="X44" s="3">
+      <c r="Y44" s="3">
         <v>4700</v>
       </c>
-      <c r="Y44" s="3">
+      <c r="Z44" s="3">
         <v>6400</v>
       </c>
-      <c r="Z44" s="3">
+      <c r="AA44" s="3">
         <v>5200</v>
       </c>
-      <c r="AA44" s="3">
+      <c r="AB44" s="3">
         <v>5600</v>
       </c>
-      <c r="AB44" s="3">
+      <c r="AC44" s="3">
         <v>4400</v>
       </c>
-      <c r="AC44" s="3">
+      <c r="AD44" s="3">
         <v>5100</v>
       </c>
-      <c r="AD44" s="3">
+      <c r="AE44" s="3">
         <v>4200</v>
       </c>
-      <c r="AE44" s="3">
+      <c r="AF44" s="3">
         <v>4300</v>
       </c>
-      <c r="AF44" s="3">
+      <c r="AG44" s="3">
         <v>4600</v>
       </c>
-      <c r="AG44" s="3">
+      <c r="AH44" s="3">
         <v>4900</v>
       </c>
-      <c r="AH44" s="3">
+      <c r="AI44" s="3">
         <v>4100</v>
       </c>
     </row>
-    <row r="45" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
-        <v>737100</v>
+        <v>781000</v>
       </c>
       <c r="E45" s="3">
-        <v>729600</v>
+        <v>752100</v>
       </c>
       <c r="F45" s="3">
-        <v>740200</v>
+        <v>744500</v>
       </c>
       <c r="G45" s="3">
-        <v>725700</v>
+        <v>755300</v>
       </c>
       <c r="H45" s="3">
-        <v>689100</v>
+        <v>740500</v>
       </c>
       <c r="I45" s="3">
-        <v>677500</v>
+        <v>703200</v>
       </c>
       <c r="J45" s="3">
+        <v>691300</v>
+      </c>
+      <c r="K45" s="3">
         <v>584100</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>567700</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>580200</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>528800</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>552300</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>501800</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>511200</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>425500</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>433900</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>423200</v>
       </c>
-      <c r="T45" s="3">
+      <c r="U45" s="3">
         <v>378400</v>
       </c>
-      <c r="U45" s="3">
+      <c r="V45" s="3">
         <v>371100</v>
       </c>
-      <c r="V45" s="3">
+      <c r="W45" s="3">
         <v>313400</v>
       </c>
-      <c r="W45" s="3">
+      <c r="X45" s="3">
         <v>374900</v>
       </c>
-      <c r="X45" s="3">
+      <c r="Y45" s="3">
         <v>264700</v>
       </c>
-      <c r="Y45" s="3">
+      <c r="Z45" s="3">
         <v>268100</v>
       </c>
-      <c r="Z45" s="3">
+      <c r="AA45" s="3">
         <v>213400</v>
       </c>
-      <c r="AA45" s="3">
+      <c r="AB45" s="3">
         <v>191900</v>
       </c>
-      <c r="AB45" s="3">
+      <c r="AC45" s="3">
         <v>168000</v>
       </c>
-      <c r="AC45" s="3">
+      <c r="AD45" s="3">
         <v>197700</v>
       </c>
-      <c r="AD45" s="3">
+      <c r="AE45" s="3">
         <v>172000</v>
       </c>
-      <c r="AE45" s="3">
+      <c r="AF45" s="3">
         <v>168000</v>
       </c>
-      <c r="AF45" s="3">
+      <c r="AG45" s="3">
         <v>226600</v>
       </c>
-      <c r="AG45" s="3">
+      <c r="AH45" s="3">
         <v>241600</v>
       </c>
-      <c r="AH45" s="3">
+      <c r="AI45" s="3">
         <v>149500</v>
       </c>
     </row>
-    <row r="46" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
-        <v>3694300</v>
+        <v>3938600</v>
       </c>
       <c r="E46" s="3">
-        <v>3723900</v>
+        <v>3769700</v>
       </c>
       <c r="F46" s="3">
-        <v>3416300</v>
+        <v>3799900</v>
       </c>
       <c r="G46" s="3">
-        <v>3224000</v>
+        <v>3486000</v>
       </c>
       <c r="H46" s="3">
-        <v>3493200</v>
+        <v>3289900</v>
       </c>
       <c r="I46" s="3">
-        <v>3381500</v>
+        <v>3564500</v>
       </c>
       <c r="J46" s="3">
+        <v>3450500</v>
+      </c>
+      <c r="K46" s="3">
         <v>3835500</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>2944100</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>2785400</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>2571900</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>2628500</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>2957900</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>3091000</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>3107600</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>3820200</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>2625600</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>2986000</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>3094700</v>
       </c>
-      <c r="V46" s="3">
+      <c r="W46" s="3">
         <v>3043800</v>
       </c>
-      <c r="W46" s="3">
+      <c r="X46" s="3">
         <v>3059000</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Y46" s="3">
         <v>3084200</v>
       </c>
-      <c r="Y46" s="3">
+      <c r="Z46" s="3">
         <v>3083800</v>
       </c>
-      <c r="Z46" s="3">
+      <c r="AA46" s="3">
         <v>2881400</v>
       </c>
-      <c r="AA46" s="3">
+      <c r="AB46" s="3">
         <v>2599300</v>
       </c>
-      <c r="AB46" s="3">
+      <c r="AC46" s="3">
         <v>1523100</v>
       </c>
-      <c r="AC46" s="3">
+      <c r="AD46" s="3">
         <v>1837000</v>
       </c>
-      <c r="AD46" s="3">
+      <c r="AE46" s="3">
         <v>1795600</v>
       </c>
-      <c r="AE46" s="3">
+      <c r="AF46" s="3">
         <v>1818900</v>
       </c>
-      <c r="AF46" s="3">
+      <c r="AG46" s="3">
         <v>1877500</v>
       </c>
-      <c r="AG46" s="3">
+      <c r="AH46" s="3">
         <v>1917600</v>
       </c>
-      <c r="AH46" s="3">
+      <c r="AI46" s="3">
         <v>459000</v>
       </c>
     </row>
-    <row r="47" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
-        <v>2484700</v>
+        <v>2487600</v>
       </c>
       <c r="E47" s="3">
-        <v>2372900</v>
+        <v>2535400</v>
       </c>
       <c r="F47" s="3">
-        <v>2598100</v>
+        <v>2421300</v>
       </c>
       <c r="G47" s="3">
-        <v>2185800</v>
+        <v>2651200</v>
       </c>
       <c r="H47" s="3">
-        <v>1875700</v>
+        <v>2230400</v>
       </c>
       <c r="I47" s="3">
-        <v>1816200</v>
+        <v>1914000</v>
       </c>
       <c r="J47" s="3">
+        <v>1853300</v>
+      </c>
+      <c r="K47" s="3">
         <v>1337100</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>1167900</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>1019900</v>
       </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3">
         <v>960200</v>
       </c>
-      <c r="N47" s="3">
+      <c r="O47" s="3">
         <v>996500</v>
       </c>
-      <c r="O47" s="3">
+      <c r="P47" s="3">
         <v>1076500</v>
       </c>
-      <c r="P47" s="3">
+      <c r="Q47" s="3">
         <v>1100900</v>
       </c>
-      <c r="Q47" s="3">
+      <c r="R47" s="3">
         <v>1049100</v>
       </c>
-      <c r="R47" s="3">
+      <c r="S47" s="3">
         <v>898800</v>
       </c>
-      <c r="S47" s="3">
+      <c r="T47" s="3">
         <v>876900</v>
       </c>
-      <c r="T47" s="3">
+      <c r="U47" s="3">
         <v>771500</v>
       </c>
-      <c r="U47" s="3">
+      <c r="V47" s="3">
         <v>709100</v>
       </c>
-      <c r="V47" s="3">
+      <c r="W47" s="3">
         <v>347600</v>
       </c>
-      <c r="W47" s="3">
+      <c r="X47" s="3">
         <v>336200</v>
       </c>
-      <c r="X47" s="3">
+      <c r="Y47" s="3">
         <v>332500</v>
       </c>
-      <c r="Y47" s="3">
+      <c r="Z47" s="3">
         <v>320600</v>
       </c>
-      <c r="Z47" s="3">
+      <c r="AA47" s="3">
         <v>239300</v>
       </c>
-      <c r="AA47" s="3">
+      <c r="AB47" s="3">
         <v>215800</v>
       </c>
-      <c r="AB47" s="3">
+      <c r="AC47" s="3">
         <v>86400</v>
       </c>
-      <c r="AC47" s="3">
+      <c r="AD47" s="3">
         <v>90600</v>
       </c>
-      <c r="AD47" s="3">
+      <c r="AE47" s="3">
         <v>82600</v>
       </c>
-      <c r="AE47" s="3">
+      <c r="AF47" s="3">
         <v>78200</v>
       </c>
-      <c r="AF47" s="3">
+      <c r="AG47" s="3">
         <v>76400</v>
       </c>
-      <c r="AG47" s="3">
+      <c r="AH47" s="3">
         <v>78100</v>
       </c>
-      <c r="AH47" s="3">
+      <c r="AI47" s="3">
         <v>69300</v>
       </c>
     </row>
-    <row r="48" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
-        <v>4634300</v>
+        <v>4751200</v>
       </c>
       <c r="E48" s="3">
-        <v>4539000</v>
+        <v>4728900</v>
       </c>
       <c r="F48" s="3">
-        <v>4492400</v>
+        <v>4631600</v>
       </c>
       <c r="G48" s="3">
-        <v>4380000</v>
+        <v>4584100</v>
       </c>
       <c r="H48" s="3">
-        <v>4226800</v>
+        <v>4469400</v>
       </c>
       <c r="I48" s="3">
-        <v>4092500</v>
+        <v>4313100</v>
       </c>
       <c r="J48" s="3">
+        <v>4176100</v>
+      </c>
+      <c r="K48" s="3">
         <v>3977700</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>3845100</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>3707100</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>3558500</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>3435000</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>3191700</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>2895100</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>2706200</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>2552500</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>2274600</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>2237200</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>2059100</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>1814900</v>
       </c>
-      <c r="W48" s="3">
+      <c r="X48" s="3">
         <v>1577900</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Y48" s="3">
         <v>1532300</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="Z48" s="3">
         <v>1312300</v>
       </c>
-      <c r="Z48" s="3">
+      <c r="AA48" s="3">
         <v>1117100</v>
       </c>
-      <c r="AA48" s="3">
+      <c r="AB48" s="3">
         <v>1015500</v>
       </c>
-      <c r="AB48" s="3">
+      <c r="AC48" s="3">
         <v>983700</v>
       </c>
-      <c r="AC48" s="3">
+      <c r="AD48" s="3">
         <v>960700</v>
       </c>
-      <c r="AD48" s="3">
+      <c r="AE48" s="3">
         <v>866600</v>
       </c>
-      <c r="AE48" s="3">
+      <c r="AF48" s="3">
         <v>765200</v>
       </c>
-      <c r="AF48" s="3">
+      <c r="AG48" s="3">
         <v>668800</v>
       </c>
-      <c r="AG48" s="3">
+      <c r="AH48" s="3">
         <v>591300</v>
       </c>
-      <c r="AH48" s="3">
+      <c r="AI48" s="3">
         <v>479700</v>
       </c>
     </row>
-    <row r="49" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
-        <v>1373200</v>
+        <v>1415700</v>
       </c>
       <c r="E49" s="3">
-        <v>1368000</v>
+        <v>1401200</v>
       </c>
       <c r="F49" s="3">
-        <v>1369000</v>
+        <v>1396000</v>
       </c>
       <c r="G49" s="3">
-        <v>1373500</v>
+        <v>1396900</v>
       </c>
       <c r="H49" s="3">
-        <v>1372500</v>
+        <v>1401500</v>
       </c>
       <c r="I49" s="3">
-        <v>1342100</v>
+        <v>1400600</v>
       </c>
       <c r="J49" s="3">
+        <v>1369500</v>
+      </c>
+      <c r="K49" s="3">
         <v>1331500</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>1350200</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>1338000</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>1324400</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>1333000</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>1321600</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>1295800</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>1203300</v>
       </c>
-      <c r="R49" s="3">
+      <c r="S49" s="3">
         <v>1236400</v>
       </c>
-      <c r="S49" s="3">
+      <c r="T49" s="3">
         <v>1195900</v>
       </c>
-      <c r="T49" s="3">
+      <c r="U49" s="3">
         <v>1154200</v>
       </c>
-      <c r="U49" s="3">
+      <c r="V49" s="3">
         <v>1046800</v>
       </c>
-      <c r="V49" s="3">
+      <c r="W49" s="3">
         <v>1029800</v>
       </c>
-      <c r="W49" s="3">
+      <c r="X49" s="3">
         <v>987300</v>
       </c>
-      <c r="X49" s="3">
+      <c r="Y49" s="3">
         <v>983500</v>
       </c>
-      <c r="Y49" s="3">
+      <c r="Z49" s="3">
         <v>909900</v>
       </c>
-      <c r="Z49" s="3">
+      <c r="AA49" s="3">
         <v>873300</v>
       </c>
-      <c r="AA49" s="3">
+      <c r="AB49" s="3">
         <v>861700</v>
       </c>
-      <c r="AB49" s="3">
+      <c r="AC49" s="3">
         <v>880200</v>
       </c>
-      <c r="AC49" s="3">
+      <c r="AD49" s="3">
         <v>876300</v>
       </c>
-      <c r="AD49" s="3">
+      <c r="AE49" s="3">
         <v>841400</v>
       </c>
-      <c r="AE49" s="3">
+      <c r="AF49" s="3">
         <v>835000</v>
       </c>
-      <c r="AF49" s="3">
+      <c r="AG49" s="3">
         <v>815900</v>
       </c>
-      <c r="AG49" s="3">
+      <c r="AH49" s="3">
         <v>794000</v>
       </c>
-      <c r="AH49" s="3">
+      <c r="AI49" s="3">
         <v>777200</v>
       </c>
     </row>
-    <row r="50" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -4505,8 +4619,11 @@
       <c r="AH50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -4603,106 +4720,112 @@
       <c r="AH51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
-        <v>230700</v>
+        <v>250700</v>
       </c>
       <c r="E52" s="3">
-        <v>218500</v>
+        <v>235400</v>
       </c>
       <c r="F52" s="3">
-        <v>208200</v>
+        <v>223000</v>
       </c>
       <c r="G52" s="3">
-        <v>173300</v>
+        <v>212400</v>
       </c>
       <c r="H52" s="3">
-        <v>180800</v>
+        <v>176900</v>
       </c>
       <c r="I52" s="3">
+        <v>184500</v>
+      </c>
+      <c r="J52" s="3">
+        <v>220900</v>
+      </c>
+      <c r="K52" s="3">
+        <v>238500</v>
+      </c>
+      <c r="L52" s="3">
         <v>216500</v>
       </c>
-      <c r="J52" s="3">
-        <v>238500</v>
-      </c>
-      <c r="K52" s="3">
-        <v>216500</v>
-      </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>234300</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>233800</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>230200</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>251600</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>250600</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>175100</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>172000</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>170900</v>
       </c>
-      <c r="T52" s="3">
+      <c r="U52" s="3">
         <v>179500</v>
       </c>
-      <c r="U52" s="3">
+      <c r="V52" s="3">
         <v>156400</v>
       </c>
-      <c r="V52" s="3">
+      <c r="W52" s="3">
         <v>391500</v>
       </c>
-      <c r="W52" s="3">
+      <c r="X52" s="3">
         <v>232100</v>
       </c>
-      <c r="X52" s="3">
+      <c r="Y52" s="3">
         <v>172600</v>
       </c>
-      <c r="Y52" s="3">
+      <c r="Z52" s="3">
         <v>136600</v>
       </c>
-      <c r="Z52" s="3">
+      <c r="AA52" s="3">
         <v>108700</v>
       </c>
-      <c r="AA52" s="3">
+      <c r="AB52" s="3">
         <v>108200</v>
       </c>
-      <c r="AB52" s="3">
+      <c r="AC52" s="3">
         <v>87800</v>
       </c>
-      <c r="AC52" s="3">
+      <c r="AD52" s="3">
         <v>68500</v>
       </c>
-      <c r="AD52" s="3">
+      <c r="AE52" s="3">
         <v>45800</v>
       </c>
-      <c r="AE52" s="3">
+      <c r="AF52" s="3">
         <v>34600</v>
       </c>
-      <c r="AF52" s="3">
+      <c r="AG52" s="3">
         <v>28700</v>
       </c>
-      <c r="AG52" s="3">
+      <c r="AH52" s="3">
         <v>22500</v>
       </c>
-      <c r="AH52" s="3">
+      <c r="AI52" s="3">
         <v>26400</v>
       </c>
     </row>
-    <row r="53" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -4799,106 +4922,112 @@
       <c r="AH53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
-        <v>12417200</v>
+        <v>12843800</v>
       </c>
       <c r="E54" s="3">
-        <v>12222400</v>
+        <v>12670600</v>
       </c>
       <c r="F54" s="3">
-        <v>12084000</v>
+        <v>12471800</v>
       </c>
       <c r="G54" s="3">
-        <v>11336700</v>
+        <v>12330600</v>
       </c>
       <c r="H54" s="3">
-        <v>11149000</v>
+        <v>11568100</v>
       </c>
       <c r="I54" s="3">
-        <v>10848800</v>
+        <v>11376600</v>
       </c>
       <c r="J54" s="3">
+        <v>11070300</v>
+      </c>
+      <c r="K54" s="3">
         <v>10720300</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>9523700</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>9084600</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>8648800</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>8623200</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>8799300</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>8633300</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>8241300</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>8679900</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>7144000</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>7328400</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>7066200</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>6627600</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>6192400</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>6105100</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>5763100</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>5219700</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AB54" s="3">
         <v>4800400</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AC54" s="3">
         <v>3561300</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AD54" s="3">
         <v>3833100</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AE54" s="3">
         <v>3632000</v>
       </c>
-      <c r="AE54" s="3">
+      <c r="AF54" s="3">
         <v>3531800</v>
       </c>
-      <c r="AF54" s="3">
+      <c r="AG54" s="3">
         <v>3467300</v>
       </c>
-      <c r="AG54" s="3">
+      <c r="AH54" s="3">
         <v>3403600</v>
       </c>
-      <c r="AH54" s="3">
+      <c r="AI54" s="3">
         <v>1811700</v>
       </c>
     </row>
-    <row r="55" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -4933,8 +5062,9 @@
       <c r="AF55" s="3"/>
       <c r="AG55" s="3"/>
       <c r="AH55" s="3"/>
-    </row>
-    <row r="56" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI55" s="3"/>
+    </row>
+    <row r="56" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -4969,165 +5099,169 @@
       <c r="AF56" s="3"/>
       <c r="AG56" s="3"/>
       <c r="AH56" s="3"/>
-    </row>
-    <row r="57" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI56" s="3"/>
+    </row>
+    <row r="57" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
-        <v>322500</v>
+        <v>310200</v>
       </c>
       <c r="E57" s="3">
-        <v>353300</v>
+        <v>329100</v>
       </c>
       <c r="F57" s="3">
-        <v>275000</v>
+        <v>360500</v>
       </c>
       <c r="G57" s="3">
-        <v>266500</v>
+        <v>280600</v>
       </c>
       <c r="H57" s="3">
-        <v>284400</v>
+        <v>271900</v>
       </c>
       <c r="I57" s="3">
-        <v>304300</v>
+        <v>290200</v>
       </c>
       <c r="J57" s="3">
+        <v>310500</v>
+      </c>
+      <c r="K57" s="3">
         <v>245700</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>265700</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>238900</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>269700</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>231300</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>229300</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>222800</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>227700</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>216400</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>162900</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>185600</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>227200</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>167200</v>
       </c>
-      <c r="W57" s="3">
+      <c r="X57" s="3">
         <v>181100</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Y57" s="3">
         <v>157100</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="Z57" s="3">
         <v>190500</v>
       </c>
-      <c r="Z57" s="3">
+      <c r="AA57" s="3">
         <v>117200</v>
       </c>
-      <c r="AA57" s="3">
+      <c r="AB57" s="3">
         <v>130700</v>
       </c>
-      <c r="AB57" s="3">
+      <c r="AC57" s="3">
         <v>133200</v>
       </c>
-      <c r="AC57" s="3">
+      <c r="AD57" s="3">
         <v>132000</v>
       </c>
-      <c r="AD57" s="3">
+      <c r="AE57" s="3">
         <v>84900</v>
       </c>
-      <c r="AE57" s="3">
+      <c r="AF57" s="3">
         <v>73000</v>
       </c>
-      <c r="AF57" s="3">
+      <c r="AG57" s="3">
         <v>98200</v>
       </c>
-      <c r="AG57" s="3">
+      <c r="AH57" s="3">
         <v>92600</v>
       </c>
-      <c r="AH57" s="3">
+      <c r="AI57" s="3">
         <v>65500</v>
       </c>
     </row>
-    <row r="58" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
-        <v>1110900</v>
+        <v>1464900</v>
       </c>
       <c r="E58" s="3">
-        <v>1072900</v>
+        <v>1133600</v>
       </c>
       <c r="F58" s="3">
-        <v>1325200</v>
+        <v>1094800</v>
       </c>
       <c r="G58" s="3">
-        <v>925800</v>
+        <v>1352300</v>
       </c>
       <c r="H58" s="3">
-        <v>939300</v>
+        <v>944700</v>
       </c>
       <c r="I58" s="3">
-        <v>772900</v>
+        <v>958500</v>
       </c>
       <c r="J58" s="3">
+        <v>788700</v>
+      </c>
+      <c r="K58" s="3">
         <v>993100</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>1015500</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>847900</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>500600</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>678800</v>
       </c>
-      <c r="O58" s="3">
+      <c r="P58" s="3">
         <v>537500</v>
       </c>
-      <c r="P58" s="3">
+      <c r="Q58" s="3">
         <v>433100</v>
       </c>
-      <c r="Q58" s="3">
+      <c r="R58" s="3">
         <v>244900</v>
       </c>
-      <c r="R58" s="3">
+      <c r="S58" s="3">
         <v>413300</v>
       </c>
-      <c r="S58" s="3">
+      <c r="T58" s="3">
         <v>322200</v>
       </c>
-      <c r="T58" s="3">
+      <c r="U58" s="3">
         <v>47300</v>
       </c>
-      <c r="U58" s="3">
-        <v>0</v>
-      </c>
-      <c r="V58" s="3" t="s">
-        <v>8</v>
+      <c r="V58" s="3">
+        <v>0</v>
       </c>
       <c r="W58" s="3" t="s">
         <v>8</v>
@@ -5135,8 +5269,8 @@
       <c r="X58" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Y58" s="3">
-        <v>0</v>
+      <c r="Y58" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="Z58" s="3">
         <v>0</v>
@@ -5148,7 +5282,7 @@
         <v>0</v>
       </c>
       <c r="AC58" s="3">
-        <v>37100</v>
+        <v>0</v>
       </c>
       <c r="AD58" s="3">
         <v>37100</v>
@@ -5157,239 +5291,248 @@
         <v>37100</v>
       </c>
       <c r="AF58" s="3">
+        <v>37100</v>
+      </c>
+      <c r="AG58" s="3">
         <v>101800</v>
       </c>
-      <c r="AG58" s="3">
+      <c r="AH58" s="3">
         <v>65400</v>
       </c>
-      <c r="AH58" s="3">
+      <c r="AI58" s="3">
         <v>43600</v>
       </c>
     </row>
-    <row r="59" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
-        <v>1780200</v>
+        <v>1339000</v>
       </c>
       <c r="E59" s="3">
+        <v>1816600</v>
+      </c>
+      <c r="F59" s="3">
+        <v>1372900</v>
+      </c>
+      <c r="G59" s="3">
         <v>1345400</v>
       </c>
-      <c r="F59" s="3">
-        <v>1318500</v>
-      </c>
-      <c r="G59" s="3">
-        <v>1256900</v>
-      </c>
       <c r="H59" s="3">
-        <v>1415400</v>
+        <v>1282600</v>
       </c>
       <c r="I59" s="3">
-        <v>1189300</v>
+        <v>1444300</v>
       </c>
       <c r="J59" s="3">
+        <v>1213600</v>
+      </c>
+      <c r="K59" s="3">
         <v>1179100</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>1079000</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>1121000</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>1020300</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>902400</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>855200</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>966600</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>828600</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>822800</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>808400</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>1052600</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>801600</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>687500</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>630100</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Y59" s="3">
         <v>711200</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="Z59" s="3">
         <v>556200</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AA59" s="3">
         <v>432100</v>
       </c>
-      <c r="AA59" s="3">
+      <c r="AB59" s="3">
         <v>419700</v>
       </c>
-      <c r="AB59" s="3">
+      <c r="AC59" s="3">
         <v>424600</v>
       </c>
-      <c r="AC59" s="3">
+      <c r="AD59" s="3">
         <v>446300</v>
       </c>
-      <c r="AD59" s="3">
+      <c r="AE59" s="3">
         <v>419000</v>
       </c>
-      <c r="AE59" s="3">
+      <c r="AF59" s="3">
         <v>349800</v>
       </c>
-      <c r="AF59" s="3">
+      <c r="AG59" s="3">
         <v>311200</v>
       </c>
-      <c r="AG59" s="3">
+      <c r="AH59" s="3">
         <v>354300</v>
       </c>
-      <c r="AH59" s="3">
+      <c r="AI59" s="3">
         <v>296300</v>
       </c>
     </row>
-    <row r="60" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
-        <v>3213700</v>
+        <v>3114100</v>
       </c>
       <c r="E60" s="3">
-        <v>2771700</v>
+        <v>3279300</v>
       </c>
       <c r="F60" s="3">
-        <v>2918800</v>
+        <v>2828200</v>
       </c>
       <c r="G60" s="3">
-        <v>2449300</v>
+        <v>2978300</v>
       </c>
       <c r="H60" s="3">
-        <v>2639100</v>
+        <v>2499200</v>
       </c>
       <c r="I60" s="3">
-        <v>2266600</v>
+        <v>2693000</v>
       </c>
       <c r="J60" s="3">
+        <v>2312800</v>
+      </c>
+      <c r="K60" s="3">
         <v>2417900</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>2360200</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>2207700</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>1790600</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>1812500</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>1622000</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>1622600</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>1301200</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>1452600</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>1293500</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>1285600</v>
       </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
         <v>1028700</v>
       </c>
-      <c r="V60" s="3">
+      <c r="W60" s="3">
         <v>854700</v>
       </c>
-      <c r="W60" s="3">
+      <c r="X60" s="3">
         <v>811200</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Y60" s="3">
         <v>868200</v>
       </c>
-      <c r="Y60" s="3">
+      <c r="Z60" s="3">
         <v>746700</v>
       </c>
-      <c r="Z60" s="3">
+      <c r="AA60" s="3">
         <v>549300</v>
       </c>
-      <c r="AA60" s="3">
+      <c r="AB60" s="3">
         <v>550400</v>
       </c>
-      <c r="AB60" s="3">
+      <c r="AC60" s="3">
         <v>557800</v>
       </c>
-      <c r="AC60" s="3">
+      <c r="AD60" s="3">
         <v>615300</v>
       </c>
-      <c r="AD60" s="3">
+      <c r="AE60" s="3">
         <v>541000</v>
       </c>
-      <c r="AE60" s="3">
+      <c r="AF60" s="3">
         <v>459900</v>
       </c>
-      <c r="AF60" s="3">
+      <c r="AG60" s="3">
         <v>511200</v>
       </c>
-      <c r="AG60" s="3">
+      <c r="AH60" s="3">
         <v>512300</v>
       </c>
-      <c r="AH60" s="3">
+      <c r="AI60" s="3">
         <v>405500</v>
       </c>
     </row>
-    <row r="61" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
-        <v>989100</v>
+        <v>1017400</v>
       </c>
       <c r="E61" s="3">
-        <v>971200</v>
+        <v>1009300</v>
       </c>
       <c r="F61" s="3">
-        <v>996600</v>
+        <v>991000</v>
       </c>
       <c r="G61" s="3">
-        <v>989000</v>
+        <v>1016900</v>
       </c>
       <c r="H61" s="3">
-        <v>935300</v>
+        <v>1009200</v>
       </c>
       <c r="I61" s="3">
-        <v>938000</v>
+        <v>954400</v>
       </c>
       <c r="J61" s="3">
+        <v>957100</v>
+      </c>
+      <c r="K61" s="3">
         <v>966000</v>
       </c>
-      <c r="K61" s="3">
-        <v>0</v>
-      </c>
       <c r="L61" s="3">
         <v>0</v>
       </c>
@@ -5459,106 +5602,112 @@
       <c r="AH61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
-        <v>147200</v>
+        <v>116200</v>
       </c>
       <c r="E62" s="3">
-        <v>151200</v>
+        <v>150200</v>
       </c>
       <c r="F62" s="3">
-        <v>109800</v>
+        <v>154200</v>
       </c>
       <c r="G62" s="3">
-        <v>115300</v>
+        <v>112000</v>
       </c>
       <c r="H62" s="3">
-        <v>113500</v>
+        <v>117700</v>
       </c>
       <c r="I62" s="3">
-        <v>118400</v>
+        <v>115900</v>
       </c>
       <c r="J62" s="3">
+        <v>120800</v>
+      </c>
+      <c r="K62" s="3">
         <v>101000</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>110000</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>114700</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>116900</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>120300</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>115800</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>110200</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>105400</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>99300</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>104200</v>
       </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>117500</v>
       </c>
-      <c r="U62" s="3">
+      <c r="V62" s="3">
         <v>124100</v>
       </c>
-      <c r="V62" s="3">
+      <c r="W62" s="3">
         <v>95900</v>
       </c>
-      <c r="W62" s="3">
+      <c r="X62" s="3">
         <v>96500</v>
       </c>
-      <c r="X62" s="3">
+      <c r="Y62" s="3">
         <v>121000</v>
       </c>
-      <c r="Y62" s="3">
+      <c r="Z62" s="3">
         <v>39500</v>
       </c>
-      <c r="Z62" s="3">
+      <c r="AA62" s="3">
         <v>33600</v>
       </c>
-      <c r="AA62" s="3">
+      <c r="AB62" s="3">
         <v>33400</v>
       </c>
-      <c r="AB62" s="3">
+      <c r="AC62" s="3">
         <v>34000</v>
       </c>
-      <c r="AC62" s="3">
+      <c r="AD62" s="3">
         <v>35700</v>
       </c>
-      <c r="AD62" s="3">
+      <c r="AE62" s="3">
         <v>30000</v>
       </c>
-      <c r="AE62" s="3">
+      <c r="AF62" s="3">
         <v>30300</v>
       </c>
-      <c r="AF62" s="3">
+      <c r="AG62" s="3">
         <v>23500</v>
       </c>
-      <c r="AG62" s="3">
+      <c r="AH62" s="3">
         <v>19000</v>
       </c>
-      <c r="AH62" s="3">
+      <c r="AI62" s="3">
         <v>19100</v>
       </c>
     </row>
-    <row r="63" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -5655,8 +5804,11 @@
       <c r="AH63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -5753,8 +5905,11 @@
       <c r="AH64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -5851,106 +6006,112 @@
       <c r="AH65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
-        <v>4425500</v>
+        <v>4324900</v>
       </c>
       <c r="E66" s="3">
-        <v>3960100</v>
+        <v>4515900</v>
       </c>
       <c r="F66" s="3">
-        <v>4085100</v>
+        <v>4041000</v>
       </c>
       <c r="G66" s="3">
-        <v>3612900</v>
+        <v>4168500</v>
       </c>
       <c r="H66" s="3">
-        <v>3748500</v>
+        <v>3686600</v>
       </c>
       <c r="I66" s="3">
-        <v>3384200</v>
+        <v>3825000</v>
       </c>
       <c r="J66" s="3">
+        <v>3453300</v>
+      </c>
+      <c r="K66" s="3">
         <v>3547700</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>2528500</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>2353800</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>1947500</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>1953500</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>1753500</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>1752700</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>1423500</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>1568300</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>1414400</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>1419300</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>1168400</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>965800</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>919500</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>999600</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>793800</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>588000</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AB66" s="3">
         <v>584900</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AC66" s="3">
         <v>592700</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AD66" s="3">
         <v>651900</v>
       </c>
-      <c r="AD66" s="3">
+      <c r="AE66" s="3">
         <v>571800</v>
       </c>
-      <c r="AE66" s="3">
+      <c r="AF66" s="3">
         <v>491000</v>
       </c>
-      <c r="AF66" s="3">
+      <c r="AG66" s="3">
         <v>535400</v>
       </c>
-      <c r="AG66" s="3">
+      <c r="AH66" s="3">
         <v>532100</v>
       </c>
-      <c r="AH66" s="3">
+      <c r="AI66" s="3">
         <v>424600</v>
       </c>
     </row>
-    <row r="67" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -5985,8 +6146,9 @@
       <c r="AF67" s="3"/>
       <c r="AG67" s="3"/>
       <c r="AH67" s="3"/>
-    </row>
-    <row r="68" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI67" s="3"/>
+    </row>
+    <row r="68" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -6083,8 +6245,11 @@
       <c r="AH68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -6181,8 +6346,11 @@
       <c r="AH69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -6277,10 +6445,13 @@
         <v>0</v>
       </c>
       <c r="AH70" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI70" s="3">
         <v>304900</v>
       </c>
     </row>
-    <row r="71" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="71" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -6377,106 +6548,112 @@
       <c r="AH71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
-        <v>4700600</v>
+        <v>5164700</v>
       </c>
       <c r="E72" s="3">
-        <v>5015400</v>
+        <v>4796500</v>
       </c>
       <c r="F72" s="3">
-        <v>4754000</v>
+        <v>5117700</v>
       </c>
       <c r="G72" s="3">
-        <v>4465900</v>
+        <v>4851000</v>
       </c>
       <c r="H72" s="3">
-        <v>4250500</v>
+        <v>4557000</v>
       </c>
       <c r="I72" s="3">
-        <v>4070100</v>
+        <v>4337200</v>
       </c>
       <c r="J72" s="3">
+        <v>4153200</v>
+      </c>
+      <c r="K72" s="3">
         <v>3771300</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>3525800</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>3280400</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>3129900</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>2978700</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>3182700</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>3093800</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>2928600</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>2910500</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>2733500</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>2697900</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>2575600</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>2246600</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>2000300</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>1784800</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>1605100</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AA72" s="3">
         <v>1368400</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AB72" s="3">
         <v>1220100</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AC72" s="3">
         <v>1036800</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AD72" s="3">
         <v>989800</v>
       </c>
-      <c r="AD72" s="3">
+      <c r="AE72" s="3">
         <v>808400</v>
       </c>
-      <c r="AE72" s="3">
+      <c r="AF72" s="3">
         <v>702000</v>
       </c>
-      <c r="AF72" s="3">
+      <c r="AG72" s="3">
         <v>583600</v>
       </c>
-      <c r="AG72" s="3">
+      <c r="AH72" s="3">
         <v>510400</v>
       </c>
-      <c r="AH72" s="3">
+      <c r="AI72" s="3">
         <v>404700</v>
       </c>
     </row>
-    <row r="73" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -6573,8 +6750,11 @@
       <c r="AH73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -6671,8 +6851,11 @@
       <c r="AH74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -6769,106 +6952,112 @@
       <c r="AH75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
-        <v>7991600</v>
+        <v>8519000</v>
       </c>
       <c r="E76" s="3">
-        <v>8262200</v>
+        <v>8154800</v>
       </c>
       <c r="F76" s="3">
-        <v>7998900</v>
+        <v>8430900</v>
       </c>
       <c r="G76" s="3">
-        <v>7723800</v>
+        <v>8162100</v>
       </c>
       <c r="H76" s="3">
-        <v>7400500</v>
+        <v>7881400</v>
       </c>
       <c r="I76" s="3">
-        <v>7464600</v>
+        <v>7551600</v>
       </c>
       <c r="J76" s="3">
+        <v>7616900</v>
+      </c>
+      <c r="K76" s="3">
         <v>7172500</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>6995300</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>6730800</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>6701200</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>6669700</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>7045800</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>6880500</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>6817900</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>7111600</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>5729500</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>5909100</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>5897800</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>5661800</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>5272900</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>5105500</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>4969400</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>4631700</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AB76" s="3">
         <v>4215500</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AC76" s="3">
         <v>2968500</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AD76" s="3">
         <v>3181200</v>
       </c>
-      <c r="AD76" s="3">
+      <c r="AE76" s="3">
         <v>3060200</v>
       </c>
-      <c r="AE76" s="3">
+      <c r="AF76" s="3">
         <v>3040800</v>
       </c>
-      <c r="AF76" s="3">
+      <c r="AG76" s="3">
         <v>2931800</v>
       </c>
-      <c r="AG76" s="3">
+      <c r="AH76" s="3">
         <v>2871500</v>
       </c>
-      <c r="AH76" s="3">
+      <c r="AI76" s="3">
         <v>1082100</v>
       </c>
     </row>
-    <row r="77" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -6965,209 +7154,218 @@
       <c r="AH77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:35" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45473</v>
+      </c>
+      <c r="E80" s="2">
         <v>45382</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45291</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45199</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45107</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45016</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>44926</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>44834</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44742</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44651</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44561</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44469</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44377</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44286</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44196</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44104</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44012</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>43921</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>43830</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>43738</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>43646</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>43555</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>43465</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>43373</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>43281</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43190</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>43100</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>43008</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AF80" s="2">
         <v>42916</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AG80" s="2">
         <v>42825</v>
       </c>
-      <c r="AG80" s="2">
+      <c r="AH80" s="2">
         <v>42735</v>
       </c>
-      <c r="AH80" s="2">
+      <c r="AI80" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="81" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
-        <v>197000</v>
+        <v>368200</v>
       </c>
       <c r="E81" s="3">
-        <v>302900</v>
+        <v>201000</v>
       </c>
       <c r="F81" s="3">
-        <v>324000</v>
+        <v>309100</v>
       </c>
       <c r="G81" s="3">
-        <v>351100</v>
+        <v>330600</v>
       </c>
       <c r="H81" s="3">
-        <v>230800</v>
+        <v>358300</v>
       </c>
       <c r="I81" s="3">
-        <v>298800</v>
+        <v>235500</v>
       </c>
       <c r="J81" s="3">
+        <v>304900</v>
+      </c>
+      <c r="K81" s="3">
         <v>267300</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>251000</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>126000</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>242800</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>165800</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>185600</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>76600</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>179300</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>177000</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>213400</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>59100</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>358200</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>204000</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>207700</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>103600</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>185200</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>148300</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>208700</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AC81" s="3">
         <v>79900</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AD81" s="3">
         <v>181400</v>
-      </c>
-      <c r="AD81" s="3">
-        <v>106400</v>
       </c>
       <c r="AE81" s="3">
         <v>106400</v>
       </c>
       <c r="AF81" s="3">
+        <v>106400</v>
+      </c>
+      <c r="AG81" s="3">
         <v>73200</v>
       </c>
-      <c r="AG81" s="3">
+      <c r="AH81" s="3">
         <v>105700</v>
       </c>
-      <c r="AH81" s="3">
+      <c r="AI81" s="3">
         <v>73700</v>
       </c>
     </row>
-    <row r="82" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -7202,8 +7400,9 @@
       <c r="AF82" s="3"/>
       <c r="AG82" s="3"/>
       <c r="AH82" s="3"/>
-    </row>
-    <row r="83" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI82" s="3"/>
+    </row>
+    <row r="83" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
@@ -7300,8 +7499,11 @@
       <c r="AH83" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="84" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI83" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -7398,8 +7600,11 @@
       <c r="AH84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -7496,8 +7701,11 @@
       <c r="AH85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -7594,8 +7802,11 @@
       <c r="AH86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -7692,8 +7903,11 @@
       <c r="AH87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -7790,106 +8004,112 @@
       <c r="AH88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
-        <v>280600</v>
+        <v>490600</v>
       </c>
       <c r="E89" s="3">
-        <v>542000</v>
+        <v>286300</v>
       </c>
       <c r="F89" s="3">
-        <v>405900</v>
+        <v>553100</v>
       </c>
       <c r="G89" s="3">
-        <v>519700</v>
+        <v>414200</v>
       </c>
       <c r="H89" s="3">
-        <v>378300</v>
+        <v>530300</v>
       </c>
       <c r="I89" s="3">
-        <v>520800</v>
+        <v>386000</v>
       </c>
       <c r="J89" s="3">
+        <v>531500</v>
+      </c>
+      <c r="K89" s="3">
         <v>390100</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>525600</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>153700</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>416600</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>254000</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>277500</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>68500</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>284000</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>218200</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>184500</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>28000</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>348100</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>221200</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>304500</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>96300</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>261800</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AA89" s="3">
         <v>127600</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AB89" s="3">
         <v>206600</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AC89" s="3">
         <v>30700</v>
       </c>
-      <c r="AC89" s="3">
+      <c r="AD89" s="3">
         <v>203600</v>
       </c>
-      <c r="AD89" s="3">
+      <c r="AE89" s="3">
         <v>152000</v>
       </c>
-      <c r="AE89" s="3">
+      <c r="AF89" s="3">
         <v>134100</v>
       </c>
-      <c r="AF89" s="3">
+      <c r="AG89" s="3">
         <v>48200</v>
       </c>
-      <c r="AG89" s="3">
+      <c r="AH89" s="3">
         <v>166300</v>
       </c>
-      <c r="AH89" s="3">
+      <c r="AI89" s="3">
         <v>121000</v>
       </c>
     </row>
-    <row r="90" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -7924,8 +8144,9 @@
       <c r="AF90" s="3"/>
       <c r="AG90" s="3"/>
       <c r="AH90" s="3"/>
-    </row>
-    <row r="91" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI90" s="3"/>
+    </row>
+    <row r="91" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
@@ -8022,8 +8243,11 @@
       <c r="AH91" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="92" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI91" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -8120,8 +8344,11 @@
       <c r="AH92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -8218,106 +8445,112 @@
       <c r="AH93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
-        <v>-328600</v>
+        <v>-657900</v>
       </c>
       <c r="E94" s="3">
-        <v>163200</v>
+        <v>-335300</v>
       </c>
       <c r="F94" s="3">
-        <v>-556200</v>
+        <v>166500</v>
       </c>
       <c r="G94" s="3">
-        <v>-489300</v>
+        <v>-567600</v>
       </c>
       <c r="H94" s="3">
-        <v>-810500</v>
+        <v>-499300</v>
       </c>
       <c r="I94" s="3">
-        <v>-605300</v>
+        <v>-827100</v>
       </c>
       <c r="J94" s="3">
+        <v>-617600</v>
+      </c>
+      <c r="K94" s="3">
         <v>-654400</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-501800</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-460800</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-387700</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-197000</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-26500</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-627900</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-406000</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>173900</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>-161800</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>-112800</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>-314600</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>-626500</v>
       </c>
-      <c r="W94" s="3">
+      <c r="X94" s="3">
         <v>229000</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Y94" s="3">
         <v>136200</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="Z94" s="3">
         <v>-483600</v>
       </c>
-      <c r="Z94" s="3">
+      <c r="AA94" s="3">
         <v>-321300</v>
       </c>
-      <c r="AA94" s="3">
+      <c r="AB94" s="3">
         <v>-790700</v>
       </c>
-      <c r="AB94" s="3">
+      <c r="AC94" s="3">
         <v>-229200</v>
       </c>
-      <c r="AC94" s="3">
+      <c r="AD94" s="3">
         <v>-107200</v>
       </c>
-      <c r="AD94" s="3">
+      <c r="AE94" s="3">
         <v>-167600</v>
       </c>
-      <c r="AE94" s="3">
+      <c r="AF94" s="3">
         <v>-168800</v>
       </c>
-      <c r="AF94" s="3">
+      <c r="AG94" s="3">
         <v>-771600</v>
       </c>
-      <c r="AG94" s="3">
+      <c r="AH94" s="3">
         <v>-158200</v>
       </c>
-      <c r="AH94" s="3">
+      <c r="AI94" s="3">
         <v>-129200</v>
       </c>
     </row>
-    <row r="95" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -8352,8 +8585,9 @@
       <c r="AF95" s="3"/>
       <c r="AG95" s="3"/>
       <c r="AH95" s="3"/>
-    </row>
-    <row r="96" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI95" s="3"/>
+    </row>
+    <row r="96" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -8450,8 +8684,11 @@
       <c r="AH96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -8548,8 +8785,11 @@
       <c r="AH97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -8646,8 +8886,11 @@
       <c r="AH98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -8744,298 +8987,310 @@
       <c r="AH99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
-        <v>18000</v>
+        <v>-155600</v>
       </c>
       <c r="E100" s="3">
-        <v>-299300</v>
+        <v>18300</v>
       </c>
       <c r="F100" s="3">
-        <v>349500</v>
+        <v>-305400</v>
       </c>
       <c r="G100" s="3">
-        <v>-272800</v>
+        <v>356700</v>
       </c>
       <c r="H100" s="3">
-        <v>116100</v>
+        <v>-278300</v>
       </c>
       <c r="I100" s="3">
-        <v>-235900</v>
+        <v>118500</v>
       </c>
       <c r="J100" s="3">
+        <v>-240700</v>
+      </c>
+      <c r="K100" s="3">
         <v>876200</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-21800</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>358800</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>-108500</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>-308000</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>-135500</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>142800</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>-87400</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>1267700</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>9600</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>47000</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>2000</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>79800</v>
       </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
         <v>-380900</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Y100" s="3">
         <v>-2100</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="Z100" s="3">
         <v>-22300</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AA100" s="3">
         <v>193200</v>
       </c>
-      <c r="AA100" s="3">
+      <c r="AB100" s="3">
         <v>926600</v>
       </c>
-      <c r="AB100" s="3">
+      <c r="AC100" s="3">
         <v>-115500</v>
       </c>
-      <c r="AC100" s="3">
+      <c r="AD100" s="3">
         <v>-30000</v>
       </c>
-      <c r="AD100" s="3">
+      <c r="AE100" s="3">
         <v>-59900</v>
       </c>
-      <c r="AE100" s="3">
+      <c r="AF100" s="3">
         <v>-104800</v>
       </c>
-      <c r="AF100" s="3">
+      <c r="AG100" s="3">
         <v>36400</v>
       </c>
-      <c r="AG100" s="3">
+      <c r="AH100" s="3">
         <v>1358900</v>
       </c>
-      <c r="AH100" s="3">
+      <c r="AI100" s="3">
         <v>-3900</v>
       </c>
     </row>
-    <row r="101" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
-        <v>5300</v>
+        <v>-500</v>
       </c>
       <c r="E101" s="3">
+        <v>5400</v>
+      </c>
+      <c r="F101" s="3">
         <v>600</v>
       </c>
-      <c r="F101" s="3">
+      <c r="G101" s="3">
         <v>1300</v>
       </c>
-      <c r="G101" s="3">
-        <v>14500</v>
-      </c>
       <c r="H101" s="3">
-        <v>-1200</v>
+        <v>14800</v>
       </c>
       <c r="I101" s="3">
-        <v>-8200</v>
+        <v>-1300</v>
       </c>
       <c r="J101" s="3">
+        <v>-8300</v>
+      </c>
+      <c r="K101" s="3">
         <v>31000</v>
       </c>
-      <c r="K101" s="3">
+      <c r="L101" s="3">
         <v>26900</v>
       </c>
-      <c r="L101" s="3">
+      <c r="M101" s="3">
         <v>-2900</v>
       </c>
-      <c r="M101" s="3">
+      <c r="N101" s="3">
         <v>-6600</v>
       </c>
-      <c r="N101" s="3">
+      <c r="O101" s="3">
         <v>-300</v>
       </c>
-      <c r="O101" s="3">
+      <c r="P101" s="3">
         <v>-19200</v>
       </c>
-      <c r="P101" s="3">
+      <c r="Q101" s="3">
         <v>4800</v>
       </c>
-      <c r="Q101" s="3">
+      <c r="R101" s="3">
         <v>-78800</v>
       </c>
-      <c r="R101" s="3">
+      <c r="S101" s="3">
         <v>-16100</v>
       </c>
-      <c r="S101" s="3">
+      <c r="T101" s="3">
         <v>300</v>
       </c>
-      <c r="T101" s="3">
+      <c r="U101" s="3">
         <v>2700</v>
       </c>
-      <c r="U101" s="3">
+      <c r="V101" s="3">
         <v>-2000</v>
       </c>
-      <c r="V101" s="3">
+      <c r="W101" s="3">
         <v>5200</v>
       </c>
-      <c r="W101" s="3">
+      <c r="X101" s="3">
         <v>3300</v>
       </c>
-      <c r="X101" s="3">
+      <c r="Y101" s="3">
         <v>-6900</v>
       </c>
-      <c r="Y101" s="3">
+      <c r="Z101" s="3">
         <v>4700</v>
       </c>
-      <c r="Z101" s="3">
+      <c r="AA101" s="3">
         <v>14200</v>
       </c>
-      <c r="AA101" s="3">
+      <c r="AB101" s="3">
         <v>32400</v>
       </c>
-      <c r="AB101" s="3">
+      <c r="AC101" s="3">
         <v>-12800</v>
       </c>
-      <c r="AC101" s="3">
+      <c r="AD101" s="3">
         <v>-16600</v>
       </c>
-      <c r="AD101" s="3">
+      <c r="AE101" s="3">
         <v>-17500</v>
       </c>
-      <c r="AE101" s="3">
+      <c r="AF101" s="3">
         <v>-10400</v>
       </c>
-      <c r="AF101" s="3">
+      <c r="AG101" s="3">
         <v>-18100</v>
       </c>
-      <c r="AG101" s="3">
+      <c r="AH101" s="3">
         <v>40700</v>
       </c>
-      <c r="AH101" s="3">
+      <c r="AI101" s="3">
         <v>400</v>
       </c>
     </row>
-    <row r="102" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
-        <v>-24700</v>
+        <v>-323300</v>
       </c>
       <c r="E102" s="3">
-        <v>406600</v>
+        <v>-25200</v>
       </c>
       <c r="F102" s="3">
-        <v>200600</v>
+        <v>414900</v>
       </c>
       <c r="G102" s="3">
-        <v>-227900</v>
+        <v>204700</v>
       </c>
       <c r="H102" s="3">
-        <v>-317400</v>
+        <v>-232500</v>
       </c>
       <c r="I102" s="3">
-        <v>-328400</v>
+        <v>-323800</v>
       </c>
       <c r="J102" s="3">
+        <v>-335200</v>
+      </c>
+      <c r="K102" s="3">
         <v>642800</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>28900</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>48700</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>-86200</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-251300</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>96300</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>-411900</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>-288300</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>1643600</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>32700</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>-35000</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>33500</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>-320300</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>155900</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>223500</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
         <v>-239400</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AA102" s="3">
         <v>13700</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AB102" s="3">
         <v>374800</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AC102" s="3">
         <v>-326900</v>
       </c>
-      <c r="AC102" s="3">
+      <c r="AD102" s="3">
         <v>49800</v>
       </c>
-      <c r="AD102" s="3">
+      <c r="AE102" s="3">
         <v>-92900</v>
       </c>
-      <c r="AE102" s="3">
+      <c r="AF102" s="3">
         <v>-150000</v>
       </c>
-      <c r="AF102" s="3">
+      <c r="AG102" s="3">
         <v>-705100</v>
       </c>
-      <c r="AG102" s="3">
+      <c r="AH102" s="3">
         <v>1407600</v>
       </c>
-      <c r="AH102" s="3">
+      <c r="AI102" s="3">
         <v>-11700</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/ZTO_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/ZTO_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="146" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="162" uniqueCount="92">
   <si>
     <t>ZTO</t>
   </si>
@@ -656,454 +656,467 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AI102"/>
+  <dimension ref="A5:AJ102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="6.140625" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="15" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="19" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="23" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="27" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="29" max="29" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="30" max="31" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="32" max="32" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="33" max="33" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="34" max="35" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="36" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="8" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="12" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="16" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="20" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="24" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="28" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="31" max="32" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="33" max="33" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="34" max="34" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="35" max="36" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="37" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:36" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:36" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45565</v>
+      </c>
+      <c r="E7" s="2">
         <v>45473</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45382</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45291</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45199</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45107</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45016</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>44926</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44834</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44742</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44651</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44561</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44469</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44377</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44286</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44196</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44104</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44012</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>43921</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>43830</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>43738</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>43646</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>43555</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>43465</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>43373</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43281</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>43190</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>43100</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AF7" s="2">
         <v>43008</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AG7" s="2">
         <v>42916</v>
       </c>
-      <c r="AG7" s="2">
+      <c r="AH7" s="2">
         <v>42825</v>
       </c>
-      <c r="AH7" s="2">
+      <c r="AI7" s="2">
         <v>42735</v>
       </c>
-      <c r="AI7" s="2">
+      <c r="AJ7" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="8" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:36" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
-        <v>1512200</v>
+        <v>1521900</v>
       </c>
       <c r="E8" s="3">
-        <v>1404200</v>
+        <v>1476000</v>
       </c>
       <c r="F8" s="3">
-        <v>1497100</v>
+        <v>1379400</v>
       </c>
       <c r="G8" s="3">
-        <v>1279500</v>
+        <v>1497600</v>
       </c>
       <c r="H8" s="3">
-        <v>1373200</v>
+        <v>1243900</v>
       </c>
       <c r="I8" s="3">
-        <v>1266500</v>
+        <v>1343100</v>
       </c>
       <c r="J8" s="3">
+        <v>1307800</v>
+      </c>
+      <c r="K8" s="3">
         <v>1391700</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>1235800</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>1203500</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>1098800</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>1270000</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>1050600</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>1052000</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>929600</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>1149400</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>978300</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>943500</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>617800</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>1054200</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>821500</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>828600</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>695800</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>817300</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AB8" s="3">
         <v>592700</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AC8" s="3">
         <v>587500</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AD8" s="3">
         <v>508600</v>
       </c>
-      <c r="AD8" s="3">
+      <c r="AE8" s="3">
         <v>642800</v>
       </c>
-      <c r="AE8" s="3">
+      <c r="AF8" s="3">
         <v>466500</v>
       </c>
-      <c r="AF8" s="3">
+      <c r="AG8" s="3">
         <v>441000</v>
       </c>
-      <c r="AG8" s="3">
+      <c r="AH8" s="3">
         <v>380200</v>
       </c>
-      <c r="AH8" s="3">
+      <c r="AI8" s="3">
         <v>464000</v>
       </c>
-      <c r="AI8" s="3">
+      <c r="AJ8" s="3">
         <v>342200</v>
       </c>
     </row>
-    <row r="9" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:36" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
-        <v>1001700</v>
+        <v>1046400</v>
       </c>
       <c r="E9" s="3">
-        <v>980900</v>
+        <v>977800</v>
       </c>
       <c r="F9" s="3">
-        <v>1056100</v>
+        <v>963600</v>
       </c>
       <c r="G9" s="3">
-        <v>898000</v>
+        <v>1056500</v>
       </c>
       <c r="H9" s="3">
-        <v>907300</v>
+        <v>872900</v>
       </c>
       <c r="I9" s="3">
-        <v>910700</v>
+        <v>887400</v>
       </c>
       <c r="J9" s="3">
+        <v>940400</v>
+      </c>
+      <c r="K9" s="3">
         <v>1000800</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>898100</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>897200</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>873700</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>959900</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>827700</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>811700</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>772100</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>890700</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>773300</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>682800</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>488600</v>
       </c>
-      <c r="V9" s="3">
+      <c r="W9" s="3">
         <v>746900</v>
       </c>
-      <c r="W9" s="3">
+      <c r="X9" s="3">
         <v>572400</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Y9" s="3">
         <v>558400</v>
       </c>
-      <c r="Y9" s="3">
+      <c r="Z9" s="3">
         <v>504200</v>
       </c>
-      <c r="Z9" s="3">
+      <c r="AA9" s="3">
         <v>592200</v>
       </c>
-      <c r="AA9" s="3">
+      <c r="AB9" s="3">
         <v>407200</v>
       </c>
-      <c r="AB9" s="3">
+      <c r="AC9" s="3">
         <v>383600</v>
       </c>
-      <c r="AC9" s="3">
+      <c r="AD9" s="3">
         <v>360500</v>
       </c>
-      <c r="AD9" s="3">
+      <c r="AE9" s="3">
         <v>441900</v>
       </c>
-      <c r="AE9" s="3">
+      <c r="AF9" s="3">
         <v>297600</v>
       </c>
-      <c r="AF9" s="3">
+      <c r="AG9" s="3">
         <v>274200</v>
       </c>
-      <c r="AG9" s="3">
+      <c r="AH9" s="3">
         <v>274000</v>
       </c>
-      <c r="AH9" s="3">
+      <c r="AI9" s="3">
         <v>295100</v>
       </c>
-      <c r="AI9" s="3">
+      <c r="AJ9" s="3">
         <v>218200</v>
       </c>
     </row>
-    <row r="10" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:36" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
-        <v>510400</v>
+        <v>475400</v>
       </c>
       <c r="E10" s="3">
-        <v>423200</v>
+        <v>498200</v>
       </c>
       <c r="F10" s="3">
-        <v>441000</v>
+        <v>415800</v>
       </c>
       <c r="G10" s="3">
-        <v>381600</v>
+        <v>441200</v>
       </c>
       <c r="H10" s="3">
-        <v>465900</v>
+        <v>370900</v>
       </c>
       <c r="I10" s="3">
-        <v>355700</v>
+        <v>455600</v>
       </c>
       <c r="J10" s="3">
+        <v>367400</v>
+      </c>
+      <c r="K10" s="3">
         <v>390900</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>337700</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>306200</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>225100</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>310100</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>222900</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>240400</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>157500</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>258700</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>205000</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>260700</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>129200</v>
       </c>
-      <c r="V10" s="3">
+      <c r="W10" s="3">
         <v>307400</v>
       </c>
-      <c r="W10" s="3">
+      <c r="X10" s="3">
         <v>249100</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Y10" s="3">
         <v>270200</v>
       </c>
-      <c r="Y10" s="3">
+      <c r="Z10" s="3">
         <v>191600</v>
       </c>
-      <c r="Z10" s="3">
+      <c r="AA10" s="3">
         <v>225100</v>
       </c>
-      <c r="AA10" s="3">
+      <c r="AB10" s="3">
         <v>185500</v>
       </c>
-      <c r="AB10" s="3">
+      <c r="AC10" s="3">
         <v>204000</v>
       </c>
-      <c r="AC10" s="3">
+      <c r="AD10" s="3">
         <v>148100</v>
       </c>
-      <c r="AD10" s="3">
+      <c r="AE10" s="3">
         <v>200800</v>
       </c>
-      <c r="AE10" s="3">
+      <c r="AF10" s="3">
         <v>168900</v>
       </c>
-      <c r="AF10" s="3">
+      <c r="AG10" s="3">
         <v>166800</v>
       </c>
-      <c r="AG10" s="3">
+      <c r="AH10" s="3">
         <v>106300</v>
       </c>
-      <c r="AH10" s="3">
+      <c r="AI10" s="3">
         <v>168900</v>
       </c>
-      <c r="AI10" s="3">
+      <c r="AJ10" s="3">
         <v>124000</v>
       </c>
     </row>
-    <row r="11" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:36" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -1139,8 +1152,9 @@
       <c r="AG11" s="3"/>
       <c r="AH11" s="3"/>
       <c r="AI11" s="3"/>
+      <c r="AJ11" s="3"/>
     </row>
-    <row r="12" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:36" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
@@ -1240,8 +1254,11 @@
       <c r="AI12" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AJ12" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="13" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:36" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1341,46 +1358,49 @@
       <c r="AI13" s="3">
         <v>0</v>
       </c>
+      <c r="AJ13" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="14" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:36" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3">
-        <v>25800</v>
+        <v>200</v>
       </c>
       <c r="E14" s="3">
-        <v>67400</v>
+        <v>25200</v>
       </c>
       <c r="F14" s="3">
-        <v>600</v>
+        <v>66200</v>
       </c>
       <c r="G14" s="3">
+        <v>11500</v>
+      </c>
+      <c r="H14" s="3">
         <v>-1500</v>
       </c>
-      <c r="H14" s="3">
+      <c r="I14" s="3">
         <v>100</v>
       </c>
-      <c r="I14" s="3" t="s">
+      <c r="J14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="J14" s="3">
+      <c r="K14" s="3">
         <v>-1300</v>
       </c>
-      <c r="K14" s="3">
+      <c r="L14" s="3">
         <v>-4700</v>
-      </c>
-      <c r="L14" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="M14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="N14" s="3">
+      <c r="N14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="O14" s="3">
         <v>-300</v>
-      </c>
-      <c r="O14" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="P14" s="3" t="s">
         <v>8</v>
@@ -1388,12 +1408,12 @@
       <c r="Q14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="R14" s="3">
+      <c r="R14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="S14" s="3">
         <v>-200</v>
       </c>
-      <c r="S14" s="3">
-        <v>0</v>
-      </c>
       <c r="T14" s="3">
         <v>0</v>
       </c>
@@ -1401,22 +1421,22 @@
         <v>0</v>
       </c>
       <c r="V14" s="3">
+        <v>0</v>
+      </c>
+      <c r="W14" s="3">
         <v>9000</v>
       </c>
-      <c r="W14" s="3">
-        <v>0</v>
-      </c>
       <c r="X14" s="3">
         <v>0</v>
       </c>
       <c r="Y14" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z14" s="3">
         <v>100</v>
       </c>
-      <c r="Z14" s="3">
-        <v>0</v>
-      </c>
-      <c r="AA14" s="3" t="s">
-        <v>8</v>
+      <c r="AA14" s="3">
+        <v>0</v>
       </c>
       <c r="AB14" s="3" t="s">
         <v>8</v>
@@ -1424,11 +1444,11 @@
       <c r="AC14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AD14" s="3">
+      <c r="AD14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AE14" s="3">
         <v>4500</v>
-      </c>
-      <c r="AE14" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="AF14" s="3" t="s">
         <v>8</v>
@@ -1442,31 +1462,34 @@
       <c r="AI14" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AJ14" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="15" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:36" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
-        <v>0</v>
+        <v>106200</v>
       </c>
       <c r="E15" s="3">
-        <v>0</v>
+        <v>103900</v>
       </c>
       <c r="F15" s="3">
-        <v>0</v>
+        <v>108900</v>
       </c>
       <c r="G15" s="3">
-        <v>0</v>
+        <v>109900</v>
       </c>
       <c r="H15" s="3">
-        <v>0</v>
+        <v>100200</v>
       </c>
       <c r="I15" s="3">
-        <v>0</v>
+        <v>97200</v>
       </c>
       <c r="J15" s="3">
-        <v>0</v>
+        <v>99900</v>
       </c>
       <c r="K15" s="3">
         <v>0</v>
@@ -1543,8 +1566,11 @@
       <c r="AI15" s="3">
         <v>0</v>
       </c>
+      <c r="AJ15" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="16" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:36" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1577,210 +1603,217 @@
       <c r="AG16" s="3"/>
       <c r="AH16" s="3"/>
       <c r="AI16" s="3"/>
+      <c r="AJ16" s="3"/>
     </row>
-    <row r="17" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="17" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
-        <v>1084600</v>
+        <v>1116700</v>
       </c>
       <c r="E17" s="3">
-        <v>1152000</v>
+        <v>1033600</v>
       </c>
       <c r="F17" s="3">
-        <v>1109400</v>
+        <v>1065500</v>
       </c>
       <c r="G17" s="3">
-        <v>936300</v>
+        <v>1098300</v>
       </c>
       <c r="H17" s="3">
-        <v>967400</v>
+        <v>911700</v>
       </c>
       <c r="I17" s="3">
-        <v>991500</v>
+        <v>946100</v>
       </c>
       <c r="J17" s="3">
+        <v>1023800</v>
+      </c>
+      <c r="K17" s="3">
         <v>1043600</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>930600</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>927400</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>943600</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>986700</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>857200</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>843000</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>838700</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>931200</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>806000</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>700800</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>559100</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>784600</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>603000</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>600600</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>580300</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>620800</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>439900</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3">
         <v>421100</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AD17" s="3">
         <v>408300</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AE17" s="3">
         <v>465300</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AF17" s="3">
         <v>326300</v>
       </c>
-      <c r="AF17" s="3">
+      <c r="AG17" s="3">
         <v>304300</v>
       </c>
-      <c r="AG17" s="3">
+      <c r="AH17" s="3">
         <v>284700</v>
       </c>
-      <c r="AH17" s="3">
+      <c r="AI17" s="3">
         <v>322800</v>
       </c>
-      <c r="AI17" s="3">
+      <c r="AJ17" s="3">
         <v>234400</v>
       </c>
     </row>
-    <row r="18" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
-        <v>427500</v>
+        <v>405100</v>
       </c>
       <c r="E18" s="3">
-        <v>252200</v>
+        <v>442400</v>
       </c>
       <c r="F18" s="3">
-        <v>387800</v>
+        <v>313900</v>
       </c>
       <c r="G18" s="3">
-        <v>343200</v>
+        <v>399300</v>
       </c>
       <c r="H18" s="3">
-        <v>405700</v>
+        <v>332200</v>
       </c>
       <c r="I18" s="3">
-        <v>275000</v>
+        <v>396900</v>
       </c>
       <c r="J18" s="3">
+        <v>283900</v>
+      </c>
+      <c r="K18" s="3">
         <v>348100</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>305200</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>276000</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>155200</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>283300</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>193400</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>209100</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>90900</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>218200</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>172300</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>242600</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>58700</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>269700</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>218500</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>228100</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>115500</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>196500</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>152800</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AC18" s="3">
         <v>166400</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AD18" s="3">
         <v>100200</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AE18" s="3">
         <v>177500</v>
       </c>
-      <c r="AE18" s="3">
+      <c r="AF18" s="3">
         <v>140200</v>
       </c>
-      <c r="AF18" s="3">
+      <c r="AG18" s="3">
         <v>136700</v>
       </c>
-      <c r="AG18" s="3">
+      <c r="AH18" s="3">
         <v>95500</v>
       </c>
-      <c r="AH18" s="3">
+      <c r="AI18" s="3">
         <v>141200</v>
       </c>
-      <c r="AI18" s="3">
+      <c r="AJ18" s="3">
         <v>107800</v>
       </c>
     </row>
-    <row r="19" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1816,267 +1849,274 @@
       <c r="AG19" s="3"/>
       <c r="AH19" s="3"/>
       <c r="AI19" s="3"/>
+      <c r="AJ19" s="3"/>
     </row>
-    <row r="20" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="20" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
-        <v>50500</v>
+        <v>11200</v>
       </c>
       <c r="E20" s="3">
-        <v>41300</v>
+        <v>-10200</v>
       </c>
       <c r="F20" s="3">
-        <v>23700</v>
+        <v>-8900</v>
       </c>
       <c r="G20" s="3">
-        <v>36600</v>
+        <v>6200</v>
       </c>
       <c r="H20" s="3">
-        <v>42300</v>
+        <v>-3300</v>
       </c>
       <c r="I20" s="3">
-        <v>33500</v>
+        <v>-18300</v>
       </c>
       <c r="J20" s="3">
+        <v>-21700</v>
+      </c>
+      <c r="K20" s="3">
         <v>28800</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>23600</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>31200</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>13500</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>9900</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>12600</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>15600</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>13100</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>3200</v>
       </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3">
         <v>4800</v>
       </c>
-      <c r="T20" s="3">
+      <c r="U20" s="3">
         <v>17200</v>
       </c>
-      <c r="U20" s="3">
+      <c r="V20" s="3">
         <v>22500</v>
       </c>
-      <c r="V20" s="3">
+      <c r="W20" s="3">
         <v>137200</v>
       </c>
-      <c r="W20" s="3">
+      <c r="X20" s="3">
         <v>27300</v>
       </c>
-      <c r="X20" s="3">
+      <c r="Y20" s="3">
         <v>25500</v>
       </c>
-      <c r="Y20" s="3">
+      <c r="Z20" s="3">
         <v>18300</v>
       </c>
-      <c r="Z20" s="3">
+      <c r="AA20" s="3">
         <v>21500</v>
       </c>
-      <c r="AA20" s="3">
+      <c r="AB20" s="3">
         <v>24800</v>
       </c>
-      <c r="AB20" s="3">
+      <c r="AC20" s="3">
         <v>91900</v>
       </c>
-      <c r="AC20" s="3">
+      <c r="AD20" s="3">
         <v>3400</v>
       </c>
-      <c r="AD20" s="3">
+      <c r="AE20" s="3">
         <v>5700</v>
       </c>
-      <c r="AE20" s="3">
+      <c r="AF20" s="3">
         <v>2600</v>
       </c>
-      <c r="AF20" s="3">
+      <c r="AG20" s="3">
         <v>5500</v>
       </c>
-      <c r="AG20" s="3">
+      <c r="AH20" s="3">
         <v>3700</v>
       </c>
-      <c r="AH20" s="3">
+      <c r="AI20" s="3">
         <v>3500</v>
       </c>
-      <c r="AI20" s="3">
+      <c r="AJ20" s="3">
         <v>1400</v>
       </c>
     </row>
-    <row r="21" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
-        <v>473700</v>
+        <v>500100</v>
       </c>
       <c r="E21" s="3">
-        <v>404300</v>
+        <v>556600</v>
       </c>
       <c r="F21" s="3">
-        <v>409800</v>
+        <v>431700</v>
       </c>
       <c r="G21" s="3">
-        <v>385400</v>
+        <v>503100</v>
       </c>
       <c r="H21" s="3">
-        <v>450600</v>
+        <v>435600</v>
       </c>
       <c r="I21" s="3">
-        <v>405200</v>
+        <v>512500</v>
       </c>
       <c r="J21" s="3">
+        <v>405600</v>
+      </c>
+      <c r="K21" s="3">
         <v>381000</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>327900</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>312700</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>256700</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>300500</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>202200</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>231000</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>178800</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>227200</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>184900</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>262500</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>145600</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>418900</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>246500</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3">
         <v>255900</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="Z21" s="3">
         <v>176900</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AA21" s="3">
         <v>223700</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AB21" s="3">
         <v>179800</v>
       </c>
-      <c r="AB21" s="3">
+      <c r="AC21" s="3">
         <v>259900</v>
       </c>
-      <c r="AC21" s="3">
+      <c r="AD21" s="3">
         <v>130400</v>
       </c>
-      <c r="AD21" s="3">
+      <c r="AE21" s="3">
         <v>183000</v>
       </c>
-      <c r="AE21" s="3">
+      <c r="AF21" s="3">
         <v>144500</v>
       </c>
-      <c r="AF21" s="3">
+      <c r="AG21" s="3">
         <v>143100</v>
       </c>
-      <c r="AG21" s="3">
+      <c r="AH21" s="3">
         <v>118100</v>
       </c>
-      <c r="AH21" s="3">
+      <c r="AI21" s="3">
         <v>178100</v>
       </c>
-      <c r="AI21" s="3">
+      <c r="AJ21" s="3">
         <v>105200</v>
       </c>
     </row>
-    <row r="22" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
-        <v>16300</v>
+        <v>9500</v>
       </c>
       <c r="E22" s="3">
-        <v>11800</v>
+        <v>15900</v>
       </c>
       <c r="F22" s="3">
+        <v>11600</v>
+      </c>
+      <c r="G22" s="3">
         <v>8700</v>
       </c>
-      <c r="G22" s="3">
-        <v>11800</v>
-      </c>
       <c r="H22" s="3">
-        <v>10200</v>
+        <v>11500</v>
       </c>
       <c r="I22" s="3">
-        <v>10100</v>
+        <v>10000</v>
       </c>
       <c r="J22" s="3">
+        <v>10400</v>
+      </c>
+      <c r="K22" s="3">
         <v>10700</v>
       </c>
-      <c r="K22" s="3">
+      <c r="L22" s="3">
         <v>4400</v>
       </c>
-      <c r="L22" s="3">
+      <c r="M22" s="3">
         <v>3200</v>
       </c>
-      <c r="M22" s="3">
+      <c r="N22" s="3">
         <v>8300</v>
       </c>
-      <c r="N22" s="3">
+      <c r="O22" s="3">
         <v>3400</v>
       </c>
-      <c r="O22" s="3">
+      <c r="P22" s="3">
         <v>7400</v>
       </c>
-      <c r="P22" s="3">
+      <c r="Q22" s="3">
         <v>4900</v>
       </c>
-      <c r="Q22" s="3">
+      <c r="R22" s="3">
         <v>2200</v>
       </c>
-      <c r="R22" s="3">
+      <c r="S22" s="3">
         <v>1700</v>
       </c>
-      <c r="S22" s="3">
+      <c r="T22" s="3">
         <v>2000</v>
       </c>
-      <c r="T22" s="3">
+      <c r="U22" s="3">
         <v>1300</v>
       </c>
-      <c r="U22" s="3">
-        <v>0</v>
-      </c>
       <c r="V22" s="3">
         <v>0</v>
       </c>
@@ -2099,230 +2139,239 @@
         <v>0</v>
       </c>
       <c r="AC22" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD22" s="3">
         <v>100</v>
-      </c>
-      <c r="AD22" s="3">
-        <v>400</v>
       </c>
       <c r="AE22" s="3">
         <v>400</v>
       </c>
       <c r="AF22" s="3">
+        <v>400</v>
+      </c>
+      <c r="AG22" s="3">
         <v>700</v>
       </c>
-      <c r="AG22" s="3">
+      <c r="AH22" s="3">
         <v>800</v>
       </c>
-      <c r="AH22" s="3">
+      <c r="AI22" s="3">
         <v>100</v>
       </c>
-      <c r="AI22" s="3">
+      <c r="AJ22" s="3">
         <v>500</v>
       </c>
     </row>
-    <row r="23" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
-        <v>461700</v>
+        <v>418300</v>
       </c>
       <c r="E23" s="3">
-        <v>281700</v>
+        <v>451200</v>
       </c>
       <c r="F23" s="3">
-        <v>402800</v>
+        <v>278900</v>
       </c>
       <c r="G23" s="3">
-        <v>368000</v>
+        <v>401400</v>
       </c>
       <c r="H23" s="3">
-        <v>437800</v>
+        <v>359200</v>
       </c>
       <c r="I23" s="3">
-        <v>298300</v>
+        <v>428300</v>
       </c>
       <c r="J23" s="3">
+        <v>308600</v>
+      </c>
+      <c r="K23" s="3">
         <v>366100</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>324400</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>304100</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>160400</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>289800</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>198600</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>219900</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>101700</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>219700</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>175000</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>258500</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>81200</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>406900</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>245800</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>253500</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>133900</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>218000</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>177600</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>258300</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AD23" s="3">
         <v>103500</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AE23" s="3">
         <v>182800</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AF23" s="3">
         <v>142500</v>
       </c>
-      <c r="AF23" s="3">
+      <c r="AG23" s="3">
         <v>141400</v>
       </c>
-      <c r="AG23" s="3">
+      <c r="AH23" s="3">
         <v>98400</v>
       </c>
-      <c r="AH23" s="3">
+      <c r="AI23" s="3">
         <v>144600</v>
       </c>
-      <c r="AI23" s="3">
+      <c r="AJ23" s="3">
         <v>108700</v>
       </c>
     </row>
-    <row r="24" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
-        <v>93800</v>
+        <v>79100</v>
       </c>
       <c r="E24" s="3">
-        <v>79800</v>
+        <v>91500</v>
       </c>
       <c r="F24" s="3">
+        <v>78400</v>
+      </c>
+      <c r="G24" s="3">
         <v>89800</v>
       </c>
-      <c r="G24" s="3">
-        <v>38300</v>
-      </c>
       <c r="H24" s="3">
-        <v>81100</v>
+        <v>37200</v>
       </c>
       <c r="I24" s="3">
-        <v>64100</v>
+        <v>79400</v>
       </c>
       <c r="J24" s="3">
+        <v>66200</v>
+      </c>
+      <c r="K24" s="3">
         <v>70600</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>60700</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>60900</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>35500</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>51200</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>32600</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>36600</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>21500</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>40300</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>-4100</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>44000</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>20500</v>
       </c>
-      <c r="V24" s="3">
+      <c r="W24" s="3">
         <v>51000</v>
       </c>
-      <c r="W24" s="3">
+      <c r="X24" s="3">
         <v>41500</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Y24" s="3">
         <v>44100</v>
       </c>
-      <c r="Y24" s="3">
+      <c r="Z24" s="3">
         <v>29200</v>
       </c>
-      <c r="Z24" s="3">
+      <c r="AA24" s="3">
         <v>32300</v>
       </c>
-      <c r="AA24" s="3">
+      <c r="AB24" s="3">
         <v>28200</v>
       </c>
-      <c r="AB24" s="3">
+      <c r="AC24" s="3">
         <v>49100</v>
       </c>
-      <c r="AC24" s="3">
+      <c r="AD24" s="3">
         <v>22100</v>
       </c>
-      <c r="AD24" s="3">
+      <c r="AE24" s="3">
         <v>1300</v>
       </c>
-      <c r="AE24" s="3">
+      <c r="AF24" s="3">
         <v>35300</v>
       </c>
-      <c r="AF24" s="3">
+      <c r="AG24" s="3">
         <v>34600</v>
       </c>
-      <c r="AG24" s="3">
+      <c r="AH24" s="3">
         <v>24200</v>
       </c>
-      <c r="AH24" s="3">
+      <c r="AI24" s="3">
         <v>36600</v>
       </c>
-      <c r="AI24" s="3">
+      <c r="AJ24" s="3">
         <v>27100</v>
       </c>
     </row>
-    <row r="25" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2422,210 +2471,219 @@
       <c r="AI25" s="3">
         <v>0</v>
       </c>
+      <c r="AJ25" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="26" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="26" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
-        <v>367900</v>
+        <v>339200</v>
       </c>
       <c r="E26" s="3">
-        <v>201800</v>
+        <v>359700</v>
       </c>
       <c r="F26" s="3">
-        <v>313000</v>
+        <v>200500</v>
       </c>
       <c r="G26" s="3">
-        <v>329700</v>
+        <v>311600</v>
       </c>
       <c r="H26" s="3">
-        <v>356700</v>
+        <v>322000</v>
       </c>
       <c r="I26" s="3">
-        <v>234200</v>
+        <v>348900</v>
       </c>
       <c r="J26" s="3">
+        <v>242400</v>
+      </c>
+      <c r="K26" s="3">
         <v>295600</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>263700</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>243100</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>124900</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>238600</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>166000</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>183300</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>80200</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>179400</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>179100</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>214600</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>60700</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>355800</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>204200</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>209400</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>104700</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>185700</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>149400</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AC26" s="3">
         <v>209100</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AD26" s="3">
         <v>81300</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AE26" s="3">
         <v>181500</v>
       </c>
-      <c r="AE26" s="3">
+      <c r="AF26" s="3">
         <v>107200</v>
       </c>
-      <c r="AF26" s="3">
+      <c r="AG26" s="3">
         <v>106800</v>
       </c>
-      <c r="AG26" s="3">
+      <c r="AH26" s="3">
         <v>74200</v>
       </c>
-      <c r="AH26" s="3">
+      <c r="AI26" s="3">
         <v>108000</v>
       </c>
-      <c r="AI26" s="3">
+      <c r="AJ26" s="3">
         <v>81600</v>
       </c>
     </row>
-    <row r="27" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
-        <v>368200</v>
+        <v>341600</v>
       </c>
       <c r="E27" s="3">
-        <v>201000</v>
+        <v>359400</v>
       </c>
       <c r="F27" s="3">
-        <v>309100</v>
+        <v>197500</v>
       </c>
       <c r="G27" s="3">
-        <v>330600</v>
+        <v>309200</v>
       </c>
       <c r="H27" s="3">
-        <v>358300</v>
+        <v>321400</v>
       </c>
       <c r="I27" s="3">
-        <v>235500</v>
+        <v>350400</v>
       </c>
       <c r="J27" s="3">
+        <v>243200</v>
+      </c>
+      <c r="K27" s="3">
         <v>304900</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>267300</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>251000</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>126000</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>242800</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>165800</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>185600</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>76600</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>179300</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>177000</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>213400</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>59100</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>358200</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>204000</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>207700</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>103600</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>185200</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>148300</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AC27" s="3">
         <v>208700</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AD27" s="3">
         <v>79900</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AE27" s="3">
         <v>181400</v>
-      </c>
-      <c r="AE27" s="3">
-        <v>106400</v>
       </c>
       <c r="AF27" s="3">
         <v>106400</v>
       </c>
       <c r="AG27" s="3">
+        <v>106400</v>
+      </c>
+      <c r="AH27" s="3">
         <v>73200</v>
       </c>
-      <c r="AH27" s="3">
+      <c r="AI27" s="3">
         <v>105700</v>
       </c>
-      <c r="AI27" s="3">
+      <c r="AJ27" s="3">
         <v>73700</v>
       </c>
     </row>
-    <row r="28" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2725,8 +2783,11 @@
       <c r="AI28" s="3">
         <v>0</v>
       </c>
+      <c r="AJ28" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="29" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="29" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2826,8 +2887,11 @@
       <c r="AI29" s="3">
         <v>0</v>
       </c>
+      <c r="AJ29" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="30" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="30" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2927,8 +2991,11 @@
       <c r="AI30" s="3">
         <v>0</v>
       </c>
+      <c r="AJ30" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="31" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="31" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -3028,210 +3095,219 @@
       <c r="AI31" s="3">
         <v>0</v>
       </c>
+      <c r="AJ31" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="32" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="32" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
-        <v>-50500</v>
+        <v>-11200</v>
       </c>
       <c r="E32" s="3">
-        <v>-41300</v>
+        <v>10200</v>
       </c>
       <c r="F32" s="3">
-        <v>-23700</v>
+        <v>8900</v>
       </c>
       <c r="G32" s="3">
-        <v>-36600</v>
+        <v>-6200</v>
       </c>
       <c r="H32" s="3">
-        <v>-42300</v>
+        <v>3300</v>
       </c>
       <c r="I32" s="3">
-        <v>-33500</v>
+        <v>18300</v>
       </c>
       <c r="J32" s="3">
+        <v>21700</v>
+      </c>
+      <c r="K32" s="3">
         <v>-28800</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>-23600</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>-31200</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>-13500</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>-9900</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>-12600</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>-15600</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>-13100</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>-3200</v>
       </c>
-      <c r="S32" s="3">
+      <c r="T32" s="3">
         <v>-4800</v>
       </c>
-      <c r="T32" s="3">
+      <c r="U32" s="3">
         <v>-17200</v>
       </c>
-      <c r="U32" s="3">
+      <c r="V32" s="3">
         <v>-22500</v>
       </c>
-      <c r="V32" s="3">
+      <c r="W32" s="3">
         <v>-137200</v>
       </c>
-      <c r="W32" s="3">
+      <c r="X32" s="3">
         <v>-27300</v>
       </c>
-      <c r="X32" s="3">
+      <c r="Y32" s="3">
         <v>-25500</v>
       </c>
-      <c r="Y32" s="3">
+      <c r="Z32" s="3">
         <v>-18300</v>
       </c>
-      <c r="Z32" s="3">
+      <c r="AA32" s="3">
         <v>-21500</v>
       </c>
-      <c r="AA32" s="3">
+      <c r="AB32" s="3">
         <v>-24800</v>
       </c>
-      <c r="AB32" s="3">
+      <c r="AC32" s="3">
         <v>-91900</v>
       </c>
-      <c r="AC32" s="3">
+      <c r="AD32" s="3">
         <v>-3400</v>
       </c>
-      <c r="AD32" s="3">
+      <c r="AE32" s="3">
         <v>-5700</v>
       </c>
-      <c r="AE32" s="3">
+      <c r="AF32" s="3">
         <v>-2600</v>
       </c>
-      <c r="AF32" s="3">
+      <c r="AG32" s="3">
         <v>-5500</v>
       </c>
-      <c r="AG32" s="3">
+      <c r="AH32" s="3">
         <v>-3700</v>
       </c>
-      <c r="AH32" s="3">
+      <c r="AI32" s="3">
         <v>-3500</v>
       </c>
-      <c r="AI32" s="3">
+      <c r="AJ32" s="3">
         <v>-1400</v>
       </c>
     </row>
-    <row r="33" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
-        <v>368200</v>
+        <v>341600</v>
       </c>
       <c r="E33" s="3">
-        <v>201000</v>
+        <v>359400</v>
       </c>
       <c r="F33" s="3">
-        <v>309100</v>
+        <v>197500</v>
       </c>
       <c r="G33" s="3">
-        <v>330600</v>
+        <v>309200</v>
       </c>
       <c r="H33" s="3">
-        <v>358300</v>
+        <v>321400</v>
       </c>
       <c r="I33" s="3">
-        <v>235500</v>
+        <v>350400</v>
       </c>
       <c r="J33" s="3">
+        <v>243200</v>
+      </c>
+      <c r="K33" s="3">
         <v>304900</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>267300</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>251000</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>126000</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>242800</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>165800</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>185600</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>76600</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>179300</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>177000</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>213400</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>59100</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>358200</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>204000</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>207700</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>103600</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>185200</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>148300</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AC33" s="3">
         <v>208700</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AD33" s="3">
         <v>79900</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AE33" s="3">
         <v>181400</v>
-      </c>
-      <c r="AE33" s="3">
-        <v>106400</v>
       </c>
       <c r="AF33" s="3">
         <v>106400</v>
       </c>
       <c r="AG33" s="3">
+        <v>106400</v>
+      </c>
+      <c r="AH33" s="3">
         <v>73200</v>
       </c>
-      <c r="AH33" s="3">
+      <c r="AI33" s="3">
         <v>105700</v>
       </c>
-      <c r="AI33" s="3">
+      <c r="AJ33" s="3">
         <v>73700</v>
       </c>
     </row>
-    <row r="34" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3331,215 +3407,224 @@
       <c r="AI34" s="3">
         <v>0</v>
       </c>
+      <c r="AJ34" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="35" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="35" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
-        <v>368200</v>
+        <v>341600</v>
       </c>
       <c r="E35" s="3">
-        <v>201000</v>
+        <v>359400</v>
       </c>
       <c r="F35" s="3">
-        <v>309100</v>
+        <v>197500</v>
       </c>
       <c r="G35" s="3">
-        <v>330600</v>
+        <v>309200</v>
       </c>
       <c r="H35" s="3">
-        <v>358300</v>
+        <v>321400</v>
       </c>
       <c r="I35" s="3">
-        <v>235500</v>
+        <v>350400</v>
       </c>
       <c r="J35" s="3">
+        <v>243200</v>
+      </c>
+      <c r="K35" s="3">
         <v>304900</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>267300</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>251000</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>126000</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>242800</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>165800</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>185600</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>76600</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>179300</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>177000</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>213400</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>59100</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>358200</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>204000</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>207700</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>103600</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>185200</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>148300</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AC35" s="3">
         <v>208700</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AD35" s="3">
         <v>79900</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AE35" s="3">
         <v>181400</v>
-      </c>
-      <c r="AE35" s="3">
-        <v>106400</v>
       </c>
       <c r="AF35" s="3">
         <v>106400</v>
       </c>
       <c r="AG35" s="3">
+        <v>106400</v>
+      </c>
+      <c r="AH35" s="3">
         <v>73200</v>
       </c>
-      <c r="AH35" s="3">
+      <c r="AI35" s="3">
         <v>105700</v>
       </c>
-      <c r="AI35" s="3">
+      <c r="AJ35" s="3">
         <v>73700</v>
       </c>
     </row>
-    <row r="37" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:36" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45565</v>
+      </c>
+      <c r="E38" s="2">
         <v>45473</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45382</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45291</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45199</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45107</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45016</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>44926</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44834</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44742</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44651</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44561</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44469</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44377</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44286</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44196</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44104</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44012</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>43921</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>43830</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>43738</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>43646</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>43555</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>43465</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>43373</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43281</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>43190</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>43100</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AF38" s="2">
         <v>43008</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AG38" s="2">
         <v>42916</v>
       </c>
-      <c r="AG38" s="2">
+      <c r="AH38" s="2">
         <v>42825</v>
       </c>
-      <c r="AH38" s="2">
+      <c r="AI38" s="2">
         <v>42735</v>
       </c>
-      <c r="AI38" s="2">
+      <c r="AJ38" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="39" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3575,8 +3660,9 @@
       <c r="AG39" s="3"/>
       <c r="AH39" s="3"/>
       <c r="AI39" s="3"/>
+      <c r="AJ39" s="3"/>
     </row>
-    <row r="40" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="40" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3612,355 +3698,365 @@
       <c r="AG40" s="3"/>
       <c r="AH40" s="3"/>
       <c r="AI40" s="3"/>
+      <c r="AJ40" s="3"/>
     </row>
-    <row r="41" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="41" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
-        <v>1486200</v>
+        <v>1668400</v>
       </c>
       <c r="E41" s="3">
-        <v>1774100</v>
+        <v>1450700</v>
       </c>
       <c r="F41" s="3">
-        <v>1738800</v>
+        <v>1742800</v>
       </c>
       <c r="G41" s="3">
-        <v>1308900</v>
+        <v>1739400</v>
       </c>
       <c r="H41" s="3">
-        <v>1097000</v>
+        <v>1272500</v>
       </c>
       <c r="I41" s="3">
-        <v>1347200</v>
+        <v>1073000</v>
       </c>
       <c r="J41" s="3">
+        <v>1391100</v>
+      </c>
+      <c r="K41" s="3">
         <v>1648400</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>2016100</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>1380200</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>1376400</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>1339400</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>1472400</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>1737600</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>1590500</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>1978400</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>2418000</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>775400</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>792000</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>811500</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>789200</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>1086500</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>926800</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AA41" s="3">
         <v>671300</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AB41" s="3">
         <v>877700</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AC41" s="3">
         <v>848700</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AD41" s="3">
         <v>486000</v>
       </c>
-      <c r="AD41" s="3">
+      <c r="AE41" s="3">
         <v>805100</v>
       </c>
-      <c r="AE41" s="3">
+      <c r="AF41" s="3">
         <v>768800</v>
       </c>
-      <c r="AF41" s="3">
+      <c r="AG41" s="3">
         <v>848000</v>
       </c>
-      <c r="AG41" s="3">
+      <c r="AH41" s="3">
         <v>920400</v>
       </c>
-      <c r="AH41" s="3">
+      <c r="AI41" s="3">
         <v>1641600</v>
       </c>
-      <c r="AI41" s="3">
+      <c r="AJ41" s="3">
         <v>287600</v>
       </c>
     </row>
-    <row r="42" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
-        <v>1395500</v>
+        <v>1598600</v>
       </c>
       <c r="E42" s="3">
-        <v>992300</v>
+        <v>1362200</v>
       </c>
       <c r="F42" s="3">
-        <v>1051000</v>
+        <v>974800</v>
       </c>
       <c r="G42" s="3">
-        <v>1078900</v>
+        <v>1066000</v>
       </c>
       <c r="H42" s="3">
-        <v>1121700</v>
+        <v>1048900</v>
       </c>
       <c r="I42" s="3">
-        <v>1251700</v>
+        <v>1097100</v>
       </c>
       <c r="J42" s="3">
+        <v>1292500</v>
+      </c>
+      <c r="K42" s="3">
         <v>811100</v>
       </c>
-      <c r="K42" s="3">
+      <c r="L42" s="3">
         <v>960600</v>
       </c>
-      <c r="L42" s="3">
+      <c r="M42" s="3">
         <v>724400</v>
       </c>
-      <c r="M42" s="3">
+      <c r="N42" s="3">
         <v>556400</v>
       </c>
-      <c r="N42" s="3">
+      <c r="O42" s="3">
         <v>392000</v>
       </c>
-      <c r="O42" s="3">
+      <c r="P42" s="3">
         <v>336100</v>
       </c>
-      <c r="P42" s="3">
+      <c r="Q42" s="3">
         <v>450800</v>
       </c>
-      <c r="Q42" s="3">
+      <c r="R42" s="3">
         <v>794000</v>
       </c>
-      <c r="R42" s="3">
+      <c r="S42" s="3">
         <v>513700</v>
       </c>
-      <c r="S42" s="3">
+      <c r="T42" s="3">
         <v>708000</v>
       </c>
-      <c r="T42" s="3">
+      <c r="U42" s="3">
         <v>1243400</v>
       </c>
-      <c r="U42" s="3">
+      <c r="V42" s="3">
         <v>1596100</v>
       </c>
-      <c r="V42" s="3">
+      <c r="W42" s="3">
         <v>1711200</v>
       </c>
-      <c r="W42" s="3">
+      <c r="X42" s="3">
         <v>1763500</v>
       </c>
-      <c r="X42" s="3">
+      <c r="Y42" s="3">
         <v>1414900</v>
       </c>
-      <c r="Y42" s="3">
+      <c r="Z42" s="3">
         <v>1717000</v>
       </c>
-      <c r="Z42" s="3">
+      <c r="AA42" s="3">
         <v>1975100</v>
       </c>
-      <c r="AA42" s="3">
+      <c r="AB42" s="3">
         <v>1664900</v>
       </c>
-      <c r="AB42" s="3">
+      <c r="AC42" s="3">
         <v>1343800</v>
       </c>
-      <c r="AC42" s="3">
+      <c r="AD42" s="3">
         <v>795600</v>
       </c>
-      <c r="AD42" s="3">
+      <c r="AE42" s="3">
         <v>775400</v>
       </c>
-      <c r="AE42" s="3">
+      <c r="AF42" s="3">
         <v>819600</v>
       </c>
-      <c r="AF42" s="3">
+      <c r="AG42" s="3">
         <v>769700</v>
       </c>
-      <c r="AG42" s="3">
+      <c r="AH42" s="3">
         <v>700700</v>
-      </c>
-      <c r="AH42" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="AI42" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AJ42" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="43" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
-        <v>271900</v>
+        <v>307200</v>
       </c>
       <c r="E43" s="3">
-        <v>245400</v>
+        <v>265400</v>
       </c>
       <c r="F43" s="3">
-        <v>261700</v>
+        <v>241100</v>
       </c>
       <c r="G43" s="3">
-        <v>339000</v>
+        <v>280800</v>
       </c>
       <c r="H43" s="3">
-        <v>326900</v>
+        <v>329600</v>
       </c>
       <c r="I43" s="3">
-        <v>258400</v>
+        <v>319700</v>
       </c>
       <c r="J43" s="3">
+        <v>266800</v>
+      </c>
+      <c r="K43" s="3">
         <v>293900</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>265800</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>267700</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>264100</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>300200</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>260500</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>262000</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>187900</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>182600</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>252900</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>174200</v>
       </c>
-      <c r="U43" s="3">
+      <c r="V43" s="3">
         <v>210600</v>
       </c>
-      <c r="V43" s="3">
+      <c r="W43" s="3">
         <v>194200</v>
       </c>
-      <c r="W43" s="3">
+      <c r="X43" s="3">
         <v>172000</v>
       </c>
-      <c r="X43" s="3">
+      <c r="Y43" s="3">
         <v>177300</v>
       </c>
-      <c r="Y43" s="3">
+      <c r="Z43" s="3">
         <v>171100</v>
       </c>
-      <c r="Z43" s="3">
+      <c r="AA43" s="3">
         <v>162900</v>
       </c>
-      <c r="AA43" s="3">
+      <c r="AB43" s="3">
         <v>120200</v>
       </c>
-      <c r="AB43" s="3">
+      <c r="AC43" s="3">
         <v>209200</v>
       </c>
-      <c r="AC43" s="3">
+      <c r="AD43" s="3">
         <v>69200</v>
       </c>
-      <c r="AD43" s="3">
+      <c r="AE43" s="3">
         <v>53700</v>
       </c>
-      <c r="AE43" s="3">
+      <c r="AF43" s="3">
         <v>31000</v>
       </c>
-      <c r="AF43" s="3">
+      <c r="AG43" s="3">
         <v>28800</v>
       </c>
-      <c r="AG43" s="3">
+      <c r="AH43" s="3">
         <v>25200</v>
       </c>
-      <c r="AH43" s="3">
+      <c r="AI43" s="3">
         <v>29600</v>
       </c>
-      <c r="AI43" s="3">
+      <c r="AJ43" s="3">
         <v>17800</v>
       </c>
     </row>
-    <row r="44" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>3900</v>
+      </c>
+      <c r="E44" s="3">
+        <v>3900</v>
+      </c>
+      <c r="F44" s="3">
+        <v>5700</v>
+      </c>
+      <c r="G44" s="3">
         <v>4000</v>
-      </c>
-      <c r="E44" s="3">
-        <v>5800</v>
-      </c>
-      <c r="F44" s="3">
-        <v>4000</v>
-      </c>
-      <c r="G44" s="3">
-        <v>3900</v>
       </c>
       <c r="H44" s="3">
         <v>3800</v>
       </c>
       <c r="I44" s="3">
-        <v>4100</v>
+        <v>3700</v>
       </c>
       <c r="J44" s="3">
+        <v>4200</v>
+      </c>
+      <c r="K44" s="3">
         <v>5700</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>8900</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>4000</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>8200</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>11400</v>
       </c>
-      <c r="O44" s="3">
+      <c r="P44" s="3">
         <v>7100</v>
       </c>
-      <c r="P44" s="3">
+      <c r="Q44" s="3">
         <v>5700</v>
-      </c>
-      <c r="Q44" s="3">
-        <v>7400</v>
       </c>
       <c r="R44" s="3">
         <v>7400</v>
@@ -3969,560 +4065,578 @@
         <v>7400</v>
       </c>
       <c r="T44" s="3">
+        <v>7400</v>
+      </c>
+      <c r="U44" s="3">
         <v>9500</v>
       </c>
-      <c r="U44" s="3">
+      <c r="V44" s="3">
         <v>8900</v>
       </c>
-      <c r="V44" s="3">
+      <c r="W44" s="3">
         <v>6800</v>
       </c>
-      <c r="W44" s="3">
+      <c r="X44" s="3">
         <v>5600</v>
       </c>
-      <c r="X44" s="3">
+      <c r="Y44" s="3">
         <v>5400</v>
       </c>
-      <c r="Y44" s="3">
+      <c r="Z44" s="3">
         <v>4700</v>
       </c>
-      <c r="Z44" s="3">
+      <c r="AA44" s="3">
         <v>6400</v>
       </c>
-      <c r="AA44" s="3">
+      <c r="AB44" s="3">
         <v>5200</v>
       </c>
-      <c r="AB44" s="3">
+      <c r="AC44" s="3">
         <v>5600</v>
       </c>
-      <c r="AC44" s="3">
+      <c r="AD44" s="3">
         <v>4400</v>
       </c>
-      <c r="AD44" s="3">
+      <c r="AE44" s="3">
         <v>5100</v>
       </c>
-      <c r="AE44" s="3">
+      <c r="AF44" s="3">
         <v>4200</v>
       </c>
-      <c r="AF44" s="3">
+      <c r="AG44" s="3">
         <v>4300</v>
       </c>
-      <c r="AG44" s="3">
+      <c r="AH44" s="3">
         <v>4600</v>
       </c>
-      <c r="AH44" s="3">
+      <c r="AI44" s="3">
         <v>4900</v>
       </c>
-      <c r="AI44" s="3">
+      <c r="AJ44" s="3">
         <v>4100</v>
       </c>
     </row>
-    <row r="45" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
-        <v>781000</v>
+        <v>716400</v>
       </c>
       <c r="E45" s="3">
-        <v>752100</v>
+        <v>759300</v>
       </c>
       <c r="F45" s="3">
-        <v>744500</v>
+        <v>701200</v>
       </c>
       <c r="G45" s="3">
-        <v>755300</v>
+        <v>599700</v>
       </c>
       <c r="H45" s="3">
-        <v>740500</v>
+        <v>625500</v>
       </c>
       <c r="I45" s="3">
-        <v>703200</v>
+        <v>606800</v>
       </c>
       <c r="J45" s="3">
+        <v>620000</v>
+      </c>
+      <c r="K45" s="3">
         <v>691300</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>584100</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>567700</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>580200</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>528800</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>552300</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>501800</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>511200</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>425500</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>433900</v>
       </c>
-      <c r="T45" s="3">
+      <c r="U45" s="3">
         <v>423200</v>
       </c>
-      <c r="U45" s="3">
+      <c r="V45" s="3">
         <v>378400</v>
       </c>
-      <c r="V45" s="3">
+      <c r="W45" s="3">
         <v>371100</v>
       </c>
-      <c r="W45" s="3">
+      <c r="X45" s="3">
         <v>313400</v>
       </c>
-      <c r="X45" s="3">
+      <c r="Y45" s="3">
         <v>374900</v>
       </c>
-      <c r="Y45" s="3">
+      <c r="Z45" s="3">
         <v>264700</v>
       </c>
-      <c r="Z45" s="3">
+      <c r="AA45" s="3">
         <v>268100</v>
       </c>
-      <c r="AA45" s="3">
+      <c r="AB45" s="3">
         <v>213400</v>
       </c>
-      <c r="AB45" s="3">
+      <c r="AC45" s="3">
         <v>191900</v>
       </c>
-      <c r="AC45" s="3">
+      <c r="AD45" s="3">
         <v>168000</v>
       </c>
-      <c r="AD45" s="3">
+      <c r="AE45" s="3">
         <v>197700</v>
       </c>
-      <c r="AE45" s="3">
+      <c r="AF45" s="3">
         <v>172000</v>
       </c>
-      <c r="AF45" s="3">
+      <c r="AG45" s="3">
         <v>168000</v>
       </c>
-      <c r="AG45" s="3">
+      <c r="AH45" s="3">
         <v>226600</v>
       </c>
-      <c r="AH45" s="3">
+      <c r="AI45" s="3">
         <v>241600</v>
       </c>
-      <c r="AI45" s="3">
+      <c r="AJ45" s="3">
         <v>149500</v>
       </c>
     </row>
-    <row r="46" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
-        <v>3938600</v>
+        <v>4299200</v>
       </c>
       <c r="E46" s="3">
-        <v>3769700</v>
+        <v>3844500</v>
       </c>
       <c r="F46" s="3">
-        <v>3799900</v>
+        <v>3703300</v>
       </c>
       <c r="G46" s="3">
-        <v>3486000</v>
+        <v>3801100</v>
       </c>
       <c r="H46" s="3">
-        <v>3289900</v>
+        <v>3388900</v>
       </c>
       <c r="I46" s="3">
-        <v>3564500</v>
+        <v>3217700</v>
       </c>
       <c r="J46" s="3">
+        <v>3680800</v>
+      </c>
+      <c r="K46" s="3">
         <v>3450500</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>3835500</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>2944100</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>2785400</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>2571900</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>2628500</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>2957900</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>3091000</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>3107600</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>3820200</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>2625600</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>2986000</v>
       </c>
-      <c r="V46" s="3">
+      <c r="W46" s="3">
         <v>3094700</v>
       </c>
-      <c r="W46" s="3">
+      <c r="X46" s="3">
         <v>3043800</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Y46" s="3">
         <v>3059000</v>
       </c>
-      <c r="Y46" s="3">
+      <c r="Z46" s="3">
         <v>3084200</v>
       </c>
-      <c r="Z46" s="3">
+      <c r="AA46" s="3">
         <v>3083800</v>
       </c>
-      <c r="AA46" s="3">
+      <c r="AB46" s="3">
         <v>2881400</v>
       </c>
-      <c r="AB46" s="3">
+      <c r="AC46" s="3">
         <v>2599300</v>
       </c>
-      <c r="AC46" s="3">
+      <c r="AD46" s="3">
         <v>1523100</v>
       </c>
-      <c r="AD46" s="3">
+      <c r="AE46" s="3">
         <v>1837000</v>
       </c>
-      <c r="AE46" s="3">
+      <c r="AF46" s="3">
         <v>1795600</v>
       </c>
-      <c r="AF46" s="3">
+      <c r="AG46" s="3">
         <v>1818900</v>
       </c>
-      <c r="AG46" s="3">
+      <c r="AH46" s="3">
         <v>1877500</v>
       </c>
-      <c r="AH46" s="3">
+      <c r="AI46" s="3">
         <v>1917600</v>
       </c>
-      <c r="AI46" s="3">
+      <c r="AJ46" s="3">
         <v>459000</v>
       </c>
     </row>
-    <row r="47" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
-        <v>2487600</v>
+        <v>2224700</v>
       </c>
       <c r="E47" s="3">
-        <v>2535400</v>
+        <v>2219600</v>
       </c>
       <c r="F47" s="3">
-        <v>2421300</v>
+        <v>2270700</v>
       </c>
       <c r="G47" s="3">
-        <v>2651200</v>
+        <v>2203700</v>
       </c>
       <c r="H47" s="3">
-        <v>2230400</v>
+        <v>2439100</v>
       </c>
       <c r="I47" s="3">
-        <v>1914000</v>
+        <v>2055100</v>
       </c>
       <c r="J47" s="3">
+        <v>1759700</v>
+      </c>
+      <c r="K47" s="3">
         <v>1853300</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>1337100</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>1167900</v>
       </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3">
         <v>1019900</v>
       </c>
-      <c r="N47" s="3">
+      <c r="O47" s="3">
         <v>960200</v>
       </c>
-      <c r="O47" s="3">
+      <c r="P47" s="3">
         <v>996500</v>
       </c>
-      <c r="P47" s="3">
+      <c r="Q47" s="3">
         <v>1076500</v>
       </c>
-      <c r="Q47" s="3">
+      <c r="R47" s="3">
         <v>1100900</v>
       </c>
-      <c r="R47" s="3">
+      <c r="S47" s="3">
         <v>1049100</v>
       </c>
-      <c r="S47" s="3">
+      <c r="T47" s="3">
         <v>898800</v>
       </c>
-      <c r="T47" s="3">
+      <c r="U47" s="3">
         <v>876900</v>
       </c>
-      <c r="U47" s="3">
+      <c r="V47" s="3">
         <v>771500</v>
       </c>
-      <c r="V47" s="3">
+      <c r="W47" s="3">
         <v>709100</v>
       </c>
-      <c r="W47" s="3">
+      <c r="X47" s="3">
         <v>347600</v>
       </c>
-      <c r="X47" s="3">
+      <c r="Y47" s="3">
         <v>336200</v>
       </c>
-      <c r="Y47" s="3">
+      <c r="Z47" s="3">
         <v>332500</v>
       </c>
-      <c r="Z47" s="3">
+      <c r="AA47" s="3">
         <v>320600</v>
       </c>
-      <c r="AA47" s="3">
+      <c r="AB47" s="3">
         <v>239300</v>
       </c>
-      <c r="AB47" s="3">
+      <c r="AC47" s="3">
         <v>215800</v>
       </c>
-      <c r="AC47" s="3">
+      <c r="AD47" s="3">
         <v>86400</v>
       </c>
-      <c r="AD47" s="3">
+      <c r="AE47" s="3">
         <v>90600</v>
       </c>
-      <c r="AE47" s="3">
+      <c r="AF47" s="3">
         <v>82600</v>
       </c>
-      <c r="AF47" s="3">
+      <c r="AG47" s="3">
         <v>78200</v>
       </c>
-      <c r="AG47" s="3">
+      <c r="AH47" s="3">
         <v>76400</v>
       </c>
-      <c r="AH47" s="3">
+      <c r="AI47" s="3">
         <v>78100</v>
       </c>
-      <c r="AI47" s="3">
+      <c r="AJ47" s="3">
         <v>69300</v>
       </c>
     </row>
-    <row r="48" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
-        <v>4751200</v>
+        <v>4870600</v>
       </c>
       <c r="E48" s="3">
-        <v>4728900</v>
+        <v>4637600</v>
       </c>
       <c r="F48" s="3">
-        <v>4631600</v>
+        <v>4645500</v>
       </c>
       <c r="G48" s="3">
-        <v>4584100</v>
+        <v>4633200</v>
       </c>
       <c r="H48" s="3">
-        <v>4469400</v>
+        <v>4456300</v>
       </c>
       <c r="I48" s="3">
-        <v>4313100</v>
+        <v>4371400</v>
       </c>
       <c r="J48" s="3">
+        <v>4453700</v>
+      </c>
+      <c r="K48" s="3">
         <v>4176100</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>3977700</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>3845100</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>3707100</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>3558500</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>3435000</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>3191700</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>2895100</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>2706200</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>2552500</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>2274600</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>2237200</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>2059100</v>
       </c>
-      <c r="W48" s="3">
+      <c r="X48" s="3">
         <v>1814900</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Y48" s="3">
         <v>1577900</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="Z48" s="3">
         <v>1532300</v>
       </c>
-      <c r="Z48" s="3">
+      <c r="AA48" s="3">
         <v>1312300</v>
       </c>
-      <c r="AA48" s="3">
+      <c r="AB48" s="3">
         <v>1117100</v>
       </c>
-      <c r="AB48" s="3">
+      <c r="AC48" s="3">
         <v>1015500</v>
       </c>
-      <c r="AC48" s="3">
+      <c r="AD48" s="3">
         <v>983700</v>
       </c>
-      <c r="AD48" s="3">
+      <c r="AE48" s="3">
         <v>960700</v>
       </c>
-      <c r="AE48" s="3">
+      <c r="AF48" s="3">
         <v>866600</v>
       </c>
-      <c r="AF48" s="3">
+      <c r="AG48" s="3">
         <v>765200</v>
       </c>
-      <c r="AG48" s="3">
+      <c r="AH48" s="3">
         <v>668800</v>
       </c>
-      <c r="AH48" s="3">
+      <c r="AI48" s="3">
         <v>591300</v>
       </c>
-      <c r="AI48" s="3">
+      <c r="AJ48" s="3">
         <v>479700</v>
       </c>
     </row>
-    <row r="49" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
-        <v>1415700</v>
+        <v>1476600</v>
       </c>
       <c r="E49" s="3">
-        <v>1401200</v>
+        <v>1381900</v>
       </c>
       <c r="F49" s="3">
-        <v>1396000</v>
+        <v>1376500</v>
       </c>
       <c r="G49" s="3">
-        <v>1396900</v>
+        <v>1396400</v>
       </c>
       <c r="H49" s="3">
-        <v>1401500</v>
+        <v>1358000</v>
       </c>
       <c r="I49" s="3">
-        <v>1400600</v>
+        <v>1370700</v>
       </c>
       <c r="J49" s="3">
+        <v>1446200</v>
+      </c>
+      <c r="K49" s="3">
         <v>1369500</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>1331500</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>1350200</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>1338000</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>1324400</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>1333000</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>1321600</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>1295800</v>
       </c>
-      <c r="R49" s="3">
+      <c r="S49" s="3">
         <v>1203300</v>
       </c>
-      <c r="S49" s="3">
+      <c r="T49" s="3">
         <v>1236400</v>
       </c>
-      <c r="T49" s="3">
+      <c r="U49" s="3">
         <v>1195900</v>
       </c>
-      <c r="U49" s="3">
+      <c r="V49" s="3">
         <v>1154200</v>
       </c>
-      <c r="V49" s="3">
+      <c r="W49" s="3">
         <v>1046800</v>
       </c>
-      <c r="W49" s="3">
+      <c r="X49" s="3">
         <v>1029800</v>
       </c>
-      <c r="X49" s="3">
+      <c r="Y49" s="3">
         <v>987300</v>
       </c>
-      <c r="Y49" s="3">
+      <c r="Z49" s="3">
         <v>983500</v>
       </c>
-      <c r="Z49" s="3">
+      <c r="AA49" s="3">
         <v>909900</v>
       </c>
-      <c r="AA49" s="3">
+      <c r="AB49" s="3">
         <v>873300</v>
       </c>
-      <c r="AB49" s="3">
+      <c r="AC49" s="3">
         <v>861700</v>
       </c>
-      <c r="AC49" s="3">
+      <c r="AD49" s="3">
         <v>880200</v>
       </c>
-      <c r="AD49" s="3">
+      <c r="AE49" s="3">
         <v>876300</v>
       </c>
-      <c r="AE49" s="3">
+      <c r="AF49" s="3">
         <v>841400</v>
       </c>
-      <c r="AF49" s="3">
+      <c r="AG49" s="3">
         <v>835000</v>
       </c>
-      <c r="AG49" s="3">
+      <c r="AH49" s="3">
         <v>815900</v>
       </c>
-      <c r="AH49" s="3">
+      <c r="AI49" s="3">
         <v>794000</v>
       </c>
-      <c r="AI49" s="3">
+      <c r="AJ49" s="3">
         <v>777200</v>
       </c>
     </row>
-    <row r="50" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -4622,8 +4736,11 @@
       <c r="AI50" s="3">
         <v>0</v>
       </c>
+      <c r="AJ50" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="51" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="51" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -4723,109 +4840,115 @@
       <c r="AI51" s="3">
         <v>0</v>
       </c>
+      <c r="AJ51" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="52" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="52" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
-        <v>250700</v>
+        <v>74300</v>
       </c>
       <c r="E52" s="3">
-        <v>235400</v>
+        <v>128200</v>
       </c>
       <c r="F52" s="3">
-        <v>223000</v>
+        <v>99600</v>
       </c>
       <c r="G52" s="3">
-        <v>212400</v>
+        <v>99000</v>
       </c>
       <c r="H52" s="3">
-        <v>176900</v>
+        <v>72800</v>
       </c>
       <c r="I52" s="3">
-        <v>184500</v>
+        <v>53000</v>
       </c>
       <c r="J52" s="3">
+        <v>74600</v>
+      </c>
+      <c r="K52" s="3">
         <v>220900</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>238500</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>216500</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>234300</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>233800</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>230200</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>251600</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>250600</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>175100</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>172000</v>
       </c>
-      <c r="T52" s="3">
+      <c r="U52" s="3">
         <v>170900</v>
       </c>
-      <c r="U52" s="3">
+      <c r="V52" s="3">
         <v>179500</v>
       </c>
-      <c r="V52" s="3">
+      <c r="W52" s="3">
         <v>156400</v>
       </c>
-      <c r="W52" s="3">
+      <c r="X52" s="3">
         <v>391500</v>
       </c>
-      <c r="X52" s="3">
+      <c r="Y52" s="3">
         <v>232100</v>
       </c>
-      <c r="Y52" s="3">
+      <c r="Z52" s="3">
         <v>172600</v>
       </c>
-      <c r="Z52" s="3">
+      <c r="AA52" s="3">
         <v>136600</v>
       </c>
-      <c r="AA52" s="3">
+      <c r="AB52" s="3">
         <v>108700</v>
       </c>
-      <c r="AB52" s="3">
+      <c r="AC52" s="3">
         <v>108200</v>
       </c>
-      <c r="AC52" s="3">
+      <c r="AD52" s="3">
         <v>87800</v>
       </c>
-      <c r="AD52" s="3">
+      <c r="AE52" s="3">
         <v>68500</v>
       </c>
-      <c r="AE52" s="3">
+      <c r="AF52" s="3">
         <v>45800</v>
       </c>
-      <c r="AF52" s="3">
+      <c r="AG52" s="3">
         <v>34600</v>
       </c>
-      <c r="AG52" s="3">
+      <c r="AH52" s="3">
         <v>28700</v>
       </c>
-      <c r="AH52" s="3">
+      <c r="AI52" s="3">
         <v>22500</v>
       </c>
-      <c r="AI52" s="3">
+      <c r="AJ52" s="3">
         <v>26400</v>
       </c>
     </row>
-    <row r="53" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -4925,109 +5048,115 @@
       <c r="AI53" s="3">
         <v>0</v>
       </c>
+      <c r="AJ53" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="54" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="54" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
-        <v>12843800</v>
+        <v>13303900</v>
       </c>
       <c r="E54" s="3">
-        <v>12670600</v>
+        <v>12536800</v>
       </c>
       <c r="F54" s="3">
-        <v>12471800</v>
+        <v>12447200</v>
       </c>
       <c r="G54" s="3">
-        <v>12330600</v>
+        <v>12475900</v>
       </c>
       <c r="H54" s="3">
-        <v>11568100</v>
+        <v>11986900</v>
       </c>
       <c r="I54" s="3">
-        <v>11376600</v>
+        <v>11314300</v>
       </c>
       <c r="J54" s="3">
+        <v>11747600</v>
+      </c>
+      <c r="K54" s="3">
         <v>11070300</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>10720300</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>9523700</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>9084600</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>8648800</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>8623200</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>8799300</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>8633300</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>8241300</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>8679900</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>7144000</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>7328400</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>7066200</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>6627600</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>6192400</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>6105100</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>5763100</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AB54" s="3">
         <v>5219700</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AC54" s="3">
         <v>4800400</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AD54" s="3">
         <v>3561300</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AE54" s="3">
         <v>3833100</v>
       </c>
-      <c r="AE54" s="3">
+      <c r="AF54" s="3">
         <v>3632000</v>
       </c>
-      <c r="AF54" s="3">
+      <c r="AG54" s="3">
         <v>3531800</v>
       </c>
-      <c r="AG54" s="3">
+      <c r="AH54" s="3">
         <v>3467300</v>
       </c>
-      <c r="AH54" s="3">
+      <c r="AI54" s="3">
         <v>3403600</v>
       </c>
-      <c r="AI54" s="3">
+      <c r="AJ54" s="3">
         <v>1811700</v>
       </c>
     </row>
-    <row r="55" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -5063,8 +5192,9 @@
       <c r="AG55" s="3"/>
       <c r="AH55" s="3"/>
       <c r="AI55" s="3"/>
+      <c r="AJ55" s="3"/>
     </row>
-    <row r="56" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="56" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -5100,171 +5230,175 @@
       <c r="AG56" s="3"/>
       <c r="AH56" s="3"/>
       <c r="AI56" s="3"/>
+      <c r="AJ56" s="3"/>
     </row>
-    <row r="57" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="57" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
-        <v>310200</v>
+        <v>323200</v>
       </c>
       <c r="E57" s="3">
-        <v>329100</v>
+        <v>308300</v>
       </c>
       <c r="F57" s="3">
-        <v>360500</v>
+        <v>323300</v>
       </c>
       <c r="G57" s="3">
-        <v>280600</v>
+        <v>368200</v>
       </c>
       <c r="H57" s="3">
-        <v>271900</v>
+        <v>300100</v>
       </c>
       <c r="I57" s="3">
-        <v>290200</v>
+        <v>293200</v>
       </c>
       <c r="J57" s="3">
+        <v>345800</v>
+      </c>
+      <c r="K57" s="3">
         <v>310500</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>245700</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>265700</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>238900</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>269700</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>231300</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>229300</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>222800</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>227700</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>216400</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>162900</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>185600</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>227200</v>
       </c>
-      <c r="W57" s="3">
+      <c r="X57" s="3">
         <v>167200</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Y57" s="3">
         <v>181100</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="Z57" s="3">
         <v>157100</v>
       </c>
-      <c r="Z57" s="3">
+      <c r="AA57" s="3">
         <v>190500</v>
       </c>
-      <c r="AA57" s="3">
+      <c r="AB57" s="3">
         <v>117200</v>
       </c>
-      <c r="AB57" s="3">
+      <c r="AC57" s="3">
         <v>130700</v>
       </c>
-      <c r="AC57" s="3">
+      <c r="AD57" s="3">
         <v>133200</v>
       </c>
-      <c r="AD57" s="3">
+      <c r="AE57" s="3">
         <v>132000</v>
       </c>
-      <c r="AE57" s="3">
+      <c r="AF57" s="3">
         <v>84900</v>
       </c>
-      <c r="AF57" s="3">
+      <c r="AG57" s="3">
         <v>73000</v>
       </c>
-      <c r="AG57" s="3">
+      <c r="AH57" s="3">
         <v>98200</v>
       </c>
-      <c r="AH57" s="3">
+      <c r="AI57" s="3">
         <v>92600</v>
       </c>
-      <c r="AI57" s="3">
+      <c r="AJ57" s="3">
         <v>65500</v>
       </c>
     </row>
-    <row r="58" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
-        <v>1464900</v>
+        <v>2554100</v>
       </c>
       <c r="E58" s="3">
-        <v>1133600</v>
+        <v>1451100</v>
       </c>
       <c r="F58" s="3">
-        <v>1094800</v>
+        <v>1138800</v>
       </c>
       <c r="G58" s="3">
-        <v>1352300</v>
+        <v>1121500</v>
       </c>
       <c r="H58" s="3">
-        <v>944700</v>
+        <v>1346600</v>
       </c>
       <c r="I58" s="3">
-        <v>958500</v>
+        <v>958600</v>
       </c>
       <c r="J58" s="3">
+        <v>994900</v>
+      </c>
+      <c r="K58" s="3">
         <v>788700</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>993100</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>1015500</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>847900</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>500600</v>
       </c>
-      <c r="O58" s="3">
+      <c r="P58" s="3">
         <v>678800</v>
       </c>
-      <c r="P58" s="3">
+      <c r="Q58" s="3">
         <v>537500</v>
       </c>
-      <c r="Q58" s="3">
+      <c r="R58" s="3">
         <v>433100</v>
       </c>
-      <c r="R58" s="3">
+      <c r="S58" s="3">
         <v>244900</v>
       </c>
-      <c r="S58" s="3">
+      <c r="T58" s="3">
         <v>413300</v>
       </c>
-      <c r="T58" s="3">
+      <c r="U58" s="3">
         <v>322200</v>
       </c>
-      <c r="U58" s="3">
+      <c r="V58" s="3">
         <v>47300</v>
       </c>
-      <c r="V58" s="3">
-        <v>0</v>
-      </c>
-      <c r="W58" s="3" t="s">
-        <v>8</v>
+      <c r="W58" s="3">
+        <v>0</v>
       </c>
       <c r="X58" s="3" t="s">
         <v>8</v>
@@ -5272,8 +5406,8 @@
       <c r="Y58" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Z58" s="3">
-        <v>0</v>
+      <c r="Z58" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="AA58" s="3">
         <v>0</v>
@@ -5285,7 +5419,7 @@
         <v>0</v>
       </c>
       <c r="AD58" s="3">
-        <v>37100</v>
+        <v>0</v>
       </c>
       <c r="AE58" s="3">
         <v>37100</v>
@@ -5294,248 +5428,257 @@
         <v>37100</v>
       </c>
       <c r="AG58" s="3">
+        <v>37100</v>
+      </c>
+      <c r="AH58" s="3">
         <v>101800</v>
       </c>
-      <c r="AH58" s="3">
+      <c r="AI58" s="3">
         <v>65400</v>
       </c>
-      <c r="AI58" s="3">
+      <c r="AJ58" s="3">
         <v>43600</v>
       </c>
     </row>
-    <row r="59" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
-        <v>1339000</v>
+        <v>1582400</v>
       </c>
       <c r="E59" s="3">
-        <v>1816600</v>
+        <v>1280300</v>
       </c>
       <c r="F59" s="3">
-        <v>1372900</v>
+        <v>1759300</v>
       </c>
       <c r="G59" s="3">
-        <v>1345400</v>
+        <v>1114400</v>
       </c>
       <c r="H59" s="3">
-        <v>1282600</v>
+        <v>1248600</v>
       </c>
       <c r="I59" s="3">
-        <v>1444300</v>
+        <v>1192600</v>
       </c>
       <c r="J59" s="3">
+        <v>1440100</v>
+      </c>
+      <c r="K59" s="3">
         <v>1213600</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>1179100</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>1079000</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>1121000</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>1020300</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>902400</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>855200</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>966600</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>828600</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>822800</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>808400</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>1052600</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>801600</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>687500</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Y59" s="3">
         <v>630100</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="Z59" s="3">
         <v>711200</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AA59" s="3">
         <v>556200</v>
       </c>
-      <c r="AA59" s="3">
+      <c r="AB59" s="3">
         <v>432100</v>
       </c>
-      <c r="AB59" s="3">
+      <c r="AC59" s="3">
         <v>419700</v>
       </c>
-      <c r="AC59" s="3">
+      <c r="AD59" s="3">
         <v>424600</v>
       </c>
-      <c r="AD59" s="3">
+      <c r="AE59" s="3">
         <v>446300</v>
       </c>
-      <c r="AE59" s="3">
+      <c r="AF59" s="3">
         <v>419000</v>
       </c>
-      <c r="AF59" s="3">
+      <c r="AG59" s="3">
         <v>349800</v>
       </c>
-      <c r="AG59" s="3">
+      <c r="AH59" s="3">
         <v>311200</v>
       </c>
-      <c r="AH59" s="3">
+      <c r="AI59" s="3">
         <v>354300</v>
       </c>
-      <c r="AI59" s="3">
+      <c r="AJ59" s="3">
         <v>296300</v>
       </c>
     </row>
-    <row r="60" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
-        <v>3114100</v>
+        <v>4459700</v>
       </c>
       <c r="E60" s="3">
-        <v>3279300</v>
+        <v>3039700</v>
       </c>
       <c r="F60" s="3">
-        <v>2828200</v>
+        <v>3221500</v>
       </c>
       <c r="G60" s="3">
-        <v>2978300</v>
+        <v>2829100</v>
       </c>
       <c r="H60" s="3">
-        <v>2499200</v>
+        <v>2895300</v>
       </c>
       <c r="I60" s="3">
-        <v>2693000</v>
+        <v>2444400</v>
       </c>
       <c r="J60" s="3">
+        <v>2780800</v>
+      </c>
+      <c r="K60" s="3">
         <v>2312800</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>2417900</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>2360200</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>2207700</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>1790600</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>1812500</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>1622000</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>1622600</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>1301200</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>1452600</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>1293500</v>
       </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
         <v>1285600</v>
       </c>
-      <c r="V60" s="3">
+      <c r="W60" s="3">
         <v>1028700</v>
       </c>
-      <c r="W60" s="3">
+      <c r="X60" s="3">
         <v>854700</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Y60" s="3">
         <v>811200</v>
       </c>
-      <c r="Y60" s="3">
+      <c r="Z60" s="3">
         <v>868200</v>
       </c>
-      <c r="Z60" s="3">
+      <c r="AA60" s="3">
         <v>746700</v>
       </c>
-      <c r="AA60" s="3">
+      <c r="AB60" s="3">
         <v>549300</v>
       </c>
-      <c r="AB60" s="3">
+      <c r="AC60" s="3">
         <v>550400</v>
       </c>
-      <c r="AC60" s="3">
+      <c r="AD60" s="3">
         <v>557800</v>
       </c>
-      <c r="AD60" s="3">
+      <c r="AE60" s="3">
         <v>615300</v>
       </c>
-      <c r="AE60" s="3">
+      <c r="AF60" s="3">
         <v>541000</v>
       </c>
-      <c r="AF60" s="3">
+      <c r="AG60" s="3">
         <v>459900</v>
       </c>
-      <c r="AG60" s="3">
+      <c r="AH60" s="3">
         <v>511200</v>
       </c>
-      <c r="AH60" s="3">
+      <c r="AI60" s="3">
         <v>512300</v>
       </c>
-      <c r="AI60" s="3">
+      <c r="AJ60" s="3">
         <v>405500</v>
       </c>
     </row>
-    <row r="61" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
-        <v>1017400</v>
+        <v>53300</v>
       </c>
       <c r="E61" s="3">
-        <v>1009300</v>
+        <v>1038300</v>
       </c>
       <c r="F61" s="3">
-        <v>991000</v>
+        <v>1047500</v>
       </c>
       <c r="G61" s="3">
-        <v>1016900</v>
+        <v>1055600</v>
       </c>
       <c r="H61" s="3">
-        <v>1009200</v>
+        <v>1050000</v>
       </c>
       <c r="I61" s="3">
-        <v>954400</v>
+        <v>1054200</v>
       </c>
       <c r="J61" s="3">
+        <v>1055700</v>
+      </c>
+      <c r="K61" s="3">
         <v>957100</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>966000</v>
       </c>
-      <c r="L61" s="3">
-        <v>0</v>
-      </c>
       <c r="M61" s="3">
         <v>0</v>
       </c>
@@ -5605,109 +5748,115 @@
       <c r="AI61" s="3">
         <v>0</v>
       </c>
+      <c r="AJ61" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="62" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
-      <c r="D62" s="3">
-        <v>116200</v>
-      </c>
-      <c r="E62" s="3">
-        <v>150200</v>
-      </c>
-      <c r="F62" s="3">
-        <v>154200</v>
-      </c>
-      <c r="G62" s="3">
-        <v>112000</v>
-      </c>
-      <c r="H62" s="3">
-        <v>117700</v>
-      </c>
-      <c r="I62" s="3">
-        <v>115900</v>
-      </c>
-      <c r="J62" s="3">
+      <c r="D62" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E62" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F62" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="G62" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="H62" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I62" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J62" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="K62" s="3">
         <v>120800</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>101000</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>110000</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>114700</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>116900</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>120300</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>115800</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>110200</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>105400</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>99300</v>
       </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>104200</v>
       </c>
-      <c r="U62" s="3">
+      <c r="V62" s="3">
         <v>117500</v>
       </c>
-      <c r="V62" s="3">
+      <c r="W62" s="3">
         <v>124100</v>
       </c>
-      <c r="W62" s="3">
+      <c r="X62" s="3">
         <v>95900</v>
       </c>
-      <c r="X62" s="3">
+      <c r="Y62" s="3">
         <v>96500</v>
       </c>
-      <c r="Y62" s="3">
+      <c r="Z62" s="3">
         <v>121000</v>
       </c>
-      <c r="Z62" s="3">
+      <c r="AA62" s="3">
         <v>39500</v>
       </c>
-      <c r="AA62" s="3">
+      <c r="AB62" s="3">
         <v>33600</v>
       </c>
-      <c r="AB62" s="3">
+      <c r="AC62" s="3">
         <v>33400</v>
       </c>
-      <c r="AC62" s="3">
+      <c r="AD62" s="3">
         <v>34000</v>
       </c>
-      <c r="AD62" s="3">
+      <c r="AE62" s="3">
         <v>35700</v>
       </c>
-      <c r="AE62" s="3">
+      <c r="AF62" s="3">
         <v>30000</v>
       </c>
-      <c r="AF62" s="3">
+      <c r="AG62" s="3">
         <v>30300</v>
       </c>
-      <c r="AG62" s="3">
+      <c r="AH62" s="3">
         <v>23500</v>
       </c>
-      <c r="AH62" s="3">
+      <c r="AI62" s="3">
         <v>19000</v>
       </c>
-      <c r="AI62" s="3">
+      <c r="AJ62" s="3">
         <v>19100</v>
       </c>
     </row>
-    <row r="63" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -5807,8 +5956,11 @@
       <c r="AI63" s="3">
         <v>0</v>
       </c>
+      <c r="AJ63" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="64" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="64" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -5908,8 +6060,11 @@
       <c r="AI64" s="3">
         <v>0</v>
       </c>
+      <c r="AJ64" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="65" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="65" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -6009,109 +6164,115 @@
       <c r="AI65" s="3">
         <v>0</v>
       </c>
+      <c r="AJ65" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="66" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="66" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
-        <v>4324900</v>
+        <v>4590200</v>
       </c>
       <c r="E66" s="3">
-        <v>4515900</v>
+        <v>4146200</v>
       </c>
       <c r="F66" s="3">
-        <v>4041000</v>
+        <v>4360500</v>
       </c>
       <c r="G66" s="3">
-        <v>4168500</v>
+        <v>3974800</v>
       </c>
       <c r="H66" s="3">
-        <v>3686600</v>
+        <v>3992800</v>
       </c>
       <c r="I66" s="3">
-        <v>3825000</v>
+        <v>3546600</v>
       </c>
       <c r="J66" s="3">
+        <v>3885900</v>
+      </c>
+      <c r="K66" s="3">
         <v>3453300</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>3547700</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>2528500</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>2353800</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>1947500</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>1953500</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>1753500</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>1752700</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>1423500</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>1568300</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>1414400</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>1419300</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>1168400</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>965800</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>919500</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>999600</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>793800</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AB66" s="3">
         <v>588000</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AC66" s="3">
         <v>584900</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AD66" s="3">
         <v>592700</v>
       </c>
-      <c r="AD66" s="3">
+      <c r="AE66" s="3">
         <v>651900</v>
       </c>
-      <c r="AE66" s="3">
+      <c r="AF66" s="3">
         <v>571800</v>
       </c>
-      <c r="AF66" s="3">
+      <c r="AG66" s="3">
         <v>491000</v>
       </c>
-      <c r="AG66" s="3">
+      <c r="AH66" s="3">
         <v>535400</v>
       </c>
-      <c r="AH66" s="3">
+      <c r="AI66" s="3">
         <v>532100</v>
       </c>
-      <c r="AI66" s="3">
+      <c r="AJ66" s="3">
         <v>424600</v>
       </c>
     </row>
-    <row r="67" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -6147,8 +6308,9 @@
       <c r="AG67" s="3"/>
       <c r="AH67" s="3"/>
       <c r="AI67" s="3"/>
+      <c r="AJ67" s="3"/>
     </row>
-    <row r="68" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="68" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -6248,8 +6410,11 @@
       <c r="AI68" s="3">
         <v>0</v>
       </c>
+      <c r="AJ68" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="69" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="69" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -6349,8 +6514,11 @@
       <c r="AI69" s="3">
         <v>0</v>
       </c>
+      <c r="AJ69" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="70" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="70" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -6448,10 +6616,13 @@
         <v>0</v>
       </c>
       <c r="AI70" s="3">
+        <v>0</v>
+      </c>
+      <c r="AJ70" s="3">
         <v>304900</v>
       </c>
     </row>
-    <row r="71" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="71" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -6551,109 +6722,115 @@
       <c r="AI71" s="3">
         <v>0</v>
       </c>
+      <c r="AJ71" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="72" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="72" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
-        <v>5164700</v>
+        <v>5234300</v>
       </c>
       <c r="E72" s="3">
-        <v>4796500</v>
+        <v>5041300</v>
       </c>
       <c r="F72" s="3">
-        <v>5117700</v>
+        <v>4711900</v>
       </c>
       <c r="G72" s="3">
-        <v>4851000</v>
+        <v>5119400</v>
       </c>
       <c r="H72" s="3">
-        <v>4557000</v>
+        <v>4715800</v>
       </c>
       <c r="I72" s="3">
-        <v>4337200</v>
+        <v>4457100</v>
       </c>
       <c r="J72" s="3">
+        <v>4478700</v>
+      </c>
+      <c r="K72" s="3">
         <v>4153200</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>3771300</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>3525800</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>3280400</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>3129900</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>2978700</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>3182700</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>3093800</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>2928600</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>2910500</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>2733500</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>2697900</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>2575600</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>2246600</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>2000300</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>1784800</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AA72" s="3">
         <v>1605100</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AB72" s="3">
         <v>1368400</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AC72" s="3">
         <v>1220100</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AD72" s="3">
         <v>1036800</v>
       </c>
-      <c r="AD72" s="3">
+      <c r="AE72" s="3">
         <v>989800</v>
       </c>
-      <c r="AE72" s="3">
+      <c r="AF72" s="3">
         <v>808400</v>
       </c>
-      <c r="AF72" s="3">
+      <c r="AG72" s="3">
         <v>702000</v>
       </c>
-      <c r="AG72" s="3">
+      <c r="AH72" s="3">
         <v>583600</v>
       </c>
-      <c r="AH72" s="3">
+      <c r="AI72" s="3">
         <v>510400</v>
       </c>
-      <c r="AI72" s="3">
+      <c r="AJ72" s="3">
         <v>404700</v>
       </c>
     </row>
-    <row r="73" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -6753,8 +6930,11 @@
       <c r="AI73" s="3">
         <v>0</v>
       </c>
+      <c r="AJ73" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="74" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="74" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -6854,8 +7034,11 @@
       <c r="AI74" s="3">
         <v>0</v>
       </c>
+      <c r="AJ74" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="75" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="75" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -6955,109 +7138,115 @@
       <c r="AI75" s="3">
         <v>0</v>
       </c>
+      <c r="AJ75" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="76" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="76" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
-        <v>8519000</v>
+        <v>8638000</v>
       </c>
       <c r="E76" s="3">
-        <v>8154800</v>
+        <v>8315300</v>
       </c>
       <c r="F76" s="3">
-        <v>8430900</v>
+        <v>8011000</v>
       </c>
       <c r="G76" s="3">
-        <v>8162100</v>
+        <v>8433600</v>
       </c>
       <c r="H76" s="3">
-        <v>7881400</v>
+        <v>7934600</v>
       </c>
       <c r="I76" s="3">
-        <v>7551600</v>
+        <v>7708500</v>
       </c>
       <c r="J76" s="3">
+        <v>7797800</v>
+      </c>
+      <c r="K76" s="3">
         <v>7616900</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>7172500</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>6995300</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>6730800</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>6701200</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>6669700</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>7045800</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>6880500</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>6817900</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>7111600</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>5729500</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>5909100</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>5897800</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>5661800</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>5272900</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>5105500</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>4969400</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AB76" s="3">
         <v>4631700</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AC76" s="3">
         <v>4215500</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AD76" s="3">
         <v>2968500</v>
       </c>
-      <c r="AD76" s="3">
+      <c r="AE76" s="3">
         <v>3181200</v>
       </c>
-      <c r="AE76" s="3">
+      <c r="AF76" s="3">
         <v>3060200</v>
       </c>
-      <c r="AF76" s="3">
+      <c r="AG76" s="3">
         <v>3040800</v>
       </c>
-      <c r="AG76" s="3">
+      <c r="AH76" s="3">
         <v>2931800</v>
       </c>
-      <c r="AH76" s="3">
+      <c r="AI76" s="3">
         <v>2871500</v>
       </c>
-      <c r="AI76" s="3">
+      <c r="AJ76" s="3">
         <v>1082100</v>
       </c>
     </row>
-    <row r="77" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -7157,215 +7346,224 @@
       <c r="AI77" s="3">
         <v>0</v>
       </c>
+      <c r="AJ77" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="79" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="79" spans="2:36" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45565</v>
+      </c>
+      <c r="E80" s="2">
         <v>45473</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45382</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45291</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45199</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45107</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45016</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>44926</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44834</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44742</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44651</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44561</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44469</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44377</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44286</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44196</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44104</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44012</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>43921</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>43830</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>43738</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>43646</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>43555</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>43465</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>43373</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43281</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>43190</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>43100</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AF80" s="2">
         <v>43008</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AG80" s="2">
         <v>42916</v>
       </c>
-      <c r="AG80" s="2">
+      <c r="AH80" s="2">
         <v>42825</v>
       </c>
-      <c r="AH80" s="2">
+      <c r="AI80" s="2">
         <v>42735</v>
       </c>
-      <c r="AI80" s="2">
+      <c r="AJ80" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="81" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
-        <v>368200</v>
+        <v>341600</v>
       </c>
       <c r="E81" s="3">
-        <v>201000</v>
+        <v>359400</v>
       </c>
       <c r="F81" s="3">
-        <v>309100</v>
+        <v>197500</v>
       </c>
       <c r="G81" s="3">
-        <v>330600</v>
+        <v>309200</v>
       </c>
       <c r="H81" s="3">
-        <v>358300</v>
+        <v>321400</v>
       </c>
       <c r="I81" s="3">
-        <v>235500</v>
+        <v>350400</v>
       </c>
       <c r="J81" s="3">
+        <v>243200</v>
+      </c>
+      <c r="K81" s="3">
         <v>304900</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>267300</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>251000</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>126000</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>242800</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>165800</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>185600</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>76600</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>179300</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>177000</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>213400</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>59100</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>358200</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>204000</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>207700</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>103600</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>185200</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>148300</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AC81" s="3">
         <v>208700</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AD81" s="3">
         <v>79900</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AE81" s="3">
         <v>181400</v>
-      </c>
-      <c r="AE81" s="3">
-        <v>106400</v>
       </c>
       <c r="AF81" s="3">
         <v>106400</v>
       </c>
       <c r="AG81" s="3">
+        <v>106400</v>
+      </c>
+      <c r="AH81" s="3">
         <v>73200</v>
       </c>
-      <c r="AH81" s="3">
+      <c r="AI81" s="3">
         <v>105700</v>
       </c>
-      <c r="AI81" s="3">
+      <c r="AJ81" s="3">
         <v>73700</v>
       </c>
     </row>
-    <row r="82" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -7401,31 +7599,32 @@
       <c r="AG82" s="3"/>
       <c r="AH82" s="3"/>
       <c r="AI82" s="3"/>
+      <c r="AJ82" s="3"/>
     </row>
-    <row r="83" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="83" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
-        <v>0</v>
+        <v>95300</v>
       </c>
       <c r="E83" s="3">
-        <v>0</v>
+        <v>92600</v>
       </c>
       <c r="F83" s="3">
-        <v>0</v>
+        <v>94900</v>
       </c>
       <c r="G83" s="3">
-        <v>0</v>
+        <v>96500</v>
       </c>
       <c r="H83" s="3">
-        <v>0</v>
+        <v>89000</v>
       </c>
       <c r="I83" s="3">
-        <v>0</v>
+        <v>95600</v>
       </c>
       <c r="J83" s="3">
-        <v>0</v>
+        <v>94900</v>
       </c>
       <c r="K83" s="3">
         <v>0</v>
@@ -7502,8 +7701,11 @@
       <c r="AI83" s="3">
         <v>0</v>
       </c>
+      <c r="AJ83" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="84" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -7603,8 +7805,11 @@
       <c r="AI84" s="3">
         <v>0</v>
       </c>
+      <c r="AJ84" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="85" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="85" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -7704,8 +7909,11 @@
       <c r="AI85" s="3">
         <v>0</v>
       </c>
+      <c r="AJ85" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="86" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="86" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -7805,8 +8013,11 @@
       <c r="AI86" s="3">
         <v>0</v>
       </c>
+      <c r="AJ86" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="87" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="87" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -7906,8 +8117,11 @@
       <c r="AI87" s="3">
         <v>0</v>
       </c>
+      <c r="AJ87" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="88" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="88" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -8007,109 +8221,115 @@
       <c r="AI88" s="3">
         <v>0</v>
       </c>
+      <c r="AJ88" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="89" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="89" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
-        <v>490600</v>
+        <v>443600</v>
       </c>
       <c r="E89" s="3">
-        <v>286300</v>
+        <v>478900</v>
       </c>
       <c r="F89" s="3">
-        <v>553100</v>
+        <v>281300</v>
       </c>
       <c r="G89" s="3">
-        <v>414200</v>
+        <v>553300</v>
       </c>
       <c r="H89" s="3">
-        <v>530300</v>
+        <v>402700</v>
       </c>
       <c r="I89" s="3">
-        <v>386000</v>
+        <v>518700</v>
       </c>
       <c r="J89" s="3">
+        <v>398600</v>
+      </c>
+      <c r="K89" s="3">
         <v>531500</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>390100</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>525600</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>153700</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>416600</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>254000</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>277500</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>68500</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>284000</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>218200</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>184500</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>28000</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>348100</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>221200</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>304500</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>96300</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AA89" s="3">
         <v>261800</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AB89" s="3">
         <v>127600</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AC89" s="3">
         <v>206600</v>
       </c>
-      <c r="AC89" s="3">
+      <c r="AD89" s="3">
         <v>30700</v>
       </c>
-      <c r="AD89" s="3">
+      <c r="AE89" s="3">
         <v>203600</v>
       </c>
-      <c r="AE89" s="3">
+      <c r="AF89" s="3">
         <v>152000</v>
       </c>
-      <c r="AF89" s="3">
+      <c r="AG89" s="3">
         <v>134100</v>
       </c>
-      <c r="AG89" s="3">
+      <c r="AH89" s="3">
         <v>48200</v>
       </c>
-      <c r="AH89" s="3">
+      <c r="AI89" s="3">
         <v>166300</v>
       </c>
-      <c r="AI89" s="3">
+      <c r="AJ89" s="3">
         <v>121000</v>
       </c>
     </row>
-    <row r="90" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -8145,31 +8365,32 @@
       <c r="AG90" s="3"/>
       <c r="AH90" s="3"/>
       <c r="AI90" s="3"/>
+      <c r="AJ90" s="3"/>
     </row>
-    <row r="91" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="91" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
-      <c r="D91" s="3">
-        <v>-2167300</v>
+      <c r="D91" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="E91" s="3">
-        <v>0</v>
-      </c>
-      <c r="F91" s="3">
-        <v>0</v>
+        <v>-364200</v>
+      </c>
+      <c r="F91" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="G91" s="3">
-        <v>0</v>
-      </c>
-      <c r="H91" s="3">
-        <v>0</v>
+        <v>-920700</v>
+      </c>
+      <c r="H91" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="I91" s="3">
-        <v>0</v>
-      </c>
-      <c r="J91" s="3">
-        <v>0</v>
+        <v>-613200</v>
+      </c>
+      <c r="J91" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="K91" s="3">
         <v>0</v>
@@ -8246,8 +8467,11 @@
       <c r="AI91" s="3">
         <v>0</v>
       </c>
+      <c r="AJ91" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="92" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -8347,8 +8571,11 @@
       <c r="AI92" s="3">
         <v>0</v>
       </c>
+      <c r="AJ92" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="93" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="93" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -8448,109 +8675,115 @@
       <c r="AI93" s="3">
         <v>0</v>
       </c>
+      <c r="AJ93" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="94" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="94" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
-        <v>-657900</v>
+        <v>-272300</v>
       </c>
       <c r="E94" s="3">
-        <v>-335300</v>
+        <v>-642100</v>
       </c>
       <c r="F94" s="3">
-        <v>166500</v>
+        <v>-329400</v>
       </c>
       <c r="G94" s="3">
-        <v>-567600</v>
+        <v>166600</v>
       </c>
       <c r="H94" s="3">
-        <v>-499300</v>
+        <v>-551700</v>
       </c>
       <c r="I94" s="3">
-        <v>-827100</v>
+        <v>-488300</v>
       </c>
       <c r="J94" s="3">
+        <v>-854000</v>
+      </c>
+      <c r="K94" s="3">
         <v>-617600</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-654400</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-501800</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-460800</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-387700</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-197000</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-26500</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-627900</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-406000</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>173900</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>-161800</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>-112800</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>-314600</v>
       </c>
-      <c r="W94" s="3">
+      <c r="X94" s="3">
         <v>-626500</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Y94" s="3">
         <v>229000</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="Z94" s="3">
         <v>136200</v>
       </c>
-      <c r="Z94" s="3">
+      <c r="AA94" s="3">
         <v>-483600</v>
       </c>
-      <c r="AA94" s="3">
+      <c r="AB94" s="3">
         <v>-321300</v>
       </c>
-      <c r="AB94" s="3">
+      <c r="AC94" s="3">
         <v>-790700</v>
       </c>
-      <c r="AC94" s="3">
+      <c r="AD94" s="3">
         <v>-229200</v>
       </c>
-      <c r="AD94" s="3">
+      <c r="AE94" s="3">
         <v>-107200</v>
       </c>
-      <c r="AE94" s="3">
+      <c r="AF94" s="3">
         <v>-167600</v>
       </c>
-      <c r="AF94" s="3">
+      <c r="AG94" s="3">
         <v>-168800</v>
       </c>
-      <c r="AG94" s="3">
+      <c r="AH94" s="3">
         <v>-771600</v>
       </c>
-      <c r="AH94" s="3">
+      <c r="AI94" s="3">
         <v>-158200</v>
       </c>
-      <c r="AI94" s="3">
+      <c r="AJ94" s="3">
         <v>-129200</v>
       </c>
     </row>
-    <row r="95" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -8586,31 +8819,32 @@
       <c r="AG95" s="3"/>
       <c r="AH95" s="3"/>
       <c r="AI95" s="3"/>
+      <c r="AJ95" s="3"/>
     </row>
-    <row r="96" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="96" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
-      <c r="D96" s="3">
-        <v>0</v>
+      <c r="D96" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="E96" s="3">
-        <v>0</v>
-      </c>
-      <c r="F96" s="3">
-        <v>0</v>
+        <v>495400</v>
+      </c>
+      <c r="F96" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="G96" s="3">
-        <v>0</v>
-      </c>
-      <c r="H96" s="3">
-        <v>0</v>
+        <v>292300</v>
+      </c>
+      <c r="H96" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="I96" s="3">
-        <v>0</v>
-      </c>
-      <c r="J96" s="3">
-        <v>0</v>
+        <v>285800</v>
+      </c>
+      <c r="J96" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="K96" s="3">
         <v>0</v>
@@ -8687,8 +8921,11 @@
       <c r="AI96" s="3">
         <v>0</v>
       </c>
+      <c r="AJ96" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="97" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="97" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -8788,8 +9025,11 @@
       <c r="AI97" s="3">
         <v>0</v>
       </c>
+      <c r="AJ97" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="98" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="98" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -8889,8 +9129,11 @@
       <c r="AI98" s="3">
         <v>0</v>
       </c>
+      <c r="AJ98" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="99" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="99" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -8990,307 +9233,319 @@
       <c r="AI99" s="3">
         <v>0</v>
       </c>
+      <c r="AJ99" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="100" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="100" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
-        <v>-155600</v>
+        <v>1500</v>
       </c>
       <c r="E100" s="3">
-        <v>18300</v>
+        <v>-151900</v>
       </c>
       <c r="F100" s="3">
-        <v>-305400</v>
+        <v>18000</v>
       </c>
       <c r="G100" s="3">
-        <v>356700</v>
+        <v>-305500</v>
       </c>
       <c r="H100" s="3">
-        <v>-278300</v>
+        <v>346700</v>
       </c>
       <c r="I100" s="3">
-        <v>118500</v>
+        <v>-272200</v>
       </c>
       <c r="J100" s="3">
+        <v>122400</v>
+      </c>
+      <c r="K100" s="3">
         <v>-240700</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>876200</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>-21800</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>358800</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>-108500</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>-308000</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>-135500</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>142800</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>-87400</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>1267700</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>9600</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>47000</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>2000</v>
       </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
         <v>79800</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Y100" s="3">
         <v>-380900</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="Z100" s="3">
         <v>-2100</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AA100" s="3">
         <v>-22300</v>
       </c>
-      <c r="AA100" s="3">
+      <c r="AB100" s="3">
         <v>193200</v>
       </c>
-      <c r="AB100" s="3">
+      <c r="AC100" s="3">
         <v>926600</v>
       </c>
-      <c r="AC100" s="3">
+      <c r="AD100" s="3">
         <v>-115500</v>
       </c>
-      <c r="AD100" s="3">
+      <c r="AE100" s="3">
         <v>-30000</v>
       </c>
-      <c r="AE100" s="3">
+      <c r="AF100" s="3">
         <v>-59900</v>
       </c>
-      <c r="AF100" s="3">
+      <c r="AG100" s="3">
         <v>-104800</v>
       </c>
-      <c r="AG100" s="3">
+      <c r="AH100" s="3">
         <v>36400</v>
       </c>
-      <c r="AH100" s="3">
+      <c r="AI100" s="3">
         <v>1358900</v>
       </c>
-      <c r="AI100" s="3">
+      <c r="AJ100" s="3">
         <v>-3900</v>
       </c>
     </row>
-    <row r="101" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
-        <v>-500</v>
+        <v>1300</v>
       </c>
       <c r="E101" s="3">
-        <v>5400</v>
+        <v>14500</v>
       </c>
       <c r="F101" s="3">
-        <v>600</v>
+        <v>-1300</v>
       </c>
       <c r="G101" s="3">
-        <v>1300</v>
+        <v>-8600</v>
       </c>
       <c r="H101" s="3">
-        <v>14800</v>
+        <v>31600</v>
       </c>
       <c r="I101" s="3">
-        <v>-1300</v>
+        <v>28900</v>
       </c>
       <c r="J101" s="3">
+        <v>-3300</v>
+      </c>
+      <c r="K101" s="3">
         <v>-8300</v>
       </c>
-      <c r="K101" s="3">
+      <c r="L101" s="3">
         <v>31000</v>
       </c>
-      <c r="L101" s="3">
+      <c r="M101" s="3">
         <v>26900</v>
       </c>
-      <c r="M101" s="3">
+      <c r="N101" s="3">
         <v>-2900</v>
       </c>
-      <c r="N101" s="3">
+      <c r="O101" s="3">
         <v>-6600</v>
       </c>
-      <c r="O101" s="3">
+      <c r="P101" s="3">
         <v>-300</v>
       </c>
-      <c r="P101" s="3">
+      <c r="Q101" s="3">
         <v>-19200</v>
       </c>
-      <c r="Q101" s="3">
+      <c r="R101" s="3">
         <v>4800</v>
       </c>
-      <c r="R101" s="3">
+      <c r="S101" s="3">
         <v>-78800</v>
       </c>
-      <c r="S101" s="3">
+      <c r="T101" s="3">
         <v>-16100</v>
       </c>
-      <c r="T101" s="3">
+      <c r="U101" s="3">
         <v>300</v>
       </c>
-      <c r="U101" s="3">
+      <c r="V101" s="3">
         <v>2700</v>
       </c>
-      <c r="V101" s="3">
+      <c r="W101" s="3">
         <v>-2000</v>
       </c>
-      <c r="W101" s="3">
+      <c r="X101" s="3">
         <v>5200</v>
       </c>
-      <c r="X101" s="3">
+      <c r="Y101" s="3">
         <v>3300</v>
       </c>
-      <c r="Y101" s="3">
+      <c r="Z101" s="3">
         <v>-6900</v>
       </c>
-      <c r="Z101" s="3">
+      <c r="AA101" s="3">
         <v>4700</v>
       </c>
-      <c r="AA101" s="3">
+      <c r="AB101" s="3">
         <v>14200</v>
       </c>
-      <c r="AB101" s="3">
+      <c r="AC101" s="3">
         <v>32400</v>
       </c>
-      <c r="AC101" s="3">
+      <c r="AD101" s="3">
         <v>-12800</v>
       </c>
-      <c r="AD101" s="3">
+      <c r="AE101" s="3">
         <v>-16600</v>
       </c>
-      <c r="AE101" s="3">
+      <c r="AF101" s="3">
         <v>-17500</v>
       </c>
-      <c r="AF101" s="3">
+      <c r="AG101" s="3">
         <v>-10400</v>
       </c>
-      <c r="AG101" s="3">
+      <c r="AH101" s="3">
         <v>-18100</v>
       </c>
-      <c r="AH101" s="3">
+      <c r="AI101" s="3">
         <v>40700</v>
       </c>
-      <c r="AI101" s="3">
+      <c r="AJ101" s="3">
         <v>400</v>
       </c>
     </row>
-    <row r="102" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
-        <v>-323300</v>
+        <v>166600</v>
       </c>
       <c r="E102" s="3">
-        <v>-25200</v>
+        <v>-315600</v>
       </c>
       <c r="F102" s="3">
-        <v>414900</v>
+        <v>-24800</v>
       </c>
       <c r="G102" s="3">
-        <v>204700</v>
+        <v>415000</v>
       </c>
       <c r="H102" s="3">
-        <v>-232500</v>
+        <v>199000</v>
       </c>
       <c r="I102" s="3">
-        <v>-323800</v>
+        <v>-227400</v>
       </c>
       <c r="J102" s="3">
+        <v>-334400</v>
+      </c>
+      <c r="K102" s="3">
         <v>-335200</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>642800</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>28900</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>48700</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-86200</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>-251300</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>96300</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>-411900</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>-288300</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>1643600</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>32700</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>-35000</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>33500</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>-320300</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>155900</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
         <v>223500</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AA102" s="3">
         <v>-239400</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AB102" s="3">
         <v>13700</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AC102" s="3">
         <v>374800</v>
       </c>
-      <c r="AC102" s="3">
+      <c r="AD102" s="3">
         <v>-326900</v>
       </c>
-      <c r="AD102" s="3">
+      <c r="AE102" s="3">
         <v>49800</v>
       </c>
-      <c r="AE102" s="3">
+      <c r="AF102" s="3">
         <v>-92900</v>
       </c>
-      <c r="AF102" s="3">
+      <c r="AG102" s="3">
         <v>-150000</v>
       </c>
-      <c r="AG102" s="3">
+      <c r="AH102" s="3">
         <v>-705100</v>
       </c>
-      <c r="AH102" s="3">
+      <c r="AI102" s="3">
         <v>1407600</v>
       </c>
-      <c r="AI102" s="3">
+      <c r="AJ102" s="3">
         <v>-11700</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/ZTO_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/ZTO_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="162" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="166" uniqueCount="92">
   <si>
     <t>ZTO</t>
   </si>
@@ -656,467 +656,479 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AJ102"/>
+  <dimension ref="A5:AK102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="6.140625" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="8" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="12" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="16" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="20" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="24" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="28" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="29" max="29" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="30" max="30" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="31" max="32" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="33" max="33" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="34" max="34" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="35" max="36" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="37" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="17" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="21" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="25" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="29" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="32" max="33" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="34" max="34" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="35" max="35" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="36" max="37" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="38" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:37" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:37" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:37" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45657</v>
+      </c>
+      <c r="E7" s="2">
         <v>45565</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45473</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45382</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45291</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45199</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45107</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45016</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44926</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44834</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44742</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44651</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44561</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44469</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44377</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44286</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44196</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44104</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>44012</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>43921</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>43830</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>43738</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>43646</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>43555</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>43465</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43373</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>43281</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>43190</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AF7" s="2">
         <v>43100</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AG7" s="2">
         <v>43008</v>
       </c>
-      <c r="AG7" s="2">
+      <c r="AH7" s="2">
         <v>42916</v>
       </c>
-      <c r="AH7" s="2">
+      <c r="AI7" s="2">
         <v>42825</v>
       </c>
-      <c r="AI7" s="2">
+      <c r="AJ7" s="2">
         <v>42735</v>
       </c>
-      <c r="AJ7" s="2">
+      <c r="AK7" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="8" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:37" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>1770000</v>
+      </c>
+      <c r="E8" s="3">
         <v>1521900</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>1476000</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>1379400</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>1497600</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>1243900</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>1343100</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>1307800</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>1391700</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>1235800</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>1203500</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>1098800</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>1270000</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>1050600</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>1052000</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>929600</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>1149400</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>978300</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>943500</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>617800</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>1054200</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>821500</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>828600</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>695800</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AB8" s="3">
         <v>817300</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AC8" s="3">
         <v>592700</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AD8" s="3">
         <v>587500</v>
       </c>
-      <c r="AD8" s="3">
+      <c r="AE8" s="3">
         <v>508600</v>
       </c>
-      <c r="AE8" s="3">
+      <c r="AF8" s="3">
         <v>642800</v>
       </c>
-      <c r="AF8" s="3">
+      <c r="AG8" s="3">
         <v>466500</v>
       </c>
-      <c r="AG8" s="3">
+      <c r="AH8" s="3">
         <v>441000</v>
       </c>
-      <c r="AH8" s="3">
+      <c r="AI8" s="3">
         <v>380200</v>
       </c>
-      <c r="AI8" s="3">
+      <c r="AJ8" s="3">
         <v>464000</v>
       </c>
-      <c r="AJ8" s="3">
+      <c r="AK8" s="3">
         <v>342200</v>
       </c>
     </row>
-    <row r="9" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:37" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>1254900</v>
+      </c>
+      <c r="E9" s="3">
         <v>1046400</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>977800</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>963600</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>1056500</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>872900</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>887400</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>940400</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>1000800</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>898100</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>897200</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>873700</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>959900</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>827700</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>811700</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>772100</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>890700</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>773300</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>682800</v>
       </c>
-      <c r="V9" s="3">
+      <c r="W9" s="3">
         <v>488600</v>
       </c>
-      <c r="W9" s="3">
+      <c r="X9" s="3">
         <v>746900</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Y9" s="3">
         <v>572400</v>
       </c>
-      <c r="Y9" s="3">
+      <c r="Z9" s="3">
         <v>558400</v>
       </c>
-      <c r="Z9" s="3">
+      <c r="AA9" s="3">
         <v>504200</v>
       </c>
-      <c r="AA9" s="3">
+      <c r="AB9" s="3">
         <v>592200</v>
       </c>
-      <c r="AB9" s="3">
+      <c r="AC9" s="3">
         <v>407200</v>
       </c>
-      <c r="AC9" s="3">
+      <c r="AD9" s="3">
         <v>383600</v>
       </c>
-      <c r="AD9" s="3">
+      <c r="AE9" s="3">
         <v>360500</v>
       </c>
-      <c r="AE9" s="3">
+      <c r="AF9" s="3">
         <v>441900</v>
       </c>
-      <c r="AF9" s="3">
+      <c r="AG9" s="3">
         <v>297600</v>
       </c>
-      <c r="AG9" s="3">
+      <c r="AH9" s="3">
         <v>274200</v>
       </c>
-      <c r="AH9" s="3">
+      <c r="AI9" s="3">
         <v>274000</v>
       </c>
-      <c r="AI9" s="3">
+      <c r="AJ9" s="3">
         <v>295100</v>
       </c>
-      <c r="AJ9" s="3">
+      <c r="AK9" s="3">
         <v>218200</v>
       </c>
     </row>
-    <row r="10" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:37" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
+        <v>515100</v>
+      </c>
+      <c r="E10" s="3">
         <v>475400</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>498200</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>415800</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>441200</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>370900</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>455600</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>367400</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>390900</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>337700</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>306200</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>225100</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>310100</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>222900</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>240400</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>157500</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>258700</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>205000</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>260700</v>
       </c>
-      <c r="V10" s="3">
+      <c r="W10" s="3">
         <v>129200</v>
       </c>
-      <c r="W10" s="3">
+      <c r="X10" s="3">
         <v>307400</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Y10" s="3">
         <v>249100</v>
       </c>
-      <c r="Y10" s="3">
+      <c r="Z10" s="3">
         <v>270200</v>
       </c>
-      <c r="Z10" s="3">
+      <c r="AA10" s="3">
         <v>191600</v>
       </c>
-      <c r="AA10" s="3">
+      <c r="AB10" s="3">
         <v>225100</v>
       </c>
-      <c r="AB10" s="3">
+      <c r="AC10" s="3">
         <v>185500</v>
       </c>
-      <c r="AC10" s="3">
+      <c r="AD10" s="3">
         <v>204000</v>
       </c>
-      <c r="AD10" s="3">
+      <c r="AE10" s="3">
         <v>148100</v>
       </c>
-      <c r="AE10" s="3">
+      <c r="AF10" s="3">
         <v>200800</v>
       </c>
-      <c r="AF10" s="3">
+      <c r="AG10" s="3">
         <v>168900</v>
       </c>
-      <c r="AG10" s="3">
+      <c r="AH10" s="3">
         <v>166800</v>
       </c>
-      <c r="AH10" s="3">
+      <c r="AI10" s="3">
         <v>106300</v>
       </c>
-      <c r="AI10" s="3">
+      <c r="AJ10" s="3">
         <v>168900</v>
       </c>
-      <c r="AJ10" s="3">
+      <c r="AK10" s="3">
         <v>124000</v>
       </c>
     </row>
-    <row r="11" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:37" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -1153,8 +1165,9 @@
       <c r="AH11" s="3"/>
       <c r="AI11" s="3"/>
       <c r="AJ11" s="3"/>
+      <c r="AK11" s="3"/>
     </row>
-    <row r="12" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:37" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
@@ -1257,8 +1270,11 @@
       <c r="AJ12" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AK12" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="13" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:37" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1361,49 +1377,52 @@
       <c r="AJ13" s="3">
         <v>0</v>
       </c>
+      <c r="AK13" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="14" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:37" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3">
+        <v>38300</v>
+      </c>
+      <c r="E14" s="3">
         <v>200</v>
       </c>
-      <c r="E14" s="3">
+      <c r="F14" s="3">
         <v>25200</v>
       </c>
-      <c r="F14" s="3">
+      <c r="G14" s="3">
         <v>66200</v>
       </c>
-      <c r="G14" s="3">
+      <c r="H14" s="3">
         <v>11500</v>
       </c>
-      <c r="H14" s="3">
+      <c r="I14" s="3">
         <v>-1500</v>
       </c>
-      <c r="I14" s="3">
+      <c r="J14" s="3">
         <v>100</v>
       </c>
-      <c r="J14" s="3" t="s">
+      <c r="K14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="K14" s="3">
+      <c r="L14" s="3">
         <v>-1300</v>
       </c>
-      <c r="L14" s="3">
+      <c r="M14" s="3">
         <v>-4700</v>
-      </c>
-      <c r="M14" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="N14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="O14" s="3">
+      <c r="O14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="P14" s="3">
         <v>-300</v>
-      </c>
-      <c r="P14" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="Q14" s="3" t="s">
         <v>8</v>
@@ -1411,12 +1430,12 @@
       <c r="R14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="S14" s="3">
+      <c r="S14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="T14" s="3">
         <v>-200</v>
       </c>
-      <c r="T14" s="3">
-        <v>0</v>
-      </c>
       <c r="U14" s="3">
         <v>0</v>
       </c>
@@ -1424,22 +1443,22 @@
         <v>0</v>
       </c>
       <c r="W14" s="3">
+        <v>0</v>
+      </c>
+      <c r="X14" s="3">
         <v>9000</v>
       </c>
-      <c r="X14" s="3">
-        <v>0</v>
-      </c>
       <c r="Y14" s="3">
         <v>0</v>
       </c>
       <c r="Z14" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA14" s="3">
         <v>100</v>
       </c>
-      <c r="AA14" s="3">
-        <v>0</v>
-      </c>
-      <c r="AB14" s="3" t="s">
-        <v>8</v>
+      <c r="AB14" s="3">
+        <v>0</v>
       </c>
       <c r="AC14" s="3" t="s">
         <v>8</v>
@@ -1447,11 +1466,11 @@
       <c r="AD14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AE14" s="3">
+      <c r="AE14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AF14" s="3">
         <v>4500</v>
-      </c>
-      <c r="AF14" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="AG14" s="3" t="s">
         <v>8</v>
@@ -1465,35 +1484,38 @@
       <c r="AJ14" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AK14" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="15" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:37" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
-        <v>106200</v>
+        <v>102900</v>
       </c>
       <c r="E15" s="3">
+        <v>104200</v>
+      </c>
+      <c r="F15" s="3">
         <v>103900</v>
       </c>
-      <c r="F15" s="3">
+      <c r="G15" s="3">
         <v>108900</v>
       </c>
-      <c r="G15" s="3">
+      <c r="H15" s="3">
         <v>109900</v>
       </c>
-      <c r="H15" s="3">
-        <v>100200</v>
-      </c>
       <c r="I15" s="3">
+        <v>102100</v>
+      </c>
+      <c r="J15" s="3">
         <v>97200</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>99900</v>
       </c>
-      <c r="K15" s="3">
-        <v>0</v>
-      </c>
       <c r="L15" s="3">
         <v>0</v>
       </c>
@@ -1569,8 +1591,11 @@
       <c r="AJ15" s="3">
         <v>0</v>
       </c>
+      <c r="AK15" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="16" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:37" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1604,216 +1629,223 @@
       <c r="AH16" s="3"/>
       <c r="AI16" s="3"/>
       <c r="AJ16" s="3"/>
+      <c r="AK16" s="3"/>
     </row>
-    <row r="17" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="17" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>1296900</v>
+      </c>
+      <c r="E17" s="3">
         <v>1116700</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>1033600</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>1065500</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>1098300</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>911700</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>946100</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>1023800</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>1043600</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>930600</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>927400</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>943600</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>986700</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>857200</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>843000</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>838700</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>931200</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>806000</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>700800</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>559100</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>784600</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>603000</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>600600</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>580300</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>620800</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3">
         <v>439900</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AD17" s="3">
         <v>421100</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AE17" s="3">
         <v>408300</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AF17" s="3">
         <v>465300</v>
       </c>
-      <c r="AF17" s="3">
+      <c r="AG17" s="3">
         <v>326300</v>
       </c>
-      <c r="AG17" s="3">
+      <c r="AH17" s="3">
         <v>304300</v>
       </c>
-      <c r="AH17" s="3">
+      <c r="AI17" s="3">
         <v>284700</v>
       </c>
-      <c r="AI17" s="3">
+      <c r="AJ17" s="3">
         <v>322800</v>
       </c>
-      <c r="AJ17" s="3">
+      <c r="AK17" s="3">
         <v>234400</v>
       </c>
     </row>
-    <row r="18" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>473100</v>
+      </c>
+      <c r="E18" s="3">
         <v>405100</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>442400</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>313900</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>399300</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>332200</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>396900</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>283900</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>348100</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>305200</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>276000</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>155200</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>283300</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>193400</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>209100</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>90900</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>218200</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>172300</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>242600</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>58700</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>269700</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>218500</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>228100</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>115500</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>196500</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AC18" s="3">
         <v>152800</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AD18" s="3">
         <v>166400</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AE18" s="3">
         <v>100200</v>
       </c>
-      <c r="AE18" s="3">
+      <c r="AF18" s="3">
         <v>177500</v>
       </c>
-      <c r="AF18" s="3">
+      <c r="AG18" s="3">
         <v>140200</v>
       </c>
-      <c r="AG18" s="3">
+      <c r="AH18" s="3">
         <v>136700</v>
       </c>
-      <c r="AH18" s="3">
+      <c r="AI18" s="3">
         <v>95500</v>
       </c>
-      <c r="AI18" s="3">
+      <c r="AJ18" s="3">
         <v>141200</v>
       </c>
-      <c r="AJ18" s="3">
+      <c r="AK18" s="3">
         <v>107800</v>
       </c>
     </row>
-    <row r="19" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1850,276 +1882,283 @@
       <c r="AH19" s="3"/>
       <c r="AI19" s="3"/>
       <c r="AJ19" s="3"/>
+      <c r="AK19" s="3"/>
     </row>
-    <row r="20" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="20" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>-25000</v>
+      </c>
+      <c r="E20" s="3">
         <v>11200</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>-10200</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>-8900</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>6200</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>-3300</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>-18300</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>-21700</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>28800</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>23600</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>31200</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>13500</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>9900</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>12600</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>15600</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>13100</v>
       </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3">
         <v>3200</v>
       </c>
-      <c r="T20" s="3">
+      <c r="U20" s="3">
         <v>4800</v>
       </c>
-      <c r="U20" s="3">
+      <c r="V20" s="3">
         <v>17200</v>
       </c>
-      <c r="V20" s="3">
+      <c r="W20" s="3">
         <v>22500</v>
       </c>
-      <c r="W20" s="3">
+      <c r="X20" s="3">
         <v>137200</v>
       </c>
-      <c r="X20" s="3">
+      <c r="Y20" s="3">
         <v>27300</v>
       </c>
-      <c r="Y20" s="3">
+      <c r="Z20" s="3">
         <v>25500</v>
       </c>
-      <c r="Z20" s="3">
+      <c r="AA20" s="3">
         <v>18300</v>
       </c>
-      <c r="AA20" s="3">
+      <c r="AB20" s="3">
         <v>21500</v>
       </c>
-      <c r="AB20" s="3">
+      <c r="AC20" s="3">
         <v>24800</v>
       </c>
-      <c r="AC20" s="3">
+      <c r="AD20" s="3">
         <v>91900</v>
       </c>
-      <c r="AD20" s="3">
+      <c r="AE20" s="3">
         <v>3400</v>
       </c>
-      <c r="AE20" s="3">
+      <c r="AF20" s="3">
         <v>5700</v>
       </c>
-      <c r="AF20" s="3">
+      <c r="AG20" s="3">
         <v>2600</v>
       </c>
-      <c r="AG20" s="3">
+      <c r="AH20" s="3">
         <v>5500</v>
       </c>
-      <c r="AH20" s="3">
+      <c r="AI20" s="3">
         <v>3700</v>
       </c>
-      <c r="AI20" s="3">
+      <c r="AJ20" s="3">
         <v>3500</v>
       </c>
-      <c r="AJ20" s="3">
+      <c r="AK20" s="3">
         <v>1400</v>
       </c>
     </row>
-    <row r="21" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
-        <v>500100</v>
+        <v>601000</v>
       </c>
       <c r="E21" s="3">
+        <v>498100</v>
+      </c>
+      <c r="F21" s="3">
         <v>556600</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>431700</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>503100</v>
       </c>
-      <c r="H21" s="3">
-        <v>435600</v>
-      </c>
       <c r="I21" s="3">
+        <v>437500</v>
+      </c>
+      <c r="J21" s="3">
         <v>512500</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>405600</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>381000</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>327900</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>312700</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>256700</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>300500</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>202200</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>231000</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>178800</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>227200</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>184900</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>262500</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>145600</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>418900</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3">
         <v>246500</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="Z21" s="3">
         <v>255900</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AA21" s="3">
         <v>176900</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AB21" s="3">
         <v>223700</v>
       </c>
-      <c r="AB21" s="3">
+      <c r="AC21" s="3">
         <v>179800</v>
       </c>
-      <c r="AC21" s="3">
+      <c r="AD21" s="3">
         <v>259900</v>
       </c>
-      <c r="AD21" s="3">
+      <c r="AE21" s="3">
         <v>130400</v>
       </c>
-      <c r="AE21" s="3">
+      <c r="AF21" s="3">
         <v>183000</v>
       </c>
-      <c r="AF21" s="3">
+      <c r="AG21" s="3">
         <v>144500</v>
       </c>
-      <c r="AG21" s="3">
+      <c r="AH21" s="3">
         <v>143100</v>
       </c>
-      <c r="AH21" s="3">
+      <c r="AI21" s="3">
         <v>118100</v>
       </c>
-      <c r="AI21" s="3">
+      <c r="AJ21" s="3">
         <v>178100</v>
       </c>
-      <c r="AJ21" s="3">
+      <c r="AK21" s="3">
         <v>105200</v>
       </c>
     </row>
-    <row r="22" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
+        <v>9800</v>
+      </c>
+      <c r="E22" s="3">
         <v>9500</v>
       </c>
-      <c r="E22" s="3">
+      <c r="F22" s="3">
         <v>15900</v>
       </c>
-      <c r="F22" s="3">
+      <c r="G22" s="3">
         <v>11600</v>
       </c>
-      <c r="G22" s="3">
+      <c r="H22" s="3">
         <v>8700</v>
       </c>
-      <c r="H22" s="3">
+      <c r="I22" s="3">
         <v>11500</v>
       </c>
-      <c r="I22" s="3">
+      <c r="J22" s="3">
         <v>10000</v>
       </c>
-      <c r="J22" s="3">
+      <c r="K22" s="3">
         <v>10400</v>
       </c>
-      <c r="K22" s="3">
+      <c r="L22" s="3">
         <v>10700</v>
       </c>
-      <c r="L22" s="3">
+      <c r="M22" s="3">
         <v>4400</v>
       </c>
-      <c r="M22" s="3">
+      <c r="N22" s="3">
         <v>3200</v>
       </c>
-      <c r="N22" s="3">
+      <c r="O22" s="3">
         <v>8300</v>
       </c>
-      <c r="O22" s="3">
+      <c r="P22" s="3">
         <v>3400</v>
       </c>
-      <c r="P22" s="3">
+      <c r="Q22" s="3">
         <v>7400</v>
       </c>
-      <c r="Q22" s="3">
+      <c r="R22" s="3">
         <v>4900</v>
       </c>
-      <c r="R22" s="3">
+      <c r="S22" s="3">
         <v>2200</v>
       </c>
-      <c r="S22" s="3">
+      <c r="T22" s="3">
         <v>1700</v>
       </c>
-      <c r="T22" s="3">
+      <c r="U22" s="3">
         <v>2000</v>
       </c>
-      <c r="U22" s="3">
+      <c r="V22" s="3">
         <v>1300</v>
       </c>
-      <c r="V22" s="3">
-        <v>0</v>
-      </c>
       <c r="W22" s="3">
         <v>0</v>
       </c>
@@ -2142,236 +2181,245 @@
         <v>0</v>
       </c>
       <c r="AD22" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE22" s="3">
         <v>100</v>
-      </c>
-      <c r="AE22" s="3">
-        <v>400</v>
       </c>
       <c r="AF22" s="3">
         <v>400</v>
       </c>
       <c r="AG22" s="3">
+        <v>400</v>
+      </c>
+      <c r="AH22" s="3">
         <v>700</v>
       </c>
-      <c r="AH22" s="3">
+      <c r="AI22" s="3">
         <v>800</v>
       </c>
-      <c r="AI22" s="3">
+      <c r="AJ22" s="3">
         <v>100</v>
       </c>
-      <c r="AJ22" s="3">
+      <c r="AK22" s="3">
         <v>500</v>
       </c>
     </row>
-    <row r="23" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>480300</v>
+      </c>
+      <c r="E23" s="3">
         <v>418300</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>451200</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>278900</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>401400</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>359200</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>428300</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>308600</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>366100</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>324400</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>304100</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>160400</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>289800</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>198600</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>219900</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>101700</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>219700</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>175000</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>258500</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>81200</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>406900</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>245800</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>253500</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>133900</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>218000</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>177600</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AD23" s="3">
         <v>258300</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AE23" s="3">
         <v>103500</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AF23" s="3">
         <v>182800</v>
       </c>
-      <c r="AF23" s="3">
+      <c r="AG23" s="3">
         <v>142500</v>
       </c>
-      <c r="AG23" s="3">
+      <c r="AH23" s="3">
         <v>141400</v>
       </c>
-      <c r="AH23" s="3">
+      <c r="AI23" s="3">
         <v>98400</v>
       </c>
-      <c r="AI23" s="3">
+      <c r="AJ23" s="3">
         <v>144600</v>
       </c>
-      <c r="AJ23" s="3">
+      <c r="AK23" s="3">
         <v>108700</v>
       </c>
     </row>
-    <row r="24" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>145100</v>
+      </c>
+      <c r="E24" s="3">
         <v>79100</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>91500</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>78400</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>89800</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>37200</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>79400</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>66200</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>70600</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>60700</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>60900</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>35500</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>51200</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>32600</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>36600</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>21500</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>40300</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>-4100</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>44000</v>
       </c>
-      <c r="V24" s="3">
+      <c r="W24" s="3">
         <v>20500</v>
       </c>
-      <c r="W24" s="3">
+      <c r="X24" s="3">
         <v>51000</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Y24" s="3">
         <v>41500</v>
       </c>
-      <c r="Y24" s="3">
+      <c r="Z24" s="3">
         <v>44100</v>
       </c>
-      <c r="Z24" s="3">
+      <c r="AA24" s="3">
         <v>29200</v>
       </c>
-      <c r="AA24" s="3">
+      <c r="AB24" s="3">
         <v>32300</v>
       </c>
-      <c r="AB24" s="3">
+      <c r="AC24" s="3">
         <v>28200</v>
       </c>
-      <c r="AC24" s="3">
+      <c r="AD24" s="3">
         <v>49100</v>
       </c>
-      <c r="AD24" s="3">
+      <c r="AE24" s="3">
         <v>22100</v>
       </c>
-      <c r="AE24" s="3">
+      <c r="AF24" s="3">
         <v>1300</v>
       </c>
-      <c r="AF24" s="3">
+      <c r="AG24" s="3">
         <v>35300</v>
       </c>
-      <c r="AG24" s="3">
+      <c r="AH24" s="3">
         <v>34600</v>
       </c>
-      <c r="AH24" s="3">
+      <c r="AI24" s="3">
         <v>24200</v>
       </c>
-      <c r="AI24" s="3">
+      <c r="AJ24" s="3">
         <v>36600</v>
       </c>
-      <c r="AJ24" s="3">
+      <c r="AK24" s="3">
         <v>27100</v>
       </c>
     </row>
-    <row r="25" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2474,216 +2522,225 @@
       <c r="AJ25" s="3">
         <v>0</v>
       </c>
+      <c r="AK25" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="26" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="26" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>335200</v>
+      </c>
+      <c r="E26" s="3">
         <v>339200</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>359700</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>200500</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>311600</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>322000</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>348900</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>242400</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>295600</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>263700</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>243100</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>124900</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>238600</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>166000</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>183300</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>80200</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>179400</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>179100</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>214600</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>60700</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>355800</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>204200</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>209400</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>104700</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>185700</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AC26" s="3">
         <v>149400</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AD26" s="3">
         <v>209100</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AE26" s="3">
         <v>81300</v>
       </c>
-      <c r="AE26" s="3">
+      <c r="AF26" s="3">
         <v>181500</v>
       </c>
-      <c r="AF26" s="3">
+      <c r="AG26" s="3">
         <v>107200</v>
       </c>
-      <c r="AG26" s="3">
+      <c r="AH26" s="3">
         <v>106800</v>
       </c>
-      <c r="AH26" s="3">
+      <c r="AI26" s="3">
         <v>74200</v>
       </c>
-      <c r="AI26" s="3">
+      <c r="AJ26" s="3">
         <v>108000</v>
       </c>
-      <c r="AJ26" s="3">
+      <c r="AK26" s="3">
         <v>81600</v>
       </c>
     </row>
-    <row r="27" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>326400</v>
+      </c>
+      <c r="E27" s="3">
         <v>341600</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>359400</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>197500</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>309200</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>321400</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>350400</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>243200</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>304900</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>267300</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>251000</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>126000</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>242800</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>165800</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>185600</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>76600</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>179300</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>177000</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>213400</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>59100</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>358200</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>204000</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>207700</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>103600</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>185200</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AC27" s="3">
         <v>148300</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AD27" s="3">
         <v>208700</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AE27" s="3">
         <v>79900</v>
       </c>
-      <c r="AE27" s="3">
+      <c r="AF27" s="3">
         <v>181400</v>
-      </c>
-      <c r="AF27" s="3">
-        <v>106400</v>
       </c>
       <c r="AG27" s="3">
         <v>106400</v>
       </c>
       <c r="AH27" s="3">
+        <v>106400</v>
+      </c>
+      <c r="AI27" s="3">
         <v>73200</v>
       </c>
-      <c r="AI27" s="3">
+      <c r="AJ27" s="3">
         <v>105700</v>
       </c>
-      <c r="AJ27" s="3">
+      <c r="AK27" s="3">
         <v>73700</v>
       </c>
     </row>
-    <row r="28" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2786,8 +2843,11 @@
       <c r="AJ28" s="3">
         <v>0</v>
       </c>
+      <c r="AK28" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="29" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="29" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2890,8 +2950,11 @@
       <c r="AJ29" s="3">
         <v>0</v>
       </c>
+      <c r="AK29" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="30" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="30" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2994,8 +3057,11 @@
       <c r="AJ30" s="3">
         <v>0</v>
       </c>
+      <c r="AK30" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="31" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="31" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -3098,216 +3164,225 @@
       <c r="AJ31" s="3">
         <v>0</v>
       </c>
+      <c r="AK31" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="32" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="32" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>25000</v>
+      </c>
+      <c r="E32" s="3">
         <v>-11200</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>10200</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>8900</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>-6200</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>3300</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>18300</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>21700</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>-28800</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>-23600</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>-31200</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>-13500</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>-9900</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>-12600</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>-15600</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>-13100</v>
       </c>
-      <c r="S32" s="3">
+      <c r="T32" s="3">
         <v>-3200</v>
       </c>
-      <c r="T32" s="3">
+      <c r="U32" s="3">
         <v>-4800</v>
       </c>
-      <c r="U32" s="3">
+      <c r="V32" s="3">
         <v>-17200</v>
       </c>
-      <c r="V32" s="3">
+      <c r="W32" s="3">
         <v>-22500</v>
       </c>
-      <c r="W32" s="3">
+      <c r="X32" s="3">
         <v>-137200</v>
       </c>
-      <c r="X32" s="3">
+      <c r="Y32" s="3">
         <v>-27300</v>
       </c>
-      <c r="Y32" s="3">
+      <c r="Z32" s="3">
         <v>-25500</v>
       </c>
-      <c r="Z32" s="3">
+      <c r="AA32" s="3">
         <v>-18300</v>
       </c>
-      <c r="AA32" s="3">
+      <c r="AB32" s="3">
         <v>-21500</v>
       </c>
-      <c r="AB32" s="3">
+      <c r="AC32" s="3">
         <v>-24800</v>
       </c>
-      <c r="AC32" s="3">
+      <c r="AD32" s="3">
         <v>-91900</v>
       </c>
-      <c r="AD32" s="3">
+      <c r="AE32" s="3">
         <v>-3400</v>
       </c>
-      <c r="AE32" s="3">
+      <c r="AF32" s="3">
         <v>-5700</v>
       </c>
-      <c r="AF32" s="3">
+      <c r="AG32" s="3">
         <v>-2600</v>
       </c>
-      <c r="AG32" s="3">
+      <c r="AH32" s="3">
         <v>-5500</v>
       </c>
-      <c r="AH32" s="3">
+      <c r="AI32" s="3">
         <v>-3700</v>
       </c>
-      <c r="AI32" s="3">
+      <c r="AJ32" s="3">
         <v>-3500</v>
       </c>
-      <c r="AJ32" s="3">
+      <c r="AK32" s="3">
         <v>-1400</v>
       </c>
     </row>
-    <row r="33" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>326400</v>
+      </c>
+      <c r="E33" s="3">
         <v>341600</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>359400</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>197500</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>309200</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>321400</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>350400</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>243200</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>304900</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>267300</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>251000</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>126000</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>242800</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>165800</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>185600</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>76600</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>179300</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>177000</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>213400</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>59100</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>358200</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>204000</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>207700</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>103600</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>185200</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AC33" s="3">
         <v>148300</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AD33" s="3">
         <v>208700</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AE33" s="3">
         <v>79900</v>
       </c>
-      <c r="AE33" s="3">
+      <c r="AF33" s="3">
         <v>181400</v>
-      </c>
-      <c r="AF33" s="3">
-        <v>106400</v>
       </c>
       <c r="AG33" s="3">
         <v>106400</v>
       </c>
       <c r="AH33" s="3">
+        <v>106400</v>
+      </c>
+      <c r="AI33" s="3">
         <v>73200</v>
       </c>
-      <c r="AI33" s="3">
+      <c r="AJ33" s="3">
         <v>105700</v>
       </c>
-      <c r="AJ33" s="3">
+      <c r="AK33" s="3">
         <v>73700</v>
       </c>
     </row>
-    <row r="34" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3410,221 +3485,230 @@
       <c r="AJ34" s="3">
         <v>0</v>
       </c>
+      <c r="AK34" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="35" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="35" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>326400</v>
+      </c>
+      <c r="E35" s="3">
         <v>341600</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>359400</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>197500</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>309200</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>321400</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>350400</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>243200</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>304900</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>267300</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>251000</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>126000</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>242800</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>165800</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>185600</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>76600</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>179300</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>177000</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>213400</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>59100</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>358200</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>204000</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>207700</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>103600</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>185200</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AC35" s="3">
         <v>148300</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AD35" s="3">
         <v>208700</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AE35" s="3">
         <v>79900</v>
       </c>
-      <c r="AE35" s="3">
+      <c r="AF35" s="3">
         <v>181400</v>
-      </c>
-      <c r="AF35" s="3">
-        <v>106400</v>
       </c>
       <c r="AG35" s="3">
         <v>106400</v>
       </c>
       <c r="AH35" s="3">
+        <v>106400</v>
+      </c>
+      <c r="AI35" s="3">
         <v>73200</v>
       </c>
-      <c r="AI35" s="3">
+      <c r="AJ35" s="3">
         <v>105700</v>
       </c>
-      <c r="AJ35" s="3">
+      <c r="AK35" s="3">
         <v>73700</v>
       </c>
     </row>
-    <row r="37" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:37" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45657</v>
+      </c>
+      <c r="E38" s="2">
         <v>45565</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45473</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45382</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45291</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45199</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45107</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45016</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44926</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44834</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44742</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44651</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44561</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44469</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44377</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44286</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44196</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44104</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>44012</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>43921</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>43830</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>43738</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>43646</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>43555</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>43465</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43373</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>43281</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>43190</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AF38" s="2">
         <v>43100</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AG38" s="2">
         <v>43008</v>
       </c>
-      <c r="AG38" s="2">
+      <c r="AH38" s="2">
         <v>42916</v>
       </c>
-      <c r="AH38" s="2">
+      <c r="AI38" s="2">
         <v>42825</v>
       </c>
-      <c r="AI38" s="2">
+      <c r="AJ38" s="2">
         <v>42735</v>
       </c>
-      <c r="AJ38" s="2">
+      <c r="AK38" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="39" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3661,8 +3745,9 @@
       <c r="AH39" s="3"/>
       <c r="AI39" s="3"/>
       <c r="AJ39" s="3"/>
+      <c r="AK39" s="3"/>
     </row>
-    <row r="40" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="40" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3699,367 +3784,377 @@
       <c r="AH40" s="3"/>
       <c r="AI40" s="3"/>
       <c r="AJ40" s="3"/>
+      <c r="AK40" s="3"/>
     </row>
-    <row r="41" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="41" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>1844800</v>
+      </c>
+      <c r="E41" s="3">
         <v>1668400</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>1450700</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>1742800</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>1739400</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>1272500</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>1073000</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>1391100</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>1648400</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>2016100</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>1380200</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>1376400</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>1339400</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>1472400</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>1737600</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>1590500</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>1978400</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>2418000</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>775400</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>792000</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>811500</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>789200</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>1086500</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AA41" s="3">
         <v>926800</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AB41" s="3">
         <v>671300</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AC41" s="3">
         <v>877700</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AD41" s="3">
         <v>848700</v>
       </c>
-      <c r="AD41" s="3">
+      <c r="AE41" s="3">
         <v>486000</v>
       </c>
-      <c r="AE41" s="3">
+      <c r="AF41" s="3">
         <v>805100</v>
       </c>
-      <c r="AF41" s="3">
+      <c r="AG41" s="3">
         <v>768800</v>
       </c>
-      <c r="AG41" s="3">
+      <c r="AH41" s="3">
         <v>848000</v>
       </c>
-      <c r="AH41" s="3">
+      <c r="AI41" s="3">
         <v>920400</v>
       </c>
-      <c r="AI41" s="3">
+      <c r="AJ41" s="3">
         <v>1641600</v>
       </c>
-      <c r="AJ41" s="3">
+      <c r="AK41" s="3">
         <v>287600</v>
       </c>
     </row>
-    <row r="42" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>1212300</v>
+      </c>
+      <c r="E42" s="3">
         <v>1598600</v>
       </c>
-      <c r="E42" s="3">
+      <c r="F42" s="3">
         <v>1362200</v>
       </c>
-      <c r="F42" s="3">
+      <c r="G42" s="3">
         <v>974800</v>
       </c>
-      <c r="G42" s="3">
+      <c r="H42" s="3">
         <v>1066000</v>
       </c>
-      <c r="H42" s="3">
+      <c r="I42" s="3">
         <v>1048900</v>
       </c>
-      <c r="I42" s="3">
+      <c r="J42" s="3">
         <v>1097100</v>
       </c>
-      <c r="J42" s="3">
+      <c r="K42" s="3">
         <v>1292500</v>
       </c>
-      <c r="K42" s="3">
+      <c r="L42" s="3">
         <v>811100</v>
       </c>
-      <c r="L42" s="3">
+      <c r="M42" s="3">
         <v>960600</v>
       </c>
-      <c r="M42" s="3">
+      <c r="N42" s="3">
         <v>724400</v>
       </c>
-      <c r="N42" s="3">
+      <c r="O42" s="3">
         <v>556400</v>
       </c>
-      <c r="O42" s="3">
+      <c r="P42" s="3">
         <v>392000</v>
       </c>
-      <c r="P42" s="3">
+      <c r="Q42" s="3">
         <v>336100</v>
       </c>
-      <c r="Q42" s="3">
+      <c r="R42" s="3">
         <v>450800</v>
       </c>
-      <c r="R42" s="3">
+      <c r="S42" s="3">
         <v>794000</v>
       </c>
-      <c r="S42" s="3">
+      <c r="T42" s="3">
         <v>513700</v>
       </c>
-      <c r="T42" s="3">
+      <c r="U42" s="3">
         <v>708000</v>
       </c>
-      <c r="U42" s="3">
+      <c r="V42" s="3">
         <v>1243400</v>
       </c>
-      <c r="V42" s="3">
+      <c r="W42" s="3">
         <v>1596100</v>
       </c>
-      <c r="W42" s="3">
+      <c r="X42" s="3">
         <v>1711200</v>
       </c>
-      <c r="X42" s="3">
+      <c r="Y42" s="3">
         <v>1763500</v>
       </c>
-      <c r="Y42" s="3">
+      <c r="Z42" s="3">
         <v>1414900</v>
       </c>
-      <c r="Z42" s="3">
+      <c r="AA42" s="3">
         <v>1717000</v>
       </c>
-      <c r="AA42" s="3">
+      <c r="AB42" s="3">
         <v>1975100</v>
       </c>
-      <c r="AB42" s="3">
+      <c r="AC42" s="3">
         <v>1664900</v>
       </c>
-      <c r="AC42" s="3">
+      <c r="AD42" s="3">
         <v>1343800</v>
       </c>
-      <c r="AD42" s="3">
+      <c r="AE42" s="3">
         <v>795600</v>
       </c>
-      <c r="AE42" s="3">
+      <c r="AF42" s="3">
         <v>775400</v>
       </c>
-      <c r="AF42" s="3">
+      <c r="AG42" s="3">
         <v>819600</v>
       </c>
-      <c r="AG42" s="3">
+      <c r="AH42" s="3">
         <v>769700</v>
       </c>
-      <c r="AH42" s="3">
+      <c r="AI42" s="3">
         <v>700700</v>
-      </c>
-      <c r="AI42" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="AJ42" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AK42" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="43" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>390500</v>
+      </c>
+      <c r="E43" s="3">
         <v>307200</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>265400</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>241100</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>280800</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>329600</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>319700</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>266800</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>293900</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>265800</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>267700</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>264100</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>300200</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>260500</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>262000</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>187900</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>182600</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>252900</v>
       </c>
-      <c r="U43" s="3">
+      <c r="V43" s="3">
         <v>174200</v>
       </c>
-      <c r="V43" s="3">
+      <c r="W43" s="3">
         <v>210600</v>
       </c>
-      <c r="W43" s="3">
+      <c r="X43" s="3">
         <v>194200</v>
       </c>
-      <c r="X43" s="3">
+      <c r="Y43" s="3">
         <v>172000</v>
       </c>
-      <c r="Y43" s="3">
+      <c r="Z43" s="3">
         <v>177300</v>
       </c>
-      <c r="Z43" s="3">
+      <c r="AA43" s="3">
         <v>171100</v>
       </c>
-      <c r="AA43" s="3">
+      <c r="AB43" s="3">
         <v>162900</v>
       </c>
-      <c r="AB43" s="3">
+      <c r="AC43" s="3">
         <v>120200</v>
       </c>
-      <c r="AC43" s="3">
+      <c r="AD43" s="3">
         <v>209200</v>
       </c>
-      <c r="AD43" s="3">
+      <c r="AE43" s="3">
         <v>69200</v>
       </c>
-      <c r="AE43" s="3">
+      <c r="AF43" s="3">
         <v>53700</v>
       </c>
-      <c r="AF43" s="3">
+      <c r="AG43" s="3">
         <v>31000</v>
       </c>
-      <c r="AG43" s="3">
+      <c r="AH43" s="3">
         <v>28800</v>
       </c>
-      <c r="AH43" s="3">
+      <c r="AI43" s="3">
         <v>25200</v>
       </c>
-      <c r="AI43" s="3">
+      <c r="AJ43" s="3">
         <v>29600</v>
       </c>
-      <c r="AJ43" s="3">
+      <c r="AK43" s="3">
         <v>17800</v>
       </c>
     </row>
-    <row r="44" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
-        <v>3900</v>
+        <v>5300</v>
       </c>
       <c r="E44" s="3">
         <v>3900</v>
       </c>
       <c r="F44" s="3">
+        <v>3900</v>
+      </c>
+      <c r="G44" s="3">
         <v>5700</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>4000</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>3800</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>3700</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>4200</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>5700</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>8900</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>4000</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>8200</v>
       </c>
-      <c r="O44" s="3">
+      <c r="P44" s="3">
         <v>11400</v>
       </c>
-      <c r="P44" s="3">
+      <c r="Q44" s="3">
         <v>7100</v>
       </c>
-      <c r="Q44" s="3">
+      <c r="R44" s="3">
         <v>5700</v>
-      </c>
-      <c r="R44" s="3">
-        <v>7400</v>
       </c>
       <c r="S44" s="3">
         <v>7400</v>
@@ -4068,575 +4163,593 @@
         <v>7400</v>
       </c>
       <c r="U44" s="3">
+        <v>7400</v>
+      </c>
+      <c r="V44" s="3">
         <v>9500</v>
       </c>
-      <c r="V44" s="3">
+      <c r="W44" s="3">
         <v>8900</v>
       </c>
-      <c r="W44" s="3">
+      <c r="X44" s="3">
         <v>6800</v>
       </c>
-      <c r="X44" s="3">
+      <c r="Y44" s="3">
         <v>5600</v>
       </c>
-      <c r="Y44" s="3">
+      <c r="Z44" s="3">
         <v>5400</v>
       </c>
-      <c r="Z44" s="3">
+      <c r="AA44" s="3">
         <v>4700</v>
       </c>
-      <c r="AA44" s="3">
+      <c r="AB44" s="3">
         <v>6400</v>
       </c>
-      <c r="AB44" s="3">
+      <c r="AC44" s="3">
         <v>5200</v>
       </c>
-      <c r="AC44" s="3">
+      <c r="AD44" s="3">
         <v>5600</v>
       </c>
-      <c r="AD44" s="3">
+      <c r="AE44" s="3">
         <v>4400</v>
       </c>
-      <c r="AE44" s="3">
+      <c r="AF44" s="3">
         <v>5100</v>
       </c>
-      <c r="AF44" s="3">
+      <c r="AG44" s="3">
         <v>4200</v>
       </c>
-      <c r="AG44" s="3">
+      <c r="AH44" s="3">
         <v>4300</v>
       </c>
-      <c r="AH44" s="3">
+      <c r="AI44" s="3">
         <v>4600</v>
       </c>
-      <c r="AI44" s="3">
+      <c r="AJ44" s="3">
         <v>4900</v>
       </c>
-      <c r="AJ44" s="3">
+      <c r="AK44" s="3">
         <v>4100</v>
       </c>
     </row>
-    <row r="45" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>700500</v>
+      </c>
+      <c r="E45" s="3">
         <v>716400</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>759300</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>701200</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>599700</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>625500</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>606800</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>620000</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>691300</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>584100</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>567700</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>580200</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>528800</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>552300</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>501800</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>511200</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>425500</v>
       </c>
-      <c r="T45" s="3">
+      <c r="U45" s="3">
         <v>433900</v>
       </c>
-      <c r="U45" s="3">
+      <c r="V45" s="3">
         <v>423200</v>
       </c>
-      <c r="V45" s="3">
+      <c r="W45" s="3">
         <v>378400</v>
       </c>
-      <c r="W45" s="3">
+      <c r="X45" s="3">
         <v>371100</v>
       </c>
-      <c r="X45" s="3">
+      <c r="Y45" s="3">
         <v>313400</v>
       </c>
-      <c r="Y45" s="3">
+      <c r="Z45" s="3">
         <v>374900</v>
       </c>
-      <c r="Z45" s="3">
+      <c r="AA45" s="3">
         <v>264700</v>
       </c>
-      <c r="AA45" s="3">
+      <c r="AB45" s="3">
         <v>268100</v>
       </c>
-      <c r="AB45" s="3">
+      <c r="AC45" s="3">
         <v>213400</v>
       </c>
-      <c r="AC45" s="3">
+      <c r="AD45" s="3">
         <v>191900</v>
       </c>
-      <c r="AD45" s="3">
+      <c r="AE45" s="3">
         <v>168000</v>
       </c>
-      <c r="AE45" s="3">
+      <c r="AF45" s="3">
         <v>197700</v>
       </c>
-      <c r="AF45" s="3">
+      <c r="AG45" s="3">
         <v>172000</v>
       </c>
-      <c r="AG45" s="3">
+      <c r="AH45" s="3">
         <v>168000</v>
       </c>
-      <c r="AH45" s="3">
+      <c r="AI45" s="3">
         <v>226600</v>
       </c>
-      <c r="AI45" s="3">
+      <c r="AJ45" s="3">
         <v>241600</v>
       </c>
-      <c r="AJ45" s="3">
+      <c r="AK45" s="3">
         <v>149500</v>
       </c>
     </row>
-    <row r="46" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>4158600</v>
+      </c>
+      <c r="E46" s="3">
         <v>4299200</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>3844500</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>3703300</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>3801100</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>3388900</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>3217700</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>3680800</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>3450500</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>3835500</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>2944100</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>2785400</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>2571900</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>2628500</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>2957900</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>3091000</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>3107600</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>3820200</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>2625600</v>
       </c>
-      <c r="V46" s="3">
+      <c r="W46" s="3">
         <v>2986000</v>
       </c>
-      <c r="W46" s="3">
+      <c r="X46" s="3">
         <v>3094700</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Y46" s="3">
         <v>3043800</v>
       </c>
-      <c r="Y46" s="3">
+      <c r="Z46" s="3">
         <v>3059000</v>
       </c>
-      <c r="Z46" s="3">
+      <c r="AA46" s="3">
         <v>3084200</v>
       </c>
-      <c r="AA46" s="3">
+      <c r="AB46" s="3">
         <v>3083800</v>
       </c>
-      <c r="AB46" s="3">
+      <c r="AC46" s="3">
         <v>2881400</v>
       </c>
-      <c r="AC46" s="3">
+      <c r="AD46" s="3">
         <v>2599300</v>
       </c>
-      <c r="AD46" s="3">
+      <c r="AE46" s="3">
         <v>1523100</v>
       </c>
-      <c r="AE46" s="3">
+      <c r="AF46" s="3">
         <v>1837000</v>
       </c>
-      <c r="AF46" s="3">
+      <c r="AG46" s="3">
         <v>1795600</v>
       </c>
-      <c r="AG46" s="3">
+      <c r="AH46" s="3">
         <v>1818900</v>
       </c>
-      <c r="AH46" s="3">
+      <c r="AI46" s="3">
         <v>1877500</v>
       </c>
-      <c r="AI46" s="3">
+      <c r="AJ46" s="3">
         <v>1917600</v>
       </c>
-      <c r="AJ46" s="3">
+      <c r="AK46" s="3">
         <v>459000</v>
       </c>
     </row>
-    <row r="47" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>1902800</v>
+      </c>
+      <c r="E47" s="3">
         <v>2224700</v>
       </c>
-      <c r="E47" s="3">
+      <c r="F47" s="3">
         <v>2219600</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>2270700</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>2203700</v>
       </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3">
         <v>2439100</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>2055100</v>
       </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>1759700</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>1853300</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>1337100</v>
       </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3">
         <v>1167900</v>
       </c>
-      <c r="N47" s="3">
+      <c r="O47" s="3">
         <v>1019900</v>
       </c>
-      <c r="O47" s="3">
+      <c r="P47" s="3">
         <v>960200</v>
       </c>
-      <c r="P47" s="3">
+      <c r="Q47" s="3">
         <v>996500</v>
       </c>
-      <c r="Q47" s="3">
+      <c r="R47" s="3">
         <v>1076500</v>
       </c>
-      <c r="R47" s="3">
+      <c r="S47" s="3">
         <v>1100900</v>
       </c>
-      <c r="S47" s="3">
+      <c r="T47" s="3">
         <v>1049100</v>
       </c>
-      <c r="T47" s="3">
+      <c r="U47" s="3">
         <v>898800</v>
       </c>
-      <c r="U47" s="3">
+      <c r="V47" s="3">
         <v>876900</v>
       </c>
-      <c r="V47" s="3">
+      <c r="W47" s="3">
         <v>771500</v>
       </c>
-      <c r="W47" s="3">
+      <c r="X47" s="3">
         <v>709100</v>
       </c>
-      <c r="X47" s="3">
+      <c r="Y47" s="3">
         <v>347600</v>
       </c>
-      <c r="Y47" s="3">
+      <c r="Z47" s="3">
         <v>336200</v>
       </c>
-      <c r="Z47" s="3">
+      <c r="AA47" s="3">
         <v>332500</v>
       </c>
-      <c r="AA47" s="3">
+      <c r="AB47" s="3">
         <v>320600</v>
       </c>
-      <c r="AB47" s="3">
+      <c r="AC47" s="3">
         <v>239300</v>
       </c>
-      <c r="AC47" s="3">
+      <c r="AD47" s="3">
         <v>215800</v>
       </c>
-      <c r="AD47" s="3">
+      <c r="AE47" s="3">
         <v>86400</v>
       </c>
-      <c r="AE47" s="3">
+      <c r="AF47" s="3">
         <v>90600</v>
       </c>
-      <c r="AF47" s="3">
+      <c r="AG47" s="3">
         <v>82600</v>
       </c>
-      <c r="AG47" s="3">
+      <c r="AH47" s="3">
         <v>78200</v>
       </c>
-      <c r="AH47" s="3">
+      <c r="AI47" s="3">
         <v>76400</v>
       </c>
-      <c r="AI47" s="3">
+      <c r="AJ47" s="3">
         <v>78100</v>
       </c>
-      <c r="AJ47" s="3">
+      <c r="AK47" s="3">
         <v>69300</v>
       </c>
     </row>
-    <row r="48" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>4724100</v>
+      </c>
+      <c r="E48" s="3">
         <v>4870600</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>4637600</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>4645500</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>4633200</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>4456300</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>4371400</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>4453700</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>4176100</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>3977700</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>3845100</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>3707100</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>3558500</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>3435000</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>3191700</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>2895100</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>2706200</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>2552500</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>2274600</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>2237200</v>
       </c>
-      <c r="W48" s="3">
+      <c r="X48" s="3">
         <v>2059100</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Y48" s="3">
         <v>1814900</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="Z48" s="3">
         <v>1577900</v>
       </c>
-      <c r="Z48" s="3">
+      <c r="AA48" s="3">
         <v>1532300</v>
       </c>
-      <c r="AA48" s="3">
+      <c r="AB48" s="3">
         <v>1312300</v>
       </c>
-      <c r="AB48" s="3">
+      <c r="AC48" s="3">
         <v>1117100</v>
       </c>
-      <c r="AC48" s="3">
+      <c r="AD48" s="3">
         <v>1015500</v>
       </c>
-      <c r="AD48" s="3">
+      <c r="AE48" s="3">
         <v>983700</v>
       </c>
-      <c r="AE48" s="3">
+      <c r="AF48" s="3">
         <v>960700</v>
       </c>
-      <c r="AF48" s="3">
+      <c r="AG48" s="3">
         <v>866600</v>
       </c>
-      <c r="AG48" s="3">
+      <c r="AH48" s="3">
         <v>765200</v>
       </c>
-      <c r="AH48" s="3">
+      <c r="AI48" s="3">
         <v>668800</v>
       </c>
-      <c r="AI48" s="3">
+      <c r="AJ48" s="3">
         <v>591300</v>
       </c>
-      <c r="AJ48" s="3">
+      <c r="AK48" s="3">
         <v>479700</v>
       </c>
     </row>
-    <row r="49" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>1428800</v>
+      </c>
+      <c r="E49" s="3">
         <v>1476600</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>1381900</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>1376500</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>1396400</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>1358000</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>1370700</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>1446200</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>1369500</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>1331500</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>1350200</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>1338000</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>1324400</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>1333000</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>1321600</v>
       </c>
-      <c r="R49" s="3">
+      <c r="S49" s="3">
         <v>1295800</v>
       </c>
-      <c r="S49" s="3">
+      <c r="T49" s="3">
         <v>1203300</v>
       </c>
-      <c r="T49" s="3">
+      <c r="U49" s="3">
         <v>1236400</v>
       </c>
-      <c r="U49" s="3">
+      <c r="V49" s="3">
         <v>1195900</v>
       </c>
-      <c r="V49" s="3">
+      <c r="W49" s="3">
         <v>1154200</v>
       </c>
-      <c r="W49" s="3">
+      <c r="X49" s="3">
         <v>1046800</v>
       </c>
-      <c r="X49" s="3">
+      <c r="Y49" s="3">
         <v>1029800</v>
       </c>
-      <c r="Y49" s="3">
+      <c r="Z49" s="3">
         <v>987300</v>
       </c>
-      <c r="Z49" s="3">
+      <c r="AA49" s="3">
         <v>983500</v>
       </c>
-      <c r="AA49" s="3">
+      <c r="AB49" s="3">
         <v>909900</v>
       </c>
-      <c r="AB49" s="3">
+      <c r="AC49" s="3">
         <v>873300</v>
       </c>
-      <c r="AC49" s="3">
+      <c r="AD49" s="3">
         <v>861700</v>
       </c>
-      <c r="AD49" s="3">
+      <c r="AE49" s="3">
         <v>880200</v>
       </c>
-      <c r="AE49" s="3">
+      <c r="AF49" s="3">
         <v>876300</v>
       </c>
-      <c r="AF49" s="3">
+      <c r="AG49" s="3">
         <v>841400</v>
       </c>
-      <c r="AG49" s="3">
+      <c r="AH49" s="3">
         <v>835000</v>
       </c>
-      <c r="AH49" s="3">
+      <c r="AI49" s="3">
         <v>815900</v>
       </c>
-      <c r="AI49" s="3">
+      <c r="AJ49" s="3">
         <v>794000</v>
       </c>
-      <c r="AJ49" s="3">
+      <c r="AK49" s="3">
         <v>777200</v>
       </c>
     </row>
-    <row r="50" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -4739,8 +4852,11 @@
       <c r="AJ50" s="3">
         <v>0</v>
       </c>
+      <c r="AK50" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="51" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="51" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -4843,112 +4959,118 @@
       <c r="AJ51" s="3">
         <v>0</v>
       </c>
+      <c r="AK51" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="52" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="52" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>126000</v>
+      </c>
+      <c r="E52" s="3">
         <v>74300</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>128200</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>99600</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>99000</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>72800</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>53000</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>74600</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>220900</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>238500</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>216500</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>234300</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>233800</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>230200</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>251600</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>250600</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>175100</v>
       </c>
-      <c r="T52" s="3">
+      <c r="U52" s="3">
         <v>172000</v>
       </c>
-      <c r="U52" s="3">
+      <c r="V52" s="3">
         <v>170900</v>
       </c>
-      <c r="V52" s="3">
+      <c r="W52" s="3">
         <v>179500</v>
       </c>
-      <c r="W52" s="3">
+      <c r="X52" s="3">
         <v>156400</v>
       </c>
-      <c r="X52" s="3">
+      <c r="Y52" s="3">
         <v>391500</v>
       </c>
-      <c r="Y52" s="3">
+      <c r="Z52" s="3">
         <v>232100</v>
       </c>
-      <c r="Z52" s="3">
+      <c r="AA52" s="3">
         <v>172600</v>
       </c>
-      <c r="AA52" s="3">
+      <c r="AB52" s="3">
         <v>136600</v>
       </c>
-      <c r="AB52" s="3">
+      <c r="AC52" s="3">
         <v>108700</v>
       </c>
-      <c r="AC52" s="3">
+      <c r="AD52" s="3">
         <v>108200</v>
       </c>
-      <c r="AD52" s="3">
+      <c r="AE52" s="3">
         <v>87800</v>
       </c>
-      <c r="AE52" s="3">
+      <c r="AF52" s="3">
         <v>68500</v>
       </c>
-      <c r="AF52" s="3">
+      <c r="AG52" s="3">
         <v>45800</v>
       </c>
-      <c r="AG52" s="3">
+      <c r="AH52" s="3">
         <v>34600</v>
       </c>
-      <c r="AH52" s="3">
+      <c r="AI52" s="3">
         <v>28700</v>
       </c>
-      <c r="AI52" s="3">
+      <c r="AJ52" s="3">
         <v>22500</v>
       </c>
-      <c r="AJ52" s="3">
+      <c r="AK52" s="3">
         <v>26400</v>
       </c>
     </row>
-    <row r="53" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -5051,112 +5173,118 @@
       <c r="AJ53" s="3">
         <v>0</v>
       </c>
+      <c r="AK53" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="54" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="54" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>12650900</v>
+      </c>
+      <c r="E54" s="3">
         <v>13303900</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>12536800</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>12447200</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>12475900</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>11986900</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>11314300</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>11747600</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>11070300</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>10720300</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>9523700</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>9084600</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>8648800</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>8623200</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>8799300</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>8633300</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>8241300</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>8679900</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>7144000</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>7328400</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>7066200</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>6627600</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>6192400</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>6105100</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AB54" s="3">
         <v>5763100</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AC54" s="3">
         <v>5219700</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AD54" s="3">
         <v>4800400</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AE54" s="3">
         <v>3561300</v>
       </c>
-      <c r="AE54" s="3">
+      <c r="AF54" s="3">
         <v>3833100</v>
       </c>
-      <c r="AF54" s="3">
+      <c r="AG54" s="3">
         <v>3632000</v>
       </c>
-      <c r="AG54" s="3">
+      <c r="AH54" s="3">
         <v>3531800</v>
       </c>
-      <c r="AH54" s="3">
+      <c r="AI54" s="3">
         <v>3467300</v>
       </c>
-      <c r="AI54" s="3">
+      <c r="AJ54" s="3">
         <v>3403600</v>
       </c>
-      <c r="AJ54" s="3">
+      <c r="AK54" s="3">
         <v>1811700</v>
       </c>
     </row>
-    <row r="55" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -5193,8 +5321,9 @@
       <c r="AH55" s="3"/>
       <c r="AI55" s="3"/>
       <c r="AJ55" s="3"/>
+      <c r="AK55" s="3"/>
     </row>
-    <row r="56" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="56" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -5231,177 +5360,181 @@
       <c r="AH56" s="3"/>
       <c r="AI56" s="3"/>
       <c r="AJ56" s="3"/>
+      <c r="AK56" s="3"/>
     </row>
-    <row r="57" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="57" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>337500</v>
+      </c>
+      <c r="E57" s="3">
         <v>323200</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>308300</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>323300</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>368200</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>300100</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>293200</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>345800</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>310500</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>245700</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>265700</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>238900</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>269700</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>231300</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>229300</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>222800</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>227700</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>216400</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>162900</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>185600</v>
       </c>
-      <c r="W57" s="3">
+      <c r="X57" s="3">
         <v>227200</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Y57" s="3">
         <v>167200</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="Z57" s="3">
         <v>181100</v>
       </c>
-      <c r="Z57" s="3">
+      <c r="AA57" s="3">
         <v>157100</v>
       </c>
-      <c r="AA57" s="3">
+      <c r="AB57" s="3">
         <v>190500</v>
       </c>
-      <c r="AB57" s="3">
+      <c r="AC57" s="3">
         <v>117200</v>
       </c>
-      <c r="AC57" s="3">
+      <c r="AD57" s="3">
         <v>130700</v>
       </c>
-      <c r="AD57" s="3">
+      <c r="AE57" s="3">
         <v>133200</v>
       </c>
-      <c r="AE57" s="3">
+      <c r="AF57" s="3">
         <v>132000</v>
       </c>
-      <c r="AF57" s="3">
+      <c r="AG57" s="3">
         <v>84900</v>
       </c>
-      <c r="AG57" s="3">
+      <c r="AH57" s="3">
         <v>73000</v>
       </c>
-      <c r="AH57" s="3">
+      <c r="AI57" s="3">
         <v>98200</v>
       </c>
-      <c r="AI57" s="3">
+      <c r="AJ57" s="3">
         <v>92600</v>
       </c>
-      <c r="AJ57" s="3">
+      <c r="AK57" s="3">
         <v>65500</v>
       </c>
     </row>
-    <row r="58" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>2324600</v>
+      </c>
+      <c r="E58" s="3">
         <v>2554100</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>1451100</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>1138800</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>1121500</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>1346600</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>958600</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>994900</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>788700</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>993100</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>1015500</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>847900</v>
       </c>
-      <c r="O58" s="3">
+      <c r="P58" s="3">
         <v>500600</v>
       </c>
-      <c r="P58" s="3">
+      <c r="Q58" s="3">
         <v>678800</v>
       </c>
-      <c r="Q58" s="3">
+      <c r="R58" s="3">
         <v>537500</v>
       </c>
-      <c r="R58" s="3">
+      <c r="S58" s="3">
         <v>433100</v>
       </c>
-      <c r="S58" s="3">
+      <c r="T58" s="3">
         <v>244900</v>
       </c>
-      <c r="T58" s="3">
+      <c r="U58" s="3">
         <v>413300</v>
       </c>
-      <c r="U58" s="3">
+      <c r="V58" s="3">
         <v>322200</v>
       </c>
-      <c r="V58" s="3">
+      <c r="W58" s="3">
         <v>47300</v>
       </c>
-      <c r="W58" s="3">
-        <v>0</v>
-      </c>
-      <c r="X58" s="3" t="s">
-        <v>8</v>
+      <c r="X58" s="3">
+        <v>0</v>
       </c>
       <c r="Y58" s="3" t="s">
         <v>8</v>
@@ -5409,8 +5542,8 @@
       <c r="Z58" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AA58" s="3">
-        <v>0</v>
+      <c r="AA58" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="AB58" s="3">
         <v>0</v>
@@ -5422,7 +5555,7 @@
         <v>0</v>
       </c>
       <c r="AE58" s="3">
-        <v>37100</v>
+        <v>0</v>
       </c>
       <c r="AF58" s="3">
         <v>37100</v>
@@ -5431,257 +5564,266 @@
         <v>37100</v>
       </c>
       <c r="AH58" s="3">
+        <v>37100</v>
+      </c>
+      <c r="AI58" s="3">
         <v>101800</v>
       </c>
-      <c r="AI58" s="3">
+      <c r="AJ58" s="3">
         <v>65400</v>
       </c>
-      <c r="AJ58" s="3">
+      <c r="AK58" s="3">
         <v>43600</v>
       </c>
     </row>
-    <row r="59" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>1211400</v>
+      </c>
+      <c r="E59" s="3">
         <v>1582400</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>1280300</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>1759300</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>1114400</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>1248600</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>1192600</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>1440100</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>1213600</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>1179100</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>1079000</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>1121000</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>1020300</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>902400</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>855200</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>966600</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>828600</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>822800</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>808400</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>1052600</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>801600</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Y59" s="3">
         <v>687500</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="Z59" s="3">
         <v>630100</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AA59" s="3">
         <v>711200</v>
       </c>
-      <c r="AA59" s="3">
+      <c r="AB59" s="3">
         <v>556200</v>
       </c>
-      <c r="AB59" s="3">
+      <c r="AC59" s="3">
         <v>432100</v>
       </c>
-      <c r="AC59" s="3">
+      <c r="AD59" s="3">
         <v>419700</v>
       </c>
-      <c r="AD59" s="3">
+      <c r="AE59" s="3">
         <v>424600</v>
       </c>
-      <c r="AE59" s="3">
+      <c r="AF59" s="3">
         <v>446300</v>
       </c>
-      <c r="AF59" s="3">
+      <c r="AG59" s="3">
         <v>419000</v>
       </c>
-      <c r="AG59" s="3">
+      <c r="AH59" s="3">
         <v>349800</v>
       </c>
-      <c r="AH59" s="3">
+      <c r="AI59" s="3">
         <v>311200</v>
       </c>
-      <c r="AI59" s="3">
+      <c r="AJ59" s="3">
         <v>354300</v>
       </c>
-      <c r="AJ59" s="3">
+      <c r="AK59" s="3">
         <v>296300</v>
       </c>
     </row>
-    <row r="60" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>3873500</v>
+      </c>
+      <c r="E60" s="3">
         <v>4459700</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>3039700</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>3221500</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>2829100</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>2895300</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>2444400</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>2780800</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>2312800</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>2417900</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>2360200</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>2207700</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>1790600</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>1812500</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>1622000</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>1622600</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>1301200</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>1452600</v>
       </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
         <v>1293500</v>
       </c>
-      <c r="V60" s="3">
+      <c r="W60" s="3">
         <v>1285600</v>
       </c>
-      <c r="W60" s="3">
+      <c r="X60" s="3">
         <v>1028700</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Y60" s="3">
         <v>854700</v>
       </c>
-      <c r="Y60" s="3">
+      <c r="Z60" s="3">
         <v>811200</v>
       </c>
-      <c r="Z60" s="3">
+      <c r="AA60" s="3">
         <v>868200</v>
       </c>
-      <c r="AA60" s="3">
+      <c r="AB60" s="3">
         <v>746700</v>
       </c>
-      <c r="AB60" s="3">
+      <c r="AC60" s="3">
         <v>549300</v>
       </c>
-      <c r="AC60" s="3">
+      <c r="AD60" s="3">
         <v>550400</v>
       </c>
-      <c r="AD60" s="3">
+      <c r="AE60" s="3">
         <v>557800</v>
       </c>
-      <c r="AE60" s="3">
+      <c r="AF60" s="3">
         <v>615300</v>
       </c>
-      <c r="AF60" s="3">
+      <c r="AG60" s="3">
         <v>541000</v>
       </c>
-      <c r="AG60" s="3">
+      <c r="AH60" s="3">
         <v>459900</v>
       </c>
-      <c r="AH60" s="3">
+      <c r="AI60" s="3">
         <v>511200</v>
       </c>
-      <c r="AI60" s="3">
+      <c r="AJ60" s="3">
         <v>512300</v>
       </c>
-      <c r="AJ60" s="3">
+      <c r="AK60" s="3">
         <v>405500</v>
       </c>
     </row>
-    <row r="61" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>51700</v>
+      </c>
+      <c r="E61" s="3">
         <v>53300</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>1038300</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>1047500</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>1055600</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>1050000</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>1054200</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>1055700</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>957100</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>966000</v>
       </c>
-      <c r="M61" s="3">
-        <v>0</v>
-      </c>
       <c r="N61" s="3">
         <v>0</v>
       </c>
@@ -5751,8 +5893,11 @@
       <c r="AJ61" s="3">
         <v>0</v>
       </c>
+      <c r="AK61" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="62" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
@@ -5777,86 +5922,89 @@
       <c r="J62" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="K62" s="3">
+      <c r="K62" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="L62" s="3">
         <v>120800</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>101000</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>110000</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>114700</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>116900</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>120300</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>115800</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>110200</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>105400</v>
       </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>99300</v>
       </c>
-      <c r="U62" s="3">
+      <c r="V62" s="3">
         <v>104200</v>
       </c>
-      <c r="V62" s="3">
+      <c r="W62" s="3">
         <v>117500</v>
       </c>
-      <c r="W62" s="3">
+      <c r="X62" s="3">
         <v>124100</v>
       </c>
-      <c r="X62" s="3">
+      <c r="Y62" s="3">
         <v>95900</v>
       </c>
-      <c r="Y62" s="3">
+      <c r="Z62" s="3">
         <v>96500</v>
       </c>
-      <c r="Z62" s="3">
+      <c r="AA62" s="3">
         <v>121000</v>
       </c>
-      <c r="AA62" s="3">
+      <c r="AB62" s="3">
         <v>39500</v>
       </c>
-      <c r="AB62" s="3">
+      <c r="AC62" s="3">
         <v>33600</v>
       </c>
-      <c r="AC62" s="3">
+      <c r="AD62" s="3">
         <v>33400</v>
       </c>
-      <c r="AD62" s="3">
+      <c r="AE62" s="3">
         <v>34000</v>
       </c>
-      <c r="AE62" s="3">
+      <c r="AF62" s="3">
         <v>35700</v>
       </c>
-      <c r="AF62" s="3">
+      <c r="AG62" s="3">
         <v>30000</v>
       </c>
-      <c r="AG62" s="3">
+      <c r="AH62" s="3">
         <v>30300</v>
       </c>
-      <c r="AH62" s="3">
+      <c r="AI62" s="3">
         <v>23500</v>
       </c>
-      <c r="AI62" s="3">
+      <c r="AJ62" s="3">
         <v>19000</v>
       </c>
-      <c r="AJ62" s="3">
+      <c r="AK62" s="3">
         <v>19100</v>
       </c>
     </row>
-    <row r="63" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -5959,8 +6107,11 @@
       <c r="AJ63" s="3">
         <v>0</v>
       </c>
+      <c r="AK63" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="64" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="64" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -6063,8 +6214,11 @@
       <c r="AJ64" s="3">
         <v>0</v>
       </c>
+      <c r="AK64" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="65" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="65" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -6167,112 +6321,118 @@
       <c r="AJ65" s="3">
         <v>0</v>
       </c>
+      <c r="AK65" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="66" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="66" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>4064300</v>
+      </c>
+      <c r="E66" s="3">
         <v>4590200</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>4146200</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>4360500</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>3974800</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>3992800</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>3546600</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>3885900</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>3453300</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>3547700</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>2528500</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>2353800</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>1947500</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>1953500</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>1753500</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>1752700</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>1423500</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>1568300</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>1414400</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>1419300</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>1168400</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>965800</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>919500</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>999600</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AB66" s="3">
         <v>793800</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AC66" s="3">
         <v>588000</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AD66" s="3">
         <v>584900</v>
       </c>
-      <c r="AD66" s="3">
+      <c r="AE66" s="3">
         <v>592700</v>
       </c>
-      <c r="AE66" s="3">
+      <c r="AF66" s="3">
         <v>651900</v>
       </c>
-      <c r="AF66" s="3">
+      <c r="AG66" s="3">
         <v>571800</v>
       </c>
-      <c r="AG66" s="3">
+      <c r="AH66" s="3">
         <v>491000</v>
       </c>
-      <c r="AH66" s="3">
+      <c r="AI66" s="3">
         <v>535400</v>
       </c>
-      <c r="AI66" s="3">
+      <c r="AJ66" s="3">
         <v>532100</v>
       </c>
-      <c r="AJ66" s="3">
+      <c r="AK66" s="3">
         <v>424600</v>
       </c>
     </row>
-    <row r="67" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -6309,8 +6469,9 @@
       <c r="AH67" s="3"/>
       <c r="AI67" s="3"/>
       <c r="AJ67" s="3"/>
+      <c r="AK67" s="3"/>
     </row>
-    <row r="68" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="68" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -6413,8 +6574,11 @@
       <c r="AJ68" s="3">
         <v>0</v>
       </c>
+      <c r="AK68" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="69" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="69" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -6517,8 +6681,11 @@
       <c r="AJ69" s="3">
         <v>0</v>
       </c>
+      <c r="AK69" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="70" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="70" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -6619,10 +6786,13 @@
         <v>0</v>
       </c>
       <c r="AJ70" s="3">
+        <v>0</v>
+      </c>
+      <c r="AK70" s="3">
         <v>304900</v>
       </c>
     </row>
-    <row r="71" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="71" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -6725,112 +6895,118 @@
       <c r="AJ71" s="3">
         <v>0</v>
       </c>
+      <c r="AK71" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="72" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="72" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>5356600</v>
+      </c>
+      <c r="E72" s="3">
         <v>5234300</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>5041300</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>4711900</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>5119400</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>4715800</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>4457100</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>4478700</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>4153200</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>3771300</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>3525800</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>3280400</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>3129900</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>2978700</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>3182700</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>3093800</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>2928600</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>2910500</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>2733500</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>2697900</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>2575600</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>2246600</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>2000300</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AA72" s="3">
         <v>1784800</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AB72" s="3">
         <v>1605100</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AC72" s="3">
         <v>1368400</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AD72" s="3">
         <v>1220100</v>
       </c>
-      <c r="AD72" s="3">
+      <c r="AE72" s="3">
         <v>1036800</v>
       </c>
-      <c r="AE72" s="3">
+      <c r="AF72" s="3">
         <v>989800</v>
       </c>
-      <c r="AF72" s="3">
+      <c r="AG72" s="3">
         <v>808400</v>
       </c>
-      <c r="AG72" s="3">
+      <c r="AH72" s="3">
         <v>702000</v>
       </c>
-      <c r="AH72" s="3">
+      <c r="AI72" s="3">
         <v>583600</v>
       </c>
-      <c r="AI72" s="3">
+      <c r="AJ72" s="3">
         <v>510400</v>
       </c>
-      <c r="AJ72" s="3">
+      <c r="AK72" s="3">
         <v>404700</v>
       </c>
     </row>
-    <row r="73" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -6933,8 +7109,11 @@
       <c r="AJ73" s="3">
         <v>0</v>
       </c>
+      <c r="AK73" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="74" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="74" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -7037,8 +7216,11 @@
       <c r="AJ74" s="3">
         <v>0</v>
       </c>
+      <c r="AK74" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="75" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="75" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -7141,112 +7323,118 @@
       <c r="AJ75" s="3">
         <v>0</v>
       </c>
+      <c r="AK75" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="76" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="76" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>8502700</v>
+      </c>
+      <c r="E76" s="3">
         <v>8638000</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>8315300</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>8011000</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>8433600</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>7934600</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>7708500</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>7797800</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>7616900</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>7172500</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>6995300</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>6730800</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>6701200</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>6669700</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>7045800</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>6880500</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>6817900</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>7111600</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>5729500</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>5909100</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>5897800</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>5661800</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>5272900</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>5105500</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AB76" s="3">
         <v>4969400</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AC76" s="3">
         <v>4631700</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AD76" s="3">
         <v>4215500</v>
       </c>
-      <c r="AD76" s="3">
+      <c r="AE76" s="3">
         <v>2968500</v>
       </c>
-      <c r="AE76" s="3">
+      <c r="AF76" s="3">
         <v>3181200</v>
       </c>
-      <c r="AF76" s="3">
+      <c r="AG76" s="3">
         <v>3060200</v>
       </c>
-      <c r="AG76" s="3">
+      <c r="AH76" s="3">
         <v>3040800</v>
       </c>
-      <c r="AH76" s="3">
+      <c r="AI76" s="3">
         <v>2931800</v>
       </c>
-      <c r="AI76" s="3">
+      <c r="AJ76" s="3">
         <v>2871500</v>
       </c>
-      <c r="AJ76" s="3">
+      <c r="AK76" s="3">
         <v>1082100</v>
       </c>
     </row>
-    <row r="77" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -7349,221 +7537,230 @@
       <c r="AJ77" s="3">
         <v>0</v>
       </c>
+      <c r="AK77" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="79" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="79" spans="2:37" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45657</v>
+      </c>
+      <c r="E80" s="2">
         <v>45565</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45473</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45382</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45291</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45199</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45107</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45016</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44926</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44834</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44742</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44651</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44561</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44469</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44377</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44286</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44196</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44104</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>44012</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>43921</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>43830</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>43738</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>43646</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>43555</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>43465</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43373</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>43281</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>43190</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AF80" s="2">
         <v>43100</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AG80" s="2">
         <v>43008</v>
       </c>
-      <c r="AG80" s="2">
+      <c r="AH80" s="2">
         <v>42916</v>
       </c>
-      <c r="AH80" s="2">
+      <c r="AI80" s="2">
         <v>42825</v>
       </c>
-      <c r="AI80" s="2">
+      <c r="AJ80" s="2">
         <v>42735</v>
       </c>
-      <c r="AJ80" s="2">
+      <c r="AK80" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="81" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>326400</v>
+      </c>
+      <c r="E81" s="3">
         <v>341600</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>359400</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>197500</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>309200</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>321400</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>350400</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>243200</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>304900</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>267300</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>251000</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>126000</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>242800</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>165800</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>185600</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>76600</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>179300</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>177000</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>213400</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>59100</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>358200</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>204000</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>207700</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>103600</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>185200</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AC81" s="3">
         <v>148300</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AD81" s="3">
         <v>208700</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AE81" s="3">
         <v>79900</v>
       </c>
-      <c r="AE81" s="3">
+      <c r="AF81" s="3">
         <v>181400</v>
-      </c>
-      <c r="AF81" s="3">
-        <v>106400</v>
       </c>
       <c r="AG81" s="3">
         <v>106400</v>
       </c>
       <c r="AH81" s="3">
+        <v>106400</v>
+      </c>
+      <c r="AI81" s="3">
         <v>73200</v>
       </c>
-      <c r="AI81" s="3">
+      <c r="AJ81" s="3">
         <v>105700</v>
       </c>
-      <c r="AJ81" s="3">
+      <c r="AK81" s="3">
         <v>73700</v>
       </c>
     </row>
-    <row r="82" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -7600,35 +7797,36 @@
       <c r="AH82" s="3"/>
       <c r="AI82" s="3"/>
       <c r="AJ82" s="3"/>
+      <c r="AK82" s="3"/>
     </row>
-    <row r="83" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="83" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
-        <v>95300</v>
+        <v>99400</v>
       </c>
       <c r="E83" s="3">
+        <v>97700</v>
+      </c>
+      <c r="F83" s="3">
         <v>92600</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>94900</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>96500</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>89000</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>95600</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>94900</v>
       </c>
-      <c r="K83" s="3">
-        <v>0</v>
-      </c>
       <c r="L83" s="3">
         <v>0</v>
       </c>
@@ -7704,8 +7902,11 @@
       <c r="AJ83" s="3">
         <v>0</v>
       </c>
+      <c r="AK83" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="84" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -7808,8 +8009,11 @@
       <c r="AJ84" s="3">
         <v>0</v>
       </c>
+      <c r="AK84" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="85" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="85" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -7912,8 +8116,11 @@
       <c r="AJ85" s="3">
         <v>0</v>
       </c>
+      <c r="AK85" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="86" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="86" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -8016,8 +8223,11 @@
       <c r="AJ86" s="3">
         <v>0</v>
       </c>
+      <c r="AK86" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="87" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="87" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -8120,8 +8330,11 @@
       <c r="AJ87" s="3">
         <v>0</v>
       </c>
+      <c r="AK87" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="88" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="88" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -8224,112 +8437,118 @@
       <c r="AJ88" s="3">
         <v>0</v>
       </c>
+      <c r="AK88" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="89" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="89" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>384500</v>
+      </c>
+      <c r="E89" s="3">
         <v>443600</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>478900</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>281300</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>553300</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>402700</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>518700</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>398600</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>531500</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>390100</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>525600</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>153700</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>416600</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>254000</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>277500</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>68500</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>284000</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>218200</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>184500</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>28000</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>348100</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>221200</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>304500</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AA89" s="3">
         <v>96300</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AB89" s="3">
         <v>261800</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AC89" s="3">
         <v>127600</v>
       </c>
-      <c r="AC89" s="3">
+      <c r="AD89" s="3">
         <v>206600</v>
       </c>
-      <c r="AD89" s="3">
+      <c r="AE89" s="3">
         <v>30700</v>
       </c>
-      <c r="AE89" s="3">
+      <c r="AF89" s="3">
         <v>203600</v>
       </c>
-      <c r="AF89" s="3">
+      <c r="AG89" s="3">
         <v>152000</v>
       </c>
-      <c r="AG89" s="3">
+      <c r="AH89" s="3">
         <v>134100</v>
       </c>
-      <c r="AH89" s="3">
+      <c r="AI89" s="3">
         <v>48200</v>
       </c>
-      <c r="AI89" s="3">
+      <c r="AJ89" s="3">
         <v>166300</v>
       </c>
-      <c r="AJ89" s="3">
+      <c r="AK89" s="3">
         <v>121000</v>
       </c>
     </row>
-    <row r="90" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -8366,35 +8585,36 @@
       <c r="AH90" s="3"/>
       <c r="AI90" s="3"/>
       <c r="AJ90" s="3"/>
+      <c r="AK90" s="3"/>
     </row>
-    <row r="91" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="91" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="E91" s="3">
+      <c r="E91" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F91" s="3">
         <v>-364200</v>
       </c>
-      <c r="F91" s="3" t="s">
+      <c r="G91" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-920700</v>
       </c>
-      <c r="H91" s="3" t="s">
+      <c r="I91" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-613200</v>
       </c>
-      <c r="J91" s="3" t="s">
+      <c r="K91" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="K91" s="3">
-        <v>0</v>
-      </c>
       <c r="L91" s="3">
         <v>0</v>
       </c>
@@ -8470,8 +8690,11 @@
       <c r="AJ91" s="3">
         <v>0</v>
       </c>
+      <c r="AK91" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="92" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -8574,8 +8797,11 @@
       <c r="AJ92" s="3">
         <v>0</v>
       </c>
+      <c r="AK92" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="93" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="93" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -8678,112 +8904,118 @@
       <c r="AJ93" s="3">
         <v>0</v>
       </c>
+      <c r="AK93" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="94" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="94" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>407500</v>
+      </c>
+      <c r="E94" s="3">
         <v>-272300</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-642100</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-329400</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>166600</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-551700</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-488300</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-854000</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-617600</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-654400</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-501800</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-460800</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-387700</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-197000</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-26500</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-627900</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>-406000</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>173900</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>-161800</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>-112800</v>
       </c>
-      <c r="W94" s="3">
+      <c r="X94" s="3">
         <v>-314600</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Y94" s="3">
         <v>-626500</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="Z94" s="3">
         <v>229000</v>
       </c>
-      <c r="Z94" s="3">
+      <c r="AA94" s="3">
         <v>136200</v>
       </c>
-      <c r="AA94" s="3">
+      <c r="AB94" s="3">
         <v>-483600</v>
       </c>
-      <c r="AB94" s="3">
+      <c r="AC94" s="3">
         <v>-321300</v>
       </c>
-      <c r="AC94" s="3">
+      <c r="AD94" s="3">
         <v>-790700</v>
       </c>
-      <c r="AD94" s="3">
+      <c r="AE94" s="3">
         <v>-229200</v>
       </c>
-      <c r="AE94" s="3">
+      <c r="AF94" s="3">
         <v>-107200</v>
       </c>
-      <c r="AF94" s="3">
+      <c r="AG94" s="3">
         <v>-167600</v>
       </c>
-      <c r="AG94" s="3">
+      <c r="AH94" s="3">
         <v>-168800</v>
       </c>
-      <c r="AH94" s="3">
+      <c r="AI94" s="3">
         <v>-771600</v>
       </c>
-      <c r="AI94" s="3">
+      <c r="AJ94" s="3">
         <v>-158200</v>
       </c>
-      <c r="AJ94" s="3">
+      <c r="AK94" s="3">
         <v>-129200</v>
       </c>
     </row>
-    <row r="95" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -8820,35 +9052,36 @@
       <c r="AH95" s="3"/>
       <c r="AI95" s="3"/>
       <c r="AJ95" s="3"/>
+      <c r="AK95" s="3"/>
     </row>
-    <row r="96" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="96" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
       <c r="D96" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="E96" s="3">
+      <c r="E96" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F96" s="3">
         <v>495400</v>
       </c>
-      <c r="F96" s="3" t="s">
+      <c r="G96" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="G96" s="3">
+      <c r="H96" s="3">
         <v>292300</v>
       </c>
-      <c r="H96" s="3" t="s">
+      <c r="I96" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="I96" s="3">
+      <c r="J96" s="3">
         <v>285800</v>
       </c>
-      <c r="J96" s="3" t="s">
+      <c r="K96" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="K96" s="3">
-        <v>0</v>
-      </c>
       <c r="L96" s="3">
         <v>0</v>
       </c>
@@ -8924,8 +9157,11 @@
       <c r="AJ96" s="3">
         <v>0</v>
       </c>
+      <c r="AK96" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="97" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="97" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -9028,8 +9264,11 @@
       <c r="AJ97" s="3">
         <v>0</v>
       </c>
+      <c r="AK97" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="98" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="98" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -9132,8 +9371,11 @@
       <c r="AJ98" s="3">
         <v>0</v>
       </c>
+      <c r="AK98" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="99" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="99" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -9236,316 +9478,328 @@
       <c r="AJ99" s="3">
         <v>0</v>
       </c>
+      <c r="AK99" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="100" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="100" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-552400</v>
+      </c>
+      <c r="E100" s="3">
         <v>1500</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-151900</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>18000</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-305500</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>346700</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-272200</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>122400</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-240700</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>876200</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>-21800</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>358800</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>-108500</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>-308000</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>-135500</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>142800</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>-87400</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>1267700</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>9600</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>47000</v>
       </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
         <v>2000</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Y100" s="3">
         <v>79800</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="Z100" s="3">
         <v>-380900</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AA100" s="3">
         <v>-2100</v>
       </c>
-      <c r="AA100" s="3">
+      <c r="AB100" s="3">
         <v>-22300</v>
       </c>
-      <c r="AB100" s="3">
+      <c r="AC100" s="3">
         <v>193200</v>
       </c>
-      <c r="AC100" s="3">
+      <c r="AD100" s="3">
         <v>926600</v>
       </c>
-      <c r="AD100" s="3">
+      <c r="AE100" s="3">
         <v>-115500</v>
       </c>
-      <c r="AE100" s="3">
+      <c r="AF100" s="3">
         <v>-30000</v>
       </c>
-      <c r="AF100" s="3">
+      <c r="AG100" s="3">
         <v>-59900</v>
       </c>
-      <c r="AG100" s="3">
+      <c r="AH100" s="3">
         <v>-104800</v>
       </c>
-      <c r="AH100" s="3">
+      <c r="AI100" s="3">
         <v>36400</v>
       </c>
-      <c r="AI100" s="3">
+      <c r="AJ100" s="3">
         <v>1358900</v>
       </c>
-      <c r="AJ100" s="3">
+      <c r="AK100" s="3">
         <v>-3900</v>
       </c>
     </row>
-    <row r="101" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>600</v>
+      </c>
+      <c r="E101" s="3">
         <v>1300</v>
       </c>
-      <c r="E101" s="3">
+      <c r="F101" s="3">
         <v>14500</v>
       </c>
-      <c r="F101" s="3">
+      <c r="G101" s="3">
         <v>-1300</v>
       </c>
-      <c r="G101" s="3">
+      <c r="H101" s="3">
         <v>-8600</v>
       </c>
-      <c r="H101" s="3">
+      <c r="I101" s="3">
         <v>31600</v>
       </c>
-      <c r="I101" s="3">
+      <c r="J101" s="3">
         <v>28900</v>
       </c>
-      <c r="J101" s="3">
+      <c r="K101" s="3">
         <v>-3300</v>
       </c>
-      <c r="K101" s="3">
+      <c r="L101" s="3">
         <v>-8300</v>
       </c>
-      <c r="L101" s="3">
+      <c r="M101" s="3">
         <v>31000</v>
       </c>
-      <c r="M101" s="3">
+      <c r="N101" s="3">
         <v>26900</v>
       </c>
-      <c r="N101" s="3">
+      <c r="O101" s="3">
         <v>-2900</v>
       </c>
-      <c r="O101" s="3">
+      <c r="P101" s="3">
         <v>-6600</v>
       </c>
-      <c r="P101" s="3">
+      <c r="Q101" s="3">
         <v>-300</v>
       </c>
-      <c r="Q101" s="3">
+      <c r="R101" s="3">
         <v>-19200</v>
       </c>
-      <c r="R101" s="3">
+      <c r="S101" s="3">
         <v>4800</v>
       </c>
-      <c r="S101" s="3">
+      <c r="T101" s="3">
         <v>-78800</v>
       </c>
-      <c r="T101" s="3">
+      <c r="U101" s="3">
         <v>-16100</v>
       </c>
-      <c r="U101" s="3">
+      <c r="V101" s="3">
         <v>300</v>
       </c>
-      <c r="V101" s="3">
+      <c r="W101" s="3">
         <v>2700</v>
       </c>
-      <c r="W101" s="3">
+      <c r="X101" s="3">
         <v>-2000</v>
       </c>
-      <c r="X101" s="3">
+      <c r="Y101" s="3">
         <v>5200</v>
       </c>
-      <c r="Y101" s="3">
+      <c r="Z101" s="3">
         <v>3300</v>
       </c>
-      <c r="Z101" s="3">
+      <c r="AA101" s="3">
         <v>-6900</v>
       </c>
-      <c r="AA101" s="3">
+      <c r="AB101" s="3">
         <v>4700</v>
       </c>
-      <c r="AB101" s="3">
+      <c r="AC101" s="3">
         <v>14200</v>
       </c>
-      <c r="AC101" s="3">
+      <c r="AD101" s="3">
         <v>32400</v>
       </c>
-      <c r="AD101" s="3">
+      <c r="AE101" s="3">
         <v>-12800</v>
       </c>
-      <c r="AE101" s="3">
+      <c r="AF101" s="3">
         <v>-16600</v>
       </c>
-      <c r="AF101" s="3">
+      <c r="AG101" s="3">
         <v>-17500</v>
       </c>
-      <c r="AG101" s="3">
+      <c r="AH101" s="3">
         <v>-10400</v>
       </c>
-      <c r="AH101" s="3">
+      <c r="AI101" s="3">
         <v>-18100</v>
       </c>
-      <c r="AI101" s="3">
+      <c r="AJ101" s="3">
         <v>40700</v>
       </c>
-      <c r="AJ101" s="3">
+      <c r="AK101" s="3">
         <v>400</v>
       </c>
     </row>
-    <row r="102" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>244300</v>
+      </c>
+      <c r="E102" s="3">
         <v>166600</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>-315600</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>-24800</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>415000</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>199000</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>-227400</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-334400</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-335200</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>642800</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>28900</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>48700</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>-86200</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>-251300</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>96300</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>-411900</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>-288300</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>1643600</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>32700</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>-35000</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>33500</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>-320300</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
         <v>155900</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AA102" s="3">
         <v>223500</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AB102" s="3">
         <v>-239400</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AC102" s="3">
         <v>13700</v>
       </c>
-      <c r="AC102" s="3">
+      <c r="AD102" s="3">
         <v>374800</v>
       </c>
-      <c r="AD102" s="3">
+      <c r="AE102" s="3">
         <v>-326900</v>
       </c>
-      <c r="AE102" s="3">
+      <c r="AF102" s="3">
         <v>49800</v>
       </c>
-      <c r="AF102" s="3">
+      <c r="AG102" s="3">
         <v>-92900</v>
       </c>
-      <c r="AG102" s="3">
+      <c r="AH102" s="3">
         <v>-150000</v>
       </c>
-      <c r="AH102" s="3">
+      <c r="AI102" s="3">
         <v>-705100</v>
       </c>
-      <c r="AI102" s="3">
+      <c r="AJ102" s="3">
         <v>1407600</v>
       </c>
-      <c r="AJ102" s="3">
+      <c r="AK102" s="3">
         <v>-11700</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/ZTO_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/ZTO_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="166" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="164" uniqueCount="92">
   <si>
     <t>ZTO</t>
   </si>
@@ -1386,7 +1386,7 @@
         <v>10</v>
       </c>
       <c r="D14" s="3">
-        <v>38300</v>
+        <v>41500</v>
       </c>
       <c r="E14" s="3">
         <v>200</v>
@@ -1505,7 +1505,7 @@
         <v>108900</v>
       </c>
       <c r="H15" s="3">
-        <v>109900</v>
+        <v>104200</v>
       </c>
       <c r="I15" s="3">
         <v>102100</v>
@@ -1636,7 +1636,7 @@
         <v>12</v>
       </c>
       <c r="D17" s="3">
-        <v>1296900</v>
+        <v>1293800</v>
       </c>
       <c r="E17" s="3">
         <v>1116700</v>
@@ -1743,7 +1743,7 @@
         <v>13</v>
       </c>
       <c r="D18" s="3">
-        <v>473100</v>
+        <v>476300</v>
       </c>
       <c r="E18" s="3">
         <v>405100</v>
@@ -1996,7 +1996,7 @@
         <v>16</v>
       </c>
       <c r="D21" s="3">
-        <v>601000</v>
+        <v>604100</v>
       </c>
       <c r="E21" s="3">
         <v>498100</v>
@@ -2008,7 +2008,7 @@
         <v>431700</v>
       </c>
       <c r="H21" s="3">
-        <v>503100</v>
+        <v>497400</v>
       </c>
       <c r="I21" s="3">
         <v>437500</v>
@@ -3898,7 +3898,7 @@
         <v>35</v>
       </c>
       <c r="D42" s="3">
-        <v>1212300</v>
+        <v>1237300</v>
       </c>
       <c r="E42" s="3">
         <v>1598600</v>
@@ -4005,7 +4005,7 @@
         <v>36</v>
       </c>
       <c r="D43" s="3">
-        <v>390500</v>
+        <v>438300</v>
       </c>
       <c r="E43" s="3">
         <v>307200</v>
@@ -4219,7 +4219,7 @@
         <v>38</v>
       </c>
       <c r="D45" s="3">
-        <v>700500</v>
+        <v>614900</v>
       </c>
       <c r="E45" s="3">
         <v>716400</v>
@@ -4971,7 +4971,7 @@
         <v>126000</v>
       </c>
       <c r="E52" s="3">
-        <v>74300</v>
+        <v>135900</v>
       </c>
       <c r="F52" s="3">
         <v>128200</v>
@@ -5367,7 +5367,7 @@
         <v>50</v>
       </c>
       <c r="D57" s="3">
-        <v>337500</v>
+        <v>345000</v>
       </c>
       <c r="E57" s="3">
         <v>323200</v>
@@ -5581,7 +5581,7 @@
         <v>52</v>
       </c>
       <c r="D59" s="3">
-        <v>1211400</v>
+        <v>936500</v>
       </c>
       <c r="E59" s="3">
         <v>1582400</v>
@@ -8591,8 +8591,8 @@
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
-      <c r="D91" s="3" t="s">
-        <v>8</v>
+      <c r="D91" s="3">
+        <v>-713500</v>
       </c>
       <c r="E91" s="3" t="s">
         <v>8</v>
@@ -9058,8 +9058,8 @@
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
-      <c r="D96" s="3" t="s">
-        <v>8</v>
+      <c r="D96" s="3">
+        <v>768000</v>
       </c>
       <c r="E96" s="3" t="s">
         <v>8</v>

--- a/AAII_Financials/Quarterly/ZTO_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/ZTO_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="164" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="170" uniqueCount="92">
   <si>
     <t>ZTO</t>
   </si>
@@ -656,479 +656,505 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AK102"/>
+  <dimension ref="A5:AM102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="6.140625" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="17" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="21" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="25" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="29" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="30" max="30" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="31" max="31" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="32" max="33" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="34" max="34" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="35" max="35" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="36" max="37" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="38" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="15" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="19" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="23" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="27" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="30" max="31" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="32" max="32" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="33" max="33" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="34" max="35" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="36" max="36" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="37" max="37" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="38" max="39" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="40" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:39" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:39" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:39" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45838</v>
+      </c>
+      <c r="E7" s="2">
+        <v>45747</v>
+      </c>
+      <c r="F7" s="2">
         <v>45657</v>
       </c>
-      <c r="E7" s="2">
+      <c r="G7" s="2">
         <v>45565</v>
       </c>
-      <c r="F7" s="2">
+      <c r="H7" s="2">
         <v>45473</v>
       </c>
-      <c r="G7" s="2">
+      <c r="I7" s="2">
         <v>45382</v>
       </c>
-      <c r="H7" s="2">
+      <c r="J7" s="2">
         <v>45291</v>
       </c>
-      <c r="I7" s="2">
+      <c r="K7" s="2">
         <v>45199</v>
       </c>
-      <c r="J7" s="2">
+      <c r="L7" s="2">
         <v>45107</v>
       </c>
-      <c r="K7" s="2">
+      <c r="M7" s="2">
         <v>45016</v>
       </c>
-      <c r="L7" s="2">
+      <c r="N7" s="2">
         <v>44926</v>
       </c>
-      <c r="M7" s="2">
+      <c r="O7" s="2">
         <v>44834</v>
       </c>
-      <c r="N7" s="2">
+      <c r="P7" s="2">
         <v>44742</v>
       </c>
-      <c r="O7" s="2">
+      <c r="Q7" s="2">
         <v>44651</v>
       </c>
-      <c r="P7" s="2">
+      <c r="R7" s="2">
         <v>44561</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="S7" s="2">
         <v>44469</v>
       </c>
-      <c r="R7" s="2">
+      <c r="T7" s="2">
         <v>44377</v>
       </c>
-      <c r="S7" s="2">
+      <c r="U7" s="2">
         <v>44286</v>
       </c>
-      <c r="T7" s="2">
+      <c r="V7" s="2">
         <v>44196</v>
       </c>
-      <c r="U7" s="2">
+      <c r="W7" s="2">
         <v>44104</v>
       </c>
-      <c r="V7" s="2">
+      <c r="X7" s="2">
         <v>44012</v>
       </c>
-      <c r="W7" s="2">
+      <c r="Y7" s="2">
         <v>43921</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Z7" s="2">
         <v>43830</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="AA7" s="2">
         <v>43738</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AB7" s="2">
         <v>43646</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AC7" s="2">
         <v>43555</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AD7" s="2">
         <v>43465</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AE7" s="2">
         <v>43373</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AF7" s="2">
         <v>43281</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AG7" s="2">
         <v>43190</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AH7" s="2">
         <v>43100</v>
       </c>
-      <c r="AG7" s="2">
+      <c r="AI7" s="2">
         <v>43008</v>
       </c>
-      <c r="AH7" s="2">
+      <c r="AJ7" s="2">
         <v>42916</v>
       </c>
-      <c r="AI7" s="2">
+      <c r="AK7" s="2">
         <v>42825</v>
       </c>
-      <c r="AJ7" s="2">
+      <c r="AL7" s="2">
         <v>42735</v>
       </c>
-      <c r="AK7" s="2">
+      <c r="AM7" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="8" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:39" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>1651600</v>
+      </c>
+      <c r="E8" s="3">
+        <v>1500900</v>
+      </c>
+      <c r="F8" s="3">
         <v>1770000</v>
       </c>
-      <c r="E8" s="3">
+      <c r="G8" s="3">
         <v>1521900</v>
       </c>
-      <c r="F8" s="3">
+      <c r="H8" s="3">
         <v>1476000</v>
       </c>
-      <c r="G8" s="3">
+      <c r="I8" s="3">
         <v>1379400</v>
       </c>
-      <c r="H8" s="3">
+      <c r="J8" s="3">
         <v>1497600</v>
       </c>
-      <c r="I8" s="3">
+      <c r="K8" s="3">
         <v>1243900</v>
       </c>
-      <c r="J8" s="3">
+      <c r="L8" s="3">
         <v>1343100</v>
       </c>
-      <c r="K8" s="3">
+      <c r="M8" s="3">
         <v>1307800</v>
       </c>
-      <c r="L8" s="3">
+      <c r="N8" s="3">
         <v>1391700</v>
       </c>
-      <c r="M8" s="3">
+      <c r="O8" s="3">
         <v>1235800</v>
       </c>
-      <c r="N8" s="3">
+      <c r="P8" s="3">
         <v>1203500</v>
       </c>
-      <c r="O8" s="3">
+      <c r="Q8" s="3">
         <v>1098800</v>
       </c>
-      <c r="P8" s="3">
+      <c r="R8" s="3">
         <v>1270000</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="S8" s="3">
         <v>1050600</v>
       </c>
-      <c r="R8" s="3">
+      <c r="T8" s="3">
         <v>1052000</v>
       </c>
-      <c r="S8" s="3">
+      <c r="U8" s="3">
         <v>929600</v>
       </c>
-      <c r="T8" s="3">
+      <c r="V8" s="3">
         <v>1149400</v>
       </c>
-      <c r="U8" s="3">
+      <c r="W8" s="3">
         <v>978300</v>
       </c>
-      <c r="V8" s="3">
+      <c r="X8" s="3">
         <v>943500</v>
       </c>
-      <c r="W8" s="3">
+      <c r="Y8" s="3">
         <v>617800</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Z8" s="3">
         <v>1054200</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="AA8" s="3">
         <v>821500</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AB8" s="3">
         <v>828600</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AC8" s="3">
         <v>695800</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AD8" s="3">
         <v>817300</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AE8" s="3">
         <v>592700</v>
       </c>
-      <c r="AD8" s="3">
+      <c r="AF8" s="3">
         <v>587500</v>
       </c>
-      <c r="AE8" s="3">
+      <c r="AG8" s="3">
         <v>508600</v>
       </c>
-      <c r="AF8" s="3">
+      <c r="AH8" s="3">
         <v>642800</v>
       </c>
-      <c r="AG8" s="3">
+      <c r="AI8" s="3">
         <v>466500</v>
       </c>
-      <c r="AH8" s="3">
+      <c r="AJ8" s="3">
         <v>441000</v>
       </c>
-      <c r="AI8" s="3">
+      <c r="AK8" s="3">
         <v>380200</v>
       </c>
-      <c r="AJ8" s="3">
+      <c r="AL8" s="3">
         <v>464000</v>
       </c>
-      <c r="AK8" s="3">
+      <c r="AM8" s="3">
         <v>342200</v>
       </c>
     </row>
-    <row r="9" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:39" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>1240600</v>
+      </c>
+      <c r="E9" s="3">
+        <v>1130300</v>
+      </c>
+      <c r="F9" s="3">
         <v>1254900</v>
       </c>
-      <c r="E9" s="3">
+      <c r="G9" s="3">
         <v>1046400</v>
       </c>
-      <c r="F9" s="3">
+      <c r="H9" s="3">
         <v>977800</v>
       </c>
-      <c r="G9" s="3">
+      <c r="I9" s="3">
         <v>963600</v>
       </c>
-      <c r="H9" s="3">
+      <c r="J9" s="3">
         <v>1056500</v>
       </c>
-      <c r="I9" s="3">
+      <c r="K9" s="3">
         <v>872900</v>
       </c>
-      <c r="J9" s="3">
+      <c r="L9" s="3">
         <v>887400</v>
       </c>
-      <c r="K9" s="3">
+      <c r="M9" s="3">
         <v>940400</v>
       </c>
-      <c r="L9" s="3">
+      <c r="N9" s="3">
         <v>1000800</v>
       </c>
-      <c r="M9" s="3">
+      <c r="O9" s="3">
         <v>898100</v>
       </c>
-      <c r="N9" s="3">
+      <c r="P9" s="3">
         <v>897200</v>
       </c>
-      <c r="O9" s="3">
+      <c r="Q9" s="3">
         <v>873700</v>
       </c>
-      <c r="P9" s="3">
+      <c r="R9" s="3">
         <v>959900</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="S9" s="3">
         <v>827700</v>
       </c>
-      <c r="R9" s="3">
+      <c r="T9" s="3">
         <v>811700</v>
       </c>
-      <c r="S9" s="3">
+      <c r="U9" s="3">
         <v>772100</v>
       </c>
-      <c r="T9" s="3">
+      <c r="V9" s="3">
         <v>890700</v>
       </c>
-      <c r="U9" s="3">
+      <c r="W9" s="3">
         <v>773300</v>
       </c>
-      <c r="V9" s="3">
+      <c r="X9" s="3">
         <v>682800</v>
       </c>
-      <c r="W9" s="3">
+      <c r="Y9" s="3">
         <v>488600</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Z9" s="3">
         <v>746900</v>
       </c>
-      <c r="Y9" s="3">
+      <c r="AA9" s="3">
         <v>572400</v>
       </c>
-      <c r="Z9" s="3">
+      <c r="AB9" s="3">
         <v>558400</v>
       </c>
-      <c r="AA9" s="3">
+      <c r="AC9" s="3">
         <v>504200</v>
       </c>
-      <c r="AB9" s="3">
+      <c r="AD9" s="3">
         <v>592200</v>
       </c>
-      <c r="AC9" s="3">
+      <c r="AE9" s="3">
         <v>407200</v>
       </c>
-      <c r="AD9" s="3">
+      <c r="AF9" s="3">
         <v>383600</v>
       </c>
-      <c r="AE9" s="3">
+      <c r="AG9" s="3">
         <v>360500</v>
       </c>
-      <c r="AF9" s="3">
+      <c r="AH9" s="3">
         <v>441900</v>
       </c>
-      <c r="AG9" s="3">
+      <c r="AI9" s="3">
         <v>297600</v>
       </c>
-      <c r="AH9" s="3">
+      <c r="AJ9" s="3">
         <v>274200</v>
       </c>
-      <c r="AI9" s="3">
+      <c r="AK9" s="3">
         <v>274000</v>
       </c>
-      <c r="AJ9" s="3">
+      <c r="AL9" s="3">
         <v>295100</v>
       </c>
-      <c r="AK9" s="3">
+      <c r="AM9" s="3">
         <v>218200</v>
       </c>
     </row>
-    <row r="10" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:39" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
+        <v>411000</v>
+      </c>
+      <c r="E10" s="3">
+        <v>370600</v>
+      </c>
+      <c r="F10" s="3">
         <v>515100</v>
       </c>
-      <c r="E10" s="3">
+      <c r="G10" s="3">
         <v>475400</v>
       </c>
-      <c r="F10" s="3">
+      <c r="H10" s="3">
         <v>498200</v>
       </c>
-      <c r="G10" s="3">
+      <c r="I10" s="3">
         <v>415800</v>
       </c>
-      <c r="H10" s="3">
+      <c r="J10" s="3">
         <v>441200</v>
       </c>
-      <c r="I10" s="3">
+      <c r="K10" s="3">
         <v>370900</v>
       </c>
-      <c r="J10" s="3">
+      <c r="L10" s="3">
         <v>455600</v>
       </c>
-      <c r="K10" s="3">
+      <c r="M10" s="3">
         <v>367400</v>
       </c>
-      <c r="L10" s="3">
+      <c r="N10" s="3">
         <v>390900</v>
       </c>
-      <c r="M10" s="3">
+      <c r="O10" s="3">
         <v>337700</v>
       </c>
-      <c r="N10" s="3">
+      <c r="P10" s="3">
         <v>306200</v>
       </c>
-      <c r="O10" s="3">
+      <c r="Q10" s="3">
         <v>225100</v>
       </c>
-      <c r="P10" s="3">
+      <c r="R10" s="3">
         <v>310100</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="S10" s="3">
         <v>222900</v>
       </c>
-      <c r="R10" s="3">
+      <c r="T10" s="3">
         <v>240400</v>
       </c>
-      <c r="S10" s="3">
+      <c r="U10" s="3">
         <v>157500</v>
       </c>
-      <c r="T10" s="3">
+      <c r="V10" s="3">
         <v>258700</v>
       </c>
-      <c r="U10" s="3">
+      <c r="W10" s="3">
         <v>205000</v>
       </c>
-      <c r="V10" s="3">
+      <c r="X10" s="3">
         <v>260700</v>
       </c>
-      <c r="W10" s="3">
+      <c r="Y10" s="3">
         <v>129200</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Z10" s="3">
         <v>307400</v>
       </c>
-      <c r="Y10" s="3">
+      <c r="AA10" s="3">
         <v>249100</v>
       </c>
-      <c r="Z10" s="3">
+      <c r="AB10" s="3">
         <v>270200</v>
       </c>
-      <c r="AA10" s="3">
+      <c r="AC10" s="3">
         <v>191600</v>
       </c>
-      <c r="AB10" s="3">
+      <c r="AD10" s="3">
         <v>225100</v>
       </c>
-      <c r="AC10" s="3">
+      <c r="AE10" s="3">
         <v>185500</v>
       </c>
-      <c r="AD10" s="3">
+      <c r="AF10" s="3">
         <v>204000</v>
       </c>
-      <c r="AE10" s="3">
+      <c r="AG10" s="3">
         <v>148100</v>
       </c>
-      <c r="AF10" s="3">
+      <c r="AH10" s="3">
         <v>200800</v>
       </c>
-      <c r="AG10" s="3">
+      <c r="AI10" s="3">
         <v>168900</v>
       </c>
-      <c r="AH10" s="3">
+      <c r="AJ10" s="3">
         <v>166800</v>
       </c>
-      <c r="AI10" s="3">
+      <c r="AK10" s="3">
         <v>106300</v>
       </c>
-      <c r="AJ10" s="3">
+      <c r="AL10" s="3">
         <v>168900</v>
       </c>
-      <c r="AK10" s="3">
+      <c r="AM10" s="3">
         <v>124000</v>
       </c>
     </row>
-    <row r="11" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:39" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -1166,8 +1192,10 @@
       <c r="AI11" s="3"/>
       <c r="AJ11" s="3"/>
       <c r="AK11" s="3"/>
+      <c r="AL11" s="3"/>
+      <c r="AM11" s="3"/>
     </row>
-    <row r="12" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:39" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
@@ -1273,8 +1301,14 @@
       <c r="AK12" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AL12" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AM12" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="13" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:39" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1380,103 +1414,109 @@
       <c r="AK13" s="3">
         <v>0</v>
       </c>
+      <c r="AL13" s="3">
+        <v>0</v>
+      </c>
+      <c r="AM13" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="14" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:39" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3">
+        <v>11900</v>
+      </c>
+      <c r="E14" s="3">
+        <v>0</v>
+      </c>
+      <c r="F14" s="3">
         <v>41500</v>
       </c>
-      <c r="E14" s="3">
+      <c r="G14" s="3">
         <v>200</v>
       </c>
-      <c r="F14" s="3">
+      <c r="H14" s="3">
         <v>25200</v>
       </c>
-      <c r="G14" s="3">
+      <c r="I14" s="3">
         <v>66200</v>
       </c>
-      <c r="H14" s="3">
+      <c r="J14" s="3">
         <v>11500</v>
       </c>
-      <c r="I14" s="3">
+      <c r="K14" s="3">
         <v>-1500</v>
       </c>
-      <c r="J14" s="3">
+      <c r="L14" s="3">
         <v>100</v>
       </c>
-      <c r="K14" s="3" t="s">
+      <c r="M14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="L14" s="3">
+      <c r="N14" s="3">
         <v>-1300</v>
       </c>
-      <c r="M14" s="3">
+      <c r="O14" s="3">
         <v>-4700</v>
       </c>
-      <c r="N14" s="3" t="s">
+      <c r="P14" s="3" t="s">
         <v>8</v>
-      </c>
-      <c r="O14" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="P14" s="3">
-        <v>-300</v>
       </c>
       <c r="Q14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="R14" s="3" t="s">
-        <v>8</v>
+      <c r="R14" s="3">
+        <v>-300</v>
       </c>
       <c r="S14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="T14" s="3">
+      <c r="T14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="U14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="V14" s="3">
         <v>-200</v>
       </c>
-      <c r="U14" s="3">
-        <v>0</v>
-      </c>
-      <c r="V14" s="3">
-        <v>0</v>
-      </c>
       <c r="W14" s="3">
         <v>0</v>
       </c>
       <c r="X14" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y14" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z14" s="3">
         <v>9000</v>
       </c>
-      <c r="Y14" s="3">
-        <v>0</v>
-      </c>
-      <c r="Z14" s="3">
-        <v>0</v>
-      </c>
       <c r="AA14" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB14" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC14" s="3">
         <v>100</v>
       </c>
-      <c r="AB14" s="3">
-        <v>0</v>
-      </c>
-      <c r="AC14" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="AD14" s="3" t="s">
-        <v>8</v>
+      <c r="AD14" s="3">
+        <v>0</v>
       </c>
       <c r="AE14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AF14" s="3">
-        <v>4500</v>
+      <c r="AF14" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="AG14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AH14" s="3" t="s">
-        <v>8</v>
+      <c r="AH14" s="3">
+        <v>4500</v>
       </c>
       <c r="AI14" s="3" t="s">
         <v>8</v>
@@ -1487,41 +1527,47 @@
       <c r="AK14" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AL14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AM14" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="15" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:39" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
+        <v>123500</v>
+      </c>
+      <c r="E15" s="3">
+        <v>114000</v>
+      </c>
+      <c r="F15" s="3">
         <v>102900</v>
       </c>
-      <c r="E15" s="3">
+      <c r="G15" s="3">
         <v>104200</v>
       </c>
-      <c r="F15" s="3">
+      <c r="H15" s="3">
         <v>103900</v>
       </c>
-      <c r="G15" s="3">
+      <c r="I15" s="3">
         <v>108900</v>
       </c>
-      <c r="H15" s="3">
+      <c r="J15" s="3">
         <v>104200</v>
       </c>
-      <c r="I15" s="3">
+      <c r="K15" s="3">
         <v>102100</v>
       </c>
-      <c r="J15" s="3">
+      <c r="L15" s="3">
         <v>97200</v>
       </c>
-      <c r="K15" s="3">
+      <c r="M15" s="3">
         <v>99900</v>
       </c>
-      <c r="L15" s="3">
-        <v>0</v>
-      </c>
-      <c r="M15" s="3">
-        <v>0</v>
-      </c>
       <c r="N15" s="3">
         <v>0</v>
       </c>
@@ -1594,8 +1640,14 @@
       <c r="AK15" s="3">
         <v>0</v>
       </c>
+      <c r="AL15" s="3">
+        <v>0</v>
+      </c>
+      <c r="AM15" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="16" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:39" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1630,222 +1682,236 @@
       <c r="AI16" s="3"/>
       <c r="AJ16" s="3"/>
       <c r="AK16" s="3"/>
+      <c r="AL16" s="3"/>
+      <c r="AM16" s="3"/>
     </row>
-    <row r="17" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="17" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>1306100</v>
+      </c>
+      <c r="E17" s="3">
+        <v>1169400</v>
+      </c>
+      <c r="F17" s="3">
         <v>1293800</v>
       </c>
-      <c r="E17" s="3">
+      <c r="G17" s="3">
         <v>1116700</v>
       </c>
-      <c r="F17" s="3">
+      <c r="H17" s="3">
         <v>1033600</v>
       </c>
-      <c r="G17" s="3">
+      <c r="I17" s="3">
         <v>1065500</v>
       </c>
-      <c r="H17" s="3">
+      <c r="J17" s="3">
         <v>1098300</v>
       </c>
-      <c r="I17" s="3">
+      <c r="K17" s="3">
         <v>911700</v>
       </c>
-      <c r="J17" s="3">
+      <c r="L17" s="3">
         <v>946100</v>
       </c>
-      <c r="K17" s="3">
+      <c r="M17" s="3">
         <v>1023800</v>
       </c>
-      <c r="L17" s="3">
+      <c r="N17" s="3">
         <v>1043600</v>
       </c>
-      <c r="M17" s="3">
+      <c r="O17" s="3">
         <v>930600</v>
       </c>
-      <c r="N17" s="3">
+      <c r="P17" s="3">
         <v>927400</v>
       </c>
-      <c r="O17" s="3">
+      <c r="Q17" s="3">
         <v>943600</v>
       </c>
-      <c r="P17" s="3">
+      <c r="R17" s="3">
         <v>986700</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="S17" s="3">
         <v>857200</v>
       </c>
-      <c r="R17" s="3">
+      <c r="T17" s="3">
         <v>843000</v>
       </c>
-      <c r="S17" s="3">
+      <c r="U17" s="3">
         <v>838700</v>
       </c>
-      <c r="T17" s="3">
+      <c r="V17" s="3">
         <v>931200</v>
       </c>
-      <c r="U17" s="3">
+      <c r="W17" s="3">
         <v>806000</v>
       </c>
-      <c r="V17" s="3">
+      <c r="X17" s="3">
         <v>700800</v>
       </c>
-      <c r="W17" s="3">
+      <c r="Y17" s="3">
         <v>559100</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Z17" s="3">
         <v>784600</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="AA17" s="3">
         <v>603000</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AB17" s="3">
         <v>600600</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AC17" s="3">
         <v>580300</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AD17" s="3">
         <v>620800</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AE17" s="3">
         <v>439900</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AF17" s="3">
         <v>421100</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AG17" s="3">
         <v>408300</v>
       </c>
-      <c r="AF17" s="3">
+      <c r="AH17" s="3">
         <v>465300</v>
       </c>
-      <c r="AG17" s="3">
+      <c r="AI17" s="3">
         <v>326300</v>
       </c>
-      <c r="AH17" s="3">
+      <c r="AJ17" s="3">
         <v>304300</v>
       </c>
-      <c r="AI17" s="3">
+      <c r="AK17" s="3">
         <v>284700</v>
       </c>
-      <c r="AJ17" s="3">
+      <c r="AL17" s="3">
         <v>322800</v>
       </c>
-      <c r="AK17" s="3">
+      <c r="AM17" s="3">
         <v>234400</v>
       </c>
     </row>
-    <row r="18" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>345500</v>
+      </c>
+      <c r="E18" s="3">
+        <v>331500</v>
+      </c>
+      <c r="F18" s="3">
         <v>476300</v>
       </c>
-      <c r="E18" s="3">
+      <c r="G18" s="3">
         <v>405100</v>
       </c>
-      <c r="F18" s="3">
+      <c r="H18" s="3">
         <v>442400</v>
       </c>
-      <c r="G18" s="3">
+      <c r="I18" s="3">
         <v>313900</v>
       </c>
-      <c r="H18" s="3">
+      <c r="J18" s="3">
         <v>399300</v>
       </c>
-      <c r="I18" s="3">
+      <c r="K18" s="3">
         <v>332200</v>
       </c>
-      <c r="J18" s="3">
+      <c r="L18" s="3">
         <v>396900</v>
       </c>
-      <c r="K18" s="3">
+      <c r="M18" s="3">
         <v>283900</v>
       </c>
-      <c r="L18" s="3">
+      <c r="N18" s="3">
         <v>348100</v>
       </c>
-      <c r="M18" s="3">
+      <c r="O18" s="3">
         <v>305200</v>
       </c>
-      <c r="N18" s="3">
+      <c r="P18" s="3">
         <v>276000</v>
       </c>
-      <c r="O18" s="3">
+      <c r="Q18" s="3">
         <v>155200</v>
       </c>
-      <c r="P18" s="3">
+      <c r="R18" s="3">
         <v>283300</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="S18" s="3">
         <v>193400</v>
       </c>
-      <c r="R18" s="3">
+      <c r="T18" s="3">
         <v>209100</v>
       </c>
-      <c r="S18" s="3">
+      <c r="U18" s="3">
         <v>90900</v>
       </c>
-      <c r="T18" s="3">
+      <c r="V18" s="3">
         <v>218200</v>
       </c>
-      <c r="U18" s="3">
+      <c r="W18" s="3">
         <v>172300</v>
       </c>
-      <c r="V18" s="3">
+      <c r="X18" s="3">
         <v>242600</v>
       </c>
-      <c r="W18" s="3">
+      <c r="Y18" s="3">
         <v>58700</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Z18" s="3">
         <v>269700</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="AA18" s="3">
         <v>218500</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AB18" s="3">
         <v>228100</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AC18" s="3">
         <v>115500</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AD18" s="3">
         <v>196500</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AE18" s="3">
         <v>152800</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AF18" s="3">
         <v>166400</v>
       </c>
-      <c r="AE18" s="3">
+      <c r="AG18" s="3">
         <v>100200</v>
       </c>
-      <c r="AF18" s="3">
+      <c r="AH18" s="3">
         <v>177500</v>
       </c>
-      <c r="AG18" s="3">
+      <c r="AI18" s="3">
         <v>140200</v>
       </c>
-      <c r="AH18" s="3">
+      <c r="AJ18" s="3">
         <v>136700</v>
       </c>
-      <c r="AI18" s="3">
+      <c r="AK18" s="3">
         <v>95500</v>
       </c>
-      <c r="AJ18" s="3">
+      <c r="AL18" s="3">
         <v>141200</v>
       </c>
-      <c r="AK18" s="3">
+      <c r="AM18" s="3">
         <v>107800</v>
       </c>
     </row>
-    <row r="19" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1883,288 +1949,302 @@
       <c r="AI19" s="3"/>
       <c r="AJ19" s="3"/>
       <c r="AK19" s="3"/>
+      <c r="AL19" s="3"/>
+      <c r="AM19" s="3"/>
     </row>
-    <row r="20" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="20" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>-5500</v>
+      </c>
+      <c r="E20" s="3">
+        <v>-4900</v>
+      </c>
+      <c r="F20" s="3">
         <v>-25000</v>
       </c>
-      <c r="E20" s="3">
+      <c r="G20" s="3">
         <v>11200</v>
       </c>
-      <c r="F20" s="3">
+      <c r="H20" s="3">
         <v>-10200</v>
       </c>
-      <c r="G20" s="3">
+      <c r="I20" s="3">
         <v>-8900</v>
       </c>
-      <c r="H20" s="3">
+      <c r="J20" s="3">
         <v>6200</v>
       </c>
-      <c r="I20" s="3">
+      <c r="K20" s="3">
         <v>-3300</v>
       </c>
-      <c r="J20" s="3">
+      <c r="L20" s="3">
         <v>-18300</v>
       </c>
-      <c r="K20" s="3">
+      <c r="M20" s="3">
         <v>-21700</v>
       </c>
-      <c r="L20" s="3">
+      <c r="N20" s="3">
         <v>28800</v>
       </c>
-      <c r="M20" s="3">
+      <c r="O20" s="3">
         <v>23600</v>
       </c>
-      <c r="N20" s="3">
+      <c r="P20" s="3">
         <v>31200</v>
       </c>
-      <c r="O20" s="3">
+      <c r="Q20" s="3">
         <v>13500</v>
       </c>
-      <c r="P20" s="3">
+      <c r="R20" s="3">
         <v>9900</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="S20" s="3">
         <v>12600</v>
       </c>
-      <c r="R20" s="3">
+      <c r="T20" s="3">
         <v>15600</v>
       </c>
-      <c r="S20" s="3">
+      <c r="U20" s="3">
         <v>13100</v>
       </c>
-      <c r="T20" s="3">
+      <c r="V20" s="3">
         <v>3200</v>
       </c>
-      <c r="U20" s="3">
+      <c r="W20" s="3">
         <v>4800</v>
       </c>
-      <c r="V20" s="3">
+      <c r="X20" s="3">
         <v>17200</v>
       </c>
-      <c r="W20" s="3">
+      <c r="Y20" s="3">
         <v>22500</v>
       </c>
-      <c r="X20" s="3">
+      <c r="Z20" s="3">
         <v>137200</v>
       </c>
-      <c r="Y20" s="3">
+      <c r="AA20" s="3">
         <v>27300</v>
       </c>
-      <c r="Z20" s="3">
+      <c r="AB20" s="3">
         <v>25500</v>
       </c>
-      <c r="AA20" s="3">
+      <c r="AC20" s="3">
         <v>18300</v>
       </c>
-      <c r="AB20" s="3">
+      <c r="AD20" s="3">
         <v>21500</v>
       </c>
-      <c r="AC20" s="3">
+      <c r="AE20" s="3">
         <v>24800</v>
       </c>
-      <c r="AD20" s="3">
+      <c r="AF20" s="3">
         <v>91900</v>
       </c>
-      <c r="AE20" s="3">
+      <c r="AG20" s="3">
         <v>3400</v>
       </c>
-      <c r="AF20" s="3">
+      <c r="AH20" s="3">
         <v>5700</v>
       </c>
-      <c r="AG20" s="3">
+      <c r="AI20" s="3">
         <v>2600</v>
       </c>
-      <c r="AH20" s="3">
+      <c r="AJ20" s="3">
         <v>5500</v>
       </c>
-      <c r="AI20" s="3">
+      <c r="AK20" s="3">
         <v>3700</v>
       </c>
-      <c r="AJ20" s="3">
+      <c r="AL20" s="3">
         <v>3500</v>
       </c>
-      <c r="AK20" s="3">
+      <c r="AM20" s="3">
         <v>1400</v>
       </c>
     </row>
-    <row r="21" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>474500</v>
+      </c>
+      <c r="E21" s="3">
+        <v>450400</v>
+      </c>
+      <c r="F21" s="3">
         <v>604100</v>
       </c>
-      <c r="E21" s="3">
+      <c r="G21" s="3">
         <v>498100</v>
       </c>
-      <c r="F21" s="3">
+      <c r="H21" s="3">
         <v>556600</v>
       </c>
-      <c r="G21" s="3">
+      <c r="I21" s="3">
         <v>431700</v>
       </c>
-      <c r="H21" s="3">
+      <c r="J21" s="3">
         <v>497400</v>
       </c>
-      <c r="I21" s="3">
+      <c r="K21" s="3">
         <v>437500</v>
       </c>
-      <c r="J21" s="3">
+      <c r="L21" s="3">
         <v>512500</v>
       </c>
-      <c r="K21" s="3">
+      <c r="M21" s="3">
         <v>405600</v>
       </c>
-      <c r="L21" s="3">
+      <c r="N21" s="3">
         <v>381000</v>
       </c>
-      <c r="M21" s="3">
+      <c r="O21" s="3">
         <v>327900</v>
       </c>
-      <c r="N21" s="3">
+      <c r="P21" s="3">
         <v>312700</v>
       </c>
-      <c r="O21" s="3">
+      <c r="Q21" s="3">
         <v>256700</v>
       </c>
-      <c r="P21" s="3">
+      <c r="R21" s="3">
         <v>300500</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="S21" s="3">
         <v>202200</v>
       </c>
-      <c r="R21" s="3">
+      <c r="T21" s="3">
         <v>231000</v>
       </c>
-      <c r="S21" s="3">
+      <c r="U21" s="3">
         <v>178800</v>
       </c>
-      <c r="T21" s="3">
+      <c r="V21" s="3">
         <v>227200</v>
       </c>
-      <c r="U21" s="3">
+      <c r="W21" s="3">
         <v>184900</v>
       </c>
-      <c r="V21" s="3">
+      <c r="X21" s="3">
         <v>262500</v>
       </c>
-      <c r="W21" s="3">
+      <c r="Y21" s="3">
         <v>145600</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Z21" s="3">
         <v>418900</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="AA21" s="3">
         <v>246500</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AB21" s="3">
         <v>255900</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AC21" s="3">
         <v>176900</v>
       </c>
-      <c r="AB21" s="3">
+      <c r="AD21" s="3">
         <v>223700</v>
       </c>
-      <c r="AC21" s="3">
+      <c r="AE21" s="3">
         <v>179800</v>
       </c>
-      <c r="AD21" s="3">
+      <c r="AF21" s="3">
         <v>259900</v>
       </c>
-      <c r="AE21" s="3">
+      <c r="AG21" s="3">
         <v>130400</v>
       </c>
-      <c r="AF21" s="3">
+      <c r="AH21" s="3">
         <v>183000</v>
       </c>
-      <c r="AG21" s="3">
+      <c r="AI21" s="3">
         <v>144500</v>
       </c>
-      <c r="AH21" s="3">
+      <c r="AJ21" s="3">
         <v>143100</v>
       </c>
-      <c r="AI21" s="3">
+      <c r="AK21" s="3">
         <v>118100</v>
       </c>
-      <c r="AJ21" s="3">
+      <c r="AL21" s="3">
         <v>178100</v>
       </c>
-      <c r="AK21" s="3">
+      <c r="AM21" s="3">
         <v>105200</v>
       </c>
     </row>
-    <row r="22" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
-        <v>9800</v>
+        <v>13700</v>
       </c>
       <c r="E22" s="3">
         <v>9500</v>
       </c>
       <c r="F22" s="3">
+        <v>9800</v>
+      </c>
+      <c r="G22" s="3">
+        <v>9500</v>
+      </c>
+      <c r="H22" s="3">
         <v>15900</v>
       </c>
-      <c r="G22" s="3">
+      <c r="I22" s="3">
         <v>11600</v>
       </c>
-      <c r="H22" s="3">
+      <c r="J22" s="3">
         <v>8700</v>
       </c>
-      <c r="I22" s="3">
+      <c r="K22" s="3">
         <v>11500</v>
       </c>
-      <c r="J22" s="3">
+      <c r="L22" s="3">
         <v>10000</v>
       </c>
-      <c r="K22" s="3">
+      <c r="M22" s="3">
         <v>10400</v>
       </c>
-      <c r="L22" s="3">
+      <c r="N22" s="3">
         <v>10700</v>
       </c>
-      <c r="M22" s="3">
+      <c r="O22" s="3">
         <v>4400</v>
       </c>
-      <c r="N22" s="3">
+      <c r="P22" s="3">
         <v>3200</v>
       </c>
-      <c r="O22" s="3">
+      <c r="Q22" s="3">
         <v>8300</v>
       </c>
-      <c r="P22" s="3">
+      <c r="R22" s="3">
         <v>3400</v>
       </c>
-      <c r="Q22" s="3">
+      <c r="S22" s="3">
         <v>7400</v>
       </c>
-      <c r="R22" s="3">
+      <c r="T22" s="3">
         <v>4900</v>
       </c>
-      <c r="S22" s="3">
+      <c r="U22" s="3">
         <v>2200</v>
       </c>
-      <c r="T22" s="3">
+      <c r="V22" s="3">
         <v>1700</v>
       </c>
-      <c r="U22" s="3">
+      <c r="W22" s="3">
         <v>2000</v>
       </c>
-      <c r="V22" s="3">
+      <c r="X22" s="3">
         <v>1300</v>
       </c>
-      <c r="W22" s="3">
-        <v>0</v>
-      </c>
-      <c r="X22" s="3">
-        <v>0</v>
-      </c>
       <c r="Y22" s="3">
         <v>0</v>
       </c>
@@ -2184,242 +2264,260 @@
         <v>0</v>
       </c>
       <c r="AE22" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF22" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG22" s="3">
         <v>100</v>
       </c>
-      <c r="AF22" s="3">
+      <c r="AH22" s="3">
         <v>400</v>
       </c>
-      <c r="AG22" s="3">
+      <c r="AI22" s="3">
         <v>400</v>
       </c>
-      <c r="AH22" s="3">
+      <c r="AJ22" s="3">
         <v>700</v>
       </c>
-      <c r="AI22" s="3">
+      <c r="AK22" s="3">
         <v>800</v>
       </c>
-      <c r="AJ22" s="3">
+      <c r="AL22" s="3">
         <v>100</v>
       </c>
-      <c r="AK22" s="3">
+      <c r="AM22" s="3">
         <v>500</v>
       </c>
     </row>
-    <row r="23" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>354600</v>
+      </c>
+      <c r="E23" s="3">
+        <v>354300</v>
+      </c>
+      <c r="F23" s="3">
         <v>480300</v>
       </c>
-      <c r="E23" s="3">
+      <c r="G23" s="3">
         <v>418300</v>
       </c>
-      <c r="F23" s="3">
+      <c r="H23" s="3">
         <v>451200</v>
       </c>
-      <c r="G23" s="3">
+      <c r="I23" s="3">
         <v>278900</v>
       </c>
-      <c r="H23" s="3">
+      <c r="J23" s="3">
         <v>401400</v>
       </c>
-      <c r="I23" s="3">
+      <c r="K23" s="3">
         <v>359200</v>
       </c>
-      <c r="J23" s="3">
+      <c r="L23" s="3">
         <v>428300</v>
       </c>
-      <c r="K23" s="3">
+      <c r="M23" s="3">
         <v>308600</v>
       </c>
-      <c r="L23" s="3">
+      <c r="N23" s="3">
         <v>366100</v>
       </c>
-      <c r="M23" s="3">
+      <c r="O23" s="3">
         <v>324400</v>
       </c>
-      <c r="N23" s="3">
+      <c r="P23" s="3">
         <v>304100</v>
       </c>
-      <c r="O23" s="3">
+      <c r="Q23" s="3">
         <v>160400</v>
       </c>
-      <c r="P23" s="3">
+      <c r="R23" s="3">
         <v>289800</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="S23" s="3">
         <v>198600</v>
       </c>
-      <c r="R23" s="3">
+      <c r="T23" s="3">
         <v>219900</v>
       </c>
-      <c r="S23" s="3">
+      <c r="U23" s="3">
         <v>101700</v>
       </c>
-      <c r="T23" s="3">
+      <c r="V23" s="3">
         <v>219700</v>
       </c>
-      <c r="U23" s="3">
+      <c r="W23" s="3">
         <v>175000</v>
       </c>
-      <c r="V23" s="3">
+      <c r="X23" s="3">
         <v>258500</v>
       </c>
-      <c r="W23" s="3">
+      <c r="Y23" s="3">
         <v>81200</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Z23" s="3">
         <v>406900</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="AA23" s="3">
         <v>245800</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AB23" s="3">
         <v>253500</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AC23" s="3">
         <v>133900</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AD23" s="3">
         <v>218000</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AE23" s="3">
         <v>177600</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AF23" s="3">
         <v>258300</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AG23" s="3">
         <v>103500</v>
       </c>
-      <c r="AF23" s="3">
+      <c r="AH23" s="3">
         <v>182800</v>
       </c>
-      <c r="AG23" s="3">
+      <c r="AI23" s="3">
         <v>142500</v>
       </c>
-      <c r="AH23" s="3">
+      <c r="AJ23" s="3">
         <v>141400</v>
       </c>
-      <c r="AI23" s="3">
+      <c r="AK23" s="3">
         <v>98400</v>
       </c>
-      <c r="AJ23" s="3">
+      <c r="AL23" s="3">
         <v>144600</v>
       </c>
-      <c r="AK23" s="3">
+      <c r="AM23" s="3">
         <v>108700</v>
       </c>
     </row>
-    <row r="24" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>80300</v>
+      </c>
+      <c r="E24" s="3">
+        <v>73300</v>
+      </c>
+      <c r="F24" s="3">
         <v>145100</v>
       </c>
-      <c r="E24" s="3">
+      <c r="G24" s="3">
         <v>79100</v>
       </c>
-      <c r="F24" s="3">
+      <c r="H24" s="3">
         <v>91500</v>
       </c>
-      <c r="G24" s="3">
+      <c r="I24" s="3">
         <v>78400</v>
       </c>
-      <c r="H24" s="3">
+      <c r="J24" s="3">
         <v>89800</v>
       </c>
-      <c r="I24" s="3">
+      <c r="K24" s="3">
         <v>37200</v>
       </c>
-      <c r="J24" s="3">
+      <c r="L24" s="3">
         <v>79400</v>
       </c>
-      <c r="K24" s="3">
+      <c r="M24" s="3">
         <v>66200</v>
       </c>
-      <c r="L24" s="3">
+      <c r="N24" s="3">
         <v>70600</v>
       </c>
-      <c r="M24" s="3">
+      <c r="O24" s="3">
         <v>60700</v>
       </c>
-      <c r="N24" s="3">
+      <c r="P24" s="3">
         <v>60900</v>
       </c>
-      <c r="O24" s="3">
+      <c r="Q24" s="3">
         <v>35500</v>
       </c>
-      <c r="P24" s="3">
+      <c r="R24" s="3">
         <v>51200</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="S24" s="3">
         <v>32600</v>
       </c>
-      <c r="R24" s="3">
+      <c r="T24" s="3">
         <v>36600</v>
       </c>
-      <c r="S24" s="3">
+      <c r="U24" s="3">
         <v>21500</v>
       </c>
-      <c r="T24" s="3">
+      <c r="V24" s="3">
         <v>40300</v>
       </c>
-      <c r="U24" s="3">
+      <c r="W24" s="3">
         <v>-4100</v>
       </c>
-      <c r="V24" s="3">
+      <c r="X24" s="3">
         <v>44000</v>
       </c>
-      <c r="W24" s="3">
+      <c r="Y24" s="3">
         <v>20500</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Z24" s="3">
         <v>51000</v>
       </c>
-      <c r="Y24" s="3">
+      <c r="AA24" s="3">
         <v>41500</v>
       </c>
-      <c r="Z24" s="3">
+      <c r="AB24" s="3">
         <v>44100</v>
       </c>
-      <c r="AA24" s="3">
+      <c r="AC24" s="3">
         <v>29200</v>
       </c>
-      <c r="AB24" s="3">
+      <c r="AD24" s="3">
         <v>32300</v>
       </c>
-      <c r="AC24" s="3">
+      <c r="AE24" s="3">
         <v>28200</v>
       </c>
-      <c r="AD24" s="3">
+      <c r="AF24" s="3">
         <v>49100</v>
       </c>
-      <c r="AE24" s="3">
+      <c r="AG24" s="3">
         <v>22100</v>
       </c>
-      <c r="AF24" s="3">
+      <c r="AH24" s="3">
         <v>1300</v>
       </c>
-      <c r="AG24" s="3">
+      <c r="AI24" s="3">
         <v>35300</v>
       </c>
-      <c r="AH24" s="3">
+      <c r="AJ24" s="3">
         <v>34600</v>
       </c>
-      <c r="AI24" s="3">
+      <c r="AK24" s="3">
         <v>24200</v>
       </c>
-      <c r="AJ24" s="3">
+      <c r="AL24" s="3">
         <v>36600</v>
       </c>
-      <c r="AK24" s="3">
+      <c r="AM24" s="3">
         <v>27100</v>
       </c>
     </row>
-    <row r="25" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2525,222 +2623,240 @@
       <c r="AK25" s="3">
         <v>0</v>
       </c>
+      <c r="AL25" s="3">
+        <v>0</v>
+      </c>
+      <c r="AM25" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="26" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="26" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>274200</v>
+      </c>
+      <c r="E26" s="3">
+        <v>281000</v>
+      </c>
+      <c r="F26" s="3">
         <v>335200</v>
       </c>
-      <c r="E26" s="3">
+      <c r="G26" s="3">
         <v>339200</v>
       </c>
-      <c r="F26" s="3">
+      <c r="H26" s="3">
         <v>359700</v>
       </c>
-      <c r="G26" s="3">
+      <c r="I26" s="3">
         <v>200500</v>
       </c>
-      <c r="H26" s="3">
+      <c r="J26" s="3">
         <v>311600</v>
       </c>
-      <c r="I26" s="3">
+      <c r="K26" s="3">
         <v>322000</v>
       </c>
-      <c r="J26" s="3">
+      <c r="L26" s="3">
         <v>348900</v>
       </c>
-      <c r="K26" s="3">
+      <c r="M26" s="3">
         <v>242400</v>
       </c>
-      <c r="L26" s="3">
+      <c r="N26" s="3">
         <v>295600</v>
       </c>
-      <c r="M26" s="3">
+      <c r="O26" s="3">
         <v>263700</v>
       </c>
-      <c r="N26" s="3">
+      <c r="P26" s="3">
         <v>243100</v>
       </c>
-      <c r="O26" s="3">
+      <c r="Q26" s="3">
         <v>124900</v>
       </c>
-      <c r="P26" s="3">
+      <c r="R26" s="3">
         <v>238600</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="S26" s="3">
         <v>166000</v>
       </c>
-      <c r="R26" s="3">
+      <c r="T26" s="3">
         <v>183300</v>
       </c>
-      <c r="S26" s="3">
+      <c r="U26" s="3">
         <v>80200</v>
       </c>
-      <c r="T26" s="3">
+      <c r="V26" s="3">
         <v>179400</v>
       </c>
-      <c r="U26" s="3">
+      <c r="W26" s="3">
         <v>179100</v>
       </c>
-      <c r="V26" s="3">
+      <c r="X26" s="3">
         <v>214600</v>
       </c>
-      <c r="W26" s="3">
+      <c r="Y26" s="3">
         <v>60700</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Z26" s="3">
         <v>355800</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="AA26" s="3">
         <v>204200</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AB26" s="3">
         <v>209400</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AC26" s="3">
         <v>104700</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AD26" s="3">
         <v>185700</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AE26" s="3">
         <v>149400</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AF26" s="3">
         <v>209100</v>
       </c>
-      <c r="AE26" s="3">
+      <c r="AG26" s="3">
         <v>81300</v>
       </c>
-      <c r="AF26" s="3">
+      <c r="AH26" s="3">
         <v>181500</v>
       </c>
-      <c r="AG26" s="3">
+      <c r="AI26" s="3">
         <v>107200</v>
       </c>
-      <c r="AH26" s="3">
+      <c r="AJ26" s="3">
         <v>106800</v>
       </c>
-      <c r="AI26" s="3">
+      <c r="AK26" s="3">
         <v>74200</v>
       </c>
-      <c r="AJ26" s="3">
+      <c r="AL26" s="3">
         <v>108000</v>
       </c>
-      <c r="AK26" s="3">
+      <c r="AM26" s="3">
         <v>81600</v>
       </c>
     </row>
-    <row r="27" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>270600</v>
+      </c>
+      <c r="E27" s="3">
+        <v>274700</v>
+      </c>
+      <c r="F27" s="3">
         <v>326400</v>
       </c>
-      <c r="E27" s="3">
+      <c r="G27" s="3">
         <v>341600</v>
       </c>
-      <c r="F27" s="3">
+      <c r="H27" s="3">
         <v>359400</v>
       </c>
-      <c r="G27" s="3">
+      <c r="I27" s="3">
         <v>197500</v>
       </c>
-      <c r="H27" s="3">
+      <c r="J27" s="3">
         <v>309200</v>
       </c>
-      <c r="I27" s="3">
+      <c r="K27" s="3">
         <v>321400</v>
       </c>
-      <c r="J27" s="3">
+      <c r="L27" s="3">
         <v>350400</v>
       </c>
-      <c r="K27" s="3">
+      <c r="M27" s="3">
         <v>243200</v>
       </c>
-      <c r="L27" s="3">
+      <c r="N27" s="3">
         <v>304900</v>
       </c>
-      <c r="M27" s="3">
+      <c r="O27" s="3">
         <v>267300</v>
       </c>
-      <c r="N27" s="3">
+      <c r="P27" s="3">
         <v>251000</v>
       </c>
-      <c r="O27" s="3">
+      <c r="Q27" s="3">
         <v>126000</v>
       </c>
-      <c r="P27" s="3">
+      <c r="R27" s="3">
         <v>242800</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="S27" s="3">
         <v>165800</v>
       </c>
-      <c r="R27" s="3">
+      <c r="T27" s="3">
         <v>185600</v>
       </c>
-      <c r="S27" s="3">
+      <c r="U27" s="3">
         <v>76600</v>
       </c>
-      <c r="T27" s="3">
+      <c r="V27" s="3">
         <v>179300</v>
       </c>
-      <c r="U27" s="3">
+      <c r="W27" s="3">
         <v>177000</v>
       </c>
-      <c r="V27" s="3">
+      <c r="X27" s="3">
         <v>213400</v>
       </c>
-      <c r="W27" s="3">
+      <c r="Y27" s="3">
         <v>59100</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Z27" s="3">
         <v>358200</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="AA27" s="3">
         <v>204000</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AB27" s="3">
         <v>207700</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AC27" s="3">
         <v>103600</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AD27" s="3">
         <v>185200</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AE27" s="3">
         <v>148300</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AF27" s="3">
         <v>208700</v>
       </c>
-      <c r="AE27" s="3">
+      <c r="AG27" s="3">
         <v>79900</v>
       </c>
-      <c r="AF27" s="3">
+      <c r="AH27" s="3">
         <v>181400</v>
       </c>
-      <c r="AG27" s="3">
+      <c r="AI27" s="3">
         <v>106400</v>
       </c>
-      <c r="AH27" s="3">
+      <c r="AJ27" s="3">
         <v>106400</v>
       </c>
-      <c r="AI27" s="3">
+      <c r="AK27" s="3">
         <v>73200</v>
       </c>
-      <c r="AJ27" s="3">
+      <c r="AL27" s="3">
         <v>105700</v>
       </c>
-      <c r="AK27" s="3">
+      <c r="AM27" s="3">
         <v>73700</v>
       </c>
     </row>
-    <row r="28" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2846,8 +2962,14 @@
       <c r="AK28" s="3">
         <v>0</v>
       </c>
+      <c r="AL28" s="3">
+        <v>0</v>
+      </c>
+      <c r="AM28" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="29" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="29" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2953,8 +3075,14 @@
       <c r="AK29" s="3">
         <v>0</v>
       </c>
+      <c r="AL29" s="3">
+        <v>0</v>
+      </c>
+      <c r="AM29" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="30" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="30" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -3060,8 +3188,14 @@
       <c r="AK30" s="3">
         <v>0</v>
       </c>
+      <c r="AL30" s="3">
+        <v>0</v>
+      </c>
+      <c r="AM30" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="31" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="31" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -3167,222 +3301,240 @@
       <c r="AK31" s="3">
         <v>0</v>
       </c>
+      <c r="AL31" s="3">
+        <v>0</v>
+      </c>
+      <c r="AM31" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="32" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="32" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>5500</v>
+      </c>
+      <c r="E32" s="3">
+        <v>4900</v>
+      </c>
+      <c r="F32" s="3">
         <v>25000</v>
       </c>
-      <c r="E32" s="3">
+      <c r="G32" s="3">
         <v>-11200</v>
       </c>
-      <c r="F32" s="3">
+      <c r="H32" s="3">
         <v>10200</v>
       </c>
-      <c r="G32" s="3">
+      <c r="I32" s="3">
         <v>8900</v>
       </c>
-      <c r="H32" s="3">
+      <c r="J32" s="3">
         <v>-6200</v>
       </c>
-      <c r="I32" s="3">
+      <c r="K32" s="3">
         <v>3300</v>
       </c>
-      <c r="J32" s="3">
+      <c r="L32" s="3">
         <v>18300</v>
       </c>
-      <c r="K32" s="3">
+      <c r="M32" s="3">
         <v>21700</v>
       </c>
-      <c r="L32" s="3">
+      <c r="N32" s="3">
         <v>-28800</v>
       </c>
-      <c r="M32" s="3">
+      <c r="O32" s="3">
         <v>-23600</v>
       </c>
-      <c r="N32" s="3">
+      <c r="P32" s="3">
         <v>-31200</v>
       </c>
-      <c r="O32" s="3">
+      <c r="Q32" s="3">
         <v>-13500</v>
       </c>
-      <c r="P32" s="3">
+      <c r="R32" s="3">
         <v>-9900</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="S32" s="3">
         <v>-12600</v>
       </c>
-      <c r="R32" s="3">
+      <c r="T32" s="3">
         <v>-15600</v>
       </c>
-      <c r="S32" s="3">
+      <c r="U32" s="3">
         <v>-13100</v>
       </c>
-      <c r="T32" s="3">
+      <c r="V32" s="3">
         <v>-3200</v>
       </c>
-      <c r="U32" s="3">
+      <c r="W32" s="3">
         <v>-4800</v>
       </c>
-      <c r="V32" s="3">
+      <c r="X32" s="3">
         <v>-17200</v>
       </c>
-      <c r="W32" s="3">
+      <c r="Y32" s="3">
         <v>-22500</v>
       </c>
-      <c r="X32" s="3">
+      <c r="Z32" s="3">
         <v>-137200</v>
       </c>
-      <c r="Y32" s="3">
+      <c r="AA32" s="3">
         <v>-27300</v>
       </c>
-      <c r="Z32" s="3">
+      <c r="AB32" s="3">
         <v>-25500</v>
       </c>
-      <c r="AA32" s="3">
+      <c r="AC32" s="3">
         <v>-18300</v>
       </c>
-      <c r="AB32" s="3">
+      <c r="AD32" s="3">
         <v>-21500</v>
       </c>
-      <c r="AC32" s="3">
+      <c r="AE32" s="3">
         <v>-24800</v>
       </c>
-      <c r="AD32" s="3">
+      <c r="AF32" s="3">
         <v>-91900</v>
       </c>
-      <c r="AE32" s="3">
+      <c r="AG32" s="3">
         <v>-3400</v>
       </c>
-      <c r="AF32" s="3">
+      <c r="AH32" s="3">
         <v>-5700</v>
       </c>
-      <c r="AG32" s="3">
+      <c r="AI32" s="3">
         <v>-2600</v>
       </c>
-      <c r="AH32" s="3">
+      <c r="AJ32" s="3">
         <v>-5500</v>
       </c>
-      <c r="AI32" s="3">
+      <c r="AK32" s="3">
         <v>-3700</v>
       </c>
-      <c r="AJ32" s="3">
+      <c r="AL32" s="3">
         <v>-3500</v>
       </c>
-      <c r="AK32" s="3">
+      <c r="AM32" s="3">
         <v>-1400</v>
       </c>
     </row>
-    <row r="33" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>270600</v>
+      </c>
+      <c r="E33" s="3">
+        <v>274700</v>
+      </c>
+      <c r="F33" s="3">
         <v>326400</v>
       </c>
-      <c r="E33" s="3">
+      <c r="G33" s="3">
         <v>341600</v>
       </c>
-      <c r="F33" s="3">
+      <c r="H33" s="3">
         <v>359400</v>
       </c>
-      <c r="G33" s="3">
+      <c r="I33" s="3">
         <v>197500</v>
       </c>
-      <c r="H33" s="3">
+      <c r="J33" s="3">
         <v>309200</v>
       </c>
-      <c r="I33" s="3">
+      <c r="K33" s="3">
         <v>321400</v>
       </c>
-      <c r="J33" s="3">
+      <c r="L33" s="3">
         <v>350400</v>
       </c>
-      <c r="K33" s="3">
+      <c r="M33" s="3">
         <v>243200</v>
       </c>
-      <c r="L33" s="3">
+      <c r="N33" s="3">
         <v>304900</v>
       </c>
-      <c r="M33" s="3">
+      <c r="O33" s="3">
         <v>267300</v>
       </c>
-      <c r="N33" s="3">
+      <c r="P33" s="3">
         <v>251000</v>
       </c>
-      <c r="O33" s="3">
+      <c r="Q33" s="3">
         <v>126000</v>
       </c>
-      <c r="P33" s="3">
+      <c r="R33" s="3">
         <v>242800</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="S33" s="3">
         <v>165800</v>
       </c>
-      <c r="R33" s="3">
+      <c r="T33" s="3">
         <v>185600</v>
       </c>
-      <c r="S33" s="3">
+      <c r="U33" s="3">
         <v>76600</v>
       </c>
-      <c r="T33" s="3">
+      <c r="V33" s="3">
         <v>179300</v>
       </c>
-      <c r="U33" s="3">
+      <c r="W33" s="3">
         <v>177000</v>
       </c>
-      <c r="V33" s="3">
+      <c r="X33" s="3">
         <v>213400</v>
       </c>
-      <c r="W33" s="3">
+      <c r="Y33" s="3">
         <v>59100</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Z33" s="3">
         <v>358200</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="AA33" s="3">
         <v>204000</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AB33" s="3">
         <v>207700</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AC33" s="3">
         <v>103600</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AD33" s="3">
         <v>185200</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AE33" s="3">
         <v>148300</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AF33" s="3">
         <v>208700</v>
       </c>
-      <c r="AE33" s="3">
+      <c r="AG33" s="3">
         <v>79900</v>
       </c>
-      <c r="AF33" s="3">
+      <c r="AH33" s="3">
         <v>181400</v>
       </c>
-      <c r="AG33" s="3">
+      <c r="AI33" s="3">
         <v>106400</v>
       </c>
-      <c r="AH33" s="3">
+      <c r="AJ33" s="3">
         <v>106400</v>
       </c>
-      <c r="AI33" s="3">
+      <c r="AK33" s="3">
         <v>73200</v>
       </c>
-      <c r="AJ33" s="3">
+      <c r="AL33" s="3">
         <v>105700</v>
       </c>
-      <c r="AK33" s="3">
+      <c r="AM33" s="3">
         <v>73700</v>
       </c>
     </row>
-    <row r="34" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3488,227 +3640,245 @@
       <c r="AK34" s="3">
         <v>0</v>
       </c>
+      <c r="AL34" s="3">
+        <v>0</v>
+      </c>
+      <c r="AM34" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="35" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="35" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>270600</v>
+      </c>
+      <c r="E35" s="3">
+        <v>274700</v>
+      </c>
+      <c r="F35" s="3">
         <v>326400</v>
       </c>
-      <c r="E35" s="3">
+      <c r="G35" s="3">
         <v>341600</v>
       </c>
-      <c r="F35" s="3">
+      <c r="H35" s="3">
         <v>359400</v>
       </c>
-      <c r="G35" s="3">
+      <c r="I35" s="3">
         <v>197500</v>
       </c>
-      <c r="H35" s="3">
+      <c r="J35" s="3">
         <v>309200</v>
       </c>
-      <c r="I35" s="3">
+      <c r="K35" s="3">
         <v>321400</v>
       </c>
-      <c r="J35" s="3">
+      <c r="L35" s="3">
         <v>350400</v>
       </c>
-      <c r="K35" s="3">
+      <c r="M35" s="3">
         <v>243200</v>
       </c>
-      <c r="L35" s="3">
+      <c r="N35" s="3">
         <v>304900</v>
       </c>
-      <c r="M35" s="3">
+      <c r="O35" s="3">
         <v>267300</v>
       </c>
-      <c r="N35" s="3">
+      <c r="P35" s="3">
         <v>251000</v>
       </c>
-      <c r="O35" s="3">
+      <c r="Q35" s="3">
         <v>126000</v>
       </c>
-      <c r="P35" s="3">
+      <c r="R35" s="3">
         <v>242800</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="S35" s="3">
         <v>165800</v>
       </c>
-      <c r="R35" s="3">
+      <c r="T35" s="3">
         <v>185600</v>
       </c>
-      <c r="S35" s="3">
+      <c r="U35" s="3">
         <v>76600</v>
       </c>
-      <c r="T35" s="3">
+      <c r="V35" s="3">
         <v>179300</v>
       </c>
-      <c r="U35" s="3">
+      <c r="W35" s="3">
         <v>177000</v>
       </c>
-      <c r="V35" s="3">
+      <c r="X35" s="3">
         <v>213400</v>
       </c>
-      <c r="W35" s="3">
+      <c r="Y35" s="3">
         <v>59100</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Z35" s="3">
         <v>358200</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="AA35" s="3">
         <v>204000</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AB35" s="3">
         <v>207700</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AC35" s="3">
         <v>103600</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AD35" s="3">
         <v>185200</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AE35" s="3">
         <v>148300</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AF35" s="3">
         <v>208700</v>
       </c>
-      <c r="AE35" s="3">
+      <c r="AG35" s="3">
         <v>79900</v>
       </c>
-      <c r="AF35" s="3">
+      <c r="AH35" s="3">
         <v>181400</v>
       </c>
-      <c r="AG35" s="3">
+      <c r="AI35" s="3">
         <v>106400</v>
       </c>
-      <c r="AH35" s="3">
+      <c r="AJ35" s="3">
         <v>106400</v>
       </c>
-      <c r="AI35" s="3">
+      <c r="AK35" s="3">
         <v>73200</v>
       </c>
-      <c r="AJ35" s="3">
+      <c r="AL35" s="3">
         <v>105700</v>
       </c>
-      <c r="AK35" s="3">
+      <c r="AM35" s="3">
         <v>73700</v>
       </c>
     </row>
-    <row r="37" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:39" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45838</v>
+      </c>
+      <c r="E38" s="2">
+        <v>45747</v>
+      </c>
+      <c r="F38" s="2">
         <v>45657</v>
       </c>
-      <c r="E38" s="2">
+      <c r="G38" s="2">
         <v>45565</v>
       </c>
-      <c r="F38" s="2">
+      <c r="H38" s="2">
         <v>45473</v>
       </c>
-      <c r="G38" s="2">
+      <c r="I38" s="2">
         <v>45382</v>
       </c>
-      <c r="H38" s="2">
+      <c r="J38" s="2">
         <v>45291</v>
       </c>
-      <c r="I38" s="2">
+      <c r="K38" s="2">
         <v>45199</v>
       </c>
-      <c r="J38" s="2">
+      <c r="L38" s="2">
         <v>45107</v>
       </c>
-      <c r="K38" s="2">
+      <c r="M38" s="2">
         <v>45016</v>
       </c>
-      <c r="L38" s="2">
+      <c r="N38" s="2">
         <v>44926</v>
       </c>
-      <c r="M38" s="2">
+      <c r="O38" s="2">
         <v>44834</v>
       </c>
-      <c r="N38" s="2">
+      <c r="P38" s="2">
         <v>44742</v>
       </c>
-      <c r="O38" s="2">
+      <c r="Q38" s="2">
         <v>44651</v>
       </c>
-      <c r="P38" s="2">
+      <c r="R38" s="2">
         <v>44561</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="S38" s="2">
         <v>44469</v>
       </c>
-      <c r="R38" s="2">
+      <c r="T38" s="2">
         <v>44377</v>
       </c>
-      <c r="S38" s="2">
+      <c r="U38" s="2">
         <v>44286</v>
       </c>
-      <c r="T38" s="2">
+      <c r="V38" s="2">
         <v>44196</v>
       </c>
-      <c r="U38" s="2">
+      <c r="W38" s="2">
         <v>44104</v>
       </c>
-      <c r="V38" s="2">
+      <c r="X38" s="2">
         <v>44012</v>
       </c>
-      <c r="W38" s="2">
+      <c r="Y38" s="2">
         <v>43921</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Z38" s="2">
         <v>43830</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="AA38" s="2">
         <v>43738</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AB38" s="2">
         <v>43646</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AC38" s="2">
         <v>43555</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AD38" s="2">
         <v>43465</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AE38" s="2">
         <v>43373</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AF38" s="2">
         <v>43281</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AG38" s="2">
         <v>43190</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AH38" s="2">
         <v>43100</v>
       </c>
-      <c r="AG38" s="2">
+      <c r="AI38" s="2">
         <v>43008</v>
       </c>
-      <c r="AH38" s="2">
+      <c r="AJ38" s="2">
         <v>42916</v>
       </c>
-      <c r="AI38" s="2">
+      <c r="AK38" s="2">
         <v>42825</v>
       </c>
-      <c r="AJ38" s="2">
+      <c r="AL38" s="2">
         <v>42735</v>
       </c>
-      <c r="AK38" s="2">
+      <c r="AM38" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="39" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3746,8 +3916,10 @@
       <c r="AI39" s="3"/>
       <c r="AJ39" s="3"/>
       <c r="AK39" s="3"/>
+      <c r="AL39" s="3"/>
+      <c r="AM39" s="3"/>
     </row>
-    <row r="40" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="40" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3785,971 +3957,1027 @@
       <c r="AI40" s="3"/>
       <c r="AJ40" s="3"/>
       <c r="AK40" s="3"/>
+      <c r="AL40" s="3"/>
+      <c r="AM40" s="3"/>
     </row>
-    <row r="41" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="41" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>1855400</v>
+      </c>
+      <c r="E41" s="3">
+        <v>1711300</v>
+      </c>
+      <c r="F41" s="3">
         <v>1844800</v>
       </c>
-      <c r="E41" s="3">
+      <c r="G41" s="3">
         <v>1668400</v>
       </c>
-      <c r="F41" s="3">
+      <c r="H41" s="3">
         <v>1450700</v>
       </c>
-      <c r="G41" s="3">
+      <c r="I41" s="3">
         <v>1742800</v>
       </c>
-      <c r="H41" s="3">
+      <c r="J41" s="3">
         <v>1739400</v>
       </c>
-      <c r="I41" s="3">
+      <c r="K41" s="3">
         <v>1272500</v>
       </c>
-      <c r="J41" s="3">
+      <c r="L41" s="3">
         <v>1073000</v>
       </c>
-      <c r="K41" s="3">
+      <c r="M41" s="3">
         <v>1391100</v>
       </c>
-      <c r="L41" s="3">
+      <c r="N41" s="3">
         <v>1648400</v>
       </c>
-      <c r="M41" s="3">
+      <c r="O41" s="3">
         <v>2016100</v>
       </c>
-      <c r="N41" s="3">
+      <c r="P41" s="3">
         <v>1380200</v>
       </c>
-      <c r="O41" s="3">
+      <c r="Q41" s="3">
         <v>1376400</v>
       </c>
-      <c r="P41" s="3">
+      <c r="R41" s="3">
         <v>1339400</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="S41" s="3">
         <v>1472400</v>
       </c>
-      <c r="R41" s="3">
+      <c r="T41" s="3">
         <v>1737600</v>
       </c>
-      <c r="S41" s="3">
+      <c r="U41" s="3">
         <v>1590500</v>
       </c>
-      <c r="T41" s="3">
+      <c r="V41" s="3">
         <v>1978400</v>
       </c>
-      <c r="U41" s="3">
+      <c r="W41" s="3">
         <v>2418000</v>
       </c>
-      <c r="V41" s="3">
+      <c r="X41" s="3">
         <v>775400</v>
       </c>
-      <c r="W41" s="3">
+      <c r="Y41" s="3">
         <v>792000</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Z41" s="3">
         <v>811500</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="AA41" s="3">
         <v>789200</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AB41" s="3">
         <v>1086500</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AC41" s="3">
         <v>926800</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AD41" s="3">
         <v>671300</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AE41" s="3">
         <v>877700</v>
       </c>
-      <c r="AD41" s="3">
+      <c r="AF41" s="3">
         <v>848700</v>
       </c>
-      <c r="AE41" s="3">
+      <c r="AG41" s="3">
         <v>486000</v>
       </c>
-      <c r="AF41" s="3">
+      <c r="AH41" s="3">
         <v>805100</v>
       </c>
-      <c r="AG41" s="3">
+      <c r="AI41" s="3">
         <v>768800</v>
       </c>
-      <c r="AH41" s="3">
+      <c r="AJ41" s="3">
         <v>848000</v>
       </c>
-      <c r="AI41" s="3">
+      <c r="AK41" s="3">
         <v>920400</v>
       </c>
-      <c r="AJ41" s="3">
+      <c r="AL41" s="3">
         <v>1641600</v>
       </c>
-      <c r="AK41" s="3">
+      <c r="AM41" s="3">
         <v>287600</v>
       </c>
     </row>
-    <row r="42" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>1847100</v>
+      </c>
+      <c r="E42" s="3">
+        <v>1461300</v>
+      </c>
+      <c r="F42" s="3">
         <v>1237300</v>
       </c>
-      <c r="E42" s="3">
+      <c r="G42" s="3">
         <v>1598600</v>
       </c>
-      <c r="F42" s="3">
+      <c r="H42" s="3">
         <v>1362200</v>
       </c>
-      <c r="G42" s="3">
+      <c r="I42" s="3">
         <v>974800</v>
       </c>
-      <c r="H42" s="3">
+      <c r="J42" s="3">
         <v>1066000</v>
       </c>
-      <c r="I42" s="3">
+      <c r="K42" s="3">
         <v>1048900</v>
       </c>
-      <c r="J42" s="3">
+      <c r="L42" s="3">
         <v>1097100</v>
       </c>
-      <c r="K42" s="3">
+      <c r="M42" s="3">
         <v>1292500</v>
       </c>
-      <c r="L42" s="3">
+      <c r="N42" s="3">
         <v>811100</v>
       </c>
-      <c r="M42" s="3">
+      <c r="O42" s="3">
         <v>960600</v>
       </c>
-      <c r="N42" s="3">
+      <c r="P42" s="3">
         <v>724400</v>
       </c>
-      <c r="O42" s="3">
+      <c r="Q42" s="3">
         <v>556400</v>
       </c>
-      <c r="P42" s="3">
+      <c r="R42" s="3">
         <v>392000</v>
       </c>
-      <c r="Q42" s="3">
+      <c r="S42" s="3">
         <v>336100</v>
       </c>
-      <c r="R42" s="3">
+      <c r="T42" s="3">
         <v>450800</v>
       </c>
-      <c r="S42" s="3">
+      <c r="U42" s="3">
         <v>794000</v>
       </c>
-      <c r="T42" s="3">
+      <c r="V42" s="3">
         <v>513700</v>
       </c>
-      <c r="U42" s="3">
+      <c r="W42" s="3">
         <v>708000</v>
       </c>
-      <c r="V42" s="3">
+      <c r="X42" s="3">
         <v>1243400</v>
       </c>
-      <c r="W42" s="3">
+      <c r="Y42" s="3">
         <v>1596100</v>
       </c>
-      <c r="X42" s="3">
+      <c r="Z42" s="3">
         <v>1711200</v>
       </c>
-      <c r="Y42" s="3">
+      <c r="AA42" s="3">
         <v>1763500</v>
       </c>
-      <c r="Z42" s="3">
+      <c r="AB42" s="3">
         <v>1414900</v>
       </c>
-      <c r="AA42" s="3">
+      <c r="AC42" s="3">
         <v>1717000</v>
       </c>
-      <c r="AB42" s="3">
+      <c r="AD42" s="3">
         <v>1975100</v>
       </c>
-      <c r="AC42" s="3">
+      <c r="AE42" s="3">
         <v>1664900</v>
       </c>
-      <c r="AD42" s="3">
+      <c r="AF42" s="3">
         <v>1343800</v>
       </c>
-      <c r="AE42" s="3">
+      <c r="AG42" s="3">
         <v>795600</v>
       </c>
-      <c r="AF42" s="3">
+      <c r="AH42" s="3">
         <v>775400</v>
       </c>
-      <c r="AG42" s="3">
+      <c r="AI42" s="3">
         <v>819600</v>
       </c>
-      <c r="AH42" s="3">
+      <c r="AJ42" s="3">
         <v>769700</v>
       </c>
-      <c r="AI42" s="3">
+      <c r="AK42" s="3">
         <v>700700</v>
       </c>
-      <c r="AJ42" s="3" t="s">
+      <c r="AL42" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AK42" s="3" t="s">
+      <c r="AM42" s="3" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="43" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>330400</v>
+      </c>
+      <c r="E43" s="3">
+        <v>288400</v>
+      </c>
+      <c r="F43" s="3">
         <v>438300</v>
       </c>
-      <c r="E43" s="3">
+      <c r="G43" s="3">
         <v>307200</v>
       </c>
-      <c r="F43" s="3">
+      <c r="H43" s="3">
         <v>265400</v>
       </c>
-      <c r="G43" s="3">
+      <c r="I43" s="3">
         <v>241100</v>
       </c>
-      <c r="H43" s="3">
+      <c r="J43" s="3">
         <v>280800</v>
       </c>
-      <c r="I43" s="3">
+      <c r="K43" s="3">
         <v>329600</v>
       </c>
-      <c r="J43" s="3">
+      <c r="L43" s="3">
         <v>319700</v>
       </c>
-      <c r="K43" s="3">
+      <c r="M43" s="3">
         <v>266800</v>
       </c>
-      <c r="L43" s="3">
+      <c r="N43" s="3">
         <v>293900</v>
       </c>
-      <c r="M43" s="3">
+      <c r="O43" s="3">
         <v>265800</v>
       </c>
-      <c r="N43" s="3">
+      <c r="P43" s="3">
         <v>267700</v>
       </c>
-      <c r="O43" s="3">
+      <c r="Q43" s="3">
         <v>264100</v>
       </c>
-      <c r="P43" s="3">
+      <c r="R43" s="3">
         <v>300200</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="S43" s="3">
         <v>260500</v>
       </c>
-      <c r="R43" s="3">
+      <c r="T43" s="3">
         <v>262000</v>
       </c>
-      <c r="S43" s="3">
+      <c r="U43" s="3">
         <v>187900</v>
       </c>
-      <c r="T43" s="3">
+      <c r="V43" s="3">
         <v>182600</v>
       </c>
-      <c r="U43" s="3">
+      <c r="W43" s="3">
         <v>252900</v>
       </c>
-      <c r="V43" s="3">
+      <c r="X43" s="3">
         <v>174200</v>
       </c>
-      <c r="W43" s="3">
+      <c r="Y43" s="3">
         <v>210600</v>
       </c>
-      <c r="X43" s="3">
+      <c r="Z43" s="3">
         <v>194200</v>
       </c>
-      <c r="Y43" s="3">
+      <c r="AA43" s="3">
         <v>172000</v>
       </c>
-      <c r="Z43" s="3">
+      <c r="AB43" s="3">
         <v>177300</v>
       </c>
-      <c r="AA43" s="3">
+      <c r="AC43" s="3">
         <v>171100</v>
       </c>
-      <c r="AB43" s="3">
+      <c r="AD43" s="3">
         <v>162900</v>
       </c>
-      <c r="AC43" s="3">
+      <c r="AE43" s="3">
         <v>120200</v>
       </c>
-      <c r="AD43" s="3">
+      <c r="AF43" s="3">
         <v>209200</v>
       </c>
-      <c r="AE43" s="3">
+      <c r="AG43" s="3">
         <v>69200</v>
       </c>
-      <c r="AF43" s="3">
+      <c r="AH43" s="3">
         <v>53700</v>
       </c>
-      <c r="AG43" s="3">
+      <c r="AI43" s="3">
         <v>31000</v>
       </c>
-      <c r="AH43" s="3">
+      <c r="AJ43" s="3">
         <v>28800</v>
       </c>
-      <c r="AI43" s="3">
+      <c r="AK43" s="3">
         <v>25200</v>
       </c>
-      <c r="AJ43" s="3">
+      <c r="AL43" s="3">
         <v>29600</v>
       </c>
-      <c r="AK43" s="3">
+      <c r="AM43" s="3">
         <v>17800</v>
       </c>
     </row>
-    <row r="44" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>6700</v>
+      </c>
+      <c r="E44" s="3">
+        <v>4900</v>
+      </c>
+      <c r="F44" s="3">
         <v>5300</v>
       </c>
-      <c r="E44" s="3">
+      <c r="G44" s="3">
         <v>3900</v>
       </c>
-      <c r="F44" s="3">
+      <c r="H44" s="3">
         <v>3900</v>
       </c>
-      <c r="G44" s="3">
+      <c r="I44" s="3">
         <v>5700</v>
       </c>
-      <c r="H44" s="3">
+      <c r="J44" s="3">
         <v>4000</v>
       </c>
-      <c r="I44" s="3">
+      <c r="K44" s="3">
         <v>3800</v>
       </c>
-      <c r="J44" s="3">
+      <c r="L44" s="3">
         <v>3700</v>
       </c>
-      <c r="K44" s="3">
+      <c r="M44" s="3">
         <v>4200</v>
       </c>
-      <c r="L44" s="3">
+      <c r="N44" s="3">
         <v>5700</v>
       </c>
-      <c r="M44" s="3">
+      <c r="O44" s="3">
         <v>8900</v>
       </c>
-      <c r="N44" s="3">
+      <c r="P44" s="3">
         <v>4000</v>
       </c>
-      <c r="O44" s="3">
+      <c r="Q44" s="3">
         <v>8200</v>
       </c>
-      <c r="P44" s="3">
+      <c r="R44" s="3">
         <v>11400</v>
       </c>
-      <c r="Q44" s="3">
+      <c r="S44" s="3">
         <v>7100</v>
       </c>
-      <c r="R44" s="3">
+      <c r="T44" s="3">
         <v>5700</v>
-      </c>
-      <c r="S44" s="3">
-        <v>7400</v>
-      </c>
-      <c r="T44" s="3">
-        <v>7400</v>
       </c>
       <c r="U44" s="3">
         <v>7400</v>
       </c>
       <c r="V44" s="3">
+        <v>7400</v>
+      </c>
+      <c r="W44" s="3">
+        <v>7400</v>
+      </c>
+      <c r="X44" s="3">
         <v>9500</v>
       </c>
-      <c r="W44" s="3">
+      <c r="Y44" s="3">
         <v>8900</v>
       </c>
-      <c r="X44" s="3">
+      <c r="Z44" s="3">
         <v>6800</v>
       </c>
-      <c r="Y44" s="3">
+      <c r="AA44" s="3">
         <v>5600</v>
       </c>
-      <c r="Z44" s="3">
+      <c r="AB44" s="3">
         <v>5400</v>
       </c>
-      <c r="AA44" s="3">
+      <c r="AC44" s="3">
         <v>4700</v>
       </c>
-      <c r="AB44" s="3">
+      <c r="AD44" s="3">
         <v>6400</v>
       </c>
-      <c r="AC44" s="3">
+      <c r="AE44" s="3">
         <v>5200</v>
       </c>
-      <c r="AD44" s="3">
+      <c r="AF44" s="3">
         <v>5600</v>
       </c>
-      <c r="AE44" s="3">
+      <c r="AG44" s="3">
         <v>4400</v>
       </c>
-      <c r="AF44" s="3">
+      <c r="AH44" s="3">
         <v>5100</v>
       </c>
-      <c r="AG44" s="3">
+      <c r="AI44" s="3">
         <v>4200</v>
       </c>
-      <c r="AH44" s="3">
+      <c r="AJ44" s="3">
         <v>4300</v>
       </c>
-      <c r="AI44" s="3">
+      <c r="AK44" s="3">
         <v>4600</v>
       </c>
-      <c r="AJ44" s="3">
+      <c r="AL44" s="3">
         <v>4900</v>
       </c>
-      <c r="AK44" s="3">
+      <c r="AM44" s="3">
         <v>4100</v>
       </c>
     </row>
-    <row r="45" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>776000</v>
+      </c>
+      <c r="E45" s="3">
+        <v>742900</v>
+      </c>
+      <c r="F45" s="3">
         <v>614900</v>
       </c>
-      <c r="E45" s="3">
+      <c r="G45" s="3">
         <v>716400</v>
       </c>
-      <c r="F45" s="3">
+      <c r="H45" s="3">
         <v>759300</v>
       </c>
-      <c r="G45" s="3">
+      <c r="I45" s="3">
         <v>701200</v>
       </c>
-      <c r="H45" s="3">
+      <c r="J45" s="3">
         <v>599700</v>
       </c>
-      <c r="I45" s="3">
+      <c r="K45" s="3">
         <v>625500</v>
       </c>
-      <c r="J45" s="3">
+      <c r="L45" s="3">
         <v>606800</v>
       </c>
-      <c r="K45" s="3">
+      <c r="M45" s="3">
         <v>620000</v>
       </c>
-      <c r="L45" s="3">
+      <c r="N45" s="3">
         <v>691300</v>
       </c>
-      <c r="M45" s="3">
+      <c r="O45" s="3">
         <v>584100</v>
       </c>
-      <c r="N45" s="3">
+      <c r="P45" s="3">
         <v>567700</v>
       </c>
-      <c r="O45" s="3">
+      <c r="Q45" s="3">
         <v>580200</v>
       </c>
-      <c r="P45" s="3">
+      <c r="R45" s="3">
         <v>528800</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="S45" s="3">
         <v>552300</v>
       </c>
-      <c r="R45" s="3">
+      <c r="T45" s="3">
         <v>501800</v>
       </c>
-      <c r="S45" s="3">
+      <c r="U45" s="3">
         <v>511200</v>
       </c>
-      <c r="T45" s="3">
+      <c r="V45" s="3">
         <v>425500</v>
       </c>
-      <c r="U45" s="3">
+      <c r="W45" s="3">
         <v>433900</v>
       </c>
-      <c r="V45" s="3">
+      <c r="X45" s="3">
         <v>423200</v>
       </c>
-      <c r="W45" s="3">
+      <c r="Y45" s="3">
         <v>378400</v>
       </c>
-      <c r="X45" s="3">
+      <c r="Z45" s="3">
         <v>371100</v>
       </c>
-      <c r="Y45" s="3">
+      <c r="AA45" s="3">
         <v>313400</v>
       </c>
-      <c r="Z45" s="3">
+      <c r="AB45" s="3">
         <v>374900</v>
       </c>
-      <c r="AA45" s="3">
+      <c r="AC45" s="3">
         <v>264700</v>
       </c>
-      <c r="AB45" s="3">
+      <c r="AD45" s="3">
         <v>268100</v>
       </c>
-      <c r="AC45" s="3">
+      <c r="AE45" s="3">
         <v>213400</v>
       </c>
-      <c r="AD45" s="3">
+      <c r="AF45" s="3">
         <v>191900</v>
       </c>
-      <c r="AE45" s="3">
+      <c r="AG45" s="3">
         <v>168000</v>
       </c>
-      <c r="AF45" s="3">
+      <c r="AH45" s="3">
         <v>197700</v>
       </c>
-      <c r="AG45" s="3">
+      <c r="AI45" s="3">
         <v>172000</v>
       </c>
-      <c r="AH45" s="3">
+      <c r="AJ45" s="3">
         <v>168000</v>
       </c>
-      <c r="AI45" s="3">
+      <c r="AK45" s="3">
         <v>226600</v>
       </c>
-      <c r="AJ45" s="3">
+      <c r="AL45" s="3">
         <v>241600</v>
       </c>
-      <c r="AK45" s="3">
+      <c r="AM45" s="3">
         <v>149500</v>
       </c>
     </row>
-    <row r="46" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>4818800</v>
+      </c>
+      <c r="E46" s="3">
+        <v>4212900</v>
+      </c>
+      <c r="F46" s="3">
         <v>4158600</v>
       </c>
-      <c r="E46" s="3">
+      <c r="G46" s="3">
         <v>4299200</v>
       </c>
-      <c r="F46" s="3">
+      <c r="H46" s="3">
         <v>3844500</v>
       </c>
-      <c r="G46" s="3">
+      <c r="I46" s="3">
         <v>3703300</v>
       </c>
-      <c r="H46" s="3">
+      <c r="J46" s="3">
         <v>3801100</v>
       </c>
-      <c r="I46" s="3">
+      <c r="K46" s="3">
         <v>3388900</v>
       </c>
-      <c r="J46" s="3">
+      <c r="L46" s="3">
         <v>3217700</v>
       </c>
-      <c r="K46" s="3">
+      <c r="M46" s="3">
         <v>3680800</v>
       </c>
-      <c r="L46" s="3">
+      <c r="N46" s="3">
         <v>3450500</v>
       </c>
-      <c r="M46" s="3">
+      <c r="O46" s="3">
         <v>3835500</v>
       </c>
-      <c r="N46" s="3">
+      <c r="P46" s="3">
         <v>2944100</v>
       </c>
-      <c r="O46" s="3">
+      <c r="Q46" s="3">
         <v>2785400</v>
       </c>
-      <c r="P46" s="3">
+      <c r="R46" s="3">
         <v>2571900</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="S46" s="3">
         <v>2628500</v>
       </c>
-      <c r="R46" s="3">
+      <c r="T46" s="3">
         <v>2957900</v>
       </c>
-      <c r="S46" s="3">
+      <c r="U46" s="3">
         <v>3091000</v>
       </c>
-      <c r="T46" s="3">
+      <c r="V46" s="3">
         <v>3107600</v>
       </c>
-      <c r="U46" s="3">
+      <c r="W46" s="3">
         <v>3820200</v>
       </c>
-      <c r="V46" s="3">
+      <c r="X46" s="3">
         <v>2625600</v>
       </c>
-      <c r="W46" s="3">
+      <c r="Y46" s="3">
         <v>2986000</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Z46" s="3">
         <v>3094700</v>
       </c>
-      <c r="Y46" s="3">
+      <c r="AA46" s="3">
         <v>3043800</v>
       </c>
-      <c r="Z46" s="3">
+      <c r="AB46" s="3">
         <v>3059000</v>
       </c>
-      <c r="AA46" s="3">
+      <c r="AC46" s="3">
         <v>3084200</v>
       </c>
-      <c r="AB46" s="3">
+      <c r="AD46" s="3">
         <v>3083800</v>
       </c>
-      <c r="AC46" s="3">
+      <c r="AE46" s="3">
         <v>2881400</v>
       </c>
-      <c r="AD46" s="3">
+      <c r="AF46" s="3">
         <v>2599300</v>
       </c>
-      <c r="AE46" s="3">
+      <c r="AG46" s="3">
         <v>1523100</v>
       </c>
-      <c r="AF46" s="3">
+      <c r="AH46" s="3">
         <v>1837000</v>
       </c>
-      <c r="AG46" s="3">
+      <c r="AI46" s="3">
         <v>1795600</v>
       </c>
-      <c r="AH46" s="3">
+      <c r="AJ46" s="3">
         <v>1818900</v>
       </c>
-      <c r="AI46" s="3">
+      <c r="AK46" s="3">
         <v>1877500</v>
       </c>
-      <c r="AJ46" s="3">
+      <c r="AL46" s="3">
         <v>1917600</v>
       </c>
-      <c r="AK46" s="3">
+      <c r="AM46" s="3">
         <v>459000</v>
       </c>
     </row>
-    <row r="47" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>1527800</v>
+      </c>
+      <c r="E47" s="3">
+        <v>1847800</v>
+      </c>
+      <c r="F47" s="3">
         <v>1902800</v>
       </c>
-      <c r="E47" s="3">
+      <c r="G47" s="3">
         <v>2224700</v>
       </c>
-      <c r="F47" s="3">
+      <c r="H47" s="3">
         <v>2219600</v>
       </c>
-      <c r="G47" s="3">
+      <c r="I47" s="3">
         <v>2270700</v>
       </c>
-      <c r="H47" s="3">
+      <c r="J47" s="3">
         <v>2203700</v>
       </c>
-      <c r="I47" s="3">
+      <c r="K47" s="3">
         <v>2439100</v>
       </c>
-      <c r="J47" s="3">
+      <c r="L47" s="3">
         <v>2055100</v>
       </c>
-      <c r="K47" s="3">
+      <c r="M47" s="3">
         <v>1759700</v>
       </c>
-      <c r="L47" s="3">
+      <c r="N47" s="3">
         <v>1853300</v>
       </c>
-      <c r="M47" s="3">
+      <c r="O47" s="3">
         <v>1337100</v>
       </c>
-      <c r="N47" s="3">
+      <c r="P47" s="3">
         <v>1167900</v>
       </c>
-      <c r="O47" s="3">
+      <c r="Q47" s="3">
         <v>1019900</v>
       </c>
-      <c r="P47" s="3">
+      <c r="R47" s="3">
         <v>960200</v>
       </c>
-      <c r="Q47" s="3">
+      <c r="S47" s="3">
         <v>996500</v>
       </c>
-      <c r="R47" s="3">
+      <c r="T47" s="3">
         <v>1076500</v>
       </c>
-      <c r="S47" s="3">
+      <c r="U47" s="3">
         <v>1100900</v>
       </c>
-      <c r="T47" s="3">
+      <c r="V47" s="3">
         <v>1049100</v>
       </c>
-      <c r="U47" s="3">
+      <c r="W47" s="3">
         <v>898800</v>
       </c>
-      <c r="V47" s="3">
+      <c r="X47" s="3">
         <v>876900</v>
       </c>
-      <c r="W47" s="3">
+      <c r="Y47" s="3">
         <v>771500</v>
       </c>
-      <c r="X47" s="3">
+      <c r="Z47" s="3">
         <v>709100</v>
       </c>
-      <c r="Y47" s="3">
+      <c r="AA47" s="3">
         <v>347600</v>
       </c>
-      <c r="Z47" s="3">
+      <c r="AB47" s="3">
         <v>336200</v>
       </c>
-      <c r="AA47" s="3">
+      <c r="AC47" s="3">
         <v>332500</v>
       </c>
-      <c r="AB47" s="3">
+      <c r="AD47" s="3">
         <v>320600</v>
       </c>
-      <c r="AC47" s="3">
+      <c r="AE47" s="3">
         <v>239300</v>
       </c>
-      <c r="AD47" s="3">
+      <c r="AF47" s="3">
         <v>215800</v>
       </c>
-      <c r="AE47" s="3">
+      <c r="AG47" s="3">
         <v>86400</v>
       </c>
-      <c r="AF47" s="3">
+      <c r="AH47" s="3">
         <v>90600</v>
       </c>
-      <c r="AG47" s="3">
+      <c r="AI47" s="3">
         <v>82600</v>
       </c>
-      <c r="AH47" s="3">
+      <c r="AJ47" s="3">
         <v>78200</v>
       </c>
-      <c r="AI47" s="3">
+      <c r="AK47" s="3">
         <v>76400</v>
       </c>
-      <c r="AJ47" s="3">
+      <c r="AL47" s="3">
         <v>78100</v>
       </c>
-      <c r="AK47" s="3">
+      <c r="AM47" s="3">
         <v>69300</v>
       </c>
     </row>
-    <row r="48" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>4935000</v>
+      </c>
+      <c r="E48" s="3">
+        <v>4834200</v>
+      </c>
+      <c r="F48" s="3">
         <v>4724100</v>
       </c>
-      <c r="E48" s="3">
+      <c r="G48" s="3">
         <v>4870600</v>
       </c>
-      <c r="F48" s="3">
+      <c r="H48" s="3">
         <v>4637600</v>
       </c>
-      <c r="G48" s="3">
+      <c r="I48" s="3">
         <v>4645500</v>
       </c>
-      <c r="H48" s="3">
+      <c r="J48" s="3">
         <v>4633200</v>
       </c>
-      <c r="I48" s="3">
+      <c r="K48" s="3">
         <v>4456300</v>
       </c>
-      <c r="J48" s="3">
+      <c r="L48" s="3">
         <v>4371400</v>
       </c>
-      <c r="K48" s="3">
+      <c r="M48" s="3">
         <v>4453700</v>
       </c>
-      <c r="L48" s="3">
+      <c r="N48" s="3">
         <v>4176100</v>
       </c>
-      <c r="M48" s="3">
+      <c r="O48" s="3">
         <v>3977700</v>
       </c>
-      <c r="N48" s="3">
+      <c r="P48" s="3">
         <v>3845100</v>
       </c>
-      <c r="O48" s="3">
+      <c r="Q48" s="3">
         <v>3707100</v>
       </c>
-      <c r="P48" s="3">
+      <c r="R48" s="3">
         <v>3558500</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="S48" s="3">
         <v>3435000</v>
       </c>
-      <c r="R48" s="3">
+      <c r="T48" s="3">
         <v>3191700</v>
       </c>
-      <c r="S48" s="3">
+      <c r="U48" s="3">
         <v>2895100</v>
       </c>
-      <c r="T48" s="3">
+      <c r="V48" s="3">
         <v>2706200</v>
       </c>
-      <c r="U48" s="3">
+      <c r="W48" s="3">
         <v>2552500</v>
       </c>
-      <c r="V48" s="3">
+      <c r="X48" s="3">
         <v>2274600</v>
       </c>
-      <c r="W48" s="3">
+      <c r="Y48" s="3">
         <v>2237200</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Z48" s="3">
         <v>2059100</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="AA48" s="3">
         <v>1814900</v>
       </c>
-      <c r="Z48" s="3">
+      <c r="AB48" s="3">
         <v>1577900</v>
       </c>
-      <c r="AA48" s="3">
+      <c r="AC48" s="3">
         <v>1532300</v>
       </c>
-      <c r="AB48" s="3">
+      <c r="AD48" s="3">
         <v>1312300</v>
       </c>
-      <c r="AC48" s="3">
+      <c r="AE48" s="3">
         <v>1117100</v>
       </c>
-      <c r="AD48" s="3">
+      <c r="AF48" s="3">
         <v>1015500</v>
       </c>
-      <c r="AE48" s="3">
+      <c r="AG48" s="3">
         <v>983700</v>
       </c>
-      <c r="AF48" s="3">
+      <c r="AH48" s="3">
         <v>960700</v>
       </c>
-      <c r="AG48" s="3">
+      <c r="AI48" s="3">
         <v>866600</v>
       </c>
-      <c r="AH48" s="3">
+      <c r="AJ48" s="3">
         <v>765200</v>
       </c>
-      <c r="AI48" s="3">
+      <c r="AK48" s="3">
         <v>668800</v>
       </c>
-      <c r="AJ48" s="3">
+      <c r="AL48" s="3">
         <v>591300</v>
       </c>
-      <c r="AK48" s="3">
+      <c r="AM48" s="3">
         <v>479700</v>
       </c>
     </row>
-    <row r="49" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>1457000</v>
+      </c>
+      <c r="E49" s="3">
+        <v>1454800</v>
+      </c>
+      <c r="F49" s="3">
         <v>1428800</v>
       </c>
-      <c r="E49" s="3">
+      <c r="G49" s="3">
         <v>1476600</v>
       </c>
-      <c r="F49" s="3">
+      <c r="H49" s="3">
         <v>1381900</v>
       </c>
-      <c r="G49" s="3">
+      <c r="I49" s="3">
         <v>1376500</v>
       </c>
-      <c r="H49" s="3">
+      <c r="J49" s="3">
         <v>1396400</v>
       </c>
-      <c r="I49" s="3">
+      <c r="K49" s="3">
         <v>1358000</v>
       </c>
-      <c r="J49" s="3">
+      <c r="L49" s="3">
         <v>1370700</v>
       </c>
-      <c r="K49" s="3">
+      <c r="M49" s="3">
         <v>1446200</v>
       </c>
-      <c r="L49" s="3">
+      <c r="N49" s="3">
         <v>1369500</v>
       </c>
-      <c r="M49" s="3">
+      <c r="O49" s="3">
         <v>1331500</v>
       </c>
-      <c r="N49" s="3">
+      <c r="P49" s="3">
         <v>1350200</v>
       </c>
-      <c r="O49" s="3">
+      <c r="Q49" s="3">
         <v>1338000</v>
       </c>
-      <c r="P49" s="3">
+      <c r="R49" s="3">
         <v>1324400</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="S49" s="3">
         <v>1333000</v>
       </c>
-      <c r="R49" s="3">
+      <c r="T49" s="3">
         <v>1321600</v>
       </c>
-      <c r="S49" s="3">
+      <c r="U49" s="3">
         <v>1295800</v>
       </c>
-      <c r="T49" s="3">
+      <c r="V49" s="3">
         <v>1203300</v>
       </c>
-      <c r="U49" s="3">
+      <c r="W49" s="3">
         <v>1236400</v>
       </c>
-      <c r="V49" s="3">
+      <c r="X49" s="3">
         <v>1195900</v>
       </c>
-      <c r="W49" s="3">
+      <c r="Y49" s="3">
         <v>1154200</v>
       </c>
-      <c r="X49" s="3">
+      <c r="Z49" s="3">
         <v>1046800</v>
       </c>
-      <c r="Y49" s="3">
+      <c r="AA49" s="3">
         <v>1029800</v>
       </c>
-      <c r="Z49" s="3">
+      <c r="AB49" s="3">
         <v>987300</v>
       </c>
-      <c r="AA49" s="3">
+      <c r="AC49" s="3">
         <v>983500</v>
       </c>
-      <c r="AB49" s="3">
+      <c r="AD49" s="3">
         <v>909900</v>
       </c>
-      <c r="AC49" s="3">
+      <c r="AE49" s="3">
         <v>873300</v>
       </c>
-      <c r="AD49" s="3">
+      <c r="AF49" s="3">
         <v>861700</v>
       </c>
-      <c r="AE49" s="3">
+      <c r="AG49" s="3">
         <v>880200</v>
       </c>
-      <c r="AF49" s="3">
+      <c r="AH49" s="3">
         <v>876300</v>
       </c>
-      <c r="AG49" s="3">
+      <c r="AI49" s="3">
         <v>841400</v>
       </c>
-      <c r="AH49" s="3">
+      <c r="AJ49" s="3">
         <v>835000</v>
       </c>
-      <c r="AI49" s="3">
+      <c r="AK49" s="3">
         <v>815900</v>
       </c>
-      <c r="AJ49" s="3">
+      <c r="AL49" s="3">
         <v>794000</v>
       </c>
-      <c r="AK49" s="3">
+      <c r="AM49" s="3">
         <v>777200</v>
       </c>
     </row>
-    <row r="50" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -4855,8 +5083,14 @@
       <c r="AK50" s="3">
         <v>0</v>
       </c>
+      <c r="AL50" s="3">
+        <v>0</v>
+      </c>
+      <c r="AM50" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="51" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="51" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -4962,115 +5196,127 @@
       <c r="AK51" s="3">
         <v>0</v>
       </c>
+      <c r="AL51" s="3">
+        <v>0</v>
+      </c>
+      <c r="AM51" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="52" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="52" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>117300</v>
+      </c>
+      <c r="E52" s="3">
+        <v>129400</v>
+      </c>
+      <c r="F52" s="3">
         <v>126000</v>
       </c>
-      <c r="E52" s="3">
+      <c r="G52" s="3">
         <v>135900</v>
       </c>
-      <c r="F52" s="3">
+      <c r="H52" s="3">
         <v>128200</v>
       </c>
-      <c r="G52" s="3">
+      <c r="I52" s="3">
         <v>99600</v>
       </c>
-      <c r="H52" s="3">
+      <c r="J52" s="3">
         <v>99000</v>
       </c>
-      <c r="I52" s="3">
+      <c r="K52" s="3">
         <v>72800</v>
       </c>
-      <c r="J52" s="3">
+      <c r="L52" s="3">
         <v>53000</v>
       </c>
-      <c r="K52" s="3">
+      <c r="M52" s="3">
         <v>74600</v>
       </c>
-      <c r="L52" s="3">
+      <c r="N52" s="3">
         <v>220900</v>
       </c>
-      <c r="M52" s="3">
+      <c r="O52" s="3">
         <v>238500</v>
       </c>
-      <c r="N52" s="3">
+      <c r="P52" s="3">
         <v>216500</v>
       </c>
-      <c r="O52" s="3">
+      <c r="Q52" s="3">
         <v>234300</v>
       </c>
-      <c r="P52" s="3">
+      <c r="R52" s="3">
         <v>233800</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="S52" s="3">
         <v>230200</v>
       </c>
-      <c r="R52" s="3">
+      <c r="T52" s="3">
         <v>251600</v>
       </c>
-      <c r="S52" s="3">
+      <c r="U52" s="3">
         <v>250600</v>
       </c>
-      <c r="T52" s="3">
+      <c r="V52" s="3">
         <v>175100</v>
       </c>
-      <c r="U52" s="3">
+      <c r="W52" s="3">
         <v>172000</v>
       </c>
-      <c r="V52" s="3">
+      <c r="X52" s="3">
         <v>170900</v>
       </c>
-      <c r="W52" s="3">
+      <c r="Y52" s="3">
         <v>179500</v>
       </c>
-      <c r="X52" s="3">
+      <c r="Z52" s="3">
         <v>156400</v>
       </c>
-      <c r="Y52" s="3">
+      <c r="AA52" s="3">
         <v>391500</v>
       </c>
-      <c r="Z52" s="3">
+      <c r="AB52" s="3">
         <v>232100</v>
       </c>
-      <c r="AA52" s="3">
+      <c r="AC52" s="3">
         <v>172600</v>
       </c>
-      <c r="AB52" s="3">
+      <c r="AD52" s="3">
         <v>136600</v>
       </c>
-      <c r="AC52" s="3">
+      <c r="AE52" s="3">
         <v>108700</v>
       </c>
-      <c r="AD52" s="3">
+      <c r="AF52" s="3">
         <v>108200</v>
       </c>
-      <c r="AE52" s="3">
+      <c r="AG52" s="3">
         <v>87800</v>
       </c>
-      <c r="AF52" s="3">
+      <c r="AH52" s="3">
         <v>68500</v>
       </c>
-      <c r="AG52" s="3">
+      <c r="AI52" s="3">
         <v>45800</v>
       </c>
-      <c r="AH52" s="3">
+      <c r="AJ52" s="3">
         <v>34600</v>
       </c>
-      <c r="AI52" s="3">
+      <c r="AK52" s="3">
         <v>28700</v>
       </c>
-      <c r="AJ52" s="3">
+      <c r="AL52" s="3">
         <v>22500</v>
       </c>
-      <c r="AK52" s="3">
+      <c r="AM52" s="3">
         <v>26400</v>
       </c>
     </row>
-    <row r="53" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -5176,115 +5422,127 @@
       <c r="AK53" s="3">
         <v>0</v>
       </c>
+      <c r="AL53" s="3">
+        <v>0</v>
+      </c>
+      <c r="AM53" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="54" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="54" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>13208200</v>
+      </c>
+      <c r="E54" s="3">
+        <v>12836700</v>
+      </c>
+      <c r="F54" s="3">
         <v>12650900</v>
       </c>
-      <c r="E54" s="3">
+      <c r="G54" s="3">
         <v>13303900</v>
       </c>
-      <c r="F54" s="3">
+      <c r="H54" s="3">
         <v>12536800</v>
       </c>
-      <c r="G54" s="3">
+      <c r="I54" s="3">
         <v>12447200</v>
       </c>
-      <c r="H54" s="3">
+      <c r="J54" s="3">
         <v>12475900</v>
       </c>
-      <c r="I54" s="3">
+      <c r="K54" s="3">
         <v>11986900</v>
       </c>
-      <c r="J54" s="3">
+      <c r="L54" s="3">
         <v>11314300</v>
       </c>
-      <c r="K54" s="3">
+      <c r="M54" s="3">
         <v>11747600</v>
       </c>
-      <c r="L54" s="3">
+      <c r="N54" s="3">
         <v>11070300</v>
       </c>
-      <c r="M54" s="3">
+      <c r="O54" s="3">
         <v>10720300</v>
       </c>
-      <c r="N54" s="3">
+      <c r="P54" s="3">
         <v>9523700</v>
       </c>
-      <c r="O54" s="3">
+      <c r="Q54" s="3">
         <v>9084600</v>
       </c>
-      <c r="P54" s="3">
+      <c r="R54" s="3">
         <v>8648800</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="S54" s="3">
         <v>8623200</v>
       </c>
-      <c r="R54" s="3">
+      <c r="T54" s="3">
         <v>8799300</v>
       </c>
-      <c r="S54" s="3">
+      <c r="U54" s="3">
         <v>8633300</v>
       </c>
-      <c r="T54" s="3">
+      <c r="V54" s="3">
         <v>8241300</v>
       </c>
-      <c r="U54" s="3">
+      <c r="W54" s="3">
         <v>8679900</v>
       </c>
-      <c r="V54" s="3">
+      <c r="X54" s="3">
         <v>7144000</v>
       </c>
-      <c r="W54" s="3">
+      <c r="Y54" s="3">
         <v>7328400</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Z54" s="3">
         <v>7066200</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="AA54" s="3">
         <v>6627600</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AB54" s="3">
         <v>6192400</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AC54" s="3">
         <v>6105100</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AD54" s="3">
         <v>5763100</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AE54" s="3">
         <v>5219700</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AF54" s="3">
         <v>4800400</v>
       </c>
-      <c r="AE54" s="3">
+      <c r="AG54" s="3">
         <v>3561300</v>
       </c>
-      <c r="AF54" s="3">
+      <c r="AH54" s="3">
         <v>3833100</v>
       </c>
-      <c r="AG54" s="3">
+      <c r="AI54" s="3">
         <v>3632000</v>
       </c>
-      <c r="AH54" s="3">
+      <c r="AJ54" s="3">
         <v>3531800</v>
       </c>
-      <c r="AI54" s="3">
+      <c r="AK54" s="3">
         <v>3467300</v>
       </c>
-      <c r="AJ54" s="3">
+      <c r="AL54" s="3">
         <v>3403600</v>
       </c>
-      <c r="AK54" s="3">
+      <c r="AM54" s="3">
         <v>1811700</v>
       </c>
     </row>
-    <row r="55" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -5322,8 +5580,10 @@
       <c r="AI55" s="3"/>
       <c r="AJ55" s="3"/>
       <c r="AK55" s="3"/>
+      <c r="AL55" s="3"/>
+      <c r="AM55" s="3"/>
     </row>
-    <row r="56" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="56" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -5361,195 +5621,203 @@
       <c r="AI56" s="3"/>
       <c r="AJ56" s="3"/>
       <c r="AK56" s="3"/>
+      <c r="AL56" s="3"/>
+      <c r="AM56" s="3"/>
     </row>
-    <row r="57" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="57" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>343100</v>
+      </c>
+      <c r="E57" s="3">
+        <v>350200</v>
+      </c>
+      <c r="F57" s="3">
         <v>345000</v>
       </c>
-      <c r="E57" s="3">
+      <c r="G57" s="3">
         <v>323200</v>
       </c>
-      <c r="F57" s="3">
-        <v>308300</v>
-      </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
+        <v>324000</v>
+      </c>
+      <c r="I57" s="3">
         <v>323300</v>
       </c>
-      <c r="H57" s="3">
+      <c r="J57" s="3">
         <v>368200</v>
       </c>
-      <c r="I57" s="3">
+      <c r="K57" s="3">
         <v>300100</v>
       </c>
-      <c r="J57" s="3">
+      <c r="L57" s="3">
         <v>293200</v>
       </c>
-      <c r="K57" s="3">
+      <c r="M57" s="3">
         <v>345800</v>
       </c>
-      <c r="L57" s="3">
+      <c r="N57" s="3">
         <v>310500</v>
       </c>
-      <c r="M57" s="3">
+      <c r="O57" s="3">
         <v>245700</v>
       </c>
-      <c r="N57" s="3">
+      <c r="P57" s="3">
         <v>265700</v>
       </c>
-      <c r="O57" s="3">
+      <c r="Q57" s="3">
         <v>238900</v>
       </c>
-      <c r="P57" s="3">
+      <c r="R57" s="3">
         <v>269700</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="S57" s="3">
         <v>231300</v>
       </c>
-      <c r="R57" s="3">
+      <c r="T57" s="3">
         <v>229300</v>
       </c>
-      <c r="S57" s="3">
+      <c r="U57" s="3">
         <v>222800</v>
       </c>
-      <c r="T57" s="3">
+      <c r="V57" s="3">
         <v>227700</v>
       </c>
-      <c r="U57" s="3">
+      <c r="W57" s="3">
         <v>216400</v>
       </c>
-      <c r="V57" s="3">
+      <c r="X57" s="3">
         <v>162900</v>
       </c>
-      <c r="W57" s="3">
+      <c r="Y57" s="3">
         <v>185600</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Z57" s="3">
         <v>227200</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="AA57" s="3">
         <v>167200</v>
       </c>
-      <c r="Z57" s="3">
+      <c r="AB57" s="3">
         <v>181100</v>
       </c>
-      <c r="AA57" s="3">
+      <c r="AC57" s="3">
         <v>157100</v>
       </c>
-      <c r="AB57" s="3">
+      <c r="AD57" s="3">
         <v>190500</v>
       </c>
-      <c r="AC57" s="3">
+      <c r="AE57" s="3">
         <v>117200</v>
       </c>
-      <c r="AD57" s="3">
+      <c r="AF57" s="3">
         <v>130700</v>
       </c>
-      <c r="AE57" s="3">
+      <c r="AG57" s="3">
         <v>133200</v>
       </c>
-      <c r="AF57" s="3">
+      <c r="AH57" s="3">
         <v>132000</v>
       </c>
-      <c r="AG57" s="3">
+      <c r="AI57" s="3">
         <v>84900</v>
       </c>
-      <c r="AH57" s="3">
+      <c r="AJ57" s="3">
         <v>73000</v>
       </c>
-      <c r="AI57" s="3">
+      <c r="AK57" s="3">
         <v>98200</v>
       </c>
-      <c r="AJ57" s="3">
+      <c r="AL57" s="3">
         <v>92600</v>
       </c>
-      <c r="AK57" s="3">
+      <c r="AM57" s="3">
         <v>65500</v>
       </c>
     </row>
-    <row r="58" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>2564600</v>
+      </c>
+      <c r="E58" s="3">
+        <v>2301800</v>
+      </c>
+      <c r="F58" s="3">
         <v>2324600</v>
       </c>
-      <c r="E58" s="3">
+      <c r="G58" s="3">
         <v>2554100</v>
       </c>
-      <c r="F58" s="3">
+      <c r="H58" s="3">
         <v>1451100</v>
       </c>
-      <c r="G58" s="3">
+      <c r="I58" s="3">
         <v>1138800</v>
       </c>
-      <c r="H58" s="3">
+      <c r="J58" s="3">
         <v>1121500</v>
       </c>
-      <c r="I58" s="3">
+      <c r="K58" s="3">
         <v>1346600</v>
       </c>
-      <c r="J58" s="3">
+      <c r="L58" s="3">
         <v>958600</v>
       </c>
-      <c r="K58" s="3">
+      <c r="M58" s="3">
         <v>994900</v>
       </c>
-      <c r="L58" s="3">
+      <c r="N58" s="3">
         <v>788700</v>
       </c>
-      <c r="M58" s="3">
+      <c r="O58" s="3">
         <v>993100</v>
       </c>
-      <c r="N58" s="3">
+      <c r="P58" s="3">
         <v>1015500</v>
       </c>
-      <c r="O58" s="3">
+      <c r="Q58" s="3">
         <v>847900</v>
       </c>
-      <c r="P58" s="3">
+      <c r="R58" s="3">
         <v>500600</v>
       </c>
-      <c r="Q58" s="3">
+      <c r="S58" s="3">
         <v>678800</v>
       </c>
-      <c r="R58" s="3">
+      <c r="T58" s="3">
         <v>537500</v>
       </c>
-      <c r="S58" s="3">
+      <c r="U58" s="3">
         <v>433100</v>
       </c>
-      <c r="T58" s="3">
+      <c r="V58" s="3">
         <v>244900</v>
       </c>
-      <c r="U58" s="3">
+      <c r="W58" s="3">
         <v>413300</v>
       </c>
-      <c r="V58" s="3">
+      <c r="X58" s="3">
         <v>322200</v>
       </c>
-      <c r="W58" s="3">
+      <c r="Y58" s="3">
         <v>47300</v>
       </c>
-      <c r="X58" s="3">
-        <v>0</v>
-      </c>
-      <c r="Y58" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="Z58" s="3" t="s">
-        <v>8</v>
+      <c r="Z58" s="3">
+        <v>0</v>
       </c>
       <c r="AA58" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AB58" s="3">
-        <v>0</v>
-      </c>
-      <c r="AC58" s="3">
-        <v>0</v>
+      <c r="AB58" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AC58" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="AD58" s="3">
         <v>0</v>
@@ -5558,278 +5826,296 @@
         <v>0</v>
       </c>
       <c r="AF58" s="3">
-        <v>37100</v>
+        <v>0</v>
       </c>
       <c r="AG58" s="3">
-        <v>37100</v>
+        <v>0</v>
       </c>
       <c r="AH58" s="3">
         <v>37100</v>
       </c>
       <c r="AI58" s="3">
+        <v>37100</v>
+      </c>
+      <c r="AJ58" s="3">
+        <v>37100</v>
+      </c>
+      <c r="AK58" s="3">
         <v>101800</v>
       </c>
-      <c r="AJ58" s="3">
+      <c r="AL58" s="3">
         <v>65400</v>
       </c>
-      <c r="AK58" s="3">
+      <c r="AM58" s="3">
         <v>43600</v>
       </c>
     </row>
-    <row r="59" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>1064300</v>
+      </c>
+      <c r="E59" s="3">
+        <v>1352200</v>
+      </c>
+      <c r="F59" s="3">
         <v>936500</v>
       </c>
-      <c r="E59" s="3">
+      <c r="G59" s="3">
         <v>1582400</v>
       </c>
-      <c r="F59" s="3">
-        <v>1280300</v>
-      </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
+        <v>1264500</v>
+      </c>
+      <c r="I59" s="3">
         <v>1759300</v>
       </c>
-      <c r="H59" s="3">
+      <c r="J59" s="3">
         <v>1114400</v>
       </c>
-      <c r="I59" s="3">
+      <c r="K59" s="3">
         <v>1248600</v>
       </c>
-      <c r="J59" s="3">
+      <c r="L59" s="3">
         <v>1192600</v>
       </c>
-      <c r="K59" s="3">
+      <c r="M59" s="3">
         <v>1440100</v>
       </c>
-      <c r="L59" s="3">
+      <c r="N59" s="3">
         <v>1213600</v>
       </c>
-      <c r="M59" s="3">
+      <c r="O59" s="3">
         <v>1179100</v>
       </c>
-      <c r="N59" s="3">
+      <c r="P59" s="3">
         <v>1079000</v>
       </c>
-      <c r="O59" s="3">
+      <c r="Q59" s="3">
         <v>1121000</v>
       </c>
-      <c r="P59" s="3">
+      <c r="R59" s="3">
         <v>1020300</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="S59" s="3">
         <v>902400</v>
       </c>
-      <c r="R59" s="3">
+      <c r="T59" s="3">
         <v>855200</v>
       </c>
-      <c r="S59" s="3">
+      <c r="U59" s="3">
         <v>966600</v>
       </c>
-      <c r="T59" s="3">
+      <c r="V59" s="3">
         <v>828600</v>
       </c>
-      <c r="U59" s="3">
+      <c r="W59" s="3">
         <v>822800</v>
       </c>
-      <c r="V59" s="3">
+      <c r="X59" s="3">
         <v>808400</v>
       </c>
-      <c r="W59" s="3">
+      <c r="Y59" s="3">
         <v>1052600</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Z59" s="3">
         <v>801600</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="AA59" s="3">
         <v>687500</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AB59" s="3">
         <v>630100</v>
       </c>
-      <c r="AA59" s="3">
+      <c r="AC59" s="3">
         <v>711200</v>
       </c>
-      <c r="AB59" s="3">
+      <c r="AD59" s="3">
         <v>556200</v>
       </c>
-      <c r="AC59" s="3">
+      <c r="AE59" s="3">
         <v>432100</v>
       </c>
-      <c r="AD59" s="3">
+      <c r="AF59" s="3">
         <v>419700</v>
       </c>
-      <c r="AE59" s="3">
+      <c r="AG59" s="3">
         <v>424600</v>
       </c>
-      <c r="AF59" s="3">
+      <c r="AH59" s="3">
         <v>446300</v>
       </c>
-      <c r="AG59" s="3">
+      <c r="AI59" s="3">
         <v>419000</v>
       </c>
-      <c r="AH59" s="3">
+      <c r="AJ59" s="3">
         <v>349800</v>
       </c>
-      <c r="AI59" s="3">
+      <c r="AK59" s="3">
         <v>311200</v>
       </c>
-      <c r="AJ59" s="3">
+      <c r="AL59" s="3">
         <v>354300</v>
       </c>
-      <c r="AK59" s="3">
+      <c r="AM59" s="3">
         <v>296300</v>
       </c>
     </row>
-    <row r="60" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>3972000</v>
+      </c>
+      <c r="E60" s="3">
+        <v>4004200</v>
+      </c>
+      <c r="F60" s="3">
         <v>3873500</v>
       </c>
-      <c r="E60" s="3">
+      <c r="G60" s="3">
         <v>4459700</v>
       </c>
-      <c r="F60" s="3">
+      <c r="H60" s="3">
         <v>3039700</v>
       </c>
-      <c r="G60" s="3">
+      <c r="I60" s="3">
         <v>3221500</v>
       </c>
-      <c r="H60" s="3">
+      <c r="J60" s="3">
         <v>2829100</v>
       </c>
-      <c r="I60" s="3">
+      <c r="K60" s="3">
         <v>2895300</v>
       </c>
-      <c r="J60" s="3">
+      <c r="L60" s="3">
         <v>2444400</v>
       </c>
-      <c r="K60" s="3">
+      <c r="M60" s="3">
         <v>2780800</v>
       </c>
-      <c r="L60" s="3">
+      <c r="N60" s="3">
         <v>2312800</v>
       </c>
-      <c r="M60" s="3">
+      <c r="O60" s="3">
         <v>2417900</v>
       </c>
-      <c r="N60" s="3">
+      <c r="P60" s="3">
         <v>2360200</v>
       </c>
-      <c r="O60" s="3">
+      <c r="Q60" s="3">
         <v>2207700</v>
       </c>
-      <c r="P60" s="3">
+      <c r="R60" s="3">
         <v>1790600</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="S60" s="3">
         <v>1812500</v>
       </c>
-      <c r="R60" s="3">
+      <c r="T60" s="3">
         <v>1622000</v>
       </c>
-      <c r="S60" s="3">
+      <c r="U60" s="3">
         <v>1622600</v>
       </c>
-      <c r="T60" s="3">
+      <c r="V60" s="3">
         <v>1301200</v>
       </c>
-      <c r="U60" s="3">
+      <c r="W60" s="3">
         <v>1452600</v>
       </c>
-      <c r="V60" s="3">
+      <c r="X60" s="3">
         <v>1293500</v>
       </c>
-      <c r="W60" s="3">
+      <c r="Y60" s="3">
         <v>1285600</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Z60" s="3">
         <v>1028700</v>
       </c>
-      <c r="Y60" s="3">
+      <c r="AA60" s="3">
         <v>854700</v>
       </c>
-      <c r="Z60" s="3">
+      <c r="AB60" s="3">
         <v>811200</v>
       </c>
-      <c r="AA60" s="3">
+      <c r="AC60" s="3">
         <v>868200</v>
       </c>
-      <c r="AB60" s="3">
+      <c r="AD60" s="3">
         <v>746700</v>
       </c>
-      <c r="AC60" s="3">
+      <c r="AE60" s="3">
         <v>549300</v>
       </c>
-      <c r="AD60" s="3">
+      <c r="AF60" s="3">
         <v>550400</v>
       </c>
-      <c r="AE60" s="3">
+      <c r="AG60" s="3">
         <v>557800</v>
       </c>
-      <c r="AF60" s="3">
+      <c r="AH60" s="3">
         <v>615300</v>
       </c>
-      <c r="AG60" s="3">
+      <c r="AI60" s="3">
         <v>541000</v>
       </c>
-      <c r="AH60" s="3">
+      <c r="AJ60" s="3">
         <v>459900</v>
       </c>
-      <c r="AI60" s="3">
+      <c r="AK60" s="3">
         <v>511200</v>
       </c>
-      <c r="AJ60" s="3">
+      <c r="AL60" s="3">
         <v>512300</v>
       </c>
-      <c r="AK60" s="3">
+      <c r="AM60" s="3">
         <v>405500</v>
       </c>
     </row>
-    <row r="61" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>70100</v>
+      </c>
+      <c r="E61" s="3">
+        <v>52400</v>
+      </c>
+      <c r="F61" s="3">
         <v>51700</v>
       </c>
-      <c r="E61" s="3">
+      <c r="G61" s="3">
         <v>53300</v>
       </c>
-      <c r="F61" s="3">
+      <c r="H61" s="3">
         <v>1038300</v>
       </c>
-      <c r="G61" s="3">
+      <c r="I61" s="3">
         <v>1047500</v>
       </c>
-      <c r="H61" s="3">
+      <c r="J61" s="3">
         <v>1055600</v>
       </c>
-      <c r="I61" s="3">
+      <c r="K61" s="3">
         <v>1050000</v>
       </c>
-      <c r="J61" s="3">
+      <c r="L61" s="3">
         <v>1054200</v>
       </c>
-      <c r="K61" s="3">
+      <c r="M61" s="3">
         <v>1055700</v>
       </c>
-      <c r="L61" s="3">
+      <c r="N61" s="3">
         <v>957100</v>
       </c>
-      <c r="M61" s="3">
+      <c r="O61" s="3">
         <v>966000</v>
       </c>
-      <c r="N61" s="3">
-        <v>0</v>
-      </c>
-      <c r="O61" s="3">
-        <v>0</v>
-      </c>
       <c r="P61" s="3">
         <v>0</v>
       </c>
@@ -5896,8 +6182,14 @@
       <c r="AK61" s="3">
         <v>0</v>
       </c>
+      <c r="AL61" s="3">
+        <v>0</v>
+      </c>
+      <c r="AM61" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="62" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
@@ -5925,86 +6217,92 @@
       <c r="K62" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="L62" s="3">
+      <c r="L62" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="M62" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="N62" s="3">
         <v>120800</v>
       </c>
-      <c r="M62" s="3">
+      <c r="O62" s="3">
         <v>101000</v>
       </c>
-      <c r="N62" s="3">
+      <c r="P62" s="3">
         <v>110000</v>
       </c>
-      <c r="O62" s="3">
+      <c r="Q62" s="3">
         <v>114700</v>
       </c>
-      <c r="P62" s="3">
+      <c r="R62" s="3">
         <v>116900</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="S62" s="3">
         <v>120300</v>
       </c>
-      <c r="R62" s="3">
+      <c r="T62" s="3">
         <v>115800</v>
       </c>
-      <c r="S62" s="3">
+      <c r="U62" s="3">
         <v>110200</v>
       </c>
-      <c r="T62" s="3">
+      <c r="V62" s="3">
         <v>105400</v>
       </c>
-      <c r="U62" s="3">
+      <c r="W62" s="3">
         <v>99300</v>
       </c>
-      <c r="V62" s="3">
+      <c r="X62" s="3">
         <v>104200</v>
       </c>
-      <c r="W62" s="3">
+      <c r="Y62" s="3">
         <v>117500</v>
       </c>
-      <c r="X62" s="3">
+      <c r="Z62" s="3">
         <v>124100</v>
       </c>
-      <c r="Y62" s="3">
+      <c r="AA62" s="3">
         <v>95900</v>
       </c>
-      <c r="Z62" s="3">
+      <c r="AB62" s="3">
         <v>96500</v>
       </c>
-      <c r="AA62" s="3">
+      <c r="AC62" s="3">
         <v>121000</v>
       </c>
-      <c r="AB62" s="3">
+      <c r="AD62" s="3">
         <v>39500</v>
       </c>
-      <c r="AC62" s="3">
+      <c r="AE62" s="3">
         <v>33600</v>
       </c>
-      <c r="AD62" s="3">
+      <c r="AF62" s="3">
         <v>33400</v>
       </c>
-      <c r="AE62" s="3">
+      <c r="AG62" s="3">
         <v>34000</v>
       </c>
-      <c r="AF62" s="3">
+      <c r="AH62" s="3">
         <v>35700</v>
       </c>
-      <c r="AG62" s="3">
+      <c r="AI62" s="3">
         <v>30000</v>
       </c>
-      <c r="AH62" s="3">
+      <c r="AJ62" s="3">
         <v>30300</v>
       </c>
-      <c r="AI62" s="3">
+      <c r="AK62" s="3">
         <v>23500</v>
       </c>
-      <c r="AJ62" s="3">
+      <c r="AL62" s="3">
         <v>19000</v>
       </c>
-      <c r="AK62" s="3">
+      <c r="AM62" s="3">
         <v>19100</v>
       </c>
     </row>
-    <row r="63" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -6110,8 +6408,14 @@
       <c r="AK63" s="3">
         <v>0</v>
       </c>
+      <c r="AL63" s="3">
+        <v>0</v>
+      </c>
+      <c r="AM63" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="64" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="64" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -6217,8 +6521,14 @@
       <c r="AK64" s="3">
         <v>0</v>
       </c>
+      <c r="AL64" s="3">
+        <v>0</v>
+      </c>
+      <c r="AM64" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="65" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="65" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -6324,115 +6634,127 @@
       <c r="AK65" s="3">
         <v>0</v>
       </c>
+      <c r="AL65" s="3">
+        <v>0</v>
+      </c>
+      <c r="AM65" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="66" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="66" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>4154900</v>
+      </c>
+      <c r="E66" s="3">
+        <v>4173300</v>
+      </c>
+      <c r="F66" s="3">
         <v>4064300</v>
       </c>
-      <c r="E66" s="3">
+      <c r="G66" s="3">
         <v>4590200</v>
       </c>
-      <c r="F66" s="3">
+      <c r="H66" s="3">
         <v>4146200</v>
       </c>
-      <c r="G66" s="3">
+      <c r="I66" s="3">
         <v>4360500</v>
       </c>
-      <c r="H66" s="3">
+      <c r="J66" s="3">
         <v>3974800</v>
       </c>
-      <c r="I66" s="3">
+      <c r="K66" s="3">
         <v>3992800</v>
       </c>
-      <c r="J66" s="3">
+      <c r="L66" s="3">
         <v>3546600</v>
       </c>
-      <c r="K66" s="3">
+      <c r="M66" s="3">
         <v>3885900</v>
       </c>
-      <c r="L66" s="3">
+      <c r="N66" s="3">
         <v>3453300</v>
       </c>
-      <c r="M66" s="3">
+      <c r="O66" s="3">
         <v>3547700</v>
       </c>
-      <c r="N66" s="3">
+      <c r="P66" s="3">
         <v>2528500</v>
       </c>
-      <c r="O66" s="3">
+      <c r="Q66" s="3">
         <v>2353800</v>
       </c>
-      <c r="P66" s="3">
+      <c r="R66" s="3">
         <v>1947500</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="S66" s="3">
         <v>1953500</v>
       </c>
-      <c r="R66" s="3">
+      <c r="T66" s="3">
         <v>1753500</v>
       </c>
-      <c r="S66" s="3">
+      <c r="U66" s="3">
         <v>1752700</v>
       </c>
-      <c r="T66" s="3">
+      <c r="V66" s="3">
         <v>1423500</v>
       </c>
-      <c r="U66" s="3">
+      <c r="W66" s="3">
         <v>1568300</v>
       </c>
-      <c r="V66" s="3">
+      <c r="X66" s="3">
         <v>1414400</v>
       </c>
-      <c r="W66" s="3">
+      <c r="Y66" s="3">
         <v>1419300</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Z66" s="3">
         <v>1168400</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="AA66" s="3">
         <v>965800</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AB66" s="3">
         <v>919500</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AC66" s="3">
         <v>999600</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AD66" s="3">
         <v>793800</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AE66" s="3">
         <v>588000</v>
       </c>
-      <c r="AD66" s="3">
+      <c r="AF66" s="3">
         <v>584900</v>
       </c>
-      <c r="AE66" s="3">
+      <c r="AG66" s="3">
         <v>592700</v>
       </c>
-      <c r="AF66" s="3">
+      <c r="AH66" s="3">
         <v>651900</v>
       </c>
-      <c r="AG66" s="3">
+      <c r="AI66" s="3">
         <v>571800</v>
       </c>
-      <c r="AH66" s="3">
+      <c r="AJ66" s="3">
         <v>491000</v>
       </c>
-      <c r="AI66" s="3">
+      <c r="AK66" s="3">
         <v>535400</v>
       </c>
-      <c r="AJ66" s="3">
+      <c r="AL66" s="3">
         <v>532100</v>
       </c>
-      <c r="AK66" s="3">
+      <c r="AM66" s="3">
         <v>424600</v>
       </c>
     </row>
-    <row r="67" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -6470,8 +6792,10 @@
       <c r="AI67" s="3"/>
       <c r="AJ67" s="3"/>
       <c r="AK67" s="3"/>
+      <c r="AL67" s="3"/>
+      <c r="AM67" s="3"/>
     </row>
-    <row r="68" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="68" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -6577,8 +6901,14 @@
       <c r="AK68" s="3">
         <v>0</v>
       </c>
+      <c r="AL68" s="3">
+        <v>0</v>
+      </c>
+      <c r="AM68" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="69" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="69" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -6684,8 +7014,14 @@
       <c r="AK69" s="3">
         <v>0</v>
       </c>
+      <c r="AL69" s="3">
+        <v>0</v>
+      </c>
+      <c r="AM69" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="70" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="70" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -6789,10 +7125,16 @@
         <v>0</v>
       </c>
       <c r="AK70" s="3">
+        <v>0</v>
+      </c>
+      <c r="AL70" s="3">
+        <v>0</v>
+      </c>
+      <c r="AM70" s="3">
         <v>304900</v>
       </c>
     </row>
-    <row r="71" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="71" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -6898,115 +7240,127 @@
       <c r="AK71" s="3">
         <v>0</v>
       </c>
+      <c r="AL71" s="3">
+        <v>0</v>
+      </c>
+      <c r="AM71" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="72" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="72" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>5633100</v>
+      </c>
+      <c r="E72" s="3">
+        <v>5294000</v>
+      </c>
+      <c r="F72" s="3">
         <v>5356600</v>
       </c>
-      <c r="E72" s="3">
+      <c r="G72" s="3">
         <v>5234300</v>
       </c>
-      <c r="F72" s="3">
+      <c r="H72" s="3">
         <v>5041300</v>
       </c>
-      <c r="G72" s="3">
+      <c r="I72" s="3">
         <v>4711900</v>
       </c>
-      <c r="H72" s="3">
+      <c r="J72" s="3">
         <v>5119400</v>
       </c>
-      <c r="I72" s="3">
+      <c r="K72" s="3">
         <v>4715800</v>
       </c>
-      <c r="J72" s="3">
+      <c r="L72" s="3">
         <v>4457100</v>
       </c>
-      <c r="K72" s="3">
+      <c r="M72" s="3">
         <v>4478700</v>
       </c>
-      <c r="L72" s="3">
+      <c r="N72" s="3">
         <v>4153200</v>
       </c>
-      <c r="M72" s="3">
+      <c r="O72" s="3">
         <v>3771300</v>
       </c>
-      <c r="N72" s="3">
+      <c r="P72" s="3">
         <v>3525800</v>
       </c>
-      <c r="O72" s="3">
+      <c r="Q72" s="3">
         <v>3280400</v>
       </c>
-      <c r="P72" s="3">
+      <c r="R72" s="3">
         <v>3129900</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="S72" s="3">
         <v>2978700</v>
       </c>
-      <c r="R72" s="3">
+      <c r="T72" s="3">
         <v>3182700</v>
       </c>
-      <c r="S72" s="3">
+      <c r="U72" s="3">
         <v>3093800</v>
       </c>
-      <c r="T72" s="3">
+      <c r="V72" s="3">
         <v>2928600</v>
       </c>
-      <c r="U72" s="3">
+      <c r="W72" s="3">
         <v>2910500</v>
       </c>
-      <c r="V72" s="3">
+      <c r="X72" s="3">
         <v>2733500</v>
       </c>
-      <c r="W72" s="3">
+      <c r="Y72" s="3">
         <v>2697900</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Z72" s="3">
         <v>2575600</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="AA72" s="3">
         <v>2246600</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AB72" s="3">
         <v>2000300</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AC72" s="3">
         <v>1784800</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AD72" s="3">
         <v>1605100</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AE72" s="3">
         <v>1368400</v>
       </c>
-      <c r="AD72" s="3">
+      <c r="AF72" s="3">
         <v>1220100</v>
       </c>
-      <c r="AE72" s="3">
+      <c r="AG72" s="3">
         <v>1036800</v>
       </c>
-      <c r="AF72" s="3">
+      <c r="AH72" s="3">
         <v>989800</v>
       </c>
-      <c r="AG72" s="3">
+      <c r="AI72" s="3">
         <v>808400</v>
       </c>
-      <c r="AH72" s="3">
+      <c r="AJ72" s="3">
         <v>702000</v>
       </c>
-      <c r="AI72" s="3">
+      <c r="AK72" s="3">
         <v>583600</v>
       </c>
-      <c r="AJ72" s="3">
+      <c r="AL72" s="3">
         <v>510400</v>
       </c>
-      <c r="AK72" s="3">
+      <c r="AM72" s="3">
         <v>404700</v>
       </c>
     </row>
-    <row r="73" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -7112,8 +7466,14 @@
       <c r="AK73" s="3">
         <v>0</v>
       </c>
+      <c r="AL73" s="3">
+        <v>0</v>
+      </c>
+      <c r="AM73" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="74" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="74" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -7219,8 +7579,14 @@
       <c r="AK74" s="3">
         <v>0</v>
       </c>
+      <c r="AL74" s="3">
+        <v>0</v>
+      </c>
+      <c r="AM74" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="75" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="75" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -7326,115 +7692,127 @@
       <c r="AK75" s="3">
         <v>0</v>
       </c>
+      <c r="AL75" s="3">
+        <v>0</v>
+      </c>
+      <c r="AM75" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="76" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="76" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>8961400</v>
+      </c>
+      <c r="E76" s="3">
+        <v>8573600</v>
+      </c>
+      <c r="F76" s="3">
         <v>8502700</v>
       </c>
-      <c r="E76" s="3">
+      <c r="G76" s="3">
         <v>8638000</v>
       </c>
-      <c r="F76" s="3">
+      <c r="H76" s="3">
         <v>8315300</v>
       </c>
-      <c r="G76" s="3">
+      <c r="I76" s="3">
         <v>8011000</v>
       </c>
-      <c r="H76" s="3">
+      <c r="J76" s="3">
         <v>8433600</v>
       </c>
-      <c r="I76" s="3">
+      <c r="K76" s="3">
         <v>7934600</v>
       </c>
-      <c r="J76" s="3">
+      <c r="L76" s="3">
         <v>7708500</v>
       </c>
-      <c r="K76" s="3">
+      <c r="M76" s="3">
         <v>7797800</v>
       </c>
-      <c r="L76" s="3">
+      <c r="N76" s="3">
         <v>7616900</v>
       </c>
-      <c r="M76" s="3">
+      <c r="O76" s="3">
         <v>7172500</v>
       </c>
-      <c r="N76" s="3">
+      <c r="P76" s="3">
         <v>6995300</v>
       </c>
-      <c r="O76" s="3">
+      <c r="Q76" s="3">
         <v>6730800</v>
       </c>
-      <c r="P76" s="3">
+      <c r="R76" s="3">
         <v>6701200</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="S76" s="3">
         <v>6669700</v>
       </c>
-      <c r="R76" s="3">
+      <c r="T76" s="3">
         <v>7045800</v>
       </c>
-      <c r="S76" s="3">
+      <c r="U76" s="3">
         <v>6880500</v>
       </c>
-      <c r="T76" s="3">
+      <c r="V76" s="3">
         <v>6817900</v>
       </c>
-      <c r="U76" s="3">
+      <c r="W76" s="3">
         <v>7111600</v>
       </c>
-      <c r="V76" s="3">
+      <c r="X76" s="3">
         <v>5729500</v>
       </c>
-      <c r="W76" s="3">
+      <c r="Y76" s="3">
         <v>5909100</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Z76" s="3">
         <v>5897800</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="AA76" s="3">
         <v>5661800</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AB76" s="3">
         <v>5272900</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AC76" s="3">
         <v>5105500</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AD76" s="3">
         <v>4969400</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AE76" s="3">
         <v>4631700</v>
       </c>
-      <c r="AD76" s="3">
+      <c r="AF76" s="3">
         <v>4215500</v>
       </c>
-      <c r="AE76" s="3">
+      <c r="AG76" s="3">
         <v>2968500</v>
       </c>
-      <c r="AF76" s="3">
+      <c r="AH76" s="3">
         <v>3181200</v>
       </c>
-      <c r="AG76" s="3">
+      <c r="AI76" s="3">
         <v>3060200</v>
       </c>
-      <c r="AH76" s="3">
+      <c r="AJ76" s="3">
         <v>3040800</v>
       </c>
-      <c r="AI76" s="3">
+      <c r="AK76" s="3">
         <v>2931800</v>
       </c>
-      <c r="AJ76" s="3">
+      <c r="AL76" s="3">
         <v>2871500</v>
       </c>
-      <c r="AK76" s="3">
+      <c r="AM76" s="3">
         <v>1082100</v>
       </c>
     </row>
-    <row r="77" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -7540,227 +7918,245 @@
       <c r="AK77" s="3">
         <v>0</v>
       </c>
+      <c r="AL77" s="3">
+        <v>0</v>
+      </c>
+      <c r="AM77" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="79" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="79" spans="2:39" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45838</v>
+      </c>
+      <c r="E80" s="2">
+        <v>45747</v>
+      </c>
+      <c r="F80" s="2">
         <v>45657</v>
       </c>
-      <c r="E80" s="2">
+      <c r="G80" s="2">
         <v>45565</v>
       </c>
-      <c r="F80" s="2">
+      <c r="H80" s="2">
         <v>45473</v>
       </c>
-      <c r="G80" s="2">
+      <c r="I80" s="2">
         <v>45382</v>
       </c>
-      <c r="H80" s="2">
+      <c r="J80" s="2">
         <v>45291</v>
       </c>
-      <c r="I80" s="2">
+      <c r="K80" s="2">
         <v>45199</v>
       </c>
-      <c r="J80" s="2">
+      <c r="L80" s="2">
         <v>45107</v>
       </c>
-      <c r="K80" s="2">
+      <c r="M80" s="2">
         <v>45016</v>
       </c>
-      <c r="L80" s="2">
+      <c r="N80" s="2">
         <v>44926</v>
       </c>
-      <c r="M80" s="2">
+      <c r="O80" s="2">
         <v>44834</v>
       </c>
-      <c r="N80" s="2">
+      <c r="P80" s="2">
         <v>44742</v>
       </c>
-      <c r="O80" s="2">
+      <c r="Q80" s="2">
         <v>44651</v>
       </c>
-      <c r="P80" s="2">
+      <c r="R80" s="2">
         <v>44561</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="S80" s="2">
         <v>44469</v>
       </c>
-      <c r="R80" s="2">
+      <c r="T80" s="2">
         <v>44377</v>
       </c>
-      <c r="S80" s="2">
+      <c r="U80" s="2">
         <v>44286</v>
       </c>
-      <c r="T80" s="2">
+      <c r="V80" s="2">
         <v>44196</v>
       </c>
-      <c r="U80" s="2">
+      <c r="W80" s="2">
         <v>44104</v>
       </c>
-      <c r="V80" s="2">
+      <c r="X80" s="2">
         <v>44012</v>
       </c>
-      <c r="W80" s="2">
+      <c r="Y80" s="2">
         <v>43921</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Z80" s="2">
         <v>43830</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="AA80" s="2">
         <v>43738</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AB80" s="2">
         <v>43646</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AC80" s="2">
         <v>43555</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AD80" s="2">
         <v>43465</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AE80" s="2">
         <v>43373</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AF80" s="2">
         <v>43281</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AG80" s="2">
         <v>43190</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AH80" s="2">
         <v>43100</v>
       </c>
-      <c r="AG80" s="2">
+      <c r="AI80" s="2">
         <v>43008</v>
       </c>
-      <c r="AH80" s="2">
+      <c r="AJ80" s="2">
         <v>42916</v>
       </c>
-      <c r="AI80" s="2">
+      <c r="AK80" s="2">
         <v>42825</v>
       </c>
-      <c r="AJ80" s="2">
+      <c r="AL80" s="2">
         <v>42735</v>
       </c>
-      <c r="AK80" s="2">
+      <c r="AM80" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="81" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>270600</v>
+      </c>
+      <c r="E81" s="3">
+        <v>274700</v>
+      </c>
+      <c r="F81" s="3">
         <v>326400</v>
       </c>
-      <c r="E81" s="3">
+      <c r="G81" s="3">
         <v>341600</v>
       </c>
-      <c r="F81" s="3">
+      <c r="H81" s="3">
         <v>359400</v>
       </c>
-      <c r="G81" s="3">
+      <c r="I81" s="3">
         <v>197500</v>
       </c>
-      <c r="H81" s="3">
+      <c r="J81" s="3">
         <v>309200</v>
       </c>
-      <c r="I81" s="3">
+      <c r="K81" s="3">
         <v>321400</v>
       </c>
-      <c r="J81" s="3">
+      <c r="L81" s="3">
         <v>350400</v>
       </c>
-      <c r="K81" s="3">
+      <c r="M81" s="3">
         <v>243200</v>
       </c>
-      <c r="L81" s="3">
+      <c r="N81" s="3">
         <v>304900</v>
       </c>
-      <c r="M81" s="3">
+      <c r="O81" s="3">
         <v>267300</v>
       </c>
-      <c r="N81" s="3">
+      <c r="P81" s="3">
         <v>251000</v>
       </c>
-      <c r="O81" s="3">
+      <c r="Q81" s="3">
         <v>126000</v>
       </c>
-      <c r="P81" s="3">
+      <c r="R81" s="3">
         <v>242800</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="S81" s="3">
         <v>165800</v>
       </c>
-      <c r="R81" s="3">
+      <c r="T81" s="3">
         <v>185600</v>
       </c>
-      <c r="S81" s="3">
+      <c r="U81" s="3">
         <v>76600</v>
       </c>
-      <c r="T81" s="3">
+      <c r="V81" s="3">
         <v>179300</v>
       </c>
-      <c r="U81" s="3">
+      <c r="W81" s="3">
         <v>177000</v>
       </c>
-      <c r="V81" s="3">
+      <c r="X81" s="3">
         <v>213400</v>
       </c>
-      <c r="W81" s="3">
+      <c r="Y81" s="3">
         <v>59100</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Z81" s="3">
         <v>358200</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="AA81" s="3">
         <v>204000</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AB81" s="3">
         <v>207700</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AC81" s="3">
         <v>103600</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AD81" s="3">
         <v>185200</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AE81" s="3">
         <v>148300</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AF81" s="3">
         <v>208700</v>
       </c>
-      <c r="AE81" s="3">
+      <c r="AG81" s="3">
         <v>79900</v>
       </c>
-      <c r="AF81" s="3">
+      <c r="AH81" s="3">
         <v>181400</v>
       </c>
-      <c r="AG81" s="3">
+      <c r="AI81" s="3">
         <v>106400</v>
       </c>
-      <c r="AH81" s="3">
+      <c r="AJ81" s="3">
         <v>106400</v>
       </c>
-      <c r="AI81" s="3">
+      <c r="AK81" s="3">
         <v>73200</v>
       </c>
-      <c r="AJ81" s="3">
+      <c r="AL81" s="3">
         <v>105700</v>
       </c>
-      <c r="AK81" s="3">
+      <c r="AM81" s="3">
         <v>73700</v>
       </c>
     </row>
-    <row r="82" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -7798,41 +8194,43 @@
       <c r="AI82" s="3"/>
       <c r="AJ82" s="3"/>
       <c r="AK82" s="3"/>
+      <c r="AL82" s="3"/>
+      <c r="AM82" s="3"/>
     </row>
-    <row r="83" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="83" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>99200</v>
+      </c>
+      <c r="E83" s="3">
+        <v>104200</v>
+      </c>
+      <c r="F83" s="3">
         <v>99400</v>
       </c>
-      <c r="E83" s="3">
+      <c r="G83" s="3">
         <v>97700</v>
       </c>
-      <c r="F83" s="3">
+      <c r="H83" s="3">
         <v>92600</v>
       </c>
-      <c r="G83" s="3">
+      <c r="I83" s="3">
         <v>94900</v>
       </c>
-      <c r="H83" s="3">
+      <c r="J83" s="3">
         <v>96500</v>
       </c>
-      <c r="I83" s="3">
+      <c r="K83" s="3">
         <v>89000</v>
       </c>
-      <c r="J83" s="3">
+      <c r="L83" s="3">
         <v>95600</v>
       </c>
-      <c r="K83" s="3">
+      <c r="M83" s="3">
         <v>94900</v>
       </c>
-      <c r="L83" s="3">
-        <v>0</v>
-      </c>
-      <c r="M83" s="3">
-        <v>0</v>
-      </c>
       <c r="N83" s="3">
         <v>0</v>
       </c>
@@ -7905,8 +8303,14 @@
       <c r="AK83" s="3">
         <v>0</v>
       </c>
+      <c r="AL83" s="3">
+        <v>0</v>
+      </c>
+      <c r="AM83" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="84" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -8012,8 +8416,14 @@
       <c r="AK84" s="3">
         <v>0</v>
       </c>
+      <c r="AL84" s="3">
+        <v>0</v>
+      </c>
+      <c r="AM84" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="85" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="85" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -8119,8 +8529,14 @@
       <c r="AK85" s="3">
         <v>0</v>
       </c>
+      <c r="AL85" s="3">
+        <v>0</v>
+      </c>
+      <c r="AM85" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="86" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="86" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -8226,8 +8642,14 @@
       <c r="AK86" s="3">
         <v>0</v>
       </c>
+      <c r="AL86" s="3">
+        <v>0</v>
+      </c>
+      <c r="AM86" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="87" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="87" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -8333,8 +8755,14 @@
       <c r="AK87" s="3">
         <v>0</v>
       </c>
+      <c r="AL87" s="3">
+        <v>0</v>
+      </c>
+      <c r="AM87" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="88" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="88" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -8440,115 +8868,127 @@
       <c r="AK88" s="3">
         <v>0</v>
       </c>
+      <c r="AL88" s="3">
+        <v>0</v>
+      </c>
+      <c r="AM88" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="89" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="89" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>302700</v>
+      </c>
+      <c r="E89" s="3">
+        <v>325600</v>
+      </c>
+      <c r="F89" s="3">
         <v>384500</v>
       </c>
-      <c r="E89" s="3">
+      <c r="G89" s="3">
         <v>443600</v>
       </c>
-      <c r="F89" s="3">
+      <c r="H89" s="3">
         <v>478900</v>
       </c>
-      <c r="G89" s="3">
+      <c r="I89" s="3">
         <v>281300</v>
       </c>
-      <c r="H89" s="3">
+      <c r="J89" s="3">
         <v>553300</v>
       </c>
-      <c r="I89" s="3">
+      <c r="K89" s="3">
         <v>402700</v>
       </c>
-      <c r="J89" s="3">
+      <c r="L89" s="3">
         <v>518700</v>
       </c>
-      <c r="K89" s="3">
+      <c r="M89" s="3">
         <v>398600</v>
       </c>
-      <c r="L89" s="3">
+      <c r="N89" s="3">
         <v>531500</v>
       </c>
-      <c r="M89" s="3">
+      <c r="O89" s="3">
         <v>390100</v>
       </c>
-      <c r="N89" s="3">
+      <c r="P89" s="3">
         <v>525600</v>
       </c>
-      <c r="O89" s="3">
+      <c r="Q89" s="3">
         <v>153700</v>
       </c>
-      <c r="P89" s="3">
+      <c r="R89" s="3">
         <v>416600</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="S89" s="3">
         <v>254000</v>
       </c>
-      <c r="R89" s="3">
+      <c r="T89" s="3">
         <v>277500</v>
       </c>
-      <c r="S89" s="3">
+      <c r="U89" s="3">
         <v>68500</v>
       </c>
-      <c r="T89" s="3">
+      <c r="V89" s="3">
         <v>284000</v>
       </c>
-      <c r="U89" s="3">
+      <c r="W89" s="3">
         <v>218200</v>
       </c>
-      <c r="V89" s="3">
+      <c r="X89" s="3">
         <v>184500</v>
       </c>
-      <c r="W89" s="3">
+      <c r="Y89" s="3">
         <v>28000</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Z89" s="3">
         <v>348100</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="AA89" s="3">
         <v>221200</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AB89" s="3">
         <v>304500</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AC89" s="3">
         <v>96300</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AD89" s="3">
         <v>261800</v>
       </c>
-      <c r="AC89" s="3">
+      <c r="AE89" s="3">
         <v>127600</v>
       </c>
-      <c r="AD89" s="3">
+      <c r="AF89" s="3">
         <v>206600</v>
       </c>
-      <c r="AE89" s="3">
+      <c r="AG89" s="3">
         <v>30700</v>
       </c>
-      <c r="AF89" s="3">
+      <c r="AH89" s="3">
         <v>203600</v>
       </c>
-      <c r="AG89" s="3">
+      <c r="AI89" s="3">
         <v>152000</v>
       </c>
-      <c r="AH89" s="3">
+      <c r="AJ89" s="3">
         <v>134100</v>
       </c>
-      <c r="AI89" s="3">
+      <c r="AK89" s="3">
         <v>48200</v>
       </c>
-      <c r="AJ89" s="3">
+      <c r="AL89" s="3">
         <v>166300</v>
       </c>
-      <c r="AK89" s="3">
+      <c r="AM89" s="3">
         <v>121000</v>
       </c>
     </row>
-    <row r="90" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -8586,40 +9026,42 @@
       <c r="AI90" s="3"/>
       <c r="AJ90" s="3"/>
       <c r="AK90" s="3"/>
+      <c r="AL90" s="3"/>
+      <c r="AM90" s="3"/>
     </row>
-    <row r="91" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="91" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
-        <v>-713500</v>
+        <v>-408400</v>
       </c>
       <c r="E91" s="3" t="s">
         <v>8</v>
       </c>
       <c r="F91" s="3">
-        <v>-364200</v>
+        <v>-713500</v>
       </c>
       <c r="G91" s="3" t="s">
         <v>8</v>
       </c>
       <c r="H91" s="3">
-        <v>-920700</v>
+        <v>-364200</v>
       </c>
       <c r="I91" s="3" t="s">
         <v>8</v>
       </c>
       <c r="J91" s="3">
-        <v>-613200</v>
+        <v>-920700</v>
       </c>
       <c r="K91" s="3" t="s">
         <v>8</v>
       </c>
       <c r="L91" s="3">
-        <v>0</v>
-      </c>
-      <c r="M91" s="3">
-        <v>0</v>
+        <v>-613200</v>
+      </c>
+      <c r="M91" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="N91" s="3">
         <v>0</v>
@@ -8693,8 +9135,14 @@
       <c r="AK91" s="3">
         <v>0</v>
       </c>
+      <c r="AL91" s="3">
+        <v>0</v>
+      </c>
+      <c r="AM91" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="92" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -8800,8 +9248,14 @@
       <c r="AK92" s="3">
         <v>0</v>
       </c>
+      <c r="AL92" s="3">
+        <v>0</v>
+      </c>
+      <c r="AM92" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="93" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="93" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -8907,115 +9361,127 @@
       <c r="AK93" s="3">
         <v>0</v>
       </c>
+      <c r="AL93" s="3">
+        <v>0</v>
+      </c>
+      <c r="AM93" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="94" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="94" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-162400</v>
+      </c>
+      <c r="E94" s="3">
+        <v>-435300</v>
+      </c>
+      <c r="F94" s="3">
         <v>407500</v>
       </c>
-      <c r="E94" s="3">
+      <c r="G94" s="3">
         <v>-272300</v>
       </c>
-      <c r="F94" s="3">
+      <c r="H94" s="3">
         <v>-642100</v>
       </c>
-      <c r="G94" s="3">
+      <c r="I94" s="3">
         <v>-329400</v>
       </c>
-      <c r="H94" s="3">
+      <c r="J94" s="3">
         <v>166600</v>
       </c>
-      <c r="I94" s="3">
+      <c r="K94" s="3">
         <v>-551700</v>
       </c>
-      <c r="J94" s="3">
+      <c r="L94" s="3">
         <v>-488300</v>
       </c>
-      <c r="K94" s="3">
+      <c r="M94" s="3">
         <v>-854000</v>
       </c>
-      <c r="L94" s="3">
+      <c r="N94" s="3">
         <v>-617600</v>
       </c>
-      <c r="M94" s="3">
+      <c r="O94" s="3">
         <v>-654400</v>
       </c>
-      <c r="N94" s="3">
+      <c r="P94" s="3">
         <v>-501800</v>
       </c>
-      <c r="O94" s="3">
+      <c r="Q94" s="3">
         <v>-460800</v>
       </c>
-      <c r="P94" s="3">
+      <c r="R94" s="3">
         <v>-387700</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="S94" s="3">
         <v>-197000</v>
       </c>
-      <c r="R94" s="3">
+      <c r="T94" s="3">
         <v>-26500</v>
       </c>
-      <c r="S94" s="3">
+      <c r="U94" s="3">
         <v>-627900</v>
       </c>
-      <c r="T94" s="3">
+      <c r="V94" s="3">
         <v>-406000</v>
       </c>
-      <c r="U94" s="3">
+      <c r="W94" s="3">
         <v>173900</v>
       </c>
-      <c r="V94" s="3">
+      <c r="X94" s="3">
         <v>-161800</v>
       </c>
-      <c r="W94" s="3">
+      <c r="Y94" s="3">
         <v>-112800</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Z94" s="3">
         <v>-314600</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="AA94" s="3">
         <v>-626500</v>
       </c>
-      <c r="Z94" s="3">
+      <c r="AB94" s="3">
         <v>229000</v>
       </c>
-      <c r="AA94" s="3">
+      <c r="AC94" s="3">
         <v>136200</v>
       </c>
-      <c r="AB94" s="3">
+      <c r="AD94" s="3">
         <v>-483600</v>
       </c>
-      <c r="AC94" s="3">
+      <c r="AE94" s="3">
         <v>-321300</v>
       </c>
-      <c r="AD94" s="3">
+      <c r="AF94" s="3">
         <v>-790700</v>
       </c>
-      <c r="AE94" s="3">
+      <c r="AG94" s="3">
         <v>-229200</v>
       </c>
-      <c r="AF94" s="3">
+      <c r="AH94" s="3">
         <v>-107200</v>
       </c>
-      <c r="AG94" s="3">
+      <c r="AI94" s="3">
         <v>-167600</v>
       </c>
-      <c r="AH94" s="3">
+      <c r="AJ94" s="3">
         <v>-168800</v>
       </c>
-      <c r="AI94" s="3">
+      <c r="AK94" s="3">
         <v>-771600</v>
       </c>
-      <c r="AJ94" s="3">
+      <c r="AL94" s="3">
         <v>-158200</v>
       </c>
-      <c r="AK94" s="3">
+      <c r="AM94" s="3">
         <v>-129200</v>
       </c>
     </row>
-    <row r="95" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -9053,40 +9519,42 @@
       <c r="AI95" s="3"/>
       <c r="AJ95" s="3"/>
       <c r="AK95" s="3"/>
+      <c r="AL95" s="3"/>
+      <c r="AM95" s="3"/>
     </row>
-    <row r="96" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="96" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
       <c r="D96" s="3">
-        <v>768000</v>
+        <v>286900</v>
       </c>
       <c r="E96" s="3" t="s">
         <v>8</v>
       </c>
       <c r="F96" s="3">
-        <v>495400</v>
+        <v>768000</v>
       </c>
       <c r="G96" s="3" t="s">
         <v>8</v>
       </c>
       <c r="H96" s="3">
-        <v>292300</v>
+        <v>495400</v>
       </c>
       <c r="I96" s="3" t="s">
         <v>8</v>
       </c>
       <c r="J96" s="3">
-        <v>285800</v>
+        <v>292300</v>
       </c>
       <c r="K96" s="3" t="s">
         <v>8</v>
       </c>
       <c r="L96" s="3">
-        <v>0</v>
-      </c>
-      <c r="M96" s="3">
-        <v>0</v>
+        <v>285800</v>
+      </c>
+      <c r="M96" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="N96" s="3">
         <v>0</v>
@@ -9160,8 +9628,14 @@
       <c r="AK96" s="3">
         <v>0</v>
       </c>
+      <c r="AL96" s="3">
+        <v>0</v>
+      </c>
+      <c r="AM96" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="97" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="97" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -9267,8 +9741,14 @@
       <c r="AK97" s="3">
         <v>0</v>
       </c>
+      <c r="AL97" s="3">
+        <v>0</v>
+      </c>
+      <c r="AM97" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="98" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="98" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -9374,8 +9854,14 @@
       <c r="AK98" s="3">
         <v>0</v>
       </c>
+      <c r="AL98" s="3">
+        <v>0</v>
+      </c>
+      <c r="AM98" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="99" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="99" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -9481,325 +9967,349 @@
       <c r="AK99" s="3">
         <v>0</v>
       </c>
+      <c r="AL99" s="3">
+        <v>0</v>
+      </c>
+      <c r="AM99" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="100" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="100" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-16400</v>
+      </c>
+      <c r="E100" s="3">
+        <v>-36000</v>
+      </c>
+      <c r="F100" s="3">
         <v>-552400</v>
       </c>
-      <c r="E100" s="3">
+      <c r="G100" s="3">
         <v>1500</v>
       </c>
-      <c r="F100" s="3">
+      <c r="H100" s="3">
         <v>-151900</v>
       </c>
-      <c r="G100" s="3">
+      <c r="I100" s="3">
         <v>18000</v>
       </c>
-      <c r="H100" s="3">
+      <c r="J100" s="3">
         <v>-305500</v>
       </c>
-      <c r="I100" s="3">
+      <c r="K100" s="3">
         <v>346700</v>
       </c>
-      <c r="J100" s="3">
+      <c r="L100" s="3">
         <v>-272200</v>
       </c>
-      <c r="K100" s="3">
+      <c r="M100" s="3">
         <v>122400</v>
       </c>
-      <c r="L100" s="3">
+      <c r="N100" s="3">
         <v>-240700</v>
       </c>
-      <c r="M100" s="3">
+      <c r="O100" s="3">
         <v>876200</v>
       </c>
-      <c r="N100" s="3">
+      <c r="P100" s="3">
         <v>-21800</v>
       </c>
-      <c r="O100" s="3">
+      <c r="Q100" s="3">
         <v>358800</v>
       </c>
-      <c r="P100" s="3">
+      <c r="R100" s="3">
         <v>-108500</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="S100" s="3">
         <v>-308000</v>
       </c>
-      <c r="R100" s="3">
+      <c r="T100" s="3">
         <v>-135500</v>
       </c>
-      <c r="S100" s="3">
+      <c r="U100" s="3">
         <v>142800</v>
       </c>
-      <c r="T100" s="3">
+      <c r="V100" s="3">
         <v>-87400</v>
       </c>
-      <c r="U100" s="3">
+      <c r="W100" s="3">
         <v>1267700</v>
       </c>
-      <c r="V100" s="3">
+      <c r="X100" s="3">
         <v>9600</v>
       </c>
-      <c r="W100" s="3">
+      <c r="Y100" s="3">
         <v>47000</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Z100" s="3">
         <v>2000</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="AA100" s="3">
         <v>79800</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AB100" s="3">
         <v>-380900</v>
       </c>
-      <c r="AA100" s="3">
+      <c r="AC100" s="3">
         <v>-2100</v>
       </c>
-      <c r="AB100" s="3">
+      <c r="AD100" s="3">
         <v>-22300</v>
       </c>
-      <c r="AC100" s="3">
+      <c r="AE100" s="3">
         <v>193200</v>
       </c>
-      <c r="AD100" s="3">
+      <c r="AF100" s="3">
         <v>926600</v>
       </c>
-      <c r="AE100" s="3">
+      <c r="AG100" s="3">
         <v>-115500</v>
       </c>
-      <c r="AF100" s="3">
+      <c r="AH100" s="3">
         <v>-30000</v>
       </c>
-      <c r="AG100" s="3">
+      <c r="AI100" s="3">
         <v>-59900</v>
       </c>
-      <c r="AH100" s="3">
+      <c r="AJ100" s="3">
         <v>-104800</v>
       </c>
-      <c r="AI100" s="3">
+      <c r="AK100" s="3">
         <v>36400</v>
       </c>
-      <c r="AJ100" s="3">
+      <c r="AL100" s="3">
         <v>1358900</v>
       </c>
-      <c r="AK100" s="3">
+      <c r="AM100" s="3">
         <v>-3900</v>
       </c>
     </row>
-    <row r="101" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>-500</v>
+      </c>
+      <c r="E101" s="3">
+        <v>5300</v>
+      </c>
+      <c r="F101" s="3">
         <v>600</v>
       </c>
-      <c r="E101" s="3">
+      <c r="G101" s="3">
         <v>1300</v>
       </c>
-      <c r="F101" s="3">
+      <c r="H101" s="3">
         <v>14500</v>
       </c>
-      <c r="G101" s="3">
+      <c r="I101" s="3">
         <v>-1300</v>
       </c>
-      <c r="H101" s="3">
+      <c r="J101" s="3">
         <v>-8600</v>
       </c>
-      <c r="I101" s="3">
+      <c r="K101" s="3">
         <v>31600</v>
       </c>
-      <c r="J101" s="3">
+      <c r="L101" s="3">
         <v>28900</v>
       </c>
-      <c r="K101" s="3">
+      <c r="M101" s="3">
         <v>-3300</v>
       </c>
-      <c r="L101" s="3">
+      <c r="N101" s="3">
         <v>-8300</v>
       </c>
-      <c r="M101" s="3">
+      <c r="O101" s="3">
         <v>31000</v>
       </c>
-      <c r="N101" s="3">
+      <c r="P101" s="3">
         <v>26900</v>
       </c>
-      <c r="O101" s="3">
+      <c r="Q101" s="3">
         <v>-2900</v>
       </c>
-      <c r="P101" s="3">
+      <c r="R101" s="3">
         <v>-6600</v>
       </c>
-      <c r="Q101" s="3">
+      <c r="S101" s="3">
         <v>-300</v>
       </c>
-      <c r="R101" s="3">
+      <c r="T101" s="3">
         <v>-19200</v>
       </c>
-      <c r="S101" s="3">
+      <c r="U101" s="3">
         <v>4800</v>
       </c>
-      <c r="T101" s="3">
+      <c r="V101" s="3">
         <v>-78800</v>
       </c>
-      <c r="U101" s="3">
+      <c r="W101" s="3">
         <v>-16100</v>
       </c>
-      <c r="V101" s="3">
+      <c r="X101" s="3">
         <v>300</v>
       </c>
-      <c r="W101" s="3">
+      <c r="Y101" s="3">
         <v>2700</v>
       </c>
-      <c r="X101" s="3">
+      <c r="Z101" s="3">
         <v>-2000</v>
       </c>
-      <c r="Y101" s="3">
+      <c r="AA101" s="3">
         <v>5200</v>
       </c>
-      <c r="Z101" s="3">
+      <c r="AB101" s="3">
         <v>3300</v>
       </c>
-      <c r="AA101" s="3">
+      <c r="AC101" s="3">
         <v>-6900</v>
       </c>
-      <c r="AB101" s="3">
+      <c r="AD101" s="3">
         <v>4700</v>
       </c>
-      <c r="AC101" s="3">
+      <c r="AE101" s="3">
         <v>14200</v>
       </c>
-      <c r="AD101" s="3">
+      <c r="AF101" s="3">
         <v>32400</v>
       </c>
-      <c r="AE101" s="3">
+      <c r="AG101" s="3">
         <v>-12800</v>
       </c>
-      <c r="AF101" s="3">
+      <c r="AH101" s="3">
         <v>-16600</v>
       </c>
-      <c r="AG101" s="3">
+      <c r="AI101" s="3">
         <v>-17500</v>
       </c>
-      <c r="AH101" s="3">
+      <c r="AJ101" s="3">
         <v>-10400</v>
       </c>
-      <c r="AI101" s="3">
+      <c r="AK101" s="3">
         <v>-18100</v>
       </c>
-      <c r="AJ101" s="3">
+      <c r="AL101" s="3">
         <v>40700</v>
       </c>
-      <c r="AK101" s="3">
+      <c r="AM101" s="3">
         <v>400</v>
       </c>
     </row>
-    <row r="102" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>121100</v>
+      </c>
+      <c r="E102" s="3">
+        <v>-147300</v>
+      </c>
+      <c r="F102" s="3">
         <v>244300</v>
       </c>
-      <c r="E102" s="3">
+      <c r="G102" s="3">
         <v>166600</v>
       </c>
-      <c r="F102" s="3">
+      <c r="H102" s="3">
         <v>-315600</v>
       </c>
-      <c r="G102" s="3">
+      <c r="I102" s="3">
         <v>-24800</v>
       </c>
-      <c r="H102" s="3">
+      <c r="J102" s="3">
         <v>415000</v>
       </c>
-      <c r="I102" s="3">
+      <c r="K102" s="3">
         <v>199000</v>
       </c>
-      <c r="J102" s="3">
+      <c r="L102" s="3">
         <v>-227400</v>
       </c>
-      <c r="K102" s="3">
+      <c r="M102" s="3">
         <v>-334400</v>
       </c>
-      <c r="L102" s="3">
+      <c r="N102" s="3">
         <v>-335200</v>
       </c>
-      <c r="M102" s="3">
+      <c r="O102" s="3">
         <v>642800</v>
       </c>
-      <c r="N102" s="3">
+      <c r="P102" s="3">
         <v>28900</v>
       </c>
-      <c r="O102" s="3">
+      <c r="Q102" s="3">
         <v>48700</v>
       </c>
-      <c r="P102" s="3">
+      <c r="R102" s="3">
         <v>-86200</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="S102" s="3">
         <v>-251300</v>
       </c>
-      <c r="R102" s="3">
+      <c r="T102" s="3">
         <v>96300</v>
       </c>
-      <c r="S102" s="3">
+      <c r="U102" s="3">
         <v>-411900</v>
       </c>
-      <c r="T102" s="3">
+      <c r="V102" s="3">
         <v>-288300</v>
       </c>
-      <c r="U102" s="3">
+      <c r="W102" s="3">
         <v>1643600</v>
       </c>
-      <c r="V102" s="3">
+      <c r="X102" s="3">
         <v>32700</v>
       </c>
-      <c r="W102" s="3">
+      <c r="Y102" s="3">
         <v>-35000</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Z102" s="3">
         <v>33500</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="AA102" s="3">
         <v>-320300</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AB102" s="3">
         <v>155900</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AC102" s="3">
         <v>223500</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AD102" s="3">
         <v>-239400</v>
       </c>
-      <c r="AC102" s="3">
+      <c r="AE102" s="3">
         <v>13700</v>
       </c>
-      <c r="AD102" s="3">
+      <c r="AF102" s="3">
         <v>374800</v>
       </c>
-      <c r="AE102" s="3">
+      <c r="AG102" s="3">
         <v>-326900</v>
       </c>
-      <c r="AF102" s="3">
+      <c r="AH102" s="3">
         <v>49800</v>
       </c>
-      <c r="AG102" s="3">
+      <c r="AI102" s="3">
         <v>-92900</v>
       </c>
-      <c r="AH102" s="3">
+      <c r="AJ102" s="3">
         <v>-150000</v>
       </c>
-      <c r="AI102" s="3">
+      <c r="AK102" s="3">
         <v>-705100</v>
       </c>
-      <c r="AJ102" s="3">
+      <c r="AL102" s="3">
         <v>1407600</v>
       </c>
-      <c r="AK102" s="3">
+      <c r="AM102" s="3">
         <v>-11700</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/ZTO_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/ZTO_QTR_FIN.xlsx
@@ -5772,7 +5772,7 @@
         <v>345000</v>
       </c>
       <c r="H57" s="3">
-        <v>323200</v>
+        <v>301200</v>
       </c>
       <c r="I57" s="3">
         <v>324000</v>
@@ -6004,7 +6004,7 @@
         <v>936500</v>
       </c>
       <c r="H59" s="3">
-        <v>1582400</v>
+        <v>1604400</v>
       </c>
       <c r="I59" s="3">
         <v>1264500</v>

--- a/AAII_Financials/Quarterly/ZTO_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/ZTO_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="174" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="180" uniqueCount="92">
   <si>
     <t>ZTO</t>
   </si>
@@ -656,518 +656,543 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AN102"/>
+  <dimension ref="A5:AP102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="6.140625" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="8" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="12" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="16" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="20" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="24" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="28" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="29" max="29" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="30" max="30" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="31" max="32" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="33" max="33" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="34" max="34" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="35" max="36" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="37" max="37" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="38" max="38" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="39" max="40" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="41" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="22" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="26" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="30" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="32" max="32" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="33" max="34" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="35" max="35" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="36" max="36" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="37" max="38" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="39" max="39" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="40" max="40" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="41" max="42" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="43" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:40" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:42" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:40" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:42" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:40" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:42" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>46112</v>
+      </c>
+      <c r="E7" s="2">
+        <v>46022</v>
+      </c>
+      <c r="F7" s="2">
         <v>45930</v>
       </c>
-      <c r="E7" s="2">
+      <c r="G7" s="2">
         <v>45838</v>
       </c>
-      <c r="F7" s="2">
+      <c r="H7" s="2">
         <v>45747</v>
       </c>
-      <c r="G7" s="2">
+      <c r="I7" s="2">
         <v>45657</v>
       </c>
-      <c r="H7" s="2">
+      <c r="J7" s="2">
         <v>45565</v>
       </c>
-      <c r="I7" s="2">
+      <c r="K7" s="2">
         <v>45473</v>
       </c>
-      <c r="J7" s="2">
+      <c r="L7" s="2">
         <v>45382</v>
       </c>
-      <c r="K7" s="2">
+      <c r="M7" s="2">
         <v>45291</v>
       </c>
-      <c r="L7" s="2">
+      <c r="N7" s="2">
         <v>45199</v>
       </c>
-      <c r="M7" s="2">
+      <c r="O7" s="2">
         <v>45107</v>
       </c>
-      <c r="N7" s="2">
+      <c r="P7" s="2">
         <v>45016</v>
       </c>
-      <c r="O7" s="2">
+      <c r="Q7" s="2">
         <v>44926</v>
       </c>
-      <c r="P7" s="2">
+      <c r="R7" s="2">
         <v>44834</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="S7" s="2">
         <v>44742</v>
       </c>
-      <c r="R7" s="2">
+      <c r="T7" s="2">
         <v>44651</v>
       </c>
-      <c r="S7" s="2">
+      <c r="U7" s="2">
         <v>44561</v>
       </c>
-      <c r="T7" s="2">
+      <c r="V7" s="2">
         <v>44469</v>
       </c>
-      <c r="U7" s="2">
+      <c r="W7" s="2">
         <v>44377</v>
       </c>
-      <c r="V7" s="2">
+      <c r="X7" s="2">
         <v>44286</v>
       </c>
-      <c r="W7" s="2">
+      <c r="Y7" s="2">
         <v>44196</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Z7" s="2">
         <v>44104</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="AA7" s="2">
         <v>44012</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AB7" s="2">
         <v>43921</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AC7" s="2">
         <v>43830</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AD7" s="2">
         <v>43738</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AE7" s="2">
         <v>43646</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AF7" s="2">
         <v>43555</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AG7" s="2">
         <v>43465</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AH7" s="2">
         <v>43373</v>
       </c>
-      <c r="AG7" s="2">
+      <c r="AI7" s="2">
         <v>43281</v>
       </c>
-      <c r="AH7" s="2">
+      <c r="AJ7" s="2">
         <v>43190</v>
       </c>
-      <c r="AI7" s="2">
+      <c r="AK7" s="2">
         <v>43100</v>
       </c>
-      <c r="AJ7" s="2">
+      <c r="AL7" s="2">
         <v>43008</v>
       </c>
-      <c r="AK7" s="2">
+      <c r="AM7" s="2">
         <v>42916</v>
       </c>
-      <c r="AL7" s="2">
+      <c r="AN7" s="2">
         <v>42825</v>
       </c>
-      <c r="AM7" s="2">
+      <c r="AO7" s="2">
         <v>42735</v>
       </c>
-      <c r="AN7" s="2">
+      <c r="AP7" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="8" spans="1:40" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:42" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>1925700</v>
+      </c>
+      <c r="E8" s="3">
+        <v>2074600</v>
+      </c>
+      <c r="F8" s="3">
         <v>1666600</v>
       </c>
-      <c r="E8" s="3">
+      <c r="G8" s="3">
         <v>1651600</v>
       </c>
-      <c r="F8" s="3">
+      <c r="H8" s="3">
         <v>1500900</v>
       </c>
-      <c r="G8" s="3">
+      <c r="I8" s="3">
         <v>1770000</v>
       </c>
-      <c r="H8" s="3">
+      <c r="J8" s="3">
         <v>1521900</v>
       </c>
-      <c r="I8" s="3">
+      <c r="K8" s="3">
         <v>1476000</v>
       </c>
-      <c r="J8" s="3">
+      <c r="L8" s="3">
         <v>1379400</v>
       </c>
-      <c r="K8" s="3">
+      <c r="M8" s="3">
         <v>1497600</v>
       </c>
-      <c r="L8" s="3">
+      <c r="N8" s="3">
         <v>1243900</v>
       </c>
-      <c r="M8" s="3">
+      <c r="O8" s="3">
         <v>1343100</v>
       </c>
-      <c r="N8" s="3">
+      <c r="P8" s="3">
         <v>1307800</v>
       </c>
-      <c r="O8" s="3">
+      <c r="Q8" s="3">
         <v>1391700</v>
       </c>
-      <c r="P8" s="3">
+      <c r="R8" s="3">
         <v>1235800</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="S8" s="3">
         <v>1203500</v>
       </c>
-      <c r="R8" s="3">
+      <c r="T8" s="3">
         <v>1098800</v>
       </c>
-      <c r="S8" s="3">
+      <c r="U8" s="3">
         <v>1270000</v>
       </c>
-      <c r="T8" s="3">
+      <c r="V8" s="3">
         <v>1050600</v>
       </c>
-      <c r="U8" s="3">
+      <c r="W8" s="3">
         <v>1052000</v>
       </c>
-      <c r="V8" s="3">
+      <c r="X8" s="3">
         <v>929600</v>
       </c>
-      <c r="W8" s="3">
+      <c r="Y8" s="3">
         <v>1149400</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Z8" s="3">
         <v>978300</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="AA8" s="3">
         <v>943500</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AB8" s="3">
         <v>617800</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AC8" s="3">
         <v>1054200</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AD8" s="3">
         <v>821500</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AE8" s="3">
         <v>828600</v>
       </c>
-      <c r="AD8" s="3">
+      <c r="AF8" s="3">
         <v>695800</v>
       </c>
-      <c r="AE8" s="3">
+      <c r="AG8" s="3">
         <v>817300</v>
       </c>
-      <c r="AF8" s="3">
+      <c r="AH8" s="3">
         <v>592700</v>
       </c>
-      <c r="AG8" s="3">
+      <c r="AI8" s="3">
         <v>587500</v>
       </c>
-      <c r="AH8" s="3">
+      <c r="AJ8" s="3">
         <v>508600</v>
       </c>
-      <c r="AI8" s="3">
+      <c r="AK8" s="3">
         <v>642800</v>
       </c>
-      <c r="AJ8" s="3">
+      <c r="AL8" s="3">
         <v>466500</v>
       </c>
-      <c r="AK8" s="3">
+      <c r="AM8" s="3">
         <v>441000</v>
       </c>
-      <c r="AL8" s="3">
+      <c r="AN8" s="3">
         <v>380200</v>
       </c>
-      <c r="AM8" s="3">
+      <c r="AO8" s="3">
         <v>464000</v>
       </c>
-      <c r="AN8" s="3">
+      <c r="AP8" s="3">
         <v>342200</v>
       </c>
     </row>
-    <row r="9" spans="1:40" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:42" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>1456700</v>
+      </c>
+      <c r="E9" s="3">
+        <v>1548200</v>
+      </c>
+      <c r="F9" s="3">
         <v>1251400</v>
       </c>
-      <c r="E9" s="3">
+      <c r="G9" s="3">
         <v>1240600</v>
       </c>
-      <c r="F9" s="3">
+      <c r="H9" s="3">
         <v>1130300</v>
       </c>
-      <c r="G9" s="3">
+      <c r="I9" s="3">
         <v>1254900</v>
       </c>
-      <c r="H9" s="3">
+      <c r="J9" s="3">
         <v>1046400</v>
       </c>
-      <c r="I9" s="3">
+      <c r="K9" s="3">
         <v>977800</v>
       </c>
-      <c r="J9" s="3">
+      <c r="L9" s="3">
         <v>963600</v>
       </c>
-      <c r="K9" s="3">
+      <c r="M9" s="3">
         <v>1056500</v>
       </c>
-      <c r="L9" s="3">
+      <c r="N9" s="3">
         <v>872900</v>
       </c>
-      <c r="M9" s="3">
+      <c r="O9" s="3">
         <v>887400</v>
       </c>
-      <c r="N9" s="3">
+      <c r="P9" s="3">
         <v>940400</v>
       </c>
-      <c r="O9" s="3">
+      <c r="Q9" s="3">
         <v>1000800</v>
       </c>
-      <c r="P9" s="3">
+      <c r="R9" s="3">
         <v>898100</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="S9" s="3">
         <v>897200</v>
       </c>
-      <c r="R9" s="3">
+      <c r="T9" s="3">
         <v>873700</v>
       </c>
-      <c r="S9" s="3">
+      <c r="U9" s="3">
         <v>959900</v>
       </c>
-      <c r="T9" s="3">
+      <c r="V9" s="3">
         <v>827700</v>
       </c>
-      <c r="U9" s="3">
+      <c r="W9" s="3">
         <v>811700</v>
       </c>
-      <c r="V9" s="3">
+      <c r="X9" s="3">
         <v>772100</v>
       </c>
-      <c r="W9" s="3">
+      <c r="Y9" s="3">
         <v>890700</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Z9" s="3">
         <v>773300</v>
       </c>
-      <c r="Y9" s="3">
+      <c r="AA9" s="3">
         <v>682800</v>
       </c>
-      <c r="Z9" s="3">
+      <c r="AB9" s="3">
         <v>488600</v>
       </c>
-      <c r="AA9" s="3">
+      <c r="AC9" s="3">
         <v>746900</v>
       </c>
-      <c r="AB9" s="3">
+      <c r="AD9" s="3">
         <v>572400</v>
       </c>
-      <c r="AC9" s="3">
+      <c r="AE9" s="3">
         <v>558400</v>
       </c>
-      <c r="AD9" s="3">
+      <c r="AF9" s="3">
         <v>504200</v>
       </c>
-      <c r="AE9" s="3">
+      <c r="AG9" s="3">
         <v>592200</v>
       </c>
-      <c r="AF9" s="3">
+      <c r="AH9" s="3">
         <v>407200</v>
       </c>
-      <c r="AG9" s="3">
+      <c r="AI9" s="3">
         <v>383600</v>
       </c>
-      <c r="AH9" s="3">
+      <c r="AJ9" s="3">
         <v>360500</v>
       </c>
-      <c r="AI9" s="3">
+      <c r="AK9" s="3">
         <v>441900</v>
       </c>
-      <c r="AJ9" s="3">
+      <c r="AL9" s="3">
         <v>297600</v>
       </c>
-      <c r="AK9" s="3">
+      <c r="AM9" s="3">
         <v>274200</v>
       </c>
-      <c r="AL9" s="3">
+      <c r="AN9" s="3">
         <v>274000</v>
       </c>
-      <c r="AM9" s="3">
+      <c r="AO9" s="3">
         <v>295100</v>
       </c>
-      <c r="AN9" s="3">
+      <c r="AP9" s="3">
         <v>218200</v>
       </c>
     </row>
-    <row r="10" spans="1:40" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:42" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
+        <v>469000</v>
+      </c>
+      <c r="E10" s="3">
+        <v>526400</v>
+      </c>
+      <c r="F10" s="3">
         <v>415200</v>
       </c>
-      <c r="E10" s="3">
+      <c r="G10" s="3">
         <v>411000</v>
       </c>
-      <c r="F10" s="3">
+      <c r="H10" s="3">
         <v>370600</v>
       </c>
-      <c r="G10" s="3">
+      <c r="I10" s="3">
         <v>515100</v>
       </c>
-      <c r="H10" s="3">
+      <c r="J10" s="3">
         <v>475400</v>
       </c>
-      <c r="I10" s="3">
+      <c r="K10" s="3">
         <v>498200</v>
       </c>
-      <c r="J10" s="3">
+      <c r="L10" s="3">
         <v>415800</v>
       </c>
-      <c r="K10" s="3">
+      <c r="M10" s="3">
         <v>441200</v>
       </c>
-      <c r="L10" s="3">
+      <c r="N10" s="3">
         <v>370900</v>
       </c>
-      <c r="M10" s="3">
+      <c r="O10" s="3">
         <v>455600</v>
       </c>
-      <c r="N10" s="3">
+      <c r="P10" s="3">
         <v>367400</v>
       </c>
-      <c r="O10" s="3">
+      <c r="Q10" s="3">
         <v>390900</v>
       </c>
-      <c r="P10" s="3">
+      <c r="R10" s="3">
         <v>337700</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="S10" s="3">
         <v>306200</v>
       </c>
-      <c r="R10" s="3">
+      <c r="T10" s="3">
         <v>225100</v>
       </c>
-      <c r="S10" s="3">
+      <c r="U10" s="3">
         <v>310100</v>
       </c>
-      <c r="T10" s="3">
+      <c r="V10" s="3">
         <v>222900</v>
       </c>
-      <c r="U10" s="3">
+      <c r="W10" s="3">
         <v>240400</v>
       </c>
-      <c r="V10" s="3">
+      <c r="X10" s="3">
         <v>157500</v>
       </c>
-      <c r="W10" s="3">
+      <c r="Y10" s="3">
         <v>258700</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Z10" s="3">
         <v>205000</v>
       </c>
-      <c r="Y10" s="3">
+      <c r="AA10" s="3">
         <v>260700</v>
       </c>
-      <c r="Z10" s="3">
+      <c r="AB10" s="3">
         <v>129200</v>
       </c>
-      <c r="AA10" s="3">
+      <c r="AC10" s="3">
         <v>307400</v>
       </c>
-      <c r="AB10" s="3">
+      <c r="AD10" s="3">
         <v>249100</v>
       </c>
-      <c r="AC10" s="3">
+      <c r="AE10" s="3">
         <v>270200</v>
       </c>
-      <c r="AD10" s="3">
+      <c r="AF10" s="3">
         <v>191600</v>
       </c>
-      <c r="AE10" s="3">
+      <c r="AG10" s="3">
         <v>225100</v>
       </c>
-      <c r="AF10" s="3">
+      <c r="AH10" s="3">
         <v>185500</v>
       </c>
-      <c r="AG10" s="3">
+      <c r="AI10" s="3">
         <v>204000</v>
       </c>
-      <c r="AH10" s="3">
+      <c r="AJ10" s="3">
         <v>148100</v>
       </c>
-      <c r="AI10" s="3">
+      <c r="AK10" s="3">
         <v>200800</v>
       </c>
-      <c r="AJ10" s="3">
+      <c r="AL10" s="3">
         <v>168900</v>
       </c>
-      <c r="AK10" s="3">
+      <c r="AM10" s="3">
         <v>166800</v>
       </c>
-      <c r="AL10" s="3">
+      <c r="AN10" s="3">
         <v>106300</v>
       </c>
-      <c r="AM10" s="3">
+      <c r="AO10" s="3">
         <v>168900</v>
       </c>
-      <c r="AN10" s="3">
+      <c r="AP10" s="3">
         <v>124000</v>
       </c>
     </row>
-    <row r="11" spans="1:40" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:42" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -1208,8 +1233,10 @@
       <c r="AL11" s="3"/>
       <c r="AM11" s="3"/>
       <c r="AN11" s="3"/>
+      <c r="AO11" s="3"/>
+      <c r="AP11" s="3"/>
     </row>
-    <row r="12" spans="1:40" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:42" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
@@ -1324,8 +1351,14 @@
       <c r="AN12" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AO12" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AP12" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="13" spans="1:40" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:42" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1440,112 +1473,118 @@
       <c r="AN13" s="3">
         <v>0</v>
       </c>
+      <c r="AO13" s="3">
+        <v>0</v>
+      </c>
+      <c r="AP13" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="14" spans="1:40" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:42" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3">
+        <v>-100</v>
+      </c>
+      <c r="E14" s="3">
+        <v>6300</v>
+      </c>
+      <c r="F14" s="3">
         <v>-5000</v>
       </c>
-      <c r="E14" s="3">
+      <c r="G14" s="3">
         <v>11900</v>
       </c>
-      <c r="F14" s="3">
-        <v>0</v>
-      </c>
-      <c r="G14" s="3">
+      <c r="H14" s="3">
+        <v>0</v>
+      </c>
+      <c r="I14" s="3">
         <v>41500</v>
       </c>
-      <c r="H14" s="3">
+      <c r="J14" s="3">
         <v>200</v>
       </c>
-      <c r="I14" s="3">
+      <c r="K14" s="3">
         <v>25200</v>
       </c>
-      <c r="J14" s="3">
+      <c r="L14" s="3">
         <v>66200</v>
       </c>
-      <c r="K14" s="3">
+      <c r="M14" s="3">
         <v>11500</v>
       </c>
-      <c r="L14" s="3">
+      <c r="N14" s="3">
         <v>-1500</v>
       </c>
-      <c r="M14" s="3">
+      <c r="O14" s="3">
         <v>100</v>
       </c>
-      <c r="N14" s="3" t="s">
+      <c r="P14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="O14" s="3">
+      <c r="Q14" s="3">
         <v>-1300</v>
       </c>
-      <c r="P14" s="3">
+      <c r="R14" s="3">
         <v>-4700</v>
       </c>
-      <c r="Q14" s="3" t="s">
+      <c r="S14" s="3" t="s">
         <v>8</v>
-      </c>
-      <c r="R14" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="S14" s="3">
-        <v>-300</v>
       </c>
       <c r="T14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="U14" s="3" t="s">
-        <v>8</v>
+      <c r="U14" s="3">
+        <v>-300</v>
       </c>
       <c r="V14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="W14" s="3">
+      <c r="W14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="X14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="Y14" s="3">
         <v>-200</v>
       </c>
-      <c r="X14" s="3">
-        <v>0</v>
-      </c>
-      <c r="Y14" s="3">
-        <v>0</v>
-      </c>
       <c r="Z14" s="3">
         <v>0</v>
       </c>
       <c r="AA14" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB14" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC14" s="3">
         <v>9000</v>
       </c>
-      <c r="AB14" s="3">
-        <v>0</v>
-      </c>
-      <c r="AC14" s="3">
-        <v>0</v>
-      </c>
       <c r="AD14" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE14" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF14" s="3">
         <v>100</v>
       </c>
-      <c r="AE14" s="3">
-        <v>0</v>
-      </c>
-      <c r="AF14" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="AG14" s="3" t="s">
-        <v>8</v>
+      <c r="AG14" s="3">
+        <v>0</v>
       </c>
       <c r="AH14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AI14" s="3">
-        <v>4500</v>
+      <c r="AI14" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="AJ14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AK14" s="3" t="s">
-        <v>8</v>
+      <c r="AK14" s="3">
+        <v>4500</v>
       </c>
       <c r="AL14" s="3" t="s">
         <v>8</v>
@@ -1556,50 +1595,56 @@
       <c r="AN14" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AO14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AP14" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="15" spans="1:40" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:42" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
+        <v>139500</v>
+      </c>
+      <c r="E15" s="3">
+        <v>126100</v>
+      </c>
+      <c r="F15" s="3">
         <v>121100</v>
       </c>
-      <c r="E15" s="3">
+      <c r="G15" s="3">
         <v>123500</v>
       </c>
-      <c r="F15" s="3">
+      <c r="H15" s="3">
         <v>114000</v>
       </c>
-      <c r="G15" s="3">
+      <c r="I15" s="3">
         <v>102900</v>
       </c>
-      <c r="H15" s="3">
+      <c r="J15" s="3">
         <v>104200</v>
       </c>
-      <c r="I15" s="3">
+      <c r="K15" s="3">
         <v>103900</v>
       </c>
-      <c r="J15" s="3">
+      <c r="L15" s="3">
         <v>108900</v>
       </c>
-      <c r="K15" s="3">
+      <c r="M15" s="3">
         <v>104200</v>
       </c>
-      <c r="L15" s="3">
+      <c r="N15" s="3">
         <v>102100</v>
       </c>
-      <c r="M15" s="3">
+      <c r="O15" s="3">
         <v>97200</v>
       </c>
-      <c r="N15" s="3">
+      <c r="P15" s="3">
         <v>99900</v>
       </c>
-      <c r="O15" s="3">
-        <v>0</v>
-      </c>
-      <c r="P15" s="3">
-        <v>0</v>
-      </c>
       <c r="Q15" s="3">
         <v>0</v>
       </c>
@@ -1672,8 +1717,14 @@
       <c r="AN15" s="3">
         <v>0</v>
       </c>
+      <c r="AO15" s="3">
+        <v>0</v>
+      </c>
+      <c r="AP15" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="16" spans="1:40" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:42" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1711,240 +1762,254 @@
       <c r="AL16" s="3"/>
       <c r="AM16" s="3"/>
       <c r="AN16" s="3"/>
+      <c r="AO16" s="3"/>
+      <c r="AP16" s="3"/>
     </row>
-    <row r="17" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="17" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>1556700</v>
+      </c>
+      <c r="E17" s="3">
+        <v>1612100</v>
+      </c>
+      <c r="F17" s="3">
         <v>1328800</v>
       </c>
-      <c r="E17" s="3">
+      <c r="G17" s="3">
         <v>1306100</v>
       </c>
-      <c r="F17" s="3">
+      <c r="H17" s="3">
         <v>1169400</v>
       </c>
-      <c r="G17" s="3">
+      <c r="I17" s="3">
         <v>1293800</v>
       </c>
-      <c r="H17" s="3">
+      <c r="J17" s="3">
         <v>1116700</v>
       </c>
-      <c r="I17" s="3">
+      <c r="K17" s="3">
         <v>1033600</v>
       </c>
-      <c r="J17" s="3">
+      <c r="L17" s="3">
         <v>1065500</v>
       </c>
-      <c r="K17" s="3">
+      <c r="M17" s="3">
         <v>1098300</v>
       </c>
-      <c r="L17" s="3">
+      <c r="N17" s="3">
         <v>911700</v>
       </c>
-      <c r="M17" s="3">
+      <c r="O17" s="3">
         <v>946100</v>
       </c>
-      <c r="N17" s="3">
+      <c r="P17" s="3">
         <v>1023800</v>
       </c>
-      <c r="O17" s="3">
+      <c r="Q17" s="3">
         <v>1043600</v>
       </c>
-      <c r="P17" s="3">
+      <c r="R17" s="3">
         <v>930600</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="S17" s="3">
         <v>927400</v>
       </c>
-      <c r="R17" s="3">
+      <c r="T17" s="3">
         <v>943600</v>
       </c>
-      <c r="S17" s="3">
+      <c r="U17" s="3">
         <v>986700</v>
       </c>
-      <c r="T17" s="3">
+      <c r="V17" s="3">
         <v>857200</v>
       </c>
-      <c r="U17" s="3">
+      <c r="W17" s="3">
         <v>843000</v>
       </c>
-      <c r="V17" s="3">
+      <c r="X17" s="3">
         <v>838700</v>
       </c>
-      <c r="W17" s="3">
+      <c r="Y17" s="3">
         <v>931200</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Z17" s="3">
         <v>806000</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="AA17" s="3">
         <v>700800</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AB17" s="3">
         <v>559100</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AC17" s="3">
         <v>784600</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AD17" s="3">
         <v>603000</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AE17" s="3">
         <v>600600</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AF17" s="3">
         <v>580300</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AG17" s="3">
         <v>620800</v>
       </c>
-      <c r="AF17" s="3">
+      <c r="AH17" s="3">
         <v>439900</v>
       </c>
-      <c r="AG17" s="3">
+      <c r="AI17" s="3">
         <v>421100</v>
       </c>
-      <c r="AH17" s="3">
+      <c r="AJ17" s="3">
         <v>408300</v>
       </c>
-      <c r="AI17" s="3">
+      <c r="AK17" s="3">
         <v>465300</v>
       </c>
-      <c r="AJ17" s="3">
+      <c r="AL17" s="3">
         <v>326300</v>
       </c>
-      <c r="AK17" s="3">
+      <c r="AM17" s="3">
         <v>304300</v>
       </c>
-      <c r="AL17" s="3">
+      <c r="AN17" s="3">
         <v>284700</v>
       </c>
-      <c r="AM17" s="3">
+      <c r="AO17" s="3">
         <v>322800</v>
       </c>
-      <c r="AN17" s="3">
+      <c r="AP17" s="3">
         <v>234400</v>
       </c>
     </row>
-    <row r="18" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>369000</v>
+      </c>
+      <c r="E18" s="3">
+        <v>462600</v>
+      </c>
+      <c r="F18" s="3">
         <v>337800</v>
       </c>
-      <c r="E18" s="3">
+      <c r="G18" s="3">
         <v>345500</v>
       </c>
-      <c r="F18" s="3">
+      <c r="H18" s="3">
         <v>331500</v>
       </c>
-      <c r="G18" s="3">
+      <c r="I18" s="3">
         <v>476300</v>
       </c>
-      <c r="H18" s="3">
+      <c r="J18" s="3">
         <v>405100</v>
       </c>
-      <c r="I18" s="3">
+      <c r="K18" s="3">
         <v>442400</v>
       </c>
-      <c r="J18" s="3">
+      <c r="L18" s="3">
         <v>313900</v>
       </c>
-      <c r="K18" s="3">
+      <c r="M18" s="3">
         <v>399300</v>
       </c>
-      <c r="L18" s="3">
+      <c r="N18" s="3">
         <v>332200</v>
       </c>
-      <c r="M18" s="3">
+      <c r="O18" s="3">
         <v>396900</v>
       </c>
-      <c r="N18" s="3">
+      <c r="P18" s="3">
         <v>283900</v>
       </c>
-      <c r="O18" s="3">
+      <c r="Q18" s="3">
         <v>348100</v>
       </c>
-      <c r="P18" s="3">
+      <c r="R18" s="3">
         <v>305200</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="S18" s="3">
         <v>276000</v>
       </c>
-      <c r="R18" s="3">
+      <c r="T18" s="3">
         <v>155200</v>
       </c>
-      <c r="S18" s="3">
+      <c r="U18" s="3">
         <v>283300</v>
       </c>
-      <c r="T18" s="3">
+      <c r="V18" s="3">
         <v>193400</v>
       </c>
-      <c r="U18" s="3">
+      <c r="W18" s="3">
         <v>209100</v>
       </c>
-      <c r="V18" s="3">
+      <c r="X18" s="3">
         <v>90900</v>
       </c>
-      <c r="W18" s="3">
+      <c r="Y18" s="3">
         <v>218200</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Z18" s="3">
         <v>172300</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="AA18" s="3">
         <v>242600</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AB18" s="3">
         <v>58700</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AC18" s="3">
         <v>269700</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AD18" s="3">
         <v>218500</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AE18" s="3">
         <v>228100</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AF18" s="3">
         <v>115500</v>
       </c>
-      <c r="AE18" s="3">
+      <c r="AG18" s="3">
         <v>196500</v>
       </c>
-      <c r="AF18" s="3">
+      <c r="AH18" s="3">
         <v>152800</v>
       </c>
-      <c r="AG18" s="3">
+      <c r="AI18" s="3">
         <v>166400</v>
       </c>
-      <c r="AH18" s="3">
+      <c r="AJ18" s="3">
         <v>100200</v>
       </c>
-      <c r="AI18" s="3">
+      <c r="AK18" s="3">
         <v>177500</v>
       </c>
-      <c r="AJ18" s="3">
+      <c r="AL18" s="3">
         <v>140200</v>
       </c>
-      <c r="AK18" s="3">
+      <c r="AM18" s="3">
         <v>136700</v>
       </c>
-      <c r="AL18" s="3">
+      <c r="AN18" s="3">
         <v>95500</v>
       </c>
-      <c r="AM18" s="3">
+      <c r="AO18" s="3">
         <v>141200</v>
       </c>
-      <c r="AN18" s="3">
+      <c r="AP18" s="3">
         <v>107800</v>
       </c>
     </row>
-    <row r="19" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1985,315 +2050,329 @@
       <c r="AL19" s="3"/>
       <c r="AM19" s="3"/>
       <c r="AN19" s="3"/>
+      <c r="AO19" s="3"/>
+      <c r="AP19" s="3"/>
     </row>
-    <row r="20" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="20" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>-6800</v>
+      </c>
+      <c r="E20" s="3">
+        <v>-1800</v>
+      </c>
+      <c r="F20" s="3">
         <v>-17900</v>
       </c>
-      <c r="E20" s="3">
+      <c r="G20" s="3">
         <v>-5500</v>
       </c>
-      <c r="F20" s="3">
+      <c r="H20" s="3">
         <v>-4900</v>
       </c>
-      <c r="G20" s="3">
+      <c r="I20" s="3">
         <v>-25000</v>
       </c>
-      <c r="H20" s="3">
+      <c r="J20" s="3">
         <v>11200</v>
       </c>
-      <c r="I20" s="3">
+      <c r="K20" s="3">
         <v>-10200</v>
       </c>
-      <c r="J20" s="3">
+      <c r="L20" s="3">
         <v>-8900</v>
       </c>
-      <c r="K20" s="3">
+      <c r="M20" s="3">
         <v>6200</v>
       </c>
-      <c r="L20" s="3">
+      <c r="N20" s="3">
         <v>-3300</v>
       </c>
-      <c r="M20" s="3">
+      <c r="O20" s="3">
         <v>-18300</v>
       </c>
-      <c r="N20" s="3">
+      <c r="P20" s="3">
         <v>-21700</v>
       </c>
-      <c r="O20" s="3">
+      <c r="Q20" s="3">
         <v>28800</v>
       </c>
-      <c r="P20" s="3">
+      <c r="R20" s="3">
         <v>23600</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="S20" s="3">
         <v>31200</v>
       </c>
-      <c r="R20" s="3">
+      <c r="T20" s="3">
         <v>13500</v>
       </c>
-      <c r="S20" s="3">
+      <c r="U20" s="3">
         <v>9900</v>
       </c>
-      <c r="T20" s="3">
+      <c r="V20" s="3">
         <v>12600</v>
       </c>
-      <c r="U20" s="3">
+      <c r="W20" s="3">
         <v>15600</v>
       </c>
-      <c r="V20" s="3">
+      <c r="X20" s="3">
         <v>13100</v>
       </c>
-      <c r="W20" s="3">
+      <c r="Y20" s="3">
         <v>3200</v>
       </c>
-      <c r="X20" s="3">
+      <c r="Z20" s="3">
         <v>4800</v>
       </c>
-      <c r="Y20" s="3">
+      <c r="AA20" s="3">
         <v>17200</v>
       </c>
-      <c r="Z20" s="3">
+      <c r="AB20" s="3">
         <v>22500</v>
       </c>
-      <c r="AA20" s="3">
+      <c r="AC20" s="3">
         <v>137200</v>
       </c>
-      <c r="AB20" s="3">
+      <c r="AD20" s="3">
         <v>27300</v>
       </c>
-      <c r="AC20" s="3">
+      <c r="AE20" s="3">
         <v>25500</v>
       </c>
-      <c r="AD20" s="3">
+      <c r="AF20" s="3">
         <v>18300</v>
       </c>
-      <c r="AE20" s="3">
+      <c r="AG20" s="3">
         <v>21500</v>
       </c>
-      <c r="AF20" s="3">
+      <c r="AH20" s="3">
         <v>24800</v>
       </c>
-      <c r="AG20" s="3">
+      <c r="AI20" s="3">
         <v>91900</v>
       </c>
-      <c r="AH20" s="3">
+      <c r="AJ20" s="3">
         <v>3400</v>
       </c>
-      <c r="AI20" s="3">
+      <c r="AK20" s="3">
         <v>5700</v>
       </c>
-      <c r="AJ20" s="3">
+      <c r="AL20" s="3">
         <v>2600</v>
       </c>
-      <c r="AK20" s="3">
+      <c r="AM20" s="3">
         <v>5500</v>
       </c>
-      <c r="AL20" s="3">
+      <c r="AN20" s="3">
         <v>3700</v>
       </c>
-      <c r="AM20" s="3">
+      <c r="AO20" s="3">
         <v>3500</v>
       </c>
-      <c r="AN20" s="3">
+      <c r="AP20" s="3">
         <v>1400</v>
       </c>
     </row>
-    <row r="21" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>515300</v>
+      </c>
+      <c r="E21" s="3">
+        <v>590400</v>
+      </c>
+      <c r="F21" s="3">
         <v>476800</v>
       </c>
-      <c r="E21" s="3">
+      <c r="G21" s="3">
         <v>474500</v>
       </c>
-      <c r="F21" s="3">
+      <c r="H21" s="3">
         <v>450400</v>
       </c>
-      <c r="G21" s="3">
+      <c r="I21" s="3">
         <v>604100</v>
       </c>
-      <c r="H21" s="3">
+      <c r="J21" s="3">
         <v>498100</v>
       </c>
-      <c r="I21" s="3">
+      <c r="K21" s="3">
         <v>556600</v>
       </c>
-      <c r="J21" s="3">
+      <c r="L21" s="3">
         <v>431700</v>
       </c>
-      <c r="K21" s="3">
+      <c r="M21" s="3">
         <v>497400</v>
       </c>
-      <c r="L21" s="3">
+      <c r="N21" s="3">
         <v>437500</v>
       </c>
-      <c r="M21" s="3">
+      <c r="O21" s="3">
         <v>512500</v>
       </c>
-      <c r="N21" s="3">
+      <c r="P21" s="3">
         <v>405600</v>
       </c>
-      <c r="O21" s="3">
+      <c r="Q21" s="3">
         <v>381000</v>
       </c>
-      <c r="P21" s="3">
+      <c r="R21" s="3">
         <v>327900</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="S21" s="3">
         <v>312700</v>
       </c>
-      <c r="R21" s="3">
+      <c r="T21" s="3">
         <v>256700</v>
       </c>
-      <c r="S21" s="3">
+      <c r="U21" s="3">
         <v>300500</v>
       </c>
-      <c r="T21" s="3">
+      <c r="V21" s="3">
         <v>202200</v>
       </c>
-      <c r="U21" s="3">
+      <c r="W21" s="3">
         <v>231000</v>
       </c>
-      <c r="V21" s="3">
+      <c r="X21" s="3">
         <v>178800</v>
       </c>
-      <c r="W21" s="3">
+      <c r="Y21" s="3">
         <v>227200</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Z21" s="3">
         <v>184900</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="AA21" s="3">
         <v>262500</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AB21" s="3">
         <v>145600</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AC21" s="3">
         <v>418900</v>
       </c>
-      <c r="AB21" s="3">
+      <c r="AD21" s="3">
         <v>246500</v>
       </c>
-      <c r="AC21" s="3">
+      <c r="AE21" s="3">
         <v>255900</v>
       </c>
-      <c r="AD21" s="3">
+      <c r="AF21" s="3">
         <v>176900</v>
       </c>
-      <c r="AE21" s="3">
+      <c r="AG21" s="3">
         <v>223700</v>
       </c>
-      <c r="AF21" s="3">
+      <c r="AH21" s="3">
         <v>179800</v>
       </c>
-      <c r="AG21" s="3">
+      <c r="AI21" s="3">
         <v>259900</v>
       </c>
-      <c r="AH21" s="3">
+      <c r="AJ21" s="3">
         <v>130400</v>
       </c>
-      <c r="AI21" s="3">
+      <c r="AK21" s="3">
         <v>183000</v>
       </c>
-      <c r="AJ21" s="3">
+      <c r="AL21" s="3">
         <v>144500</v>
       </c>
-      <c r="AK21" s="3">
+      <c r="AM21" s="3">
         <v>143100</v>
       </c>
-      <c r="AL21" s="3">
+      <c r="AN21" s="3">
         <v>118100</v>
       </c>
-      <c r="AM21" s="3">
+      <c r="AO21" s="3">
         <v>178100</v>
       </c>
-      <c r="AN21" s="3">
+      <c r="AP21" s="3">
         <v>105200</v>
       </c>
     </row>
-    <row r="22" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
+        <v>7300</v>
+      </c>
+      <c r="E22" s="3">
+        <v>3900</v>
+      </c>
+      <c r="F22" s="3">
         <v>7600</v>
       </c>
-      <c r="E22" s="3">
+      <c r="G22" s="3">
         <v>13700</v>
-      </c>
-      <c r="F22" s="3">
-        <v>9500</v>
-      </c>
-      <c r="G22" s="3">
-        <v>9800</v>
       </c>
       <c r="H22" s="3">
         <v>9500</v>
       </c>
       <c r="I22" s="3">
+        <v>9800</v>
+      </c>
+      <c r="J22" s="3">
+        <v>9500</v>
+      </c>
+      <c r="K22" s="3">
         <v>15900</v>
       </c>
-      <c r="J22" s="3">
+      <c r="L22" s="3">
         <v>11600</v>
       </c>
-      <c r="K22" s="3">
+      <c r="M22" s="3">
         <v>8700</v>
       </c>
-      <c r="L22" s="3">
+      <c r="N22" s="3">
         <v>11500</v>
       </c>
-      <c r="M22" s="3">
+      <c r="O22" s="3">
         <v>10000</v>
       </c>
-      <c r="N22" s="3">
+      <c r="P22" s="3">
         <v>10400</v>
       </c>
-      <c r="O22" s="3">
+      <c r="Q22" s="3">
         <v>10700</v>
       </c>
-      <c r="P22" s="3">
+      <c r="R22" s="3">
         <v>4400</v>
       </c>
-      <c r="Q22" s="3">
+      <c r="S22" s="3">
         <v>3200</v>
       </c>
-      <c r="R22" s="3">
+      <c r="T22" s="3">
         <v>8300</v>
       </c>
-      <c r="S22" s="3">
+      <c r="U22" s="3">
         <v>3400</v>
       </c>
-      <c r="T22" s="3">
+      <c r="V22" s="3">
         <v>7400</v>
       </c>
-      <c r="U22" s="3">
+      <c r="W22" s="3">
         <v>4900</v>
       </c>
-      <c r="V22" s="3">
+      <c r="X22" s="3">
         <v>2200</v>
       </c>
-      <c r="W22" s="3">
+      <c r="Y22" s="3">
         <v>1700</v>
       </c>
-      <c r="X22" s="3">
+      <c r="Z22" s="3">
         <v>2000</v>
       </c>
-      <c r="Y22" s="3">
+      <c r="AA22" s="3">
         <v>1300</v>
       </c>
-      <c r="Z22" s="3">
-        <v>0</v>
-      </c>
-      <c r="AA22" s="3">
-        <v>0</v>
-      </c>
       <c r="AB22" s="3">
         <v>0</v>
       </c>
@@ -2313,260 +2392,278 @@
         <v>0</v>
       </c>
       <c r="AH22" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI22" s="3">
+        <v>0</v>
+      </c>
+      <c r="AJ22" s="3">
         <v>100</v>
       </c>
-      <c r="AI22" s="3">
+      <c r="AK22" s="3">
         <v>400</v>
       </c>
-      <c r="AJ22" s="3">
+      <c r="AL22" s="3">
         <v>400</v>
       </c>
-      <c r="AK22" s="3">
+      <c r="AM22" s="3">
         <v>700</v>
       </c>
-      <c r="AL22" s="3">
+      <c r="AN22" s="3">
         <v>800</v>
       </c>
-      <c r="AM22" s="3">
+      <c r="AO22" s="3">
         <v>100</v>
       </c>
-      <c r="AN22" s="3">
+      <c r="AP22" s="3">
         <v>500</v>
       </c>
     </row>
-    <row r="23" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>392700</v>
+      </c>
+      <c r="E23" s="3">
+        <v>476300</v>
+      </c>
+      <c r="F23" s="3">
         <v>379100</v>
       </c>
-      <c r="E23" s="3">
+      <c r="G23" s="3">
         <v>354600</v>
       </c>
-      <c r="F23" s="3">
+      <c r="H23" s="3">
         <v>354300</v>
       </c>
-      <c r="G23" s="3">
+      <c r="I23" s="3">
         <v>480300</v>
       </c>
-      <c r="H23" s="3">
+      <c r="J23" s="3">
         <v>418300</v>
       </c>
-      <c r="I23" s="3">
+      <c r="K23" s="3">
         <v>451200</v>
       </c>
-      <c r="J23" s="3">
+      <c r="L23" s="3">
         <v>278900</v>
       </c>
-      <c r="K23" s="3">
+      <c r="M23" s="3">
         <v>401400</v>
       </c>
-      <c r="L23" s="3">
+      <c r="N23" s="3">
         <v>359200</v>
       </c>
-      <c r="M23" s="3">
+      <c r="O23" s="3">
         <v>428300</v>
       </c>
-      <c r="N23" s="3">
+      <c r="P23" s="3">
         <v>308600</v>
       </c>
-      <c r="O23" s="3">
+      <c r="Q23" s="3">
         <v>366100</v>
       </c>
-      <c r="P23" s="3">
+      <c r="R23" s="3">
         <v>324400</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="S23" s="3">
         <v>304100</v>
       </c>
-      <c r="R23" s="3">
+      <c r="T23" s="3">
         <v>160400</v>
       </c>
-      <c r="S23" s="3">
+      <c r="U23" s="3">
         <v>289800</v>
       </c>
-      <c r="T23" s="3">
+      <c r="V23" s="3">
         <v>198600</v>
       </c>
-      <c r="U23" s="3">
+      <c r="W23" s="3">
         <v>219900</v>
       </c>
-      <c r="V23" s="3">
+      <c r="X23" s="3">
         <v>101700</v>
       </c>
-      <c r="W23" s="3">
+      <c r="Y23" s="3">
         <v>219700</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Z23" s="3">
         <v>175000</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="AA23" s="3">
         <v>258500</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AB23" s="3">
         <v>81200</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AC23" s="3">
         <v>406900</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AD23" s="3">
         <v>245800</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AE23" s="3">
         <v>253500</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AF23" s="3">
         <v>133900</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AG23" s="3">
         <v>218000</v>
       </c>
-      <c r="AF23" s="3">
+      <c r="AH23" s="3">
         <v>177600</v>
       </c>
-      <c r="AG23" s="3">
+      <c r="AI23" s="3">
         <v>258300</v>
       </c>
-      <c r="AH23" s="3">
+      <c r="AJ23" s="3">
         <v>103500</v>
       </c>
-      <c r="AI23" s="3">
+      <c r="AK23" s="3">
         <v>182800</v>
       </c>
-      <c r="AJ23" s="3">
+      <c r="AL23" s="3">
         <v>142500</v>
       </c>
-      <c r="AK23" s="3">
+      <c r="AM23" s="3">
         <v>141400</v>
       </c>
-      <c r="AL23" s="3">
+      <c r="AN23" s="3">
         <v>98400</v>
       </c>
-      <c r="AM23" s="3">
+      <c r="AO23" s="3">
         <v>144600</v>
       </c>
-      <c r="AN23" s="3">
+      <c r="AP23" s="3">
         <v>108700</v>
       </c>
     </row>
-    <row r="24" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>80100</v>
+      </c>
+      <c r="E24" s="3">
+        <v>91200</v>
+      </c>
+      <c r="F24" s="3">
         <v>22500</v>
       </c>
-      <c r="E24" s="3">
+      <c r="G24" s="3">
         <v>80300</v>
       </c>
-      <c r="F24" s="3">
+      <c r="H24" s="3">
         <v>73300</v>
       </c>
-      <c r="G24" s="3">
+      <c r="I24" s="3">
         <v>145100</v>
       </c>
-      <c r="H24" s="3">
+      <c r="J24" s="3">
         <v>79100</v>
       </c>
-      <c r="I24" s="3">
+      <c r="K24" s="3">
         <v>91500</v>
       </c>
-      <c r="J24" s="3">
+      <c r="L24" s="3">
         <v>78400</v>
       </c>
-      <c r="K24" s="3">
+      <c r="M24" s="3">
         <v>89800</v>
       </c>
-      <c r="L24" s="3">
+      <c r="N24" s="3">
         <v>37200</v>
       </c>
-      <c r="M24" s="3">
+      <c r="O24" s="3">
         <v>79400</v>
       </c>
-      <c r="N24" s="3">
+      <c r="P24" s="3">
         <v>66200</v>
       </c>
-      <c r="O24" s="3">
+      <c r="Q24" s="3">
         <v>70600</v>
       </c>
-      <c r="P24" s="3">
+      <c r="R24" s="3">
         <v>60700</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="S24" s="3">
         <v>60900</v>
       </c>
-      <c r="R24" s="3">
+      <c r="T24" s="3">
         <v>35500</v>
       </c>
-      <c r="S24" s="3">
+      <c r="U24" s="3">
         <v>51200</v>
       </c>
-      <c r="T24" s="3">
+      <c r="V24" s="3">
         <v>32600</v>
       </c>
-      <c r="U24" s="3">
+      <c r="W24" s="3">
         <v>36600</v>
       </c>
-      <c r="V24" s="3">
+      <c r="X24" s="3">
         <v>21500</v>
       </c>
-      <c r="W24" s="3">
+      <c r="Y24" s="3">
         <v>40300</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Z24" s="3">
         <v>-4100</v>
       </c>
-      <c r="Y24" s="3">
+      <c r="AA24" s="3">
         <v>44000</v>
       </c>
-      <c r="Z24" s="3">
+      <c r="AB24" s="3">
         <v>20500</v>
       </c>
-      <c r="AA24" s="3">
+      <c r="AC24" s="3">
         <v>51000</v>
       </c>
-      <c r="AB24" s="3">
+      <c r="AD24" s="3">
         <v>41500</v>
       </c>
-      <c r="AC24" s="3">
+      <c r="AE24" s="3">
         <v>44100</v>
       </c>
-      <c r="AD24" s="3">
+      <c r="AF24" s="3">
         <v>29200</v>
       </c>
-      <c r="AE24" s="3">
+      <c r="AG24" s="3">
         <v>32300</v>
       </c>
-      <c r="AF24" s="3">
+      <c r="AH24" s="3">
         <v>28200</v>
       </c>
-      <c r="AG24" s="3">
+      <c r="AI24" s="3">
         <v>49100</v>
       </c>
-      <c r="AH24" s="3">
+      <c r="AJ24" s="3">
         <v>22100</v>
       </c>
-      <c r="AI24" s="3">
+      <c r="AK24" s="3">
         <v>1300</v>
       </c>
-      <c r="AJ24" s="3">
+      <c r="AL24" s="3">
         <v>35300</v>
       </c>
-      <c r="AK24" s="3">
+      <c r="AM24" s="3">
         <v>34600</v>
       </c>
-      <c r="AL24" s="3">
+      <c r="AN24" s="3">
         <v>24200</v>
       </c>
-      <c r="AM24" s="3">
+      <c r="AO24" s="3">
         <v>36600</v>
       </c>
-      <c r="AN24" s="3">
+      <c r="AP24" s="3">
         <v>27100</v>
       </c>
     </row>
-    <row r="25" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2681,240 +2778,258 @@
       <c r="AN25" s="3">
         <v>0</v>
       </c>
+      <c r="AO25" s="3">
+        <v>0</v>
+      </c>
+      <c r="AP25" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="26" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="26" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>312600</v>
+      </c>
+      <c r="E26" s="3">
+        <v>385100</v>
+      </c>
+      <c r="F26" s="3">
         <v>356600</v>
       </c>
-      <c r="E26" s="3">
+      <c r="G26" s="3">
         <v>274200</v>
       </c>
-      <c r="F26" s="3">
+      <c r="H26" s="3">
         <v>281000</v>
       </c>
-      <c r="G26" s="3">
+      <c r="I26" s="3">
         <v>335200</v>
       </c>
-      <c r="H26" s="3">
+      <c r="J26" s="3">
         <v>339200</v>
       </c>
-      <c r="I26" s="3">
+      <c r="K26" s="3">
         <v>359700</v>
       </c>
-      <c r="J26" s="3">
+      <c r="L26" s="3">
         <v>200500</v>
       </c>
-      <c r="K26" s="3">
+      <c r="M26" s="3">
         <v>311600</v>
       </c>
-      <c r="L26" s="3">
+      <c r="N26" s="3">
         <v>322000</v>
       </c>
-      <c r="M26" s="3">
+      <c r="O26" s="3">
         <v>348900</v>
       </c>
-      <c r="N26" s="3">
+      <c r="P26" s="3">
         <v>242400</v>
       </c>
-      <c r="O26" s="3">
+      <c r="Q26" s="3">
         <v>295600</v>
       </c>
-      <c r="P26" s="3">
+      <c r="R26" s="3">
         <v>263700</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="S26" s="3">
         <v>243100</v>
       </c>
-      <c r="R26" s="3">
+      <c r="T26" s="3">
         <v>124900</v>
       </c>
-      <c r="S26" s="3">
+      <c r="U26" s="3">
         <v>238600</v>
       </c>
-      <c r="T26" s="3">
+      <c r="V26" s="3">
         <v>166000</v>
       </c>
-      <c r="U26" s="3">
+      <c r="W26" s="3">
         <v>183300</v>
       </c>
-      <c r="V26" s="3">
+      <c r="X26" s="3">
         <v>80200</v>
       </c>
-      <c r="W26" s="3">
+      <c r="Y26" s="3">
         <v>179400</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Z26" s="3">
         <v>179100</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="AA26" s="3">
         <v>214600</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AB26" s="3">
         <v>60700</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AC26" s="3">
         <v>355800</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AD26" s="3">
         <v>204200</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AE26" s="3">
         <v>209400</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AF26" s="3">
         <v>104700</v>
       </c>
-      <c r="AE26" s="3">
+      <c r="AG26" s="3">
         <v>185700</v>
       </c>
-      <c r="AF26" s="3">
+      <c r="AH26" s="3">
         <v>149400</v>
       </c>
-      <c r="AG26" s="3">
+      <c r="AI26" s="3">
         <v>209100</v>
       </c>
-      <c r="AH26" s="3">
+      <c r="AJ26" s="3">
         <v>81300</v>
       </c>
-      <c r="AI26" s="3">
+      <c r="AK26" s="3">
         <v>181500</v>
       </c>
-      <c r="AJ26" s="3">
+      <c r="AL26" s="3">
         <v>107200</v>
       </c>
-      <c r="AK26" s="3">
+      <c r="AM26" s="3">
         <v>106800</v>
       </c>
-      <c r="AL26" s="3">
+      <c r="AN26" s="3">
         <v>74200</v>
       </c>
-      <c r="AM26" s="3">
+      <c r="AO26" s="3">
         <v>108000</v>
       </c>
-      <c r="AN26" s="3">
+      <c r="AP26" s="3">
         <v>81600</v>
       </c>
     </row>
-    <row r="27" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>307100</v>
+      </c>
+      <c r="E27" s="3">
+        <v>375400</v>
+      </c>
+      <c r="F27" s="3">
         <v>354500</v>
       </c>
-      <c r="E27" s="3">
+      <c r="G27" s="3">
         <v>270600</v>
       </c>
-      <c r="F27" s="3">
+      <c r="H27" s="3">
         <v>274700</v>
       </c>
-      <c r="G27" s="3">
+      <c r="I27" s="3">
         <v>326400</v>
       </c>
-      <c r="H27" s="3">
+      <c r="J27" s="3">
         <v>341600</v>
       </c>
-      <c r="I27" s="3">
+      <c r="K27" s="3">
         <v>359400</v>
       </c>
-      <c r="J27" s="3">
+      <c r="L27" s="3">
         <v>197500</v>
       </c>
-      <c r="K27" s="3">
+      <c r="M27" s="3">
         <v>309200</v>
       </c>
-      <c r="L27" s="3">
+      <c r="N27" s="3">
         <v>321400</v>
       </c>
-      <c r="M27" s="3">
+      <c r="O27" s="3">
         <v>350400</v>
       </c>
-      <c r="N27" s="3">
+      <c r="P27" s="3">
         <v>243200</v>
       </c>
-      <c r="O27" s="3">
+      <c r="Q27" s="3">
         <v>304900</v>
       </c>
-      <c r="P27" s="3">
+      <c r="R27" s="3">
         <v>267300</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="S27" s="3">
         <v>251000</v>
       </c>
-      <c r="R27" s="3">
+      <c r="T27" s="3">
         <v>126000</v>
       </c>
-      <c r="S27" s="3">
+      <c r="U27" s="3">
         <v>242800</v>
       </c>
-      <c r="T27" s="3">
+      <c r="V27" s="3">
         <v>165800</v>
       </c>
-      <c r="U27" s="3">
+      <c r="W27" s="3">
         <v>185600</v>
       </c>
-      <c r="V27" s="3">
+      <c r="X27" s="3">
         <v>76600</v>
       </c>
-      <c r="W27" s="3">
+      <c r="Y27" s="3">
         <v>179300</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Z27" s="3">
         <v>177000</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="AA27" s="3">
         <v>213400</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AB27" s="3">
         <v>59100</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AC27" s="3">
         <v>358200</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AD27" s="3">
         <v>204000</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AE27" s="3">
         <v>207700</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AF27" s="3">
         <v>103600</v>
       </c>
-      <c r="AE27" s="3">
+      <c r="AG27" s="3">
         <v>185200</v>
       </c>
-      <c r="AF27" s="3">
+      <c r="AH27" s="3">
         <v>148300</v>
       </c>
-      <c r="AG27" s="3">
+      <c r="AI27" s="3">
         <v>208700</v>
       </c>
-      <c r="AH27" s="3">
+      <c r="AJ27" s="3">
         <v>79900</v>
       </c>
-      <c r="AI27" s="3">
+      <c r="AK27" s="3">
         <v>181400</v>
       </c>
-      <c r="AJ27" s="3">
+      <c r="AL27" s="3">
         <v>106400</v>
       </c>
-      <c r="AK27" s="3">
+      <c r="AM27" s="3">
         <v>106400</v>
       </c>
-      <c r="AL27" s="3">
+      <c r="AN27" s="3">
         <v>73200</v>
       </c>
-      <c r="AM27" s="3">
+      <c r="AO27" s="3">
         <v>105700</v>
       </c>
-      <c r="AN27" s="3">
+      <c r="AP27" s="3">
         <v>73700</v>
       </c>
     </row>
-    <row r="28" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -3029,8 +3144,14 @@
       <c r="AN28" s="3">
         <v>0</v>
       </c>
+      <c r="AO28" s="3">
+        <v>0</v>
+      </c>
+      <c r="AP28" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="29" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="29" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -3145,8 +3266,14 @@
       <c r="AN29" s="3">
         <v>0</v>
       </c>
+      <c r="AO29" s="3">
+        <v>0</v>
+      </c>
+      <c r="AP29" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="30" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="30" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -3261,8 +3388,14 @@
       <c r="AN30" s="3">
         <v>0</v>
       </c>
+      <c r="AO30" s="3">
+        <v>0</v>
+      </c>
+      <c r="AP30" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="31" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="31" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -3377,240 +3510,258 @@
       <c r="AN31" s="3">
         <v>0</v>
       </c>
+      <c r="AO31" s="3">
+        <v>0</v>
+      </c>
+      <c r="AP31" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="32" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="32" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>6800</v>
+      </c>
+      <c r="E32" s="3">
+        <v>1800</v>
+      </c>
+      <c r="F32" s="3">
         <v>17900</v>
       </c>
-      <c r="E32" s="3">
+      <c r="G32" s="3">
         <v>5500</v>
       </c>
-      <c r="F32" s="3">
+      <c r="H32" s="3">
         <v>4900</v>
       </c>
-      <c r="G32" s="3">
+      <c r="I32" s="3">
         <v>25000</v>
       </c>
-      <c r="H32" s="3">
+      <c r="J32" s="3">
         <v>-11200</v>
       </c>
-      <c r="I32" s="3">
+      <c r="K32" s="3">
         <v>10200</v>
       </c>
-      <c r="J32" s="3">
+      <c r="L32" s="3">
         <v>8900</v>
       </c>
-      <c r="K32" s="3">
+      <c r="M32" s="3">
         <v>-6200</v>
       </c>
-      <c r="L32" s="3">
+      <c r="N32" s="3">
         <v>3300</v>
       </c>
-      <c r="M32" s="3">
+      <c r="O32" s="3">
         <v>18300</v>
       </c>
-      <c r="N32" s="3">
+      <c r="P32" s="3">
         <v>21700</v>
       </c>
-      <c r="O32" s="3">
+      <c r="Q32" s="3">
         <v>-28800</v>
       </c>
-      <c r="P32" s="3">
+      <c r="R32" s="3">
         <v>-23600</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="S32" s="3">
         <v>-31200</v>
       </c>
-      <c r="R32" s="3">
+      <c r="T32" s="3">
         <v>-13500</v>
       </c>
-      <c r="S32" s="3">
+      <c r="U32" s="3">
         <v>-9900</v>
       </c>
-      <c r="T32" s="3">
+      <c r="V32" s="3">
         <v>-12600</v>
       </c>
-      <c r="U32" s="3">
+      <c r="W32" s="3">
         <v>-15600</v>
       </c>
-      <c r="V32" s="3">
+      <c r="X32" s="3">
         <v>-13100</v>
       </c>
-      <c r="W32" s="3">
+      <c r="Y32" s="3">
         <v>-3200</v>
       </c>
-      <c r="X32" s="3">
+      <c r="Z32" s="3">
         <v>-4800</v>
       </c>
-      <c r="Y32" s="3">
+      <c r="AA32" s="3">
         <v>-17200</v>
       </c>
-      <c r="Z32" s="3">
+      <c r="AB32" s="3">
         <v>-22500</v>
       </c>
-      <c r="AA32" s="3">
+      <c r="AC32" s="3">
         <v>-137200</v>
       </c>
-      <c r="AB32" s="3">
+      <c r="AD32" s="3">
         <v>-27300</v>
       </c>
-      <c r="AC32" s="3">
+      <c r="AE32" s="3">
         <v>-25500</v>
       </c>
-      <c r="AD32" s="3">
+      <c r="AF32" s="3">
         <v>-18300</v>
       </c>
-      <c r="AE32" s="3">
+      <c r="AG32" s="3">
         <v>-21500</v>
       </c>
-      <c r="AF32" s="3">
+      <c r="AH32" s="3">
         <v>-24800</v>
       </c>
-      <c r="AG32" s="3">
+      <c r="AI32" s="3">
         <v>-91900</v>
       </c>
-      <c r="AH32" s="3">
+      <c r="AJ32" s="3">
         <v>-3400</v>
       </c>
-      <c r="AI32" s="3">
+      <c r="AK32" s="3">
         <v>-5700</v>
       </c>
-      <c r="AJ32" s="3">
+      <c r="AL32" s="3">
         <v>-2600</v>
       </c>
-      <c r="AK32" s="3">
+      <c r="AM32" s="3">
         <v>-5500</v>
       </c>
-      <c r="AL32" s="3">
+      <c r="AN32" s="3">
         <v>-3700</v>
       </c>
-      <c r="AM32" s="3">
+      <c r="AO32" s="3">
         <v>-3500</v>
       </c>
-      <c r="AN32" s="3">
+      <c r="AP32" s="3">
         <v>-1400</v>
       </c>
     </row>
-    <row r="33" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>307100</v>
+      </c>
+      <c r="E33" s="3">
+        <v>375400</v>
+      </c>
+      <c r="F33" s="3">
         <v>354500</v>
       </c>
-      <c r="E33" s="3">
+      <c r="G33" s="3">
         <v>270600</v>
       </c>
-      <c r="F33" s="3">
+      <c r="H33" s="3">
         <v>274700</v>
       </c>
-      <c r="G33" s="3">
+      <c r="I33" s="3">
         <v>326400</v>
       </c>
-      <c r="H33" s="3">
+      <c r="J33" s="3">
         <v>341600</v>
       </c>
-      <c r="I33" s="3">
+      <c r="K33" s="3">
         <v>359400</v>
       </c>
-      <c r="J33" s="3">
+      <c r="L33" s="3">
         <v>197500</v>
       </c>
-      <c r="K33" s="3">
+      <c r="M33" s="3">
         <v>309200</v>
       </c>
-      <c r="L33" s="3">
+      <c r="N33" s="3">
         <v>321400</v>
       </c>
-      <c r="M33" s="3">
+      <c r="O33" s="3">
         <v>350400</v>
       </c>
-      <c r="N33" s="3">
+      <c r="P33" s="3">
         <v>243200</v>
       </c>
-      <c r="O33" s="3">
+      <c r="Q33" s="3">
         <v>304900</v>
       </c>
-      <c r="P33" s="3">
+      <c r="R33" s="3">
         <v>267300</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="S33" s="3">
         <v>251000</v>
       </c>
-      <c r="R33" s="3">
+      <c r="T33" s="3">
         <v>126000</v>
       </c>
-      <c r="S33" s="3">
+      <c r="U33" s="3">
         <v>242800</v>
       </c>
-      <c r="T33" s="3">
+      <c r="V33" s="3">
         <v>165800</v>
       </c>
-      <c r="U33" s="3">
+      <c r="W33" s="3">
         <v>185600</v>
       </c>
-      <c r="V33" s="3">
+      <c r="X33" s="3">
         <v>76600</v>
       </c>
-      <c r="W33" s="3">
+      <c r="Y33" s="3">
         <v>179300</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Z33" s="3">
         <v>177000</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="AA33" s="3">
         <v>213400</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AB33" s="3">
         <v>59100</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AC33" s="3">
         <v>358200</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AD33" s="3">
         <v>204000</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AE33" s="3">
         <v>207700</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AF33" s="3">
         <v>103600</v>
       </c>
-      <c r="AE33" s="3">
+      <c r="AG33" s="3">
         <v>185200</v>
       </c>
-      <c r="AF33" s="3">
+      <c r="AH33" s="3">
         <v>148300</v>
       </c>
-      <c r="AG33" s="3">
+      <c r="AI33" s="3">
         <v>208700</v>
       </c>
-      <c r="AH33" s="3">
+      <c r="AJ33" s="3">
         <v>79900</v>
       </c>
-      <c r="AI33" s="3">
+      <c r="AK33" s="3">
         <v>181400</v>
       </c>
-      <c r="AJ33" s="3">
+      <c r="AL33" s="3">
         <v>106400</v>
       </c>
-      <c r="AK33" s="3">
+      <c r="AM33" s="3">
         <v>106400</v>
       </c>
-      <c r="AL33" s="3">
+      <c r="AN33" s="3">
         <v>73200</v>
       </c>
-      <c r="AM33" s="3">
+      <c r="AO33" s="3">
         <v>105700</v>
       </c>
-      <c r="AN33" s="3">
+      <c r="AP33" s="3">
         <v>73700</v>
       </c>
     </row>
-    <row r="34" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3725,245 +3876,263 @@
       <c r="AN34" s="3">
         <v>0</v>
       </c>
+      <c r="AO34" s="3">
+        <v>0</v>
+      </c>
+      <c r="AP34" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="35" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="35" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>307100</v>
+      </c>
+      <c r="E35" s="3">
+        <v>375400</v>
+      </c>
+      <c r="F35" s="3">
         <v>354500</v>
       </c>
-      <c r="E35" s="3">
+      <c r="G35" s="3">
         <v>270600</v>
       </c>
-      <c r="F35" s="3">
+      <c r="H35" s="3">
         <v>274700</v>
       </c>
-      <c r="G35" s="3">
+      <c r="I35" s="3">
         <v>326400</v>
       </c>
-      <c r="H35" s="3">
+      <c r="J35" s="3">
         <v>341600</v>
       </c>
-      <c r="I35" s="3">
+      <c r="K35" s="3">
         <v>359400</v>
       </c>
-      <c r="J35" s="3">
+      <c r="L35" s="3">
         <v>197500</v>
       </c>
-      <c r="K35" s="3">
+      <c r="M35" s="3">
         <v>309200</v>
       </c>
-      <c r="L35" s="3">
+      <c r="N35" s="3">
         <v>321400</v>
       </c>
-      <c r="M35" s="3">
+      <c r="O35" s="3">
         <v>350400</v>
       </c>
-      <c r="N35" s="3">
+      <c r="P35" s="3">
         <v>243200</v>
       </c>
-      <c r="O35" s="3">
+      <c r="Q35" s="3">
         <v>304900</v>
       </c>
-      <c r="P35" s="3">
+      <c r="R35" s="3">
         <v>267300</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="S35" s="3">
         <v>251000</v>
       </c>
-      <c r="R35" s="3">
+      <c r="T35" s="3">
         <v>126000</v>
       </c>
-      <c r="S35" s="3">
+      <c r="U35" s="3">
         <v>242800</v>
       </c>
-      <c r="T35" s="3">
+      <c r="V35" s="3">
         <v>165800</v>
       </c>
-      <c r="U35" s="3">
+      <c r="W35" s="3">
         <v>185600</v>
       </c>
-      <c r="V35" s="3">
+      <c r="X35" s="3">
         <v>76600</v>
       </c>
-      <c r="W35" s="3">
+      <c r="Y35" s="3">
         <v>179300</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Z35" s="3">
         <v>177000</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="AA35" s="3">
         <v>213400</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AB35" s="3">
         <v>59100</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AC35" s="3">
         <v>358200</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AD35" s="3">
         <v>204000</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AE35" s="3">
         <v>207700</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AF35" s="3">
         <v>103600</v>
       </c>
-      <c r="AE35" s="3">
+      <c r="AG35" s="3">
         <v>185200</v>
       </c>
-      <c r="AF35" s="3">
+      <c r="AH35" s="3">
         <v>148300</v>
       </c>
-      <c r="AG35" s="3">
+      <c r="AI35" s="3">
         <v>208700</v>
       </c>
-      <c r="AH35" s="3">
+      <c r="AJ35" s="3">
         <v>79900</v>
       </c>
-      <c r="AI35" s="3">
+      <c r="AK35" s="3">
         <v>181400</v>
       </c>
-      <c r="AJ35" s="3">
+      <c r="AL35" s="3">
         <v>106400</v>
       </c>
-      <c r="AK35" s="3">
+      <c r="AM35" s="3">
         <v>106400</v>
       </c>
-      <c r="AL35" s="3">
+      <c r="AN35" s="3">
         <v>73200</v>
       </c>
-      <c r="AM35" s="3">
+      <c r="AO35" s="3">
         <v>105700</v>
       </c>
-      <c r="AN35" s="3">
+      <c r="AP35" s="3">
         <v>73700</v>
       </c>
     </row>
-    <row r="37" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:42" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>46112</v>
+      </c>
+      <c r="E38" s="2">
+        <v>46022</v>
+      </c>
+      <c r="F38" s="2">
         <v>45930</v>
       </c>
-      <c r="E38" s="2">
+      <c r="G38" s="2">
         <v>45838</v>
       </c>
-      <c r="F38" s="2">
+      <c r="H38" s="2">
         <v>45747</v>
       </c>
-      <c r="G38" s="2">
+      <c r="I38" s="2">
         <v>45657</v>
       </c>
-      <c r="H38" s="2">
+      <c r="J38" s="2">
         <v>45565</v>
       </c>
-      <c r="I38" s="2">
+      <c r="K38" s="2">
         <v>45473</v>
       </c>
-      <c r="J38" s="2">
+      <c r="L38" s="2">
         <v>45382</v>
       </c>
-      <c r="K38" s="2">
+      <c r="M38" s="2">
         <v>45291</v>
       </c>
-      <c r="L38" s="2">
+      <c r="N38" s="2">
         <v>45199</v>
       </c>
-      <c r="M38" s="2">
+      <c r="O38" s="2">
         <v>45107</v>
       </c>
-      <c r="N38" s="2">
+      <c r="P38" s="2">
         <v>45016</v>
       </c>
-      <c r="O38" s="2">
+      <c r="Q38" s="2">
         <v>44926</v>
       </c>
-      <c r="P38" s="2">
+      <c r="R38" s="2">
         <v>44834</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="S38" s="2">
         <v>44742</v>
       </c>
-      <c r="R38" s="2">
+      <c r="T38" s="2">
         <v>44651</v>
       </c>
-      <c r="S38" s="2">
+      <c r="U38" s="2">
         <v>44561</v>
       </c>
-      <c r="T38" s="2">
+      <c r="V38" s="2">
         <v>44469</v>
       </c>
-      <c r="U38" s="2">
+      <c r="W38" s="2">
         <v>44377</v>
       </c>
-      <c r="V38" s="2">
+      <c r="X38" s="2">
         <v>44286</v>
       </c>
-      <c r="W38" s="2">
+      <c r="Y38" s="2">
         <v>44196</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Z38" s="2">
         <v>44104</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="AA38" s="2">
         <v>44012</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AB38" s="2">
         <v>43921</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AC38" s="2">
         <v>43830</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AD38" s="2">
         <v>43738</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AE38" s="2">
         <v>43646</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AF38" s="2">
         <v>43555</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AG38" s="2">
         <v>43465</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AH38" s="2">
         <v>43373</v>
       </c>
-      <c r="AG38" s="2">
+      <c r="AI38" s="2">
         <v>43281</v>
       </c>
-      <c r="AH38" s="2">
+      <c r="AJ38" s="2">
         <v>43190</v>
       </c>
-      <c r="AI38" s="2">
+      <c r="AK38" s="2">
         <v>43100</v>
       </c>
-      <c r="AJ38" s="2">
+      <c r="AL38" s="2">
         <v>43008</v>
       </c>
-      <c r="AK38" s="2">
+      <c r="AM38" s="2">
         <v>42916</v>
       </c>
-      <c r="AL38" s="2">
+      <c r="AN38" s="2">
         <v>42825</v>
       </c>
-      <c r="AM38" s="2">
+      <c r="AO38" s="2">
         <v>42735</v>
       </c>
-      <c r="AN38" s="2">
+      <c r="AP38" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="39" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -4004,8 +4173,10 @@
       <c r="AL39" s="3"/>
       <c r="AM39" s="3"/>
       <c r="AN39" s="3"/>
+      <c r="AO39" s="3"/>
+      <c r="AP39" s="3"/>
     </row>
-    <row r="40" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="40" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -4046,1052 +4217,1108 @@
       <c r="AL40" s="3"/>
       <c r="AM40" s="3"/>
       <c r="AN40" s="3"/>
+      <c r="AO40" s="3"/>
+      <c r="AP40" s="3"/>
     </row>
-    <row r="41" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="41" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>1653800</v>
+      </c>
+      <c r="E41" s="3">
+        <v>1431400</v>
+      </c>
+      <c r="F41" s="3">
         <v>1318900</v>
       </c>
-      <c r="E41" s="3">
+      <c r="G41" s="3">
         <v>1855400</v>
       </c>
-      <c r="F41" s="3">
+      <c r="H41" s="3">
         <v>1711300</v>
       </c>
-      <c r="G41" s="3">
+      <c r="I41" s="3">
         <v>1844800</v>
       </c>
-      <c r="H41" s="3">
+      <c r="J41" s="3">
         <v>1668400</v>
       </c>
-      <c r="I41" s="3">
+      <c r="K41" s="3">
         <v>1450700</v>
       </c>
-      <c r="J41" s="3">
+      <c r="L41" s="3">
         <v>1742800</v>
       </c>
-      <c r="K41" s="3">
+      <c r="M41" s="3">
         <v>1739400</v>
       </c>
-      <c r="L41" s="3">
+      <c r="N41" s="3">
         <v>1272500</v>
       </c>
-      <c r="M41" s="3">
+      <c r="O41" s="3">
         <v>1073000</v>
       </c>
-      <c r="N41" s="3">
+      <c r="P41" s="3">
         <v>1391100</v>
       </c>
-      <c r="O41" s="3">
+      <c r="Q41" s="3">
         <v>1648400</v>
       </c>
-      <c r="P41" s="3">
+      <c r="R41" s="3">
         <v>2016100</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="S41" s="3">
         <v>1380200</v>
       </c>
-      <c r="R41" s="3">
+      <c r="T41" s="3">
         <v>1376400</v>
       </c>
-      <c r="S41" s="3">
+      <c r="U41" s="3">
         <v>1339400</v>
       </c>
-      <c r="T41" s="3">
+      <c r="V41" s="3">
         <v>1472400</v>
       </c>
-      <c r="U41" s="3">
+      <c r="W41" s="3">
         <v>1737600</v>
       </c>
-      <c r="V41" s="3">
+      <c r="X41" s="3">
         <v>1590500</v>
       </c>
-      <c r="W41" s="3">
+      <c r="Y41" s="3">
         <v>1978400</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Z41" s="3">
         <v>2418000</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="AA41" s="3">
         <v>775400</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AB41" s="3">
         <v>792000</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AC41" s="3">
         <v>811500</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AD41" s="3">
         <v>789200</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AE41" s="3">
         <v>1086500</v>
       </c>
-      <c r="AD41" s="3">
+      <c r="AF41" s="3">
         <v>926800</v>
       </c>
-      <c r="AE41" s="3">
+      <c r="AG41" s="3">
         <v>671300</v>
       </c>
-      <c r="AF41" s="3">
+      <c r="AH41" s="3">
         <v>877700</v>
       </c>
-      <c r="AG41" s="3">
+      <c r="AI41" s="3">
         <v>848700</v>
       </c>
-      <c r="AH41" s="3">
+      <c r="AJ41" s="3">
         <v>486000</v>
       </c>
-      <c r="AI41" s="3">
+      <c r="AK41" s="3">
         <v>805100</v>
       </c>
-      <c r="AJ41" s="3">
+      <c r="AL41" s="3">
         <v>768800</v>
       </c>
-      <c r="AK41" s="3">
+      <c r="AM41" s="3">
         <v>848000</v>
       </c>
-      <c r="AL41" s="3">
+      <c r="AN41" s="3">
         <v>920400</v>
       </c>
-      <c r="AM41" s="3">
+      <c r="AO41" s="3">
         <v>1641600</v>
       </c>
-      <c r="AN41" s="3">
+      <c r="AP41" s="3">
         <v>287600</v>
       </c>
     </row>
-    <row r="42" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>2766200</v>
+      </c>
+      <c r="E42" s="3">
+        <v>2260400</v>
+      </c>
+      <c r="F42" s="3">
         <v>2233200</v>
       </c>
-      <c r="E42" s="3">
+      <c r="G42" s="3">
         <v>1847100</v>
       </c>
-      <c r="F42" s="3">
+      <c r="H42" s="3">
         <v>1461300</v>
       </c>
-      <c r="G42" s="3">
+      <c r="I42" s="3">
         <v>1237300</v>
       </c>
-      <c r="H42" s="3">
+      <c r="J42" s="3">
         <v>1598600</v>
       </c>
-      <c r="I42" s="3">
+      <c r="K42" s="3">
         <v>1362200</v>
       </c>
-      <c r="J42" s="3">
+      <c r="L42" s="3">
         <v>974800</v>
       </c>
-      <c r="K42" s="3">
+      <c r="M42" s="3">
         <v>1066000</v>
       </c>
-      <c r="L42" s="3">
+      <c r="N42" s="3">
         <v>1048900</v>
       </c>
-      <c r="M42" s="3">
+      <c r="O42" s="3">
         <v>1097100</v>
       </c>
-      <c r="N42" s="3">
+      <c r="P42" s="3">
         <v>1292500</v>
       </c>
-      <c r="O42" s="3">
+      <c r="Q42" s="3">
         <v>811100</v>
       </c>
-      <c r="P42" s="3">
+      <c r="R42" s="3">
         <v>960600</v>
       </c>
-      <c r="Q42" s="3">
+      <c r="S42" s="3">
         <v>724400</v>
       </c>
-      <c r="R42" s="3">
+      <c r="T42" s="3">
         <v>556400</v>
       </c>
-      <c r="S42" s="3">
+      <c r="U42" s="3">
         <v>392000</v>
       </c>
-      <c r="T42" s="3">
+      <c r="V42" s="3">
         <v>336100</v>
       </c>
-      <c r="U42" s="3">
+      <c r="W42" s="3">
         <v>450800</v>
       </c>
-      <c r="V42" s="3">
+      <c r="X42" s="3">
         <v>794000</v>
       </c>
-      <c r="W42" s="3">
+      <c r="Y42" s="3">
         <v>513700</v>
       </c>
-      <c r="X42" s="3">
+      <c r="Z42" s="3">
         <v>708000</v>
       </c>
-      <c r="Y42" s="3">
+      <c r="AA42" s="3">
         <v>1243400</v>
       </c>
-      <c r="Z42" s="3">
+      <c r="AB42" s="3">
         <v>1596100</v>
       </c>
-      <c r="AA42" s="3">
+      <c r="AC42" s="3">
         <v>1711200</v>
       </c>
-      <c r="AB42" s="3">
+      <c r="AD42" s="3">
         <v>1763500</v>
       </c>
-      <c r="AC42" s="3">
+      <c r="AE42" s="3">
         <v>1414900</v>
       </c>
-      <c r="AD42" s="3">
+      <c r="AF42" s="3">
         <v>1717000</v>
       </c>
-      <c r="AE42" s="3">
+      <c r="AG42" s="3">
         <v>1975100</v>
       </c>
-      <c r="AF42" s="3">
+      <c r="AH42" s="3">
         <v>1664900</v>
       </c>
-      <c r="AG42" s="3">
+      <c r="AI42" s="3">
         <v>1343800</v>
       </c>
-      <c r="AH42" s="3">
+      <c r="AJ42" s="3">
         <v>795600</v>
       </c>
-      <c r="AI42" s="3">
+      <c r="AK42" s="3">
         <v>775400</v>
       </c>
-      <c r="AJ42" s="3">
+      <c r="AL42" s="3">
         <v>819600</v>
       </c>
-      <c r="AK42" s="3">
+      <c r="AM42" s="3">
         <v>769700</v>
       </c>
-      <c r="AL42" s="3">
+      <c r="AN42" s="3">
         <v>700700</v>
       </c>
-      <c r="AM42" s="3" t="s">
+      <c r="AO42" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AN42" s="3" t="s">
+      <c r="AP42" s="3" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="43" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>334100</v>
+      </c>
+      <c r="E43" s="3">
+        <v>391400</v>
+      </c>
+      <c r="F43" s="3">
         <v>279300</v>
       </c>
-      <c r="E43" s="3">
+      <c r="G43" s="3">
         <v>330400</v>
       </c>
-      <c r="F43" s="3">
+      <c r="H43" s="3">
         <v>288400</v>
       </c>
-      <c r="G43" s="3">
+      <c r="I43" s="3">
         <v>438300</v>
       </c>
-      <c r="H43" s="3">
+      <c r="J43" s="3">
         <v>307200</v>
       </c>
-      <c r="I43" s="3">
+      <c r="K43" s="3">
         <v>265400</v>
       </c>
-      <c r="J43" s="3">
+      <c r="L43" s="3">
         <v>241100</v>
       </c>
-      <c r="K43" s="3">
+      <c r="M43" s="3">
         <v>280800</v>
       </c>
-      <c r="L43" s="3">
+      <c r="N43" s="3">
         <v>329600</v>
       </c>
-      <c r="M43" s="3">
+      <c r="O43" s="3">
         <v>319700</v>
       </c>
-      <c r="N43" s="3">
+      <c r="P43" s="3">
         <v>266800</v>
       </c>
-      <c r="O43" s="3">
+      <c r="Q43" s="3">
         <v>293900</v>
       </c>
-      <c r="P43" s="3">
+      <c r="R43" s="3">
         <v>265800</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="S43" s="3">
         <v>267700</v>
       </c>
-      <c r="R43" s="3">
+      <c r="T43" s="3">
         <v>264100</v>
       </c>
-      <c r="S43" s="3">
+      <c r="U43" s="3">
         <v>300200</v>
       </c>
-      <c r="T43" s="3">
+      <c r="V43" s="3">
         <v>260500</v>
       </c>
-      <c r="U43" s="3">
+      <c r="W43" s="3">
         <v>262000</v>
       </c>
-      <c r="V43" s="3">
+      <c r="X43" s="3">
         <v>187900</v>
       </c>
-      <c r="W43" s="3">
+      <c r="Y43" s="3">
         <v>182600</v>
       </c>
-      <c r="X43" s="3">
+      <c r="Z43" s="3">
         <v>252900</v>
       </c>
-      <c r="Y43" s="3">
+      <c r="AA43" s="3">
         <v>174200</v>
       </c>
-      <c r="Z43" s="3">
+      <c r="AB43" s="3">
         <v>210600</v>
       </c>
-      <c r="AA43" s="3">
+      <c r="AC43" s="3">
         <v>194200</v>
       </c>
-      <c r="AB43" s="3">
+      <c r="AD43" s="3">
         <v>172000</v>
       </c>
-      <c r="AC43" s="3">
+      <c r="AE43" s="3">
         <v>177300</v>
       </c>
-      <c r="AD43" s="3">
+      <c r="AF43" s="3">
         <v>171100</v>
       </c>
-      <c r="AE43" s="3">
+      <c r="AG43" s="3">
         <v>162900</v>
       </c>
-      <c r="AF43" s="3">
+      <c r="AH43" s="3">
         <v>120200</v>
       </c>
-      <c r="AG43" s="3">
+      <c r="AI43" s="3">
         <v>209200</v>
       </c>
-      <c r="AH43" s="3">
+      <c r="AJ43" s="3">
         <v>69200</v>
       </c>
-      <c r="AI43" s="3">
+      <c r="AK43" s="3">
         <v>53700</v>
       </c>
-      <c r="AJ43" s="3">
+      <c r="AL43" s="3">
         <v>31000</v>
       </c>
-      <c r="AK43" s="3">
+      <c r="AM43" s="3">
         <v>28800</v>
       </c>
-      <c r="AL43" s="3">
+      <c r="AN43" s="3">
         <v>25200</v>
       </c>
-      <c r="AM43" s="3">
+      <c r="AO43" s="3">
         <v>29600</v>
       </c>
-      <c r="AN43" s="3">
+      <c r="AP43" s="3">
         <v>17800</v>
       </c>
     </row>
-    <row r="44" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>5700</v>
+      </c>
+      <c r="E44" s="3">
+        <v>5800</v>
+      </c>
+      <c r="F44" s="3">
         <v>6800</v>
       </c>
-      <c r="E44" s="3">
+      <c r="G44" s="3">
         <v>6700</v>
       </c>
-      <c r="F44" s="3">
+      <c r="H44" s="3">
         <v>4900</v>
       </c>
-      <c r="G44" s="3">
+      <c r="I44" s="3">
         <v>5300</v>
       </c>
-      <c r="H44" s="3">
+      <c r="J44" s="3">
         <v>3900</v>
       </c>
-      <c r="I44" s="3">
+      <c r="K44" s="3">
         <v>3900</v>
       </c>
-      <c r="J44" s="3">
+      <c r="L44" s="3">
         <v>5700</v>
       </c>
-      <c r="K44" s="3">
+      <c r="M44" s="3">
         <v>4000</v>
       </c>
-      <c r="L44" s="3">
+      <c r="N44" s="3">
         <v>3800</v>
       </c>
-      <c r="M44" s="3">
+      <c r="O44" s="3">
         <v>3700</v>
       </c>
-      <c r="N44" s="3">
+      <c r="P44" s="3">
         <v>4200</v>
       </c>
-      <c r="O44" s="3">
+      <c r="Q44" s="3">
         <v>5700</v>
       </c>
-      <c r="P44" s="3">
+      <c r="R44" s="3">
         <v>8900</v>
       </c>
-      <c r="Q44" s="3">
+      <c r="S44" s="3">
         <v>4000</v>
       </c>
-      <c r="R44" s="3">
+      <c r="T44" s="3">
         <v>8200</v>
       </c>
-      <c r="S44" s="3">
+      <c r="U44" s="3">
         <v>11400</v>
       </c>
-      <c r="T44" s="3">
+      <c r="V44" s="3">
         <v>7100</v>
       </c>
-      <c r="U44" s="3">
+      <c r="W44" s="3">
         <v>5700</v>
-      </c>
-      <c r="V44" s="3">
-        <v>7400</v>
-      </c>
-      <c r="W44" s="3">
-        <v>7400</v>
       </c>
       <c r="X44" s="3">
         <v>7400</v>
       </c>
       <c r="Y44" s="3">
+        <v>7400</v>
+      </c>
+      <c r="Z44" s="3">
+        <v>7400</v>
+      </c>
+      <c r="AA44" s="3">
         <v>9500</v>
       </c>
-      <c r="Z44" s="3">
+      <c r="AB44" s="3">
         <v>8900</v>
       </c>
-      <c r="AA44" s="3">
+      <c r="AC44" s="3">
         <v>6800</v>
       </c>
-      <c r="AB44" s="3">
+      <c r="AD44" s="3">
         <v>5600</v>
       </c>
-      <c r="AC44" s="3">
+      <c r="AE44" s="3">
         <v>5400</v>
       </c>
-      <c r="AD44" s="3">
+      <c r="AF44" s="3">
         <v>4700</v>
       </c>
-      <c r="AE44" s="3">
+      <c r="AG44" s="3">
         <v>6400</v>
       </c>
-      <c r="AF44" s="3">
+      <c r="AH44" s="3">
         <v>5200</v>
       </c>
-      <c r="AG44" s="3">
+      <c r="AI44" s="3">
         <v>5600</v>
       </c>
-      <c r="AH44" s="3">
+      <c r="AJ44" s="3">
         <v>4400</v>
       </c>
-      <c r="AI44" s="3">
+      <c r="AK44" s="3">
         <v>5100</v>
       </c>
-      <c r="AJ44" s="3">
+      <c r="AL44" s="3">
         <v>4200</v>
       </c>
-      <c r="AK44" s="3">
+      <c r="AM44" s="3">
         <v>4300</v>
       </c>
-      <c r="AL44" s="3">
+      <c r="AN44" s="3">
         <v>4600</v>
       </c>
-      <c r="AM44" s="3">
+      <c r="AO44" s="3">
         <v>4900</v>
       </c>
-      <c r="AN44" s="3">
+      <c r="AP44" s="3">
         <v>4100</v>
       </c>
     </row>
-    <row r="45" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>869100</v>
+      </c>
+      <c r="E45" s="3">
+        <v>750600</v>
+      </c>
+      <c r="F45" s="3">
         <v>817100</v>
       </c>
-      <c r="E45" s="3">
+      <c r="G45" s="3">
         <v>776000</v>
       </c>
-      <c r="F45" s="3">
+      <c r="H45" s="3">
         <v>742900</v>
       </c>
-      <c r="G45" s="3">
+      <c r="I45" s="3">
         <v>614900</v>
       </c>
-      <c r="H45" s="3">
+      <c r="J45" s="3">
         <v>716400</v>
       </c>
-      <c r="I45" s="3">
+      <c r="K45" s="3">
         <v>759300</v>
       </c>
-      <c r="J45" s="3">
+      <c r="L45" s="3">
         <v>701200</v>
       </c>
-      <c r="K45" s="3">
+      <c r="M45" s="3">
         <v>599700</v>
       </c>
-      <c r="L45" s="3">
+      <c r="N45" s="3">
         <v>625500</v>
       </c>
-      <c r="M45" s="3">
+      <c r="O45" s="3">
         <v>606800</v>
       </c>
-      <c r="N45" s="3">
+      <c r="P45" s="3">
         <v>620000</v>
       </c>
-      <c r="O45" s="3">
+      <c r="Q45" s="3">
         <v>691300</v>
       </c>
-      <c r="P45" s="3">
+      <c r="R45" s="3">
         <v>584100</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="S45" s="3">
         <v>567700</v>
       </c>
-      <c r="R45" s="3">
+      <c r="T45" s="3">
         <v>580200</v>
       </c>
-      <c r="S45" s="3">
+      <c r="U45" s="3">
         <v>528800</v>
       </c>
-      <c r="T45" s="3">
+      <c r="V45" s="3">
         <v>552300</v>
       </c>
-      <c r="U45" s="3">
+      <c r="W45" s="3">
         <v>501800</v>
       </c>
-      <c r="V45" s="3">
+      <c r="X45" s="3">
         <v>511200</v>
       </c>
-      <c r="W45" s="3">
+      <c r="Y45" s="3">
         <v>425500</v>
       </c>
-      <c r="X45" s="3">
+      <c r="Z45" s="3">
         <v>433900</v>
       </c>
-      <c r="Y45" s="3">
+      <c r="AA45" s="3">
         <v>423200</v>
       </c>
-      <c r="Z45" s="3">
+      <c r="AB45" s="3">
         <v>378400</v>
       </c>
-      <c r="AA45" s="3">
+      <c r="AC45" s="3">
         <v>371100</v>
       </c>
-      <c r="AB45" s="3">
+      <c r="AD45" s="3">
         <v>313400</v>
       </c>
-      <c r="AC45" s="3">
+      <c r="AE45" s="3">
         <v>374900</v>
       </c>
-      <c r="AD45" s="3">
+      <c r="AF45" s="3">
         <v>264700</v>
       </c>
-      <c r="AE45" s="3">
+      <c r="AG45" s="3">
         <v>268100</v>
       </c>
-      <c r="AF45" s="3">
+      <c r="AH45" s="3">
         <v>213400</v>
       </c>
-      <c r="AG45" s="3">
+      <c r="AI45" s="3">
         <v>191900</v>
       </c>
-      <c r="AH45" s="3">
+      <c r="AJ45" s="3">
         <v>168000</v>
       </c>
-      <c r="AI45" s="3">
+      <c r="AK45" s="3">
         <v>197700</v>
       </c>
-      <c r="AJ45" s="3">
+      <c r="AL45" s="3">
         <v>172000</v>
       </c>
-      <c r="AK45" s="3">
+      <c r="AM45" s="3">
         <v>168000</v>
       </c>
-      <c r="AL45" s="3">
+      <c r="AN45" s="3">
         <v>226600</v>
       </c>
-      <c r="AM45" s="3">
+      <c r="AO45" s="3">
         <v>241600</v>
       </c>
-      <c r="AN45" s="3">
+      <c r="AP45" s="3">
         <v>149500</v>
       </c>
     </row>
-    <row r="46" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>5633000</v>
+      </c>
+      <c r="E46" s="3">
+        <v>4856000</v>
+      </c>
+      <c r="F46" s="3">
         <v>4658500</v>
       </c>
-      <c r="E46" s="3">
+      <c r="G46" s="3">
         <v>4818800</v>
       </c>
-      <c r="F46" s="3">
+      <c r="H46" s="3">
         <v>4212900</v>
       </c>
-      <c r="G46" s="3">
+      <c r="I46" s="3">
         <v>4158600</v>
       </c>
-      <c r="H46" s="3">
+      <c r="J46" s="3">
         <v>4299200</v>
       </c>
-      <c r="I46" s="3">
+      <c r="K46" s="3">
         <v>3844500</v>
       </c>
-      <c r="J46" s="3">
+      <c r="L46" s="3">
         <v>3703300</v>
       </c>
-      <c r="K46" s="3">
+      <c r="M46" s="3">
         <v>3801100</v>
       </c>
-      <c r="L46" s="3">
+      <c r="N46" s="3">
         <v>3388900</v>
       </c>
-      <c r="M46" s="3">
+      <c r="O46" s="3">
         <v>3217700</v>
       </c>
-      <c r="N46" s="3">
+      <c r="P46" s="3">
         <v>3680800</v>
       </c>
-      <c r="O46" s="3">
+      <c r="Q46" s="3">
         <v>3450500</v>
       </c>
-      <c r="P46" s="3">
+      <c r="R46" s="3">
         <v>3835500</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="S46" s="3">
         <v>2944100</v>
       </c>
-      <c r="R46" s="3">
+      <c r="T46" s="3">
         <v>2785400</v>
       </c>
-      <c r="S46" s="3">
+      <c r="U46" s="3">
         <v>2571900</v>
       </c>
-      <c r="T46" s="3">
+      <c r="V46" s="3">
         <v>2628500</v>
       </c>
-      <c r="U46" s="3">
+      <c r="W46" s="3">
         <v>2957900</v>
       </c>
-      <c r="V46" s="3">
+      <c r="X46" s="3">
         <v>3091000</v>
       </c>
-      <c r="W46" s="3">
+      <c r="Y46" s="3">
         <v>3107600</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Z46" s="3">
         <v>3820200</v>
       </c>
-      <c r="Y46" s="3">
+      <c r="AA46" s="3">
         <v>2625600</v>
       </c>
-      <c r="Z46" s="3">
+      <c r="AB46" s="3">
         <v>2986000</v>
       </c>
-      <c r="AA46" s="3">
+      <c r="AC46" s="3">
         <v>3094700</v>
       </c>
-      <c r="AB46" s="3">
+      <c r="AD46" s="3">
         <v>3043800</v>
       </c>
-      <c r="AC46" s="3">
+      <c r="AE46" s="3">
         <v>3059000</v>
       </c>
-      <c r="AD46" s="3">
+      <c r="AF46" s="3">
         <v>3084200</v>
       </c>
-      <c r="AE46" s="3">
+      <c r="AG46" s="3">
         <v>3083800</v>
       </c>
-      <c r="AF46" s="3">
+      <c r="AH46" s="3">
         <v>2881400</v>
       </c>
-      <c r="AG46" s="3">
+      <c r="AI46" s="3">
         <v>2599300</v>
       </c>
-      <c r="AH46" s="3">
+      <c r="AJ46" s="3">
         <v>1523100</v>
       </c>
-      <c r="AI46" s="3">
+      <c r="AK46" s="3">
         <v>1837000</v>
       </c>
-      <c r="AJ46" s="3">
+      <c r="AL46" s="3">
         <v>1795600</v>
       </c>
-      <c r="AK46" s="3">
+      <c r="AM46" s="3">
         <v>1818900</v>
       </c>
-      <c r="AL46" s="3">
+      <c r="AN46" s="3">
         <v>1877500</v>
       </c>
-      <c r="AM46" s="3">
+      <c r="AO46" s="3">
         <v>1917600</v>
       </c>
-      <c r="AN46" s="3">
+      <c r="AP46" s="3">
         <v>459000</v>
       </c>
     </row>
-    <row r="47" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>1226000</v>
+      </c>
+      <c r="E47" s="3">
+        <v>1025500</v>
+      </c>
+      <c r="F47" s="3">
         <v>1094400</v>
       </c>
-      <c r="E47" s="3">
+      <c r="G47" s="3">
         <v>1527800</v>
       </c>
-      <c r="F47" s="3">
+      <c r="H47" s="3">
         <v>1847800</v>
       </c>
-      <c r="G47" s="3">
+      <c r="I47" s="3">
         <v>1902800</v>
       </c>
-      <c r="H47" s="3">
+      <c r="J47" s="3">
         <v>2224700</v>
       </c>
-      <c r="I47" s="3">
+      <c r="K47" s="3">
         <v>2219600</v>
       </c>
-      <c r="J47" s="3">
+      <c r="L47" s="3">
         <v>2270700</v>
       </c>
-      <c r="K47" s="3">
+      <c r="M47" s="3">
         <v>2203700</v>
       </c>
-      <c r="L47" s="3">
+      <c r="N47" s="3">
         <v>2439100</v>
       </c>
-      <c r="M47" s="3">
+      <c r="O47" s="3">
         <v>2055100</v>
       </c>
-      <c r="N47" s="3">
+      <c r="P47" s="3">
         <v>1759700</v>
       </c>
-      <c r="O47" s="3">
+      <c r="Q47" s="3">
         <v>1853300</v>
       </c>
-      <c r="P47" s="3">
+      <c r="R47" s="3">
         <v>1337100</v>
       </c>
-      <c r="Q47" s="3">
+      <c r="S47" s="3">
         <v>1167900</v>
       </c>
-      <c r="R47" s="3">
+      <c r="T47" s="3">
         <v>1019900</v>
       </c>
-      <c r="S47" s="3">
+      <c r="U47" s="3">
         <v>960200</v>
       </c>
-      <c r="T47" s="3">
+      <c r="V47" s="3">
         <v>996500</v>
       </c>
-      <c r="U47" s="3">
+      <c r="W47" s="3">
         <v>1076500</v>
       </c>
-      <c r="V47" s="3">
+      <c r="X47" s="3">
         <v>1100900</v>
       </c>
-      <c r="W47" s="3">
+      <c r="Y47" s="3">
         <v>1049100</v>
       </c>
-      <c r="X47" s="3">
+      <c r="Z47" s="3">
         <v>898800</v>
       </c>
-      <c r="Y47" s="3">
+      <c r="AA47" s="3">
         <v>876900</v>
       </c>
-      <c r="Z47" s="3">
+      <c r="AB47" s="3">
         <v>771500</v>
       </c>
-      <c r="AA47" s="3">
+      <c r="AC47" s="3">
         <v>709100</v>
       </c>
-      <c r="AB47" s="3">
+      <c r="AD47" s="3">
         <v>347600</v>
       </c>
-      <c r="AC47" s="3">
+      <c r="AE47" s="3">
         <v>336200</v>
       </c>
-      <c r="AD47" s="3">
+      <c r="AF47" s="3">
         <v>332500</v>
       </c>
-      <c r="AE47" s="3">
+      <c r="AG47" s="3">
         <v>320600</v>
       </c>
-      <c r="AF47" s="3">
+      <c r="AH47" s="3">
         <v>239300</v>
       </c>
-      <c r="AG47" s="3">
+      <c r="AI47" s="3">
         <v>215800</v>
       </c>
-      <c r="AH47" s="3">
+      <c r="AJ47" s="3">
         <v>86400</v>
       </c>
-      <c r="AI47" s="3">
+      <c r="AK47" s="3">
         <v>90600</v>
       </c>
-      <c r="AJ47" s="3">
+      <c r="AL47" s="3">
         <v>82600</v>
       </c>
-      <c r="AK47" s="3">
+      <c r="AM47" s="3">
         <v>78200</v>
       </c>
-      <c r="AL47" s="3">
+      <c r="AN47" s="3">
         <v>76400</v>
       </c>
-      <c r="AM47" s="3">
+      <c r="AO47" s="3">
         <v>78100</v>
       </c>
-      <c r="AN47" s="3">
+      <c r="AP47" s="3">
         <v>69300</v>
       </c>
     </row>
-    <row r="48" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>5301300</v>
+      </c>
+      <c r="E48" s="3">
+        <v>5122900</v>
+      </c>
+      <c r="F48" s="3">
         <v>5034900</v>
       </c>
-      <c r="E48" s="3">
+      <c r="G48" s="3">
         <v>4935000</v>
       </c>
-      <c r="F48" s="3">
+      <c r="H48" s="3">
         <v>4834200</v>
       </c>
-      <c r="G48" s="3">
+      <c r="I48" s="3">
         <v>4724100</v>
       </c>
-      <c r="H48" s="3">
+      <c r="J48" s="3">
         <v>4870600</v>
       </c>
-      <c r="I48" s="3">
+      <c r="K48" s="3">
         <v>4637600</v>
       </c>
-      <c r="J48" s="3">
+      <c r="L48" s="3">
         <v>4645500</v>
       </c>
-      <c r="K48" s="3">
+      <c r="M48" s="3">
         <v>4633200</v>
       </c>
-      <c r="L48" s="3">
+      <c r="N48" s="3">
         <v>4456300</v>
       </c>
-      <c r="M48" s="3">
+      <c r="O48" s="3">
         <v>4371400</v>
       </c>
-      <c r="N48" s="3">
+      <c r="P48" s="3">
         <v>4453700</v>
       </c>
-      <c r="O48" s="3">
+      <c r="Q48" s="3">
         <v>4176100</v>
       </c>
-      <c r="P48" s="3">
+      <c r="R48" s="3">
         <v>3977700</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="S48" s="3">
         <v>3845100</v>
       </c>
-      <c r="R48" s="3">
+      <c r="T48" s="3">
         <v>3707100</v>
       </c>
-      <c r="S48" s="3">
+      <c r="U48" s="3">
         <v>3558500</v>
       </c>
-      <c r="T48" s="3">
+      <c r="V48" s="3">
         <v>3435000</v>
       </c>
-      <c r="U48" s="3">
+      <c r="W48" s="3">
         <v>3191700</v>
       </c>
-      <c r="V48" s="3">
+      <c r="X48" s="3">
         <v>2895100</v>
       </c>
-      <c r="W48" s="3">
+      <c r="Y48" s="3">
         <v>2706200</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Z48" s="3">
         <v>2552500</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="AA48" s="3">
         <v>2274600</v>
       </c>
-      <c r="Z48" s="3">
+      <c r="AB48" s="3">
         <v>2237200</v>
       </c>
-      <c r="AA48" s="3">
+      <c r="AC48" s="3">
         <v>2059100</v>
       </c>
-      <c r="AB48" s="3">
+      <c r="AD48" s="3">
         <v>1814900</v>
       </c>
-      <c r="AC48" s="3">
+      <c r="AE48" s="3">
         <v>1577900</v>
       </c>
-      <c r="AD48" s="3">
+      <c r="AF48" s="3">
         <v>1532300</v>
       </c>
-      <c r="AE48" s="3">
+      <c r="AG48" s="3">
         <v>1312300</v>
       </c>
-      <c r="AF48" s="3">
+      <c r="AH48" s="3">
         <v>1117100</v>
       </c>
-      <c r="AG48" s="3">
+      <c r="AI48" s="3">
         <v>1015500</v>
       </c>
-      <c r="AH48" s="3">
+      <c r="AJ48" s="3">
         <v>983700</v>
       </c>
-      <c r="AI48" s="3">
+      <c r="AK48" s="3">
         <v>960700</v>
       </c>
-      <c r="AJ48" s="3">
+      <c r="AL48" s="3">
         <v>866600</v>
       </c>
-      <c r="AK48" s="3">
+      <c r="AM48" s="3">
         <v>765200</v>
       </c>
-      <c r="AL48" s="3">
+      <c r="AN48" s="3">
         <v>668800</v>
       </c>
-      <c r="AM48" s="3">
+      <c r="AO48" s="3">
         <v>591300</v>
       </c>
-      <c r="AN48" s="3">
+      <c r="AP48" s="3">
         <v>479700</v>
       </c>
     </row>
-    <row r="49" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>1606100</v>
+      </c>
+      <c r="E49" s="3">
+        <v>1568700</v>
+      </c>
+      <c r="F49" s="3">
         <v>1467400</v>
       </c>
-      <c r="E49" s="3">
+      <c r="G49" s="3">
         <v>1457000</v>
       </c>
-      <c r="F49" s="3">
+      <c r="H49" s="3">
         <v>1454800</v>
       </c>
-      <c r="G49" s="3">
+      <c r="I49" s="3">
         <v>1428800</v>
       </c>
-      <c r="H49" s="3">
+      <c r="J49" s="3">
         <v>1476600</v>
       </c>
-      <c r="I49" s="3">
+      <c r="K49" s="3">
         <v>1381900</v>
       </c>
-      <c r="J49" s="3">
+      <c r="L49" s="3">
         <v>1376500</v>
       </c>
-      <c r="K49" s="3">
+      <c r="M49" s="3">
         <v>1396400</v>
       </c>
-      <c r="L49" s="3">
+      <c r="N49" s="3">
         <v>1358000</v>
       </c>
-      <c r="M49" s="3">
+      <c r="O49" s="3">
         <v>1370700</v>
       </c>
-      <c r="N49" s="3">
+      <c r="P49" s="3">
         <v>1446200</v>
       </c>
-      <c r="O49" s="3">
+      <c r="Q49" s="3">
         <v>1369500</v>
       </c>
-      <c r="P49" s="3">
+      <c r="R49" s="3">
         <v>1331500</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="S49" s="3">
         <v>1350200</v>
       </c>
-      <c r="R49" s="3">
+      <c r="T49" s="3">
         <v>1338000</v>
       </c>
-      <c r="S49" s="3">
+      <c r="U49" s="3">
         <v>1324400</v>
       </c>
-      <c r="T49" s="3">
+      <c r="V49" s="3">
         <v>1333000</v>
       </c>
-      <c r="U49" s="3">
+      <c r="W49" s="3">
         <v>1321600</v>
       </c>
-      <c r="V49" s="3">
+      <c r="X49" s="3">
         <v>1295800</v>
       </c>
-      <c r="W49" s="3">
+      <c r="Y49" s="3">
         <v>1203300</v>
       </c>
-      <c r="X49" s="3">
+      <c r="Z49" s="3">
         <v>1236400</v>
       </c>
-      <c r="Y49" s="3">
+      <c r="AA49" s="3">
         <v>1195900</v>
       </c>
-      <c r="Z49" s="3">
+      <c r="AB49" s="3">
         <v>1154200</v>
       </c>
-      <c r="AA49" s="3">
+      <c r="AC49" s="3">
         <v>1046800</v>
       </c>
-      <c r="AB49" s="3">
+      <c r="AD49" s="3">
         <v>1029800</v>
       </c>
-      <c r="AC49" s="3">
+      <c r="AE49" s="3">
         <v>987300</v>
       </c>
-      <c r="AD49" s="3">
+      <c r="AF49" s="3">
         <v>983500</v>
       </c>
-      <c r="AE49" s="3">
+      <c r="AG49" s="3">
         <v>909900</v>
       </c>
-      <c r="AF49" s="3">
+      <c r="AH49" s="3">
         <v>873300</v>
       </c>
-      <c r="AG49" s="3">
+      <c r="AI49" s="3">
         <v>861700</v>
       </c>
-      <c r="AH49" s="3">
+      <c r="AJ49" s="3">
         <v>880200</v>
       </c>
-      <c r="AI49" s="3">
+      <c r="AK49" s="3">
         <v>876300</v>
       </c>
-      <c r="AJ49" s="3">
+      <c r="AL49" s="3">
         <v>841400</v>
       </c>
-      <c r="AK49" s="3">
+      <c r="AM49" s="3">
         <v>835000</v>
       </c>
-      <c r="AL49" s="3">
+      <c r="AN49" s="3">
         <v>815900</v>
       </c>
-      <c r="AM49" s="3">
+      <c r="AO49" s="3">
         <v>794000</v>
       </c>
-      <c r="AN49" s="3">
+      <c r="AP49" s="3">
         <v>777200</v>
       </c>
     </row>
-    <row r="50" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -5206,8 +5433,14 @@
       <c r="AN50" s="3">
         <v>0</v>
       </c>
+      <c r="AO50" s="3">
+        <v>0</v>
+      </c>
+      <c r="AP50" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="51" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="51" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -5322,124 +5555,136 @@
       <c r="AN51" s="3">
         <v>0</v>
       </c>
+      <c r="AO51" s="3">
+        <v>0</v>
+      </c>
+      <c r="AP51" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="52" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="52" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>93500</v>
+      </c>
+      <c r="E52" s="3">
+        <v>134200</v>
+      </c>
+      <c r="F52" s="3">
         <v>101200</v>
       </c>
-      <c r="E52" s="3">
+      <c r="G52" s="3">
         <v>117300</v>
       </c>
-      <c r="F52" s="3">
+      <c r="H52" s="3">
         <v>129400</v>
       </c>
-      <c r="G52" s="3">
+      <c r="I52" s="3">
         <v>126000</v>
       </c>
-      <c r="H52" s="3">
+      <c r="J52" s="3">
         <v>135900</v>
       </c>
-      <c r="I52" s="3">
+      <c r="K52" s="3">
         <v>128200</v>
       </c>
-      <c r="J52" s="3">
+      <c r="L52" s="3">
         <v>99600</v>
       </c>
-      <c r="K52" s="3">
+      <c r="M52" s="3">
         <v>99000</v>
       </c>
-      <c r="L52" s="3">
+      <c r="N52" s="3">
         <v>72800</v>
       </c>
-      <c r="M52" s="3">
+      <c r="O52" s="3">
         <v>53000</v>
       </c>
-      <c r="N52" s="3">
+      <c r="P52" s="3">
         <v>74600</v>
       </c>
-      <c r="O52" s="3">
+      <c r="Q52" s="3">
         <v>220900</v>
       </c>
-      <c r="P52" s="3">
+      <c r="R52" s="3">
         <v>238500</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="S52" s="3">
         <v>216500</v>
       </c>
-      <c r="R52" s="3">
+      <c r="T52" s="3">
         <v>234300</v>
       </c>
-      <c r="S52" s="3">
+      <c r="U52" s="3">
         <v>233800</v>
       </c>
-      <c r="T52" s="3">
+      <c r="V52" s="3">
         <v>230200</v>
       </c>
-      <c r="U52" s="3">
+      <c r="W52" s="3">
         <v>251600</v>
       </c>
-      <c r="V52" s="3">
+      <c r="X52" s="3">
         <v>250600</v>
       </c>
-      <c r="W52" s="3">
+      <c r="Y52" s="3">
         <v>175100</v>
       </c>
-      <c r="X52" s="3">
+      <c r="Z52" s="3">
         <v>172000</v>
       </c>
-      <c r="Y52" s="3">
+      <c r="AA52" s="3">
         <v>170900</v>
       </c>
-      <c r="Z52" s="3">
+      <c r="AB52" s="3">
         <v>179500</v>
       </c>
-      <c r="AA52" s="3">
+      <c r="AC52" s="3">
         <v>156400</v>
       </c>
-      <c r="AB52" s="3">
+      <c r="AD52" s="3">
         <v>391500</v>
       </c>
-      <c r="AC52" s="3">
+      <c r="AE52" s="3">
         <v>232100</v>
       </c>
-      <c r="AD52" s="3">
+      <c r="AF52" s="3">
         <v>172600</v>
       </c>
-      <c r="AE52" s="3">
+      <c r="AG52" s="3">
         <v>136600</v>
       </c>
-      <c r="AF52" s="3">
+      <c r="AH52" s="3">
         <v>108700</v>
       </c>
-      <c r="AG52" s="3">
+      <c r="AI52" s="3">
         <v>108200</v>
       </c>
-      <c r="AH52" s="3">
+      <c r="AJ52" s="3">
         <v>87800</v>
       </c>
-      <c r="AI52" s="3">
+      <c r="AK52" s="3">
         <v>68500</v>
       </c>
-      <c r="AJ52" s="3">
+      <c r="AL52" s="3">
         <v>45800</v>
       </c>
-      <c r="AK52" s="3">
+      <c r="AM52" s="3">
         <v>34600</v>
       </c>
-      <c r="AL52" s="3">
+      <c r="AN52" s="3">
         <v>28700</v>
       </c>
-      <c r="AM52" s="3">
+      <c r="AO52" s="3">
         <v>22500</v>
       </c>
-      <c r="AN52" s="3">
+      <c r="AP52" s="3">
         <v>26400</v>
       </c>
     </row>
-    <row r="53" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -5554,124 +5799,136 @@
       <c r="AN53" s="3">
         <v>0</v>
       </c>
+      <c r="AO53" s="3">
+        <v>0</v>
+      </c>
+      <c r="AP53" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="54" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="54" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>14176200</v>
+      </c>
+      <c r="E54" s="3">
+        <v>13013800</v>
+      </c>
+      <c r="F54" s="3">
         <v>12718000</v>
       </c>
-      <c r="E54" s="3">
+      <c r="G54" s="3">
         <v>13208200</v>
       </c>
-      <c r="F54" s="3">
+      <c r="H54" s="3">
         <v>12836700</v>
       </c>
-      <c r="G54" s="3">
+      <c r="I54" s="3">
         <v>12650900</v>
       </c>
-      <c r="H54" s="3">
+      <c r="J54" s="3">
         <v>13303900</v>
       </c>
-      <c r="I54" s="3">
+      <c r="K54" s="3">
         <v>12536800</v>
       </c>
-      <c r="J54" s="3">
+      <c r="L54" s="3">
         <v>12447200</v>
       </c>
-      <c r="K54" s="3">
+      <c r="M54" s="3">
         <v>12475900</v>
       </c>
-      <c r="L54" s="3">
+      <c r="N54" s="3">
         <v>11986900</v>
       </c>
-      <c r="M54" s="3">
+      <c r="O54" s="3">
         <v>11314300</v>
       </c>
-      <c r="N54" s="3">
+      <c r="P54" s="3">
         <v>11747600</v>
       </c>
-      <c r="O54" s="3">
+      <c r="Q54" s="3">
         <v>11070300</v>
       </c>
-      <c r="P54" s="3">
+      <c r="R54" s="3">
         <v>10720300</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="S54" s="3">
         <v>9523700</v>
       </c>
-      <c r="R54" s="3">
+      <c r="T54" s="3">
         <v>9084600</v>
       </c>
-      <c r="S54" s="3">
+      <c r="U54" s="3">
         <v>8648800</v>
       </c>
-      <c r="T54" s="3">
+      <c r="V54" s="3">
         <v>8623200</v>
       </c>
-      <c r="U54" s="3">
+      <c r="W54" s="3">
         <v>8799300</v>
       </c>
-      <c r="V54" s="3">
+      <c r="X54" s="3">
         <v>8633300</v>
       </c>
-      <c r="W54" s="3">
+      <c r="Y54" s="3">
         <v>8241300</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Z54" s="3">
         <v>8679900</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="AA54" s="3">
         <v>7144000</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AB54" s="3">
         <v>7328400</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AC54" s="3">
         <v>7066200</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AD54" s="3">
         <v>6627600</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AE54" s="3">
         <v>6192400</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AF54" s="3">
         <v>6105100</v>
       </c>
-      <c r="AE54" s="3">
+      <c r="AG54" s="3">
         <v>5763100</v>
       </c>
-      <c r="AF54" s="3">
+      <c r="AH54" s="3">
         <v>5219700</v>
       </c>
-      <c r="AG54" s="3">
+      <c r="AI54" s="3">
         <v>4800400</v>
       </c>
-      <c r="AH54" s="3">
+      <c r="AJ54" s="3">
         <v>3561300</v>
       </c>
-      <c r="AI54" s="3">
+      <c r="AK54" s="3">
         <v>3833100</v>
       </c>
-      <c r="AJ54" s="3">
+      <c r="AL54" s="3">
         <v>3632000</v>
       </c>
-      <c r="AK54" s="3">
+      <c r="AM54" s="3">
         <v>3531800</v>
       </c>
-      <c r="AL54" s="3">
+      <c r="AN54" s="3">
         <v>3467300</v>
       </c>
-      <c r="AM54" s="3">
+      <c r="AO54" s="3">
         <v>3403600</v>
       </c>
-      <c r="AN54" s="3">
+      <c r="AP54" s="3">
         <v>1811700</v>
       </c>
     </row>
-    <row r="55" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -5712,8 +5969,10 @@
       <c r="AL55" s="3"/>
       <c r="AM55" s="3"/>
       <c r="AN55" s="3"/>
+      <c r="AO55" s="3"/>
+      <c r="AP55" s="3"/>
     </row>
-    <row r="56" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="56" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -5754,213 +6013,221 @@
       <c r="AL56" s="3"/>
       <c r="AM56" s="3"/>
       <c r="AN56" s="3"/>
+      <c r="AO56" s="3"/>
+      <c r="AP56" s="3"/>
     </row>
-    <row r="57" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="57" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>350900</v>
+      </c>
+      <c r="E57" s="3">
+        <v>374700</v>
+      </c>
+      <c r="F57" s="3">
         <v>319400</v>
       </c>
-      <c r="E57" s="3">
+      <c r="G57" s="3">
         <v>343100</v>
       </c>
-      <c r="F57" s="3">
+      <c r="H57" s="3">
         <v>350200</v>
       </c>
-      <c r="G57" s="3">
+      <c r="I57" s="3">
         <v>345000</v>
       </c>
-      <c r="H57" s="3">
+      <c r="J57" s="3">
         <v>301200</v>
       </c>
-      <c r="I57" s="3">
+      <c r="K57" s="3">
         <v>324000</v>
       </c>
-      <c r="J57" s="3">
+      <c r="L57" s="3">
         <v>323300</v>
       </c>
-      <c r="K57" s="3">
+      <c r="M57" s="3">
         <v>368200</v>
       </c>
-      <c r="L57" s="3">
+      <c r="N57" s="3">
         <v>300100</v>
       </c>
-      <c r="M57" s="3">
+      <c r="O57" s="3">
         <v>293200</v>
       </c>
-      <c r="N57" s="3">
+      <c r="P57" s="3">
         <v>345800</v>
       </c>
-      <c r="O57" s="3">
+      <c r="Q57" s="3">
         <v>310500</v>
       </c>
-      <c r="P57" s="3">
+      <c r="R57" s="3">
         <v>245700</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="S57" s="3">
         <v>265700</v>
       </c>
-      <c r="R57" s="3">
+      <c r="T57" s="3">
         <v>238900</v>
       </c>
-      <c r="S57" s="3">
+      <c r="U57" s="3">
         <v>269700</v>
       </c>
-      <c r="T57" s="3">
+      <c r="V57" s="3">
         <v>231300</v>
       </c>
-      <c r="U57" s="3">
+      <c r="W57" s="3">
         <v>229300</v>
       </c>
-      <c r="V57" s="3">
+      <c r="X57" s="3">
         <v>222800</v>
       </c>
-      <c r="W57" s="3">
+      <c r="Y57" s="3">
         <v>227700</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Z57" s="3">
         <v>216400</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="AA57" s="3">
         <v>162900</v>
       </c>
-      <c r="Z57" s="3">
+      <c r="AB57" s="3">
         <v>185600</v>
       </c>
-      <c r="AA57" s="3">
+      <c r="AC57" s="3">
         <v>227200</v>
       </c>
-      <c r="AB57" s="3">
+      <c r="AD57" s="3">
         <v>167200</v>
       </c>
-      <c r="AC57" s="3">
+      <c r="AE57" s="3">
         <v>181100</v>
       </c>
-      <c r="AD57" s="3">
+      <c r="AF57" s="3">
         <v>157100</v>
       </c>
-      <c r="AE57" s="3">
+      <c r="AG57" s="3">
         <v>190500</v>
       </c>
-      <c r="AF57" s="3">
+      <c r="AH57" s="3">
         <v>117200</v>
       </c>
-      <c r="AG57" s="3">
+      <c r="AI57" s="3">
         <v>130700</v>
       </c>
-      <c r="AH57" s="3">
+      <c r="AJ57" s="3">
         <v>133200</v>
       </c>
-      <c r="AI57" s="3">
+      <c r="AK57" s="3">
         <v>132000</v>
       </c>
-      <c r="AJ57" s="3">
+      <c r="AL57" s="3">
         <v>84900</v>
       </c>
-      <c r="AK57" s="3">
+      <c r="AM57" s="3">
         <v>73000</v>
       </c>
-      <c r="AL57" s="3">
+      <c r="AN57" s="3">
         <v>98200</v>
       </c>
-      <c r="AM57" s="3">
+      <c r="AO57" s="3">
         <v>92600</v>
       </c>
-      <c r="AN57" s="3">
+      <c r="AP57" s="3">
         <v>65500</v>
       </c>
     </row>
-    <row r="58" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>1625200</v>
+      </c>
+      <c r="E58" s="3">
+        <v>1583300</v>
+      </c>
+      <c r="F58" s="3">
         <v>1654600</v>
       </c>
-      <c r="E58" s="3">
+      <c r="G58" s="3">
         <v>2564600</v>
       </c>
-      <c r="F58" s="3">
+      <c r="H58" s="3">
         <v>2301800</v>
       </c>
-      <c r="G58" s="3">
+      <c r="I58" s="3">
         <v>2324600</v>
       </c>
-      <c r="H58" s="3">
+      <c r="J58" s="3">
         <v>2554100</v>
       </c>
-      <c r="I58" s="3">
+      <c r="K58" s="3">
         <v>1451100</v>
       </c>
-      <c r="J58" s="3">
+      <c r="L58" s="3">
         <v>1138800</v>
       </c>
-      <c r="K58" s="3">
+      <c r="M58" s="3">
         <v>1121500</v>
       </c>
-      <c r="L58" s="3">
+      <c r="N58" s="3">
         <v>1346600</v>
       </c>
-      <c r="M58" s="3">
+      <c r="O58" s="3">
         <v>958600</v>
       </c>
-      <c r="N58" s="3">
+      <c r="P58" s="3">
         <v>994900</v>
       </c>
-      <c r="O58" s="3">
+      <c r="Q58" s="3">
         <v>788700</v>
       </c>
-      <c r="P58" s="3">
+      <c r="R58" s="3">
         <v>993100</v>
       </c>
-      <c r="Q58" s="3">
+      <c r="S58" s="3">
         <v>1015500</v>
       </c>
-      <c r="R58" s="3">
+      <c r="T58" s="3">
         <v>847900</v>
       </c>
-      <c r="S58" s="3">
+      <c r="U58" s="3">
         <v>500600</v>
       </c>
-      <c r="T58" s="3">
+      <c r="V58" s="3">
         <v>678800</v>
       </c>
-      <c r="U58" s="3">
+      <c r="W58" s="3">
         <v>537500</v>
       </c>
-      <c r="V58" s="3">
+      <c r="X58" s="3">
         <v>433100</v>
       </c>
-      <c r="W58" s="3">
+      <c r="Y58" s="3">
         <v>244900</v>
       </c>
-      <c r="X58" s="3">
+      <c r="Z58" s="3">
         <v>413300</v>
       </c>
-      <c r="Y58" s="3">
+      <c r="AA58" s="3">
         <v>322200</v>
       </c>
-      <c r="Z58" s="3">
+      <c r="AB58" s="3">
         <v>47300</v>
       </c>
-      <c r="AA58" s="3">
-        <v>0</v>
-      </c>
-      <c r="AB58" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="AC58" s="3" t="s">
-        <v>8</v>
+      <c r="AC58" s="3">
+        <v>0</v>
       </c>
       <c r="AD58" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AE58" s="3">
-        <v>0</v>
-      </c>
-      <c r="AF58" s="3">
-        <v>0</v>
+      <c r="AE58" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AF58" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="AG58" s="3">
         <v>0</v>
@@ -5969,305 +6236,323 @@
         <v>0</v>
       </c>
       <c r="AI58" s="3">
-        <v>37100</v>
+        <v>0</v>
       </c>
       <c r="AJ58" s="3">
-        <v>37100</v>
+        <v>0</v>
       </c>
       <c r="AK58" s="3">
         <v>37100</v>
       </c>
       <c r="AL58" s="3">
+        <v>37100</v>
+      </c>
+      <c r="AM58" s="3">
+        <v>37100</v>
+      </c>
+      <c r="AN58" s="3">
         <v>101800</v>
       </c>
-      <c r="AM58" s="3">
+      <c r="AO58" s="3">
         <v>65400</v>
       </c>
-      <c r="AN58" s="3">
+      <c r="AP58" s="3">
         <v>43600</v>
       </c>
     </row>
-    <row r="59" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>1458400</v>
+      </c>
+      <c r="E59" s="3">
+        <v>1071300</v>
+      </c>
+      <c r="F59" s="3">
         <v>1407500</v>
       </c>
-      <c r="E59" s="3">
+      <c r="G59" s="3">
         <v>1064300</v>
       </c>
-      <c r="F59" s="3">
+      <c r="H59" s="3">
         <v>1352200</v>
       </c>
-      <c r="G59" s="3">
+      <c r="I59" s="3">
         <v>936500</v>
       </c>
-      <c r="H59" s="3">
+      <c r="J59" s="3">
         <v>1604400</v>
       </c>
-      <c r="I59" s="3">
+      <c r="K59" s="3">
         <v>1264500</v>
       </c>
-      <c r="J59" s="3">
+      <c r="L59" s="3">
         <v>1759300</v>
       </c>
-      <c r="K59" s="3">
+      <c r="M59" s="3">
         <v>1114400</v>
       </c>
-      <c r="L59" s="3">
+      <c r="N59" s="3">
         <v>1248600</v>
       </c>
-      <c r="M59" s="3">
+      <c r="O59" s="3">
         <v>1192600</v>
       </c>
-      <c r="N59" s="3">
+      <c r="P59" s="3">
         <v>1440100</v>
       </c>
-      <c r="O59" s="3">
+      <c r="Q59" s="3">
         <v>1213600</v>
       </c>
-      <c r="P59" s="3">
+      <c r="R59" s="3">
         <v>1179100</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="S59" s="3">
         <v>1079000</v>
       </c>
-      <c r="R59" s="3">
+      <c r="T59" s="3">
         <v>1121000</v>
       </c>
-      <c r="S59" s="3">
+      <c r="U59" s="3">
         <v>1020300</v>
       </c>
-      <c r="T59" s="3">
+      <c r="V59" s="3">
         <v>902400</v>
       </c>
-      <c r="U59" s="3">
+      <c r="W59" s="3">
         <v>855200</v>
       </c>
-      <c r="V59" s="3">
+      <c r="X59" s="3">
         <v>966600</v>
       </c>
-      <c r="W59" s="3">
+      <c r="Y59" s="3">
         <v>828600</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Z59" s="3">
         <v>822800</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="AA59" s="3">
         <v>808400</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AB59" s="3">
         <v>1052600</v>
       </c>
-      <c r="AA59" s="3">
+      <c r="AC59" s="3">
         <v>801600</v>
       </c>
-      <c r="AB59" s="3">
+      <c r="AD59" s="3">
         <v>687500</v>
       </c>
-      <c r="AC59" s="3">
+      <c r="AE59" s="3">
         <v>630100</v>
       </c>
-      <c r="AD59" s="3">
+      <c r="AF59" s="3">
         <v>711200</v>
       </c>
-      <c r="AE59" s="3">
+      <c r="AG59" s="3">
         <v>556200</v>
       </c>
-      <c r="AF59" s="3">
+      <c r="AH59" s="3">
         <v>432100</v>
       </c>
-      <c r="AG59" s="3">
+      <c r="AI59" s="3">
         <v>419700</v>
       </c>
-      <c r="AH59" s="3">
+      <c r="AJ59" s="3">
         <v>424600</v>
       </c>
-      <c r="AI59" s="3">
+      <c r="AK59" s="3">
         <v>446300</v>
       </c>
-      <c r="AJ59" s="3">
+      <c r="AL59" s="3">
         <v>419000</v>
       </c>
-      <c r="AK59" s="3">
+      <c r="AM59" s="3">
         <v>349800</v>
       </c>
-      <c r="AL59" s="3">
+      <c r="AN59" s="3">
         <v>311200</v>
       </c>
-      <c r="AM59" s="3">
+      <c r="AO59" s="3">
         <v>354300</v>
       </c>
-      <c r="AN59" s="3">
+      <c r="AP59" s="3">
         <v>296300</v>
       </c>
     </row>
-    <row r="60" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>3434500</v>
+      </c>
+      <c r="E60" s="3">
+        <v>3269600</v>
+      </c>
+      <c r="F60" s="3">
         <v>3381500</v>
       </c>
-      <c r="E60" s="3">
+      <c r="G60" s="3">
         <v>3972000</v>
       </c>
-      <c r="F60" s="3">
+      <c r="H60" s="3">
         <v>4004200</v>
       </c>
-      <c r="G60" s="3">
+      <c r="I60" s="3">
         <v>3873500</v>
       </c>
-      <c r="H60" s="3">
+      <c r="J60" s="3">
         <v>4459700</v>
       </c>
-      <c r="I60" s="3">
+      <c r="K60" s="3">
         <v>3039700</v>
       </c>
-      <c r="J60" s="3">
+      <c r="L60" s="3">
         <v>3221500</v>
       </c>
-      <c r="K60" s="3">
+      <c r="M60" s="3">
         <v>2829100</v>
       </c>
-      <c r="L60" s="3">
+      <c r="N60" s="3">
         <v>2895300</v>
       </c>
-      <c r="M60" s="3">
+      <c r="O60" s="3">
         <v>2444400</v>
       </c>
-      <c r="N60" s="3">
+      <c r="P60" s="3">
         <v>2780800</v>
       </c>
-      <c r="O60" s="3">
+      <c r="Q60" s="3">
         <v>2312800</v>
       </c>
-      <c r="P60" s="3">
+      <c r="R60" s="3">
         <v>2417900</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="S60" s="3">
         <v>2360200</v>
       </c>
-      <c r="R60" s="3">
+      <c r="T60" s="3">
         <v>2207700</v>
       </c>
-      <c r="S60" s="3">
+      <c r="U60" s="3">
         <v>1790600</v>
       </c>
-      <c r="T60" s="3">
+      <c r="V60" s="3">
         <v>1812500</v>
       </c>
-      <c r="U60" s="3">
+      <c r="W60" s="3">
         <v>1622000</v>
       </c>
-      <c r="V60" s="3">
+      <c r="X60" s="3">
         <v>1622600</v>
       </c>
-      <c r="W60" s="3">
+      <c r="Y60" s="3">
         <v>1301200</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Z60" s="3">
         <v>1452600</v>
       </c>
-      <c r="Y60" s="3">
+      <c r="AA60" s="3">
         <v>1293500</v>
       </c>
-      <c r="Z60" s="3">
+      <c r="AB60" s="3">
         <v>1285600</v>
       </c>
-      <c r="AA60" s="3">
+      <c r="AC60" s="3">
         <v>1028700</v>
       </c>
-      <c r="AB60" s="3">
+      <c r="AD60" s="3">
         <v>854700</v>
       </c>
-      <c r="AC60" s="3">
+      <c r="AE60" s="3">
         <v>811200</v>
       </c>
-      <c r="AD60" s="3">
+      <c r="AF60" s="3">
         <v>868200</v>
       </c>
-      <c r="AE60" s="3">
+      <c r="AG60" s="3">
         <v>746700</v>
       </c>
-      <c r="AF60" s="3">
+      <c r="AH60" s="3">
         <v>549300</v>
       </c>
-      <c r="AG60" s="3">
+      <c r="AI60" s="3">
         <v>550400</v>
       </c>
-      <c r="AH60" s="3">
+      <c r="AJ60" s="3">
         <v>557800</v>
       </c>
-      <c r="AI60" s="3">
+      <c r="AK60" s="3">
         <v>615300</v>
       </c>
-      <c r="AJ60" s="3">
+      <c r="AL60" s="3">
         <v>541000</v>
       </c>
-      <c r="AK60" s="3">
+      <c r="AM60" s="3">
         <v>459900</v>
       </c>
-      <c r="AL60" s="3">
+      <c r="AN60" s="3">
         <v>511200</v>
       </c>
-      <c r="AM60" s="3">
+      <c r="AO60" s="3">
         <v>512300</v>
       </c>
-      <c r="AN60" s="3">
+      <c r="AP60" s="3">
         <v>405500</v>
       </c>
     </row>
-    <row r="61" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>1534400</v>
+      </c>
+      <c r="E61" s="3">
+        <v>57700</v>
+      </c>
+      <c r="F61" s="3">
         <v>82100</v>
       </c>
-      <c r="E61" s="3">
+      <c r="G61" s="3">
         <v>70100</v>
       </c>
-      <c r="F61" s="3">
+      <c r="H61" s="3">
         <v>52400</v>
       </c>
-      <c r="G61" s="3">
+      <c r="I61" s="3">
         <v>51700</v>
       </c>
-      <c r="H61" s="3">
+      <c r="J61" s="3">
         <v>53300</v>
       </c>
-      <c r="I61" s="3">
+      <c r="K61" s="3">
         <v>1038300</v>
       </c>
-      <c r="J61" s="3">
+      <c r="L61" s="3">
         <v>1047500</v>
       </c>
-      <c r="K61" s="3">
+      <c r="M61" s="3">
         <v>1055600</v>
       </c>
-      <c r="L61" s="3">
+      <c r="N61" s="3">
         <v>1050000</v>
       </c>
-      <c r="M61" s="3">
+      <c r="O61" s="3">
         <v>1054200</v>
       </c>
-      <c r="N61" s="3">
+      <c r="P61" s="3">
         <v>1055700</v>
       </c>
-      <c r="O61" s="3">
+      <c r="Q61" s="3">
         <v>957100</v>
       </c>
-      <c r="P61" s="3">
+      <c r="R61" s="3">
         <v>966000</v>
       </c>
-      <c r="Q61" s="3">
-        <v>0</v>
-      </c>
-      <c r="R61" s="3">
-        <v>0</v>
-      </c>
       <c r="S61" s="3">
         <v>0</v>
       </c>
@@ -6334,8 +6619,14 @@
       <c r="AN61" s="3">
         <v>0</v>
       </c>
+      <c r="AO61" s="3">
+        <v>0</v>
+      </c>
+      <c r="AP61" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="62" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
@@ -6372,86 +6663,92 @@
       <c r="N62" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="O62" s="3">
+      <c r="O62" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="P62" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q62" s="3">
         <v>120800</v>
       </c>
-      <c r="P62" s="3">
+      <c r="R62" s="3">
         <v>101000</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="S62" s="3">
         <v>110000</v>
       </c>
-      <c r="R62" s="3">
+      <c r="T62" s="3">
         <v>114700</v>
       </c>
-      <c r="S62" s="3">
+      <c r="U62" s="3">
         <v>116900</v>
       </c>
-      <c r="T62" s="3">
+      <c r="V62" s="3">
         <v>120300</v>
       </c>
-      <c r="U62" s="3">
+      <c r="W62" s="3">
         <v>115800</v>
       </c>
-      <c r="V62" s="3">
+      <c r="X62" s="3">
         <v>110200</v>
       </c>
-      <c r="W62" s="3">
+      <c r="Y62" s="3">
         <v>105400</v>
       </c>
-      <c r="X62" s="3">
+      <c r="Z62" s="3">
         <v>99300</v>
       </c>
-      <c r="Y62" s="3">
+      <c r="AA62" s="3">
         <v>104200</v>
       </c>
-      <c r="Z62" s="3">
+      <c r="AB62" s="3">
         <v>117500</v>
       </c>
-      <c r="AA62" s="3">
+      <c r="AC62" s="3">
         <v>124100</v>
       </c>
-      <c r="AB62" s="3">
+      <c r="AD62" s="3">
         <v>95900</v>
       </c>
-      <c r="AC62" s="3">
+      <c r="AE62" s="3">
         <v>96500</v>
       </c>
-      <c r="AD62" s="3">
+      <c r="AF62" s="3">
         <v>121000</v>
       </c>
-      <c r="AE62" s="3">
+      <c r="AG62" s="3">
         <v>39500</v>
       </c>
-      <c r="AF62" s="3">
+      <c r="AH62" s="3">
         <v>33600</v>
       </c>
-      <c r="AG62" s="3">
+      <c r="AI62" s="3">
         <v>33400</v>
       </c>
-      <c r="AH62" s="3">
+      <c r="AJ62" s="3">
         <v>34000</v>
       </c>
-      <c r="AI62" s="3">
+      <c r="AK62" s="3">
         <v>35700</v>
       </c>
-      <c r="AJ62" s="3">
+      <c r="AL62" s="3">
         <v>30000</v>
       </c>
-      <c r="AK62" s="3">
+      <c r="AM62" s="3">
         <v>30300</v>
       </c>
-      <c r="AL62" s="3">
+      <c r="AN62" s="3">
         <v>23500</v>
       </c>
-      <c r="AM62" s="3">
+      <c r="AO62" s="3">
         <v>19000</v>
       </c>
-      <c r="AN62" s="3">
+      <c r="AP62" s="3">
         <v>19100</v>
       </c>
     </row>
-    <row r="63" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -6566,8 +6863,14 @@
       <c r="AN63" s="3">
         <v>0</v>
       </c>
+      <c r="AO63" s="3">
+        <v>0</v>
+      </c>
+      <c r="AP63" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="64" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="64" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -6682,8 +6985,14 @@
       <c r="AN64" s="3">
         <v>0</v>
       </c>
+      <c r="AO64" s="3">
+        <v>0</v>
+      </c>
+      <c r="AP64" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="65" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="65" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -6798,124 +7107,136 @@
       <c r="AN65" s="3">
         <v>0</v>
       </c>
+      <c r="AO65" s="3">
+        <v>0</v>
+      </c>
+      <c r="AP65" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="66" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="66" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>5060100</v>
+      </c>
+      <c r="E66" s="3">
+        <v>3415200</v>
+      </c>
+      <c r="F66" s="3">
         <v>3536300</v>
       </c>
-      <c r="E66" s="3">
+      <c r="G66" s="3">
         <v>4154900</v>
       </c>
-      <c r="F66" s="3">
+      <c r="H66" s="3">
         <v>4173300</v>
       </c>
-      <c r="G66" s="3">
+      <c r="I66" s="3">
         <v>4064300</v>
       </c>
-      <c r="H66" s="3">
+      <c r="J66" s="3">
         <v>4590200</v>
       </c>
-      <c r="I66" s="3">
+      <c r="K66" s="3">
         <v>4146200</v>
       </c>
-      <c r="J66" s="3">
+      <c r="L66" s="3">
         <v>4360500</v>
       </c>
-      <c r="K66" s="3">
+      <c r="M66" s="3">
         <v>3974800</v>
       </c>
-      <c r="L66" s="3">
+      <c r="N66" s="3">
         <v>3992800</v>
       </c>
-      <c r="M66" s="3">
+      <c r="O66" s="3">
         <v>3546600</v>
       </c>
-      <c r="N66" s="3">
+      <c r="P66" s="3">
         <v>3885900</v>
       </c>
-      <c r="O66" s="3">
+      <c r="Q66" s="3">
         <v>3453300</v>
       </c>
-      <c r="P66" s="3">
+      <c r="R66" s="3">
         <v>3547700</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="S66" s="3">
         <v>2528500</v>
       </c>
-      <c r="R66" s="3">
+      <c r="T66" s="3">
         <v>2353800</v>
       </c>
-      <c r="S66" s="3">
+      <c r="U66" s="3">
         <v>1947500</v>
       </c>
-      <c r="T66" s="3">
+      <c r="V66" s="3">
         <v>1953500</v>
       </c>
-      <c r="U66" s="3">
+      <c r="W66" s="3">
         <v>1753500</v>
       </c>
-      <c r="V66" s="3">
+      <c r="X66" s="3">
         <v>1752700</v>
       </c>
-      <c r="W66" s="3">
+      <c r="Y66" s="3">
         <v>1423500</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Z66" s="3">
         <v>1568300</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="AA66" s="3">
         <v>1414400</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AB66" s="3">
         <v>1419300</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AC66" s="3">
         <v>1168400</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AD66" s="3">
         <v>965800</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AE66" s="3">
         <v>919500</v>
       </c>
-      <c r="AD66" s="3">
+      <c r="AF66" s="3">
         <v>999600</v>
       </c>
-      <c r="AE66" s="3">
+      <c r="AG66" s="3">
         <v>793800</v>
       </c>
-      <c r="AF66" s="3">
+      <c r="AH66" s="3">
         <v>588000</v>
       </c>
-      <c r="AG66" s="3">
+      <c r="AI66" s="3">
         <v>584900</v>
       </c>
-      <c r="AH66" s="3">
+      <c r="AJ66" s="3">
         <v>592700</v>
       </c>
-      <c r="AI66" s="3">
+      <c r="AK66" s="3">
         <v>651900</v>
       </c>
-      <c r="AJ66" s="3">
+      <c r="AL66" s="3">
         <v>571800</v>
       </c>
-      <c r="AK66" s="3">
+      <c r="AM66" s="3">
         <v>491000</v>
       </c>
-      <c r="AL66" s="3">
+      <c r="AN66" s="3">
         <v>535400</v>
       </c>
-      <c r="AM66" s="3">
+      <c r="AO66" s="3">
         <v>532100</v>
       </c>
-      <c r="AN66" s="3">
+      <c r="AP66" s="3">
         <v>424600</v>
       </c>
     </row>
-    <row r="67" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -6956,8 +7277,10 @@
       <c r="AL67" s="3"/>
       <c r="AM67" s="3"/>
       <c r="AN67" s="3"/>
+      <c r="AO67" s="3"/>
+      <c r="AP67" s="3"/>
     </row>
-    <row r="68" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="68" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -7072,8 +7395,14 @@
       <c r="AN68" s="3">
         <v>0</v>
       </c>
+      <c r="AO68" s="3">
+        <v>0</v>
+      </c>
+      <c r="AP68" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="69" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="69" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -7188,8 +7517,14 @@
       <c r="AN69" s="3">
         <v>0</v>
       </c>
+      <c r="AO69" s="3">
+        <v>0</v>
+      </c>
+      <c r="AP69" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="70" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="70" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -7302,10 +7637,16 @@
         <v>0</v>
       </c>
       <c r="AN70" s="3">
+        <v>0</v>
+      </c>
+      <c r="AO70" s="3">
+        <v>0</v>
+      </c>
+      <c r="AP70" s="3">
         <v>304900</v>
       </c>
     </row>
-    <row r="71" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="71" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -7420,124 +7761,136 @@
       <c r="AN71" s="3">
         <v>0</v>
       </c>
+      <c r="AO71" s="3">
+        <v>0</v>
+      </c>
+      <c r="AP71" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="72" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="72" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>5778900</v>
+      </c>
+      <c r="E72" s="3">
+        <v>6136200</v>
+      </c>
+      <c r="F72" s="3">
         <v>5780500</v>
       </c>
-      <c r="E72" s="3">
+      <c r="G72" s="3">
         <v>5633100</v>
       </c>
-      <c r="F72" s="3">
+      <c r="H72" s="3">
         <v>5294000</v>
       </c>
-      <c r="G72" s="3">
+      <c r="I72" s="3">
         <v>5356600</v>
       </c>
-      <c r="H72" s="3">
+      <c r="J72" s="3">
         <v>5234300</v>
       </c>
-      <c r="I72" s="3">
+      <c r="K72" s="3">
         <v>5041300</v>
       </c>
-      <c r="J72" s="3">
+      <c r="L72" s="3">
         <v>4711900</v>
       </c>
-      <c r="K72" s="3">
+      <c r="M72" s="3">
         <v>5119400</v>
       </c>
-      <c r="L72" s="3">
+      <c r="N72" s="3">
         <v>4715800</v>
       </c>
-      <c r="M72" s="3">
+      <c r="O72" s="3">
         <v>4457100</v>
       </c>
-      <c r="N72" s="3">
+      <c r="P72" s="3">
         <v>4478700</v>
       </c>
-      <c r="O72" s="3">
+      <c r="Q72" s="3">
         <v>4153200</v>
       </c>
-      <c r="P72" s="3">
+      <c r="R72" s="3">
         <v>3771300</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="S72" s="3">
         <v>3525800</v>
       </c>
-      <c r="R72" s="3">
+      <c r="T72" s="3">
         <v>3280400</v>
       </c>
-      <c r="S72" s="3">
+      <c r="U72" s="3">
         <v>3129900</v>
       </c>
-      <c r="T72" s="3">
+      <c r="V72" s="3">
         <v>2978700</v>
       </c>
-      <c r="U72" s="3">
+      <c r="W72" s="3">
         <v>3182700</v>
       </c>
-      <c r="V72" s="3">
+      <c r="X72" s="3">
         <v>3093800</v>
       </c>
-      <c r="W72" s="3">
+      <c r="Y72" s="3">
         <v>2928600</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Z72" s="3">
         <v>2910500</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="AA72" s="3">
         <v>2733500</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AB72" s="3">
         <v>2697900</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AC72" s="3">
         <v>2575600</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AD72" s="3">
         <v>2246600</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AE72" s="3">
         <v>2000300</v>
       </c>
-      <c r="AD72" s="3">
+      <c r="AF72" s="3">
         <v>1784800</v>
       </c>
-      <c r="AE72" s="3">
+      <c r="AG72" s="3">
         <v>1605100</v>
       </c>
-      <c r="AF72" s="3">
+      <c r="AH72" s="3">
         <v>1368400</v>
       </c>
-      <c r="AG72" s="3">
+      <c r="AI72" s="3">
         <v>1220100</v>
       </c>
-      <c r="AH72" s="3">
+      <c r="AJ72" s="3">
         <v>1036800</v>
       </c>
-      <c r="AI72" s="3">
+      <c r="AK72" s="3">
         <v>989800</v>
       </c>
-      <c r="AJ72" s="3">
+      <c r="AL72" s="3">
         <v>808400</v>
       </c>
-      <c r="AK72" s="3">
+      <c r="AM72" s="3">
         <v>702000</v>
       </c>
-      <c r="AL72" s="3">
+      <c r="AN72" s="3">
         <v>583600</v>
       </c>
-      <c r="AM72" s="3">
+      <c r="AO72" s="3">
         <v>510400</v>
       </c>
-      <c r="AN72" s="3">
+      <c r="AP72" s="3">
         <v>404700</v>
       </c>
     </row>
-    <row r="73" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -7652,8 +8005,14 @@
       <c r="AN73" s="3">
         <v>0</v>
       </c>
+      <c r="AO73" s="3">
+        <v>0</v>
+      </c>
+      <c r="AP73" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="74" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="74" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -7768,8 +8127,14 @@
       <c r="AN74" s="3">
         <v>0</v>
       </c>
+      <c r="AO74" s="3">
+        <v>0</v>
+      </c>
+      <c r="AP74" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="75" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="75" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -7884,124 +8249,136 @@
       <c r="AN75" s="3">
         <v>0</v>
       </c>
+      <c r="AO75" s="3">
+        <v>0</v>
+      </c>
+      <c r="AP75" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="76" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="76" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>9006100</v>
+      </c>
+      <c r="E76" s="3">
+        <v>9491100</v>
+      </c>
+      <c r="F76" s="3">
         <v>9089100</v>
       </c>
-      <c r="E76" s="3">
+      <c r="G76" s="3">
         <v>8961400</v>
       </c>
-      <c r="F76" s="3">
+      <c r="H76" s="3">
         <v>8573600</v>
       </c>
-      <c r="G76" s="3">
+      <c r="I76" s="3">
         <v>8502700</v>
       </c>
-      <c r="H76" s="3">
+      <c r="J76" s="3">
         <v>8638000</v>
       </c>
-      <c r="I76" s="3">
+      <c r="K76" s="3">
         <v>8315300</v>
       </c>
-      <c r="J76" s="3">
+      <c r="L76" s="3">
         <v>8011000</v>
       </c>
-      <c r="K76" s="3">
+      <c r="M76" s="3">
         <v>8433600</v>
       </c>
-      <c r="L76" s="3">
+      <c r="N76" s="3">
         <v>7934600</v>
       </c>
-      <c r="M76" s="3">
+      <c r="O76" s="3">
         <v>7708500</v>
       </c>
-      <c r="N76" s="3">
+      <c r="P76" s="3">
         <v>7797800</v>
       </c>
-      <c r="O76" s="3">
+      <c r="Q76" s="3">
         <v>7616900</v>
       </c>
-      <c r="P76" s="3">
+      <c r="R76" s="3">
         <v>7172500</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="S76" s="3">
         <v>6995300</v>
       </c>
-      <c r="R76" s="3">
+      <c r="T76" s="3">
         <v>6730800</v>
       </c>
-      <c r="S76" s="3">
+      <c r="U76" s="3">
         <v>6701200</v>
       </c>
-      <c r="T76" s="3">
+      <c r="V76" s="3">
         <v>6669700</v>
       </c>
-      <c r="U76" s="3">
+      <c r="W76" s="3">
         <v>7045800</v>
       </c>
-      <c r="V76" s="3">
+      <c r="X76" s="3">
         <v>6880500</v>
       </c>
-      <c r="W76" s="3">
+      <c r="Y76" s="3">
         <v>6817900</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Z76" s="3">
         <v>7111600</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="AA76" s="3">
         <v>5729500</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AB76" s="3">
         <v>5909100</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AC76" s="3">
         <v>5897800</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AD76" s="3">
         <v>5661800</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AE76" s="3">
         <v>5272900</v>
       </c>
-      <c r="AD76" s="3">
+      <c r="AF76" s="3">
         <v>5105500</v>
       </c>
-      <c r="AE76" s="3">
+      <c r="AG76" s="3">
         <v>4969400</v>
       </c>
-      <c r="AF76" s="3">
+      <c r="AH76" s="3">
         <v>4631700</v>
       </c>
-      <c r="AG76" s="3">
+      <c r="AI76" s="3">
         <v>4215500</v>
       </c>
-      <c r="AH76" s="3">
+      <c r="AJ76" s="3">
         <v>2968500</v>
       </c>
-      <c r="AI76" s="3">
+      <c r="AK76" s="3">
         <v>3181200</v>
       </c>
-      <c r="AJ76" s="3">
+      <c r="AL76" s="3">
         <v>3060200</v>
       </c>
-      <c r="AK76" s="3">
+      <c r="AM76" s="3">
         <v>3040800</v>
       </c>
-      <c r="AL76" s="3">
+      <c r="AN76" s="3">
         <v>2931800</v>
       </c>
-      <c r="AM76" s="3">
+      <c r="AO76" s="3">
         <v>2871500</v>
       </c>
-      <c r="AN76" s="3">
+      <c r="AP76" s="3">
         <v>1082100</v>
       </c>
     </row>
-    <row r="77" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -8116,245 +8493,263 @@
       <c r="AN77" s="3">
         <v>0</v>
       </c>
+      <c r="AO77" s="3">
+        <v>0</v>
+      </c>
+      <c r="AP77" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="79" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="79" spans="2:42" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>46112</v>
+      </c>
+      <c r="E80" s="2">
+        <v>46022</v>
+      </c>
+      <c r="F80" s="2">
         <v>45930</v>
       </c>
-      <c r="E80" s="2">
+      <c r="G80" s="2">
         <v>45838</v>
       </c>
-      <c r="F80" s="2">
+      <c r="H80" s="2">
         <v>45747</v>
       </c>
-      <c r="G80" s="2">
+      <c r="I80" s="2">
         <v>45657</v>
       </c>
-      <c r="H80" s="2">
+      <c r="J80" s="2">
         <v>45565</v>
       </c>
-      <c r="I80" s="2">
+      <c r="K80" s="2">
         <v>45473</v>
       </c>
-      <c r="J80" s="2">
+      <c r="L80" s="2">
         <v>45382</v>
       </c>
-      <c r="K80" s="2">
+      <c r="M80" s="2">
         <v>45291</v>
       </c>
-      <c r="L80" s="2">
+      <c r="N80" s="2">
         <v>45199</v>
       </c>
-      <c r="M80" s="2">
+      <c r="O80" s="2">
         <v>45107</v>
       </c>
-      <c r="N80" s="2">
+      <c r="P80" s="2">
         <v>45016</v>
       </c>
-      <c r="O80" s="2">
+      <c r="Q80" s="2">
         <v>44926</v>
       </c>
-      <c r="P80" s="2">
+      <c r="R80" s="2">
         <v>44834</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="S80" s="2">
         <v>44742</v>
       </c>
-      <c r="R80" s="2">
+      <c r="T80" s="2">
         <v>44651</v>
       </c>
-      <c r="S80" s="2">
+      <c r="U80" s="2">
         <v>44561</v>
       </c>
-      <c r="T80" s="2">
+      <c r="V80" s="2">
         <v>44469</v>
       </c>
-      <c r="U80" s="2">
+      <c r="W80" s="2">
         <v>44377</v>
       </c>
-      <c r="V80" s="2">
+      <c r="X80" s="2">
         <v>44286</v>
       </c>
-      <c r="W80" s="2">
+      <c r="Y80" s="2">
         <v>44196</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Z80" s="2">
         <v>44104</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="AA80" s="2">
         <v>44012</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AB80" s="2">
         <v>43921</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AC80" s="2">
         <v>43830</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AD80" s="2">
         <v>43738</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AE80" s="2">
         <v>43646</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AF80" s="2">
         <v>43555</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AG80" s="2">
         <v>43465</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AH80" s="2">
         <v>43373</v>
       </c>
-      <c r="AG80" s="2">
+      <c r="AI80" s="2">
         <v>43281</v>
       </c>
-      <c r="AH80" s="2">
+      <c r="AJ80" s="2">
         <v>43190</v>
       </c>
-      <c r="AI80" s="2">
+      <c r="AK80" s="2">
         <v>43100</v>
       </c>
-      <c r="AJ80" s="2">
+      <c r="AL80" s="2">
         <v>43008</v>
       </c>
-      <c r="AK80" s="2">
+      <c r="AM80" s="2">
         <v>42916</v>
       </c>
-      <c r="AL80" s="2">
+      <c r="AN80" s="2">
         <v>42825</v>
       </c>
-      <c r="AM80" s="2">
+      <c r="AO80" s="2">
         <v>42735</v>
       </c>
-      <c r="AN80" s="2">
+      <c r="AP80" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="81" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>307100</v>
+      </c>
+      <c r="E81" s="3">
+        <v>375400</v>
+      </c>
+      <c r="F81" s="3">
         <v>354500</v>
       </c>
-      <c r="E81" s="3">
+      <c r="G81" s="3">
         <v>270600</v>
       </c>
-      <c r="F81" s="3">
+      <c r="H81" s="3">
         <v>274700</v>
       </c>
-      <c r="G81" s="3">
+      <c r="I81" s="3">
         <v>326400</v>
       </c>
-      <c r="H81" s="3">
+      <c r="J81" s="3">
         <v>341600</v>
       </c>
-      <c r="I81" s="3">
+      <c r="K81" s="3">
         <v>359400</v>
       </c>
-      <c r="J81" s="3">
+      <c r="L81" s="3">
         <v>197500</v>
       </c>
-      <c r="K81" s="3">
+      <c r="M81" s="3">
         <v>309200</v>
       </c>
-      <c r="L81" s="3">
+      <c r="N81" s="3">
         <v>321400</v>
       </c>
-      <c r="M81" s="3">
+      <c r="O81" s="3">
         <v>350400</v>
       </c>
-      <c r="N81" s="3">
+      <c r="P81" s="3">
         <v>243200</v>
       </c>
-      <c r="O81" s="3">
+      <c r="Q81" s="3">
         <v>304900</v>
       </c>
-      <c r="P81" s="3">
+      <c r="R81" s="3">
         <v>267300</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="S81" s="3">
         <v>251000</v>
       </c>
-      <c r="R81" s="3">
+      <c r="T81" s="3">
         <v>126000</v>
       </c>
-      <c r="S81" s="3">
+      <c r="U81" s="3">
         <v>242800</v>
       </c>
-      <c r="T81" s="3">
+      <c r="V81" s="3">
         <v>165800</v>
       </c>
-      <c r="U81" s="3">
+      <c r="W81" s="3">
         <v>185600</v>
       </c>
-      <c r="V81" s="3">
+      <c r="X81" s="3">
         <v>76600</v>
       </c>
-      <c r="W81" s="3">
+      <c r="Y81" s="3">
         <v>179300</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Z81" s="3">
         <v>177000</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="AA81" s="3">
         <v>213400</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AB81" s="3">
         <v>59100</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AC81" s="3">
         <v>358200</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AD81" s="3">
         <v>204000</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AE81" s="3">
         <v>207700</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AF81" s="3">
         <v>103600</v>
       </c>
-      <c r="AE81" s="3">
+      <c r="AG81" s="3">
         <v>185200</v>
       </c>
-      <c r="AF81" s="3">
+      <c r="AH81" s="3">
         <v>148300</v>
       </c>
-      <c r="AG81" s="3">
+      <c r="AI81" s="3">
         <v>208700</v>
       </c>
-      <c r="AH81" s="3">
+      <c r="AJ81" s="3">
         <v>79900</v>
       </c>
-      <c r="AI81" s="3">
+      <c r="AK81" s="3">
         <v>181400</v>
       </c>
-      <c r="AJ81" s="3">
+      <c r="AL81" s="3">
         <v>106400</v>
       </c>
-      <c r="AK81" s="3">
+      <c r="AM81" s="3">
         <v>106400</v>
       </c>
-      <c r="AL81" s="3">
+      <c r="AN81" s="3">
         <v>73200</v>
       </c>
-      <c r="AM81" s="3">
+      <c r="AO81" s="3">
         <v>105700</v>
       </c>
-      <c r="AN81" s="3">
+      <c r="AP81" s="3">
         <v>73700</v>
       </c>
     </row>
-    <row r="82" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -8395,50 +8790,52 @@
       <c r="AL82" s="3"/>
       <c r="AM82" s="3"/>
       <c r="AN82" s="3"/>
+      <c r="AO82" s="3"/>
+      <c r="AP82" s="3"/>
     </row>
-    <row r="83" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="83" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>108700</v>
+      </c>
+      <c r="E83" s="3">
+        <v>98700</v>
+      </c>
+      <c r="F83" s="3">
         <v>99100</v>
       </c>
-      <c r="E83" s="3">
+      <c r="G83" s="3">
         <v>99200</v>
       </c>
-      <c r="F83" s="3">
+      <c r="H83" s="3">
         <v>104200</v>
       </c>
-      <c r="G83" s="3">
+      <c r="I83" s="3">
         <v>99400</v>
       </c>
-      <c r="H83" s="3">
+      <c r="J83" s="3">
         <v>97700</v>
       </c>
-      <c r="I83" s="3">
+      <c r="K83" s="3">
         <v>92600</v>
       </c>
-      <c r="J83" s="3">
+      <c r="L83" s="3">
         <v>94900</v>
       </c>
-      <c r="K83" s="3">
+      <c r="M83" s="3">
         <v>96500</v>
       </c>
-      <c r="L83" s="3">
+      <c r="N83" s="3">
         <v>89000</v>
       </c>
-      <c r="M83" s="3">
+      <c r="O83" s="3">
         <v>95600</v>
       </c>
-      <c r="N83" s="3">
+      <c r="P83" s="3">
         <v>94900</v>
       </c>
-      <c r="O83" s="3">
-        <v>0</v>
-      </c>
-      <c r="P83" s="3">
-        <v>0</v>
-      </c>
       <c r="Q83" s="3">
         <v>0</v>
       </c>
@@ -8511,8 +8908,14 @@
       <c r="AN83" s="3">
         <v>0</v>
       </c>
+      <c r="AO83" s="3">
+        <v>0</v>
+      </c>
+      <c r="AP83" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="84" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -8627,8 +9030,14 @@
       <c r="AN84" s="3">
         <v>0</v>
       </c>
+      <c r="AO84" s="3">
+        <v>0</v>
+      </c>
+      <c r="AP84" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="85" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="85" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -8743,8 +9152,14 @@
       <c r="AN85" s="3">
         <v>0</v>
       </c>
+      <c r="AO85" s="3">
+        <v>0</v>
+      </c>
+      <c r="AP85" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="86" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="86" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -8859,8 +9274,14 @@
       <c r="AN86" s="3">
         <v>0</v>
       </c>
+      <c r="AO86" s="3">
+        <v>0</v>
+      </c>
+      <c r="AP86" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="87" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="87" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -8975,8 +9396,14 @@
       <c r="AN87" s="3">
         <v>0</v>
       </c>
+      <c r="AO87" s="3">
+        <v>0</v>
+      </c>
+      <c r="AP87" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="88" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="88" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -9091,124 +9518,136 @@
       <c r="AN88" s="3">
         <v>0</v>
       </c>
+      <c r="AO88" s="3">
+        <v>0</v>
+      </c>
+      <c r="AP88" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="89" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="89" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>404400</v>
+      </c>
+      <c r="E89" s="3">
+        <v>604200</v>
+      </c>
+      <c r="F89" s="3">
         <v>451000</v>
       </c>
-      <c r="E89" s="3">
+      <c r="G89" s="3">
         <v>302700</v>
       </c>
-      <c r="F89" s="3">
+      <c r="H89" s="3">
         <v>325600</v>
       </c>
-      <c r="G89" s="3">
+      <c r="I89" s="3">
         <v>384500</v>
       </c>
-      <c r="H89" s="3">
+      <c r="J89" s="3">
         <v>443600</v>
       </c>
-      <c r="I89" s="3">
+      <c r="K89" s="3">
         <v>478900</v>
       </c>
-      <c r="J89" s="3">
+      <c r="L89" s="3">
         <v>281300</v>
       </c>
-      <c r="K89" s="3">
+      <c r="M89" s="3">
         <v>553300</v>
       </c>
-      <c r="L89" s="3">
+      <c r="N89" s="3">
         <v>402700</v>
       </c>
-      <c r="M89" s="3">
+      <c r="O89" s="3">
         <v>518700</v>
       </c>
-      <c r="N89" s="3">
+      <c r="P89" s="3">
         <v>398600</v>
       </c>
-      <c r="O89" s="3">
+      <c r="Q89" s="3">
         <v>531500</v>
       </c>
-      <c r="P89" s="3">
+      <c r="R89" s="3">
         <v>390100</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="S89" s="3">
         <v>525600</v>
       </c>
-      <c r="R89" s="3">
+      <c r="T89" s="3">
         <v>153700</v>
       </c>
-      <c r="S89" s="3">
+      <c r="U89" s="3">
         <v>416600</v>
       </c>
-      <c r="T89" s="3">
+      <c r="V89" s="3">
         <v>254000</v>
       </c>
-      <c r="U89" s="3">
+      <c r="W89" s="3">
         <v>277500</v>
       </c>
-      <c r="V89" s="3">
+      <c r="X89" s="3">
         <v>68500</v>
       </c>
-      <c r="W89" s="3">
+      <c r="Y89" s="3">
         <v>284000</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Z89" s="3">
         <v>218200</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="AA89" s="3">
         <v>184500</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AB89" s="3">
         <v>28000</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AC89" s="3">
         <v>348100</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AD89" s="3">
         <v>221200</v>
       </c>
-      <c r="AC89" s="3">
+      <c r="AE89" s="3">
         <v>304500</v>
       </c>
-      <c r="AD89" s="3">
+      <c r="AF89" s="3">
         <v>96300</v>
       </c>
-      <c r="AE89" s="3">
+      <c r="AG89" s="3">
         <v>261800</v>
       </c>
-      <c r="AF89" s="3">
+      <c r="AH89" s="3">
         <v>127600</v>
       </c>
-      <c r="AG89" s="3">
+      <c r="AI89" s="3">
         <v>206600</v>
       </c>
-      <c r="AH89" s="3">
+      <c r="AJ89" s="3">
         <v>30700</v>
       </c>
-      <c r="AI89" s="3">
+      <c r="AK89" s="3">
         <v>203600</v>
       </c>
-      <c r="AJ89" s="3">
+      <c r="AL89" s="3">
         <v>152000</v>
       </c>
-      <c r="AK89" s="3">
+      <c r="AM89" s="3">
         <v>134100</v>
       </c>
-      <c r="AL89" s="3">
+      <c r="AN89" s="3">
         <v>48200</v>
       </c>
-      <c r="AM89" s="3">
+      <c r="AO89" s="3">
         <v>166300</v>
       </c>
-      <c r="AN89" s="3">
+      <c r="AP89" s="3">
         <v>121000</v>
       </c>
     </row>
-    <row r="90" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -9249,8 +9688,10 @@
       <c r="AL90" s="3"/>
       <c r="AM90" s="3"/>
       <c r="AN90" s="3"/>
+      <c r="AO90" s="3"/>
+      <c r="AP90" s="3"/>
     </row>
-    <row r="91" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="91" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
@@ -9258,40 +9699,40 @@
         <v>8</v>
       </c>
       <c r="E91" s="3">
-        <v>-408400</v>
+        <v>-745500</v>
       </c>
       <c r="F91" s="3" t="s">
         <v>8</v>
       </c>
       <c r="G91" s="3">
-        <v>-713500</v>
+        <v>-408400</v>
       </c>
       <c r="H91" s="3" t="s">
         <v>8</v>
       </c>
       <c r="I91" s="3">
-        <v>-364200</v>
+        <v>-713500</v>
       </c>
       <c r="J91" s="3" t="s">
         <v>8</v>
       </c>
       <c r="K91" s="3">
-        <v>-920700</v>
+        <v>-364200</v>
       </c>
       <c r="L91" s="3" t="s">
         <v>8</v>
       </c>
       <c r="M91" s="3">
-        <v>-613200</v>
+        <v>-920700</v>
       </c>
       <c r="N91" s="3" t="s">
         <v>8</v>
       </c>
       <c r="O91" s="3">
-        <v>0</v>
-      </c>
-      <c r="P91" s="3">
-        <v>0</v>
+        <v>-613200</v>
+      </c>
+      <c r="P91" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="Q91" s="3">
         <v>0</v>
@@ -9365,8 +9806,14 @@
       <c r="AN91" s="3">
         <v>0</v>
       </c>
+      <c r="AO91" s="3">
+        <v>0</v>
+      </c>
+      <c r="AP91" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="92" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -9481,8 +9928,14 @@
       <c r="AN92" s="3">
         <v>0</v>
       </c>
+      <c r="AO92" s="3">
+        <v>0</v>
+      </c>
+      <c r="AP92" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="93" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="93" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -9597,124 +10050,136 @@
       <c r="AN93" s="3">
         <v>0</v>
       </c>
+      <c r="AO93" s="3">
+        <v>0</v>
+      </c>
+      <c r="AP93" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="94" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="94" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-1040200</v>
+      </c>
+      <c r="E94" s="3">
+        <v>-11200</v>
+      </c>
+      <c r="F94" s="3">
         <v>-59900</v>
       </c>
-      <c r="E94" s="3">
+      <c r="G94" s="3">
         <v>-162400</v>
       </c>
-      <c r="F94" s="3">
+      <c r="H94" s="3">
         <v>-435300</v>
       </c>
-      <c r="G94" s="3">
+      <c r="I94" s="3">
         <v>407500</v>
       </c>
-      <c r="H94" s="3">
+      <c r="J94" s="3">
         <v>-272300</v>
       </c>
-      <c r="I94" s="3">
+      <c r="K94" s="3">
         <v>-642100</v>
       </c>
-      <c r="J94" s="3">
+      <c r="L94" s="3">
         <v>-329400</v>
       </c>
-      <c r="K94" s="3">
+      <c r="M94" s="3">
         <v>166600</v>
       </c>
-      <c r="L94" s="3">
+      <c r="N94" s="3">
         <v>-551700</v>
       </c>
-      <c r="M94" s="3">
+      <c r="O94" s="3">
         <v>-488300</v>
       </c>
-      <c r="N94" s="3">
+      <c r="P94" s="3">
         <v>-854000</v>
       </c>
-      <c r="O94" s="3">
+      <c r="Q94" s="3">
         <v>-617600</v>
       </c>
-      <c r="P94" s="3">
+      <c r="R94" s="3">
         <v>-654400</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="S94" s="3">
         <v>-501800</v>
       </c>
-      <c r="R94" s="3">
+      <c r="T94" s="3">
         <v>-460800</v>
       </c>
-      <c r="S94" s="3">
+      <c r="U94" s="3">
         <v>-387700</v>
       </c>
-      <c r="T94" s="3">
+      <c r="V94" s="3">
         <v>-197000</v>
       </c>
-      <c r="U94" s="3">
+      <c r="W94" s="3">
         <v>-26500</v>
       </c>
-      <c r="V94" s="3">
+      <c r="X94" s="3">
         <v>-627900</v>
       </c>
-      <c r="W94" s="3">
+      <c r="Y94" s="3">
         <v>-406000</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Z94" s="3">
         <v>173900</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="AA94" s="3">
         <v>-161800</v>
       </c>
-      <c r="Z94" s="3">
+      <c r="AB94" s="3">
         <v>-112800</v>
       </c>
-      <c r="AA94" s="3">
+      <c r="AC94" s="3">
         <v>-314600</v>
       </c>
-      <c r="AB94" s="3">
+      <c r="AD94" s="3">
         <v>-626500</v>
       </c>
-      <c r="AC94" s="3">
+      <c r="AE94" s="3">
         <v>229000</v>
       </c>
-      <c r="AD94" s="3">
+      <c r="AF94" s="3">
         <v>136200</v>
       </c>
-      <c r="AE94" s="3">
+      <c r="AG94" s="3">
         <v>-483600</v>
       </c>
-      <c r="AF94" s="3">
+      <c r="AH94" s="3">
         <v>-321300</v>
       </c>
-      <c r="AG94" s="3">
+      <c r="AI94" s="3">
         <v>-790700</v>
       </c>
-      <c r="AH94" s="3">
+      <c r="AJ94" s="3">
         <v>-229200</v>
       </c>
-      <c r="AI94" s="3">
+      <c r="AK94" s="3">
         <v>-107200</v>
       </c>
-      <c r="AJ94" s="3">
+      <c r="AL94" s="3">
         <v>-167600</v>
       </c>
-      <c r="AK94" s="3">
+      <c r="AM94" s="3">
         <v>-168800</v>
       </c>
-      <c r="AL94" s="3">
+      <c r="AN94" s="3">
         <v>-771600</v>
       </c>
-      <c r="AM94" s="3">
+      <c r="AO94" s="3">
         <v>-158200</v>
       </c>
-      <c r="AN94" s="3">
+      <c r="AP94" s="3">
         <v>-129200</v>
       </c>
     </row>
-    <row r="95" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -9755,8 +10220,10 @@
       <c r="AL95" s="3"/>
       <c r="AM95" s="3"/>
       <c r="AN95" s="3"/>
+      <c r="AO95" s="3"/>
+      <c r="AP95" s="3"/>
     </row>
-    <row r="96" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="96" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -9764,40 +10231,40 @@
         <v>8</v>
       </c>
       <c r="E96" s="3">
-        <v>286900</v>
+        <v>536900</v>
       </c>
       <c r="F96" s="3" t="s">
         <v>8</v>
       </c>
       <c r="G96" s="3">
-        <v>768000</v>
+        <v>286900</v>
       </c>
       <c r="H96" s="3" t="s">
         <v>8</v>
       </c>
       <c r="I96" s="3">
-        <v>495400</v>
+        <v>768000</v>
       </c>
       <c r="J96" s="3" t="s">
         <v>8</v>
       </c>
       <c r="K96" s="3">
-        <v>292300</v>
+        <v>495400</v>
       </c>
       <c r="L96" s="3" t="s">
         <v>8</v>
       </c>
       <c r="M96" s="3">
-        <v>285800</v>
+        <v>292300</v>
       </c>
       <c r="N96" s="3" t="s">
         <v>8</v>
       </c>
       <c r="O96" s="3">
-        <v>0</v>
-      </c>
-      <c r="P96" s="3">
-        <v>0</v>
+        <v>285800</v>
+      </c>
+      <c r="P96" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="Q96" s="3">
         <v>0</v>
@@ -9871,8 +10338,14 @@
       <c r="AN96" s="3">
         <v>0</v>
       </c>
+      <c r="AO96" s="3">
+        <v>0</v>
+      </c>
+      <c r="AP96" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="97" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="97" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -9987,8 +10460,14 @@
       <c r="AN97" s="3">
         <v>0</v>
       </c>
+      <c r="AO97" s="3">
+        <v>0</v>
+      </c>
+      <c r="AP97" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="98" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="98" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -10103,8 +10582,14 @@
       <c r="AN98" s="3">
         <v>0</v>
       </c>
+      <c r="AO98" s="3">
+        <v>0</v>
+      </c>
+      <c r="AP98" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="99" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="99" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -10219,352 +10704,376 @@
       <c r="AN99" s="3">
         <v>0</v>
       </c>
+      <c r="AO99" s="3">
+        <v>0</v>
+      </c>
+      <c r="AP99" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="100" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="100" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>845400</v>
+      </c>
+      <c r="E100" s="3">
+        <v>-502900</v>
+      </c>
+      <c r="F100" s="3">
         <v>-937100</v>
       </c>
-      <c r="E100" s="3">
+      <c r="G100" s="3">
         <v>-16400</v>
       </c>
-      <c r="F100" s="3">
+      <c r="H100" s="3">
         <v>-36000</v>
       </c>
-      <c r="G100" s="3">
+      <c r="I100" s="3">
         <v>-552400</v>
       </c>
-      <c r="H100" s="3">
+      <c r="J100" s="3">
         <v>1500</v>
       </c>
-      <c r="I100" s="3">
+      <c r="K100" s="3">
         <v>-151900</v>
       </c>
-      <c r="J100" s="3">
+      <c r="L100" s="3">
         <v>18000</v>
       </c>
-      <c r="K100" s="3">
+      <c r="M100" s="3">
         <v>-305500</v>
       </c>
-      <c r="L100" s="3">
+      <c r="N100" s="3">
         <v>346700</v>
       </c>
-      <c r="M100" s="3">
+      <c r="O100" s="3">
         <v>-272200</v>
       </c>
-      <c r="N100" s="3">
+      <c r="P100" s="3">
         <v>122400</v>
       </c>
-      <c r="O100" s="3">
+      <c r="Q100" s="3">
         <v>-240700</v>
       </c>
-      <c r="P100" s="3">
+      <c r="R100" s="3">
         <v>876200</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="S100" s="3">
         <v>-21800</v>
       </c>
-      <c r="R100" s="3">
+      <c r="T100" s="3">
         <v>358800</v>
       </c>
-      <c r="S100" s="3">
+      <c r="U100" s="3">
         <v>-108500</v>
       </c>
-      <c r="T100" s="3">
+      <c r="V100" s="3">
         <v>-308000</v>
       </c>
-      <c r="U100" s="3">
+      <c r="W100" s="3">
         <v>-135500</v>
       </c>
-      <c r="V100" s="3">
+      <c r="X100" s="3">
         <v>142800</v>
       </c>
-      <c r="W100" s="3">
+      <c r="Y100" s="3">
         <v>-87400</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Z100" s="3">
         <v>1267700</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="AA100" s="3">
         <v>9600</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AB100" s="3">
         <v>47000</v>
       </c>
-      <c r="AA100" s="3">
+      <c r="AC100" s="3">
         <v>2000</v>
       </c>
-      <c r="AB100" s="3">
+      <c r="AD100" s="3">
         <v>79800</v>
       </c>
-      <c r="AC100" s="3">
+      <c r="AE100" s="3">
         <v>-380900</v>
       </c>
-      <c r="AD100" s="3">
+      <c r="AF100" s="3">
         <v>-2100</v>
       </c>
-      <c r="AE100" s="3">
+      <c r="AG100" s="3">
         <v>-22300</v>
       </c>
-      <c r="AF100" s="3">
+      <c r="AH100" s="3">
         <v>193200</v>
       </c>
-      <c r="AG100" s="3">
+      <c r="AI100" s="3">
         <v>926600</v>
       </c>
-      <c r="AH100" s="3">
+      <c r="AJ100" s="3">
         <v>-115500</v>
       </c>
-      <c r="AI100" s="3">
+      <c r="AK100" s="3">
         <v>-30000</v>
       </c>
-      <c r="AJ100" s="3">
+      <c r="AL100" s="3">
         <v>-59900</v>
       </c>
-      <c r="AK100" s="3">
+      <c r="AM100" s="3">
         <v>-104800</v>
       </c>
-      <c r="AL100" s="3">
+      <c r="AN100" s="3">
         <v>36400</v>
       </c>
-      <c r="AM100" s="3">
+      <c r="AO100" s="3">
         <v>1358900</v>
       </c>
-      <c r="AN100" s="3">
+      <c r="AP100" s="3">
         <v>-3900</v>
       </c>
     </row>
-    <row r="101" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>-1700</v>
+      </c>
+      <c r="E101" s="3">
+        <v>4700</v>
+      </c>
+      <c r="F101" s="3">
         <v>-6200</v>
       </c>
-      <c r="E101" s="3">
+      <c r="G101" s="3">
         <v>-500</v>
       </c>
-      <c r="F101" s="3">
+      <c r="H101" s="3">
         <v>5300</v>
       </c>
-      <c r="G101" s="3">
+      <c r="I101" s="3">
         <v>600</v>
       </c>
-      <c r="H101" s="3">
+      <c r="J101" s="3">
         <v>1300</v>
       </c>
-      <c r="I101" s="3">
+      <c r="K101" s="3">
         <v>14500</v>
       </c>
-      <c r="J101" s="3">
+      <c r="L101" s="3">
         <v>-1300</v>
       </c>
-      <c r="K101" s="3">
+      <c r="M101" s="3">
         <v>-8600</v>
       </c>
-      <c r="L101" s="3">
+      <c r="N101" s="3">
         <v>31600</v>
       </c>
-      <c r="M101" s="3">
+      <c r="O101" s="3">
         <v>28900</v>
       </c>
-      <c r="N101" s="3">
+      <c r="P101" s="3">
         <v>-3300</v>
       </c>
-      <c r="O101" s="3">
+      <c r="Q101" s="3">
         <v>-8300</v>
       </c>
-      <c r="P101" s="3">
+      <c r="R101" s="3">
         <v>31000</v>
       </c>
-      <c r="Q101" s="3">
+      <c r="S101" s="3">
         <v>26900</v>
       </c>
-      <c r="R101" s="3">
+      <c r="T101" s="3">
         <v>-2900</v>
       </c>
-      <c r="S101" s="3">
+      <c r="U101" s="3">
         <v>-6600</v>
       </c>
-      <c r="T101" s="3">
+      <c r="V101" s="3">
         <v>-300</v>
       </c>
-      <c r="U101" s="3">
+      <c r="W101" s="3">
         <v>-19200</v>
       </c>
-      <c r="V101" s="3">
+      <c r="X101" s="3">
         <v>4800</v>
       </c>
-      <c r="W101" s="3">
+      <c r="Y101" s="3">
         <v>-78800</v>
       </c>
-      <c r="X101" s="3">
+      <c r="Z101" s="3">
         <v>-16100</v>
       </c>
-      <c r="Y101" s="3">
+      <c r="AA101" s="3">
         <v>300</v>
       </c>
-      <c r="Z101" s="3">
+      <c r="AB101" s="3">
         <v>2700</v>
       </c>
-      <c r="AA101" s="3">
+      <c r="AC101" s="3">
         <v>-2000</v>
       </c>
-      <c r="AB101" s="3">
+      <c r="AD101" s="3">
         <v>5200</v>
       </c>
-      <c r="AC101" s="3">
+      <c r="AE101" s="3">
         <v>3300</v>
       </c>
-      <c r="AD101" s="3">
+      <c r="AF101" s="3">
         <v>-6900</v>
       </c>
-      <c r="AE101" s="3">
+      <c r="AG101" s="3">
         <v>4700</v>
       </c>
-      <c r="AF101" s="3">
+      <c r="AH101" s="3">
         <v>14200</v>
       </c>
-      <c r="AG101" s="3">
+      <c r="AI101" s="3">
         <v>32400</v>
       </c>
-      <c r="AH101" s="3">
+      <c r="AJ101" s="3">
         <v>-12800</v>
       </c>
-      <c r="AI101" s="3">
+      <c r="AK101" s="3">
         <v>-16600</v>
       </c>
-      <c r="AJ101" s="3">
+      <c r="AL101" s="3">
         <v>-17500</v>
       </c>
-      <c r="AK101" s="3">
+      <c r="AM101" s="3">
         <v>-10400</v>
       </c>
-      <c r="AL101" s="3">
+      <c r="AN101" s="3">
         <v>-18100</v>
       </c>
-      <c r="AM101" s="3">
+      <c r="AO101" s="3">
         <v>40700</v>
       </c>
-      <c r="AN101" s="3">
+      <c r="AP101" s="3">
         <v>400</v>
       </c>
     </row>
-    <row r="102" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>202300</v>
+      </c>
+      <c r="E102" s="3">
+        <v>89300</v>
+      </c>
+      <c r="F102" s="3">
         <v>-548800</v>
       </c>
-      <c r="E102" s="3">
+      <c r="G102" s="3">
         <v>121100</v>
       </c>
-      <c r="F102" s="3">
+      <c r="H102" s="3">
         <v>-147300</v>
       </c>
-      <c r="G102" s="3">
+      <c r="I102" s="3">
         <v>244300</v>
       </c>
-      <c r="H102" s="3">
+      <c r="J102" s="3">
         <v>166600</v>
       </c>
-      <c r="I102" s="3">
+      <c r="K102" s="3">
         <v>-315600</v>
       </c>
-      <c r="J102" s="3">
+      <c r="L102" s="3">
         <v>-24800</v>
       </c>
-      <c r="K102" s="3">
+      <c r="M102" s="3">
         <v>415000</v>
       </c>
-      <c r="L102" s="3">
+      <c r="N102" s="3">
         <v>199000</v>
       </c>
-      <c r="M102" s="3">
+      <c r="O102" s="3">
         <v>-227400</v>
       </c>
-      <c r="N102" s="3">
+      <c r="P102" s="3">
         <v>-334400</v>
       </c>
-      <c r="O102" s="3">
+      <c r="Q102" s="3">
         <v>-335200</v>
       </c>
-      <c r="P102" s="3">
+      <c r="R102" s="3">
         <v>642800</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="S102" s="3">
         <v>28900</v>
       </c>
-      <c r="R102" s="3">
+      <c r="T102" s="3">
         <v>48700</v>
       </c>
-      <c r="S102" s="3">
+      <c r="U102" s="3">
         <v>-86200</v>
       </c>
-      <c r="T102" s="3">
+      <c r="V102" s="3">
         <v>-251300</v>
       </c>
-      <c r="U102" s="3">
+      <c r="W102" s="3">
         <v>96300</v>
       </c>
-      <c r="V102" s="3">
+      <c r="X102" s="3">
         <v>-411900</v>
       </c>
-      <c r="W102" s="3">
+      <c r="Y102" s="3">
         <v>-288300</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Z102" s="3">
         <v>1643600</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="AA102" s="3">
         <v>32700</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AB102" s="3">
         <v>-35000</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AC102" s="3">
         <v>33500</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AD102" s="3">
         <v>-320300</v>
       </c>
-      <c r="AC102" s="3">
+      <c r="AE102" s="3">
         <v>155900</v>
       </c>
-      <c r="AD102" s="3">
+      <c r="AF102" s="3">
         <v>223500</v>
       </c>
-      <c r="AE102" s="3">
+      <c r="AG102" s="3">
         <v>-239400</v>
       </c>
-      <c r="AF102" s="3">
+      <c r="AH102" s="3">
         <v>13700</v>
       </c>
-      <c r="AG102" s="3">
+      <c r="AI102" s="3">
         <v>374800</v>
       </c>
-      <c r="AH102" s="3">
+      <c r="AJ102" s="3">
         <v>-326900</v>
       </c>
-      <c r="AI102" s="3">
+      <c r="AK102" s="3">
         <v>49800</v>
       </c>
-      <c r="AJ102" s="3">
+      <c r="AL102" s="3">
         <v>-92900</v>
       </c>
-      <c r="AK102" s="3">
+      <c r="AM102" s="3">
         <v>-150000</v>
       </c>
-      <c r="AL102" s="3">
+      <c r="AN102" s="3">
         <v>-705100</v>
       </c>
-      <c r="AM102" s="3">
+      <c r="AO102" s="3">
         <v>1407600</v>
       </c>
-      <c r="AN102" s="3">
+      <c r="AP102" s="3">
         <v>-11700</v>
       </c>
     </row>
